--- a/PROCESO DE PLANTA.xlsx
+++ b/PROCESO DE PLANTA.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1131" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1133" uniqueCount="205">
   <si>
     <t xml:space="preserve">AGRO PACAYALES · PLANTA CAMOTE 2026  |  MOVIMIENTOS — registra aquí un evento por fila</t>
   </si>
@@ -645,6 +645,10 @@
   <si>
     <t xml:space="preserve">Chancho
 procesado (sacos)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chancho
+procesado (kg)</t>
   </si>
   <si>
     <t xml:space="preserve">Dom</t>
@@ -5192,32 +5196,30 @@
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A107" s="11" t="n">
+      <c r="A107" s="23" t="n">
         <v>46223</v>
       </c>
-      <c r="B107" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="C107" s="12" t="s">
+      <c r="B107" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="C107" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="D107" s="24" t="s">
+        <v>12</v>
+      </c>
+      <c r="E107" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F107" s="25" t="n">
+        <f aca="false">IF($B107="","",IF($D107="kg",N($E107),IF($D107="sacos",N($E107)*97,IF($D107="jabas",N($E107)*IFERROR(VLOOKUP($C107,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
         <v>18</v>
       </c>
-      <c r="D107" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="E107" s="13" t="n">
-        <v>22</v>
-      </c>
-      <c r="F107" s="13" t="n">
-        <f aca="false">IF($B107="","",IF($D107="kg",N($E107),IF($D107="sacos",N($E107)*97,IF($D107="jabas",N($E107)*IFERROR(VLOOKUP($C107,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
-        <v>2134</v>
-      </c>
-      <c r="G107" s="12"/>
-      <c r="H107" s="12" t="s">
-        <v>19</v>
-      </c>
+      <c r="G107" s="24"/>
+      <c r="H107" s="24"/>
       <c r="I107" s="1" t="n">
         <f aca="false">N($F107)</f>
-        <v>2134</v>
+        <v>18</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5228,7 +5230,7 @@
         <v>34</v>
       </c>
       <c r="C108" s="24" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D108" s="24" t="s">
         <v>12</v>
@@ -5238,40 +5240,42 @@
       </c>
       <c r="F108" s="25" t="n">
         <f aca="false">IF($B108="","",IF($D108="kg",N($E108),IF($D108="sacos",N($E108)*97,IF($D108="jabas",N($E108)*IFERROR(VLOOKUP($C108,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G108" s="24"/>
       <c r="H108" s="24"/>
       <c r="I108" s="1" t="n">
         <f aca="false">N($F108)</f>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A109" s="11" t="n">
+        <v>46224</v>
+      </c>
+      <c r="B109" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C109" s="12" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A109" s="23" t="n">
-        <v>46223</v>
-      </c>
-      <c r="B109" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="C109" s="24" t="s">
+      <c r="D109" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="E109" s="13" t="n">
         <v>22</v>
       </c>
-      <c r="D109" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="E109" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="F109" s="25" t="n">
+      <c r="F109" s="13" t="n">
         <f aca="false">IF($B109="","",IF($D109="kg",N($E109),IF($D109="sacos",N($E109)*97,IF($D109="jabas",N($E109)*IFERROR(VLOOKUP($C109,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
-        <v>17</v>
-      </c>
-      <c r="G109" s="24"/>
-      <c r="H109" s="24"/>
+        <v>2134</v>
+      </c>
+      <c r="G109" s="12"/>
+      <c r="H109" s="12" t="s">
+        <v>19</v>
+      </c>
       <c r="I109" s="1" t="n">
         <f aca="false">N($F109)</f>
-        <v>17</v>
+        <v>2134</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5356,32 +5360,30 @@
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A113" s="11" t="n">
+      <c r="A113" s="14" t="n">
         <v>46224</v>
       </c>
-      <c r="B113" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="C113" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="D113" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="E113" s="13" t="n">
-        <v>70</v>
-      </c>
-      <c r="F113" s="13" t="n">
+      <c r="B113" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C113" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D113" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="E113" s="16" t="n">
+        <v>47</v>
+      </c>
+      <c r="F113" s="16" t="n">
         <f aca="false">IF($B113="","",IF($D113="kg",N($E113),IF($D113="sacos",N($E113)*97,IF($D113="jabas",N($E113)*IFERROR(VLOOKUP($C113,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
-        <v>6790</v>
-      </c>
-      <c r="G113" s="12"/>
-      <c r="H113" s="12" t="s">
-        <v>19</v>
-      </c>
+        <v>705</v>
+      </c>
+      <c r="G113" s="15"/>
+      <c r="H113" s="15"/>
       <c r="I113" s="1" t="n">
         <f aca="false">N($F113)</f>
-        <v>6790</v>
+        <v>705</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5392,23 +5394,23 @@
         <v>20</v>
       </c>
       <c r="C114" s="15" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="D114" s="15" t="s">
         <v>12</v>
       </c>
       <c r="E114" s="16" t="n">
-        <v>47</v>
+        <v>11</v>
       </c>
       <c r="F114" s="16" t="n">
         <f aca="false">IF($B114="","",IF($D114="kg",N($E114),IF($D114="sacos",N($E114)*97,IF($D114="jabas",N($E114)*IFERROR(VLOOKUP($C114,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
-        <v>705</v>
+        <v>198</v>
       </c>
       <c r="G114" s="15"/>
       <c r="H114" s="15"/>
       <c r="I114" s="1" t="n">
         <f aca="false">N($F114)</f>
-        <v>705</v>
+        <v>198</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5419,23 +5421,23 @@
         <v>20</v>
       </c>
       <c r="C115" s="15" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D115" s="15" t="s">
         <v>12</v>
       </c>
       <c r="E115" s="16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F115" s="16" t="n">
         <f aca="false">IF($B115="","",IF($D115="kg",N($E115),IF($D115="sacos",N($E115)*97,IF($D115="jabas",N($E115)*IFERROR(VLOOKUP($C115,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="G115" s="15"/>
       <c r="H115" s="15"/>
       <c r="I115" s="1" t="n">
         <f aca="false">N($F115)</f>
-        <v>198</v>
+        <v>204</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5446,23 +5448,23 @@
         <v>20</v>
       </c>
       <c r="C116" s="15" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="D116" s="15" t="s">
         <v>12</v>
       </c>
       <c r="E116" s="16" t="n">
-        <v>12</v>
+        <v>72</v>
       </c>
       <c r="F116" s="16" t="n">
         <f aca="false">IF($B116="","",IF($D116="kg",N($E116),IF($D116="sacos",N($E116)*97,IF($D116="jabas",N($E116)*IFERROR(VLOOKUP($C116,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
-        <v>204</v>
+        <v>1224</v>
       </c>
       <c r="G116" s="15"/>
       <c r="H116" s="15"/>
       <c r="I116" s="1" t="n">
         <f aca="false">N($F116)</f>
-        <v>204</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5473,50 +5475,52 @@
         <v>20</v>
       </c>
       <c r="C117" s="15" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D117" s="15" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E117" s="16" t="n">
-        <v>72</v>
+        <v>4</v>
       </c>
       <c r="F117" s="16" t="n">
         <f aca="false">IF($B117="","",IF($D117="kg",N($E117),IF($D117="sacos",N($E117)*97,IF($D117="jabas",N($E117)*IFERROR(VLOOKUP($C117,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
-        <v>1224</v>
+        <v>388</v>
       </c>
       <c r="G117" s="15"/>
       <c r="H117" s="15"/>
       <c r="I117" s="1" t="n">
         <f aca="false">N($F117)</f>
-        <v>1224</v>
+        <v>388</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A118" s="14" t="n">
+      <c r="A118" s="17" t="n">
         <v>46224</v>
       </c>
-      <c r="B118" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C118" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="D118" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="E118" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="F118" s="16" t="n">
+      <c r="B118" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="C118" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="D118" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="E118" s="19" t="n">
+        <v>67</v>
+      </c>
+      <c r="F118" s="19" t="n">
         <f aca="false">IF($B118="","",IF($D118="kg",N($E118),IF($D118="sacos",N($E118)*97,IF($D118="jabas",N($E118)*IFERROR(VLOOKUP($C118,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
-        <v>388</v>
-      </c>
-      <c r="G118" s="15"/>
-      <c r="H118" s="15"/>
+        <v>1005</v>
+      </c>
+      <c r="G118" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="H118" s="18"/>
       <c r="I118" s="1" t="n">
         <f aca="false">N($F118)</f>
-        <v>388</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5527,17 +5531,17 @@
         <v>23</v>
       </c>
       <c r="C119" s="18" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="D119" s="18" t="s">
         <v>12</v>
       </c>
       <c r="E119" s="19" t="n">
-        <v>67</v>
+        <v>11</v>
       </c>
       <c r="F119" s="19" t="n">
         <f aca="false">IF($B119="","",IF($D119="kg",N($E119),IF($D119="sacos",N($E119)*97,IF($D119="jabas",N($E119)*IFERROR(VLOOKUP($C119,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
-        <v>1005</v>
+        <v>198</v>
       </c>
       <c r="G119" s="18" t="s">
         <v>41</v>
@@ -5545,7 +5549,7 @@
       <c r="H119" s="18"/>
       <c r="I119" s="1" t="n">
         <f aca="false">N($F119)</f>
-        <v>1005</v>
+        <v>198</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5556,17 +5560,17 @@
         <v>23</v>
       </c>
       <c r="C120" s="18" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D120" s="18" t="s">
         <v>12</v>
       </c>
       <c r="E120" s="19" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F120" s="19" t="n">
         <f aca="false">IF($B120="","",IF($D120="kg",N($E120),IF($D120="sacos",N($E120)*97,IF($D120="jabas",N($E120)*IFERROR(VLOOKUP($C120,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
-        <v>198</v>
+        <v>170</v>
       </c>
       <c r="G120" s="18" t="s">
         <v>41</v>
@@ -5574,7 +5578,7 @@
       <c r="H120" s="18"/>
       <c r="I120" s="1" t="n">
         <f aca="false">N($F120)</f>
-        <v>198</v>
+        <v>170</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5585,17 +5589,17 @@
         <v>23</v>
       </c>
       <c r="C121" s="18" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="D121" s="18" t="s">
         <v>12</v>
       </c>
       <c r="E121" s="19" t="n">
-        <v>10</v>
+        <v>111</v>
       </c>
       <c r="F121" s="19" t="n">
         <f aca="false">IF($B121="","",IF($D121="kg",N($E121),IF($D121="sacos",N($E121)*97,IF($D121="jabas",N($E121)*IFERROR(VLOOKUP($C121,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
-        <v>170</v>
+        <v>1887</v>
       </c>
       <c r="G121" s="18" t="s">
         <v>41</v>
@@ -5603,36 +5607,34 @@
       <c r="H121" s="18"/>
       <c r="I121" s="1" t="n">
         <f aca="false">N($F121)</f>
-        <v>170</v>
+        <v>1887</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A122" s="17" t="n">
+      <c r="A122" s="26" t="n">
         <v>46224</v>
       </c>
-      <c r="B122" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="C122" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="D122" s="18" t="s">
+      <c r="B122" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="C122" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="D122" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="E122" s="19" t="n">
-        <v>111</v>
-      </c>
-      <c r="F122" s="19" t="n">
+      <c r="E122" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F122" s="28" t="n">
         <f aca="false">IF($B122="","",IF($D122="kg",N($E122),IF($D122="sacos",N($E122)*97,IF($D122="jabas",N($E122)*IFERROR(VLOOKUP($C122,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
-        <v>1887</v>
-      </c>
-      <c r="G122" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="H122" s="18"/>
+        <v>15</v>
+      </c>
+      <c r="G122" s="27"/>
+      <c r="H122" s="27"/>
       <c r="I122" s="1" t="n">
         <f aca="false">N($F122)</f>
-        <v>1887</v>
+        <v>15</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5643,7 +5645,7 @@
         <v>42</v>
       </c>
       <c r="C123" s="27" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D123" s="27" t="s">
         <v>12</v>
@@ -5653,40 +5655,40 @@
       </c>
       <c r="F123" s="28" t="n">
         <f aca="false">IF($B123="","",IF($D123="kg",N($E123),IF($D123="sacos",N($E123)*97,IF($D123="jabas",N($E123)*IFERROR(VLOOKUP($C123,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G123" s="27"/>
       <c r="H123" s="27"/>
       <c r="I123" s="1" t="n">
         <f aca="false">N($F123)</f>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A124" s="23" t="n">
+        <v>46224</v>
+      </c>
+      <c r="B124" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="C124" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="D124" s="24" t="s">
+        <v>12</v>
+      </c>
+      <c r="E124" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F124" s="25" t="n">
+        <f aca="false">IF($B124="","",IF($D124="kg",N($E124),IF($D124="sacos",N($E124)*97,IF($D124="jabas",N($E124)*IFERROR(VLOOKUP($C124,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
         <v>15</v>
       </c>
-    </row>
-    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A124" s="26" t="n">
-        <v>46224</v>
-      </c>
-      <c r="B124" s="27" t="s">
-        <v>42</v>
-      </c>
-      <c r="C124" s="27" t="s">
-        <v>13</v>
-      </c>
-      <c r="D124" s="27" t="s">
-        <v>12</v>
-      </c>
-      <c r="E124" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F124" s="28" t="n">
-        <f aca="false">IF($B124="","",IF($D124="kg",N($E124),IF($D124="sacos",N($E124)*97,IF($D124="jabas",N($E124)*IFERROR(VLOOKUP($C124,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
-        <v>17</v>
-      </c>
-      <c r="G124" s="27"/>
-      <c r="H124" s="27"/>
+      <c r="G124" s="24"/>
+      <c r="H124" s="24"/>
       <c r="I124" s="1" t="n">
         <f aca="false">N($F124)</f>
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5697,7 +5699,7 @@
         <v>34</v>
       </c>
       <c r="C125" s="24" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D125" s="24" t="s">
         <v>12</v>
@@ -5707,69 +5709,71 @@
       </c>
       <c r="F125" s="25" t="n">
         <f aca="false">IF($B125="","",IF($D125="kg",N($E125),IF($D125="sacos",N($E125)*97,IF($D125="jabas",N($E125)*IFERROR(VLOOKUP($C125,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G125" s="24"/>
       <c r="H125" s="24"/>
       <c r="I125" s="1" t="n">
         <f aca="false">N($F125)</f>
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A126" s="23" t="n">
+      <c r="A126" s="29" t="n">
         <v>46224</v>
       </c>
-      <c r="B126" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="C126" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="D126" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="E126" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="F126" s="25" t="n">
+      <c r="B126" s="30" t="s">
+        <v>43</v>
+      </c>
+      <c r="C126" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="D126" s="30" t="s">
+        <v>44</v>
+      </c>
+      <c r="E126" s="31" t="n">
+        <v>17</v>
+      </c>
+      <c r="F126" s="31" t="n">
         <f aca="false">IF($B126="","",IF($D126="kg",N($E126),IF($D126="sacos",N($E126)*97,IF($D126="jabas",N($E126)*IFERROR(VLOOKUP($C126,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
         <v>17</v>
       </c>
-      <c r="G126" s="24"/>
-      <c r="H126" s="24"/>
+      <c r="G126" s="30"/>
+      <c r="H126" s="30" t="s">
+        <v>45</v>
+      </c>
       <c r="I126" s="1" t="n">
         <f aca="false">N($F126)</f>
         <v>17</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A127" s="29" t="n">
-        <v>46224</v>
-      </c>
-      <c r="B127" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="C127" s="30" t="s">
+      <c r="A127" s="11" t="n">
+        <v>46225</v>
+      </c>
+      <c r="B127" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C127" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="D127" s="30" t="s">
-        <v>44</v>
-      </c>
-      <c r="E127" s="31" t="n">
-        <v>17</v>
-      </c>
-      <c r="F127" s="31" t="n">
+      <c r="D127" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="E127" s="13" t="n">
+        <v>70</v>
+      </c>
+      <c r="F127" s="13" t="n">
         <f aca="false">IF($B127="","",IF($D127="kg",N($E127),IF($D127="sacos",N($E127)*97,IF($D127="jabas",N($E127)*IFERROR(VLOOKUP($C127,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
-        <v>17</v>
-      </c>
-      <c r="G127" s="30"/>
-      <c r="H127" s="30" t="s">
-        <v>45</v>
+        <v>6790</v>
+      </c>
+      <c r="G127" s="12"/>
+      <c r="H127" s="12" t="s">
+        <v>19</v>
       </c>
       <c r="I127" s="1" t="n">
         <f aca="false">N($F127)</f>
-        <v>17</v>
+        <v>6790</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6193,7 +6197,7 @@
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A143" s="11" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B143" s="12" t="s">
         <v>17</v>
@@ -6473,7 +6477,7 @@
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A153" s="11" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B153" s="12" t="s">
         <v>17</v>
@@ -6501,32 +6505,30 @@
       </c>
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A154" s="11" t="n">
-        <v>46226</v>
-      </c>
-      <c r="B154" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="C154" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="D154" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="E154" s="13" t="n">
-        <v>37</v>
-      </c>
-      <c r="F154" s="13" t="n">
+      <c r="A154" s="14" t="n">
+        <v>46227</v>
+      </c>
+      <c r="B154" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C154" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D154" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="E154" s="16" t="n">
+        <v>48</v>
+      </c>
+      <c r="F154" s="16" t="n">
         <f aca="false">IF($B154="","",IF($D154="kg",N($E154),IF($D154="sacos",N($E154)*97,IF($D154="jabas",N($E154)*IFERROR(VLOOKUP($C154,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
-        <v>3589</v>
-      </c>
-      <c r="G154" s="12"/>
-      <c r="H154" s="12" t="s">
-        <v>19</v>
-      </c>
+        <v>720</v>
+      </c>
+      <c r="G154" s="15"/>
+      <c r="H154" s="15"/>
       <c r="I154" s="1" t="n">
         <f aca="false">N($F154)</f>
-        <v>3589</v>
+        <v>720</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6537,23 +6539,23 @@
         <v>20</v>
       </c>
       <c r="C155" s="15" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="D155" s="15" t="s">
         <v>12</v>
       </c>
       <c r="E155" s="16" t="n">
-        <v>48</v>
+        <v>3</v>
       </c>
       <c r="F155" s="16" t="n">
         <f aca="false">IF($B155="","",IF($D155="kg",N($E155),IF($D155="sacos",N($E155)*97,IF($D155="jabas",N($E155)*IFERROR(VLOOKUP($C155,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
-        <v>720</v>
+        <v>54</v>
       </c>
       <c r="G155" s="15"/>
       <c r="H155" s="15"/>
       <c r="I155" s="1" t="n">
         <f aca="false">N($F155)</f>
-        <v>720</v>
+        <v>54</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6564,23 +6566,23 @@
         <v>20</v>
       </c>
       <c r="C156" s="15" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D156" s="15" t="s">
         <v>12</v>
       </c>
       <c r="E156" s="16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F156" s="16" t="n">
         <f aca="false">IF($B156="","",IF($D156="kg",N($E156),IF($D156="sacos",N($E156)*97,IF($D156="jabas",N($E156)*IFERROR(VLOOKUP($C156,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
-        <v>54</v>
+        <v>85</v>
       </c>
       <c r="G156" s="15"/>
       <c r="H156" s="15"/>
       <c r="I156" s="1" t="n">
         <f aca="false">N($F156)</f>
-        <v>54</v>
+        <v>85</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6591,23 +6593,23 @@
         <v>20</v>
       </c>
       <c r="C157" s="15" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="D157" s="15" t="s">
         <v>12</v>
       </c>
       <c r="E157" s="16" t="n">
-        <v>5</v>
+        <v>95</v>
       </c>
       <c r="F157" s="16" t="n">
         <f aca="false">IF($B157="","",IF($D157="kg",N($E157),IF($D157="sacos",N($E157)*97,IF($D157="jabas",N($E157)*IFERROR(VLOOKUP($C157,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
-        <v>85</v>
+        <v>1615</v>
       </c>
       <c r="G157" s="15"/>
       <c r="H157" s="15"/>
       <c r="I157" s="1" t="n">
         <f aca="false">N($F157)</f>
-        <v>85</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6618,50 +6620,52 @@
         <v>20</v>
       </c>
       <c r="C158" s="15" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D158" s="15" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E158" s="16" t="n">
-        <v>95</v>
+        <v>6</v>
       </c>
       <c r="F158" s="16" t="n">
         <f aca="false">IF($B158="","",IF($D158="kg",N($E158),IF($D158="sacos",N($E158)*97,IF($D158="jabas",N($E158)*IFERROR(VLOOKUP($C158,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
-        <v>1615</v>
+        <v>582</v>
       </c>
       <c r="G158" s="15"/>
       <c r="H158" s="15"/>
       <c r="I158" s="1" t="n">
         <f aca="false">N($F158)</f>
-        <v>1615</v>
+        <v>582</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A159" s="14" t="n">
+      <c r="A159" s="17" t="n">
         <v>46227</v>
       </c>
-      <c r="B159" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C159" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="D159" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="E159" s="16" t="n">
-        <v>6</v>
-      </c>
-      <c r="F159" s="16" t="n">
+      <c r="B159" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="C159" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="D159" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="E159" s="19" t="n">
+        <v>67</v>
+      </c>
+      <c r="F159" s="19" t="n">
         <f aca="false">IF($B159="","",IF($D159="kg",N($E159),IF($D159="sacos",N($E159)*97,IF($D159="jabas",N($E159)*IFERROR(VLOOKUP($C159,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
-        <v>582</v>
-      </c>
-      <c r="G159" s="15"/>
-      <c r="H159" s="15"/>
+        <v>1005</v>
+      </c>
+      <c r="G159" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="H159" s="18"/>
       <c r="I159" s="1" t="n">
         <f aca="false">N($F159)</f>
-        <v>582</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6672,17 +6676,17 @@
         <v>23</v>
       </c>
       <c r="C160" s="18" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="D160" s="18" t="s">
         <v>12</v>
       </c>
       <c r="E160" s="19" t="n">
-        <v>67</v>
+        <v>11</v>
       </c>
       <c r="F160" s="19" t="n">
         <f aca="false">IF($B160="","",IF($D160="kg",N($E160),IF($D160="sacos",N($E160)*97,IF($D160="jabas",N($E160)*IFERROR(VLOOKUP($C160,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
-        <v>1005</v>
+        <v>198</v>
       </c>
       <c r="G160" s="18" t="s">
         <v>54</v>
@@ -6690,7 +6694,7 @@
       <c r="H160" s="18"/>
       <c r="I160" s="1" t="n">
         <f aca="false">N($F160)</f>
-        <v>1005</v>
+        <v>198</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6701,17 +6705,17 @@
         <v>23</v>
       </c>
       <c r="C161" s="18" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D161" s="18" t="s">
         <v>12</v>
       </c>
       <c r="E161" s="19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F161" s="19" t="n">
         <f aca="false">IF($B161="","",IF($D161="kg",N($E161),IF($D161="sacos",N($E161)*97,IF($D161="jabas",N($E161)*IFERROR(VLOOKUP($C161,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="G161" s="18" t="s">
         <v>54</v>
@@ -6719,7 +6723,7 @@
       <c r="H161" s="18"/>
       <c r="I161" s="1" t="n">
         <f aca="false">N($F161)</f>
-        <v>198</v>
+        <v>204</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6730,17 +6734,17 @@
         <v>23</v>
       </c>
       <c r="C162" s="18" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="D162" s="18" t="s">
         <v>12</v>
       </c>
       <c r="E162" s="19" t="n">
-        <v>12</v>
+        <v>118</v>
       </c>
       <c r="F162" s="19" t="n">
         <f aca="false">IF($B162="","",IF($D162="kg",N($E162),IF($D162="sacos",N($E162)*97,IF($D162="jabas",N($E162)*IFERROR(VLOOKUP($C162,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
-        <v>204</v>
+        <v>2006</v>
       </c>
       <c r="G162" s="18" t="s">
         <v>54</v>
@@ -6748,144 +6752,144 @@
       <c r="H162" s="18"/>
       <c r="I162" s="1" t="n">
         <f aca="false">N($F162)</f>
-        <v>204</v>
+        <v>2006</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A163" s="17" t="n">
+      <c r="A163" s="26" t="n">
         <v>46227</v>
       </c>
-      <c r="B163" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="C163" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="D163" s="18" t="s">
+      <c r="B163" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="C163" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="D163" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="E163" s="19" t="n">
-        <v>118</v>
-      </c>
-      <c r="F163" s="19" t="n">
+      <c r="E163" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F163" s="28" t="n">
         <f aca="false">IF($B163="","",IF($D163="kg",N($E163),IF($D163="sacos",N($E163)*97,IF($D163="jabas",N($E163)*IFERROR(VLOOKUP($C163,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
-        <v>2006</v>
-      </c>
-      <c r="G163" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="H163" s="18"/>
+        <v>15</v>
+      </c>
+      <c r="G163" s="27"/>
+      <c r="H163" s="27"/>
       <c r="I163" s="1" t="n">
         <f aca="false">N($F163)</f>
-        <v>2006</v>
+        <v>15</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A164" s="26" t="n">
+      <c r="A164" s="29" t="n">
         <v>46227</v>
       </c>
-      <c r="B164" s="27" t="s">
-        <v>42</v>
-      </c>
-      <c r="C164" s="27" t="s">
+      <c r="B164" s="30" t="s">
+        <v>43</v>
+      </c>
+      <c r="C164" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="D164" s="27" t="s">
-        <v>12</v>
-      </c>
-      <c r="E164" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F164" s="28" t="n">
+      <c r="D164" s="30" t="s">
+        <v>44</v>
+      </c>
+      <c r="E164" s="31" t="n">
+        <v>11</v>
+      </c>
+      <c r="F164" s="31" t="n">
         <f aca="false">IF($B164="","",IF($D164="kg",N($E164),IF($D164="sacos",N($E164)*97,IF($D164="jabas",N($E164)*IFERROR(VLOOKUP($C164,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
-        <v>15</v>
-      </c>
-      <c r="G164" s="27"/>
-      <c r="H164" s="27"/>
+        <v>11</v>
+      </c>
+      <c r="G164" s="30"/>
+      <c r="H164" s="30"/>
       <c r="I164" s="1" t="n">
         <f aca="false">N($F164)</f>
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A165" s="29" t="n">
+      <c r="A165" s="26" t="n">
         <v>46227</v>
       </c>
-      <c r="B165" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="C165" s="30" t="s">
-        <v>11</v>
-      </c>
-      <c r="D165" s="30" t="s">
-        <v>44</v>
-      </c>
-      <c r="E165" s="31" t="n">
-        <v>11</v>
-      </c>
-      <c r="F165" s="31" t="n">
+      <c r="B165" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="C165" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="D165" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="E165" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F165" s="28" t="n">
         <f aca="false">IF($B165="","",IF($D165="kg",N($E165),IF($D165="sacos",N($E165)*97,IF($D165="jabas",N($E165)*IFERROR(VLOOKUP($C165,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
-        <v>11</v>
-      </c>
-      <c r="G165" s="30"/>
-      <c r="H165" s="30"/>
+        <v>17</v>
+      </c>
+      <c r="G165" s="27"/>
+      <c r="H165" s="27"/>
       <c r="I165" s="1" t="n">
         <f aca="false">N($F165)</f>
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A166" s="26" t="n">
+      <c r="A166" s="29" t="n">
         <v>46227</v>
       </c>
-      <c r="B166" s="27" t="s">
-        <v>42</v>
-      </c>
-      <c r="C166" s="27" t="s">
+      <c r="B166" s="30" t="s">
+        <v>43</v>
+      </c>
+      <c r="C166" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="D166" s="27" t="s">
-        <v>12</v>
-      </c>
-      <c r="E166" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F166" s="28" t="n">
+      <c r="D166" s="30" t="s">
+        <v>44</v>
+      </c>
+      <c r="E166" s="31" t="n">
+        <v>10</v>
+      </c>
+      <c r="F166" s="31" t="n">
         <f aca="false">IF($B166="","",IF($D166="kg",N($E166),IF($D166="sacos",N($E166)*97,IF($D166="jabas",N($E166)*IFERROR(VLOOKUP($C166,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
-        <v>17</v>
-      </c>
-      <c r="G166" s="27"/>
-      <c r="H166" s="27"/>
+        <v>10</v>
+      </c>
+      <c r="G166" s="30"/>
+      <c r="H166" s="30"/>
       <c r="I166" s="1" t="n">
         <f aca="false">N($F166)</f>
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A167" s="29" t="n">
+      <c r="A167" s="20" t="n">
         <v>46227</v>
       </c>
-      <c r="B167" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="C167" s="30" t="s">
-        <v>13</v>
-      </c>
-      <c r="D167" s="30" t="s">
-        <v>44</v>
-      </c>
-      <c r="E167" s="31" t="n">
-        <v>10</v>
-      </c>
-      <c r="F167" s="31" t="n">
+      <c r="B167" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="C167" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="D167" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="E167" s="22" t="n">
+        <v>9</v>
+      </c>
+      <c r="F167" s="22" t="n">
         <f aca="false">IF($B167="","",IF($D167="kg",N($E167),IF($D167="sacos",N($E167)*97,IF($D167="jabas",N($E167)*IFERROR(VLOOKUP($C167,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
-        <v>10</v>
-      </c>
-      <c r="G167" s="30"/>
-      <c r="H167" s="30"/>
+        <v>873</v>
+      </c>
+      <c r="G167" s="21" t="s">
+        <v>55</v>
+      </c>
+      <c r="H167" s="21"/>
       <c r="I167" s="1" t="n">
         <f aca="false">N($F167)</f>
-        <v>10</v>
+        <v>873</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6902,77 +6906,77 @@
         <v>16</v>
       </c>
       <c r="E168" s="22" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F168" s="22" t="n">
         <f aca="false">IF($B168="","",IF($D168="kg",N($E168),IF($D168="sacos",N($E168)*97,IF($D168="jabas",N($E168)*IFERROR(VLOOKUP($C168,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
-        <v>873</v>
+        <v>97</v>
       </c>
       <c r="G168" s="21" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H168" s="21"/>
       <c r="I168" s="1" t="n">
         <f aca="false">N($F168)</f>
-        <v>873</v>
+        <v>97</v>
       </c>
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A169" s="20" t="n">
+      <c r="A169" s="38" t="n">
         <v>46227</v>
       </c>
-      <c r="B169" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="C169" s="21" t="s">
-        <v>15</v>
-      </c>
-      <c r="D169" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="E169" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="F169" s="22" t="n">
+      <c r="B169" s="39" t="s">
+        <v>57</v>
+      </c>
+      <c r="C169" s="39" t="s">
+        <v>58</v>
+      </c>
+      <c r="D169" s="39" t="s">
+        <v>44</v>
+      </c>
+      <c r="E169" s="40" t="n">
+        <v>48</v>
+      </c>
+      <c r="F169" s="40" t="n">
         <f aca="false">IF($B169="","",IF($D169="kg",N($E169),IF($D169="sacos",N($E169)*97,IF($D169="jabas",N($E169)*IFERROR(VLOOKUP($C169,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
-        <v>97</v>
-      </c>
-      <c r="G169" s="21" t="s">
-        <v>56</v>
-      </c>
-      <c r="H169" s="21"/>
+        <v>48</v>
+      </c>
+      <c r="G169" s="39"/>
+      <c r="H169" s="39" t="s">
+        <v>59</v>
+      </c>
       <c r="I169" s="1" t="n">
         <f aca="false">N($F169)</f>
-        <v>97</v>
+        <v>48</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A170" s="38" t="n">
-        <v>46227</v>
-      </c>
-      <c r="B170" s="39" t="s">
-        <v>57</v>
-      </c>
-      <c r="C170" s="39" t="s">
-        <v>58</v>
-      </c>
-      <c r="D170" s="39" t="s">
-        <v>44</v>
-      </c>
-      <c r="E170" s="40" t="n">
-        <v>48</v>
-      </c>
-      <c r="F170" s="40" t="n">
+      <c r="A170" s="11" t="n">
+        <v>46228</v>
+      </c>
+      <c r="B170" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C170" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D170" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="E170" s="13" t="n">
+        <v>37</v>
+      </c>
+      <c r="F170" s="13" t="n">
         <f aca="false">IF($B170="","",IF($D170="kg",N($E170),IF($D170="sacos",N($E170)*97,IF($D170="jabas",N($E170)*IFERROR(VLOOKUP($C170,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
-        <v>48</v>
-      </c>
-      <c r="G170" s="39"/>
-      <c r="H170" s="39" t="s">
-        <v>59</v>
+        <v>3589</v>
+      </c>
+      <c r="G170" s="12"/>
+      <c r="H170" s="12" t="s">
+        <v>19</v>
       </c>
       <c r="I170" s="1" t="n">
         <f aca="false">N($F170)</f>
-        <v>48</v>
+        <v>3589</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12408,7 +12412,7 @@
       </c>
       <c r="H14" s="53" t="n">
         <f aca="false">IF($A14="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$400="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$400&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$400="COMPRA")+(MOVIMIENTOS!$B$5:$B$400="REPROCESO")+(MOVIMIENTOS!$B$5:$B$400="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$400="AJUSTE")*(MOVIMIENTOS!$C$5:$C$400&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$400&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$400&lt;=$A14)*MOVIMIENTOS!$I$5:$I$400)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$400="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$400="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$400="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$400="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$400="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$400="PROCESO")*(MOVIMIENTOS!$C$5:$C$400="Chancho"))+((MOVIMIENTOS!$B$5:$B$400="REGALO")*(MOVIMIENTOS!$C$5:$C$400&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$400="VENTA")*(MOVIMIENTOS!$C$5:$C$400&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$400&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$400&lt;=$A14)*MOVIMIENTOS!$I$5:$I$400))</f>
-        <v>4667.5</v>
+        <v>2533.5</v>
       </c>
       <c r="I14" s="49"/>
       <c r="J14" s="49" t="str">
@@ -12454,7 +12458,7 @@
       </c>
       <c r="H15" s="53" t="n">
         <f aca="false">IF($A15="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$400="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$400&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$400="COMPRA")+(MOVIMIENTOS!$B$5:$B$400="REPROCESO")+(MOVIMIENTOS!$B$5:$B$400="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$400="AJUSTE")*(MOVIMIENTOS!$C$5:$C$400&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$400&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$400&lt;=$A15)*MOVIMIENTOS!$I$5:$I$400)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$400="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$400="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$400="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$400="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$400="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$400="PROCESO")*(MOVIMIENTOS!$C$5:$C$400="Chancho"))+((MOVIMIENTOS!$B$5:$B$400="REGALO")*(MOVIMIENTOS!$C$5:$C$400&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$400="VENTA")*(MOVIMIENTOS!$C$5:$C$400&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$400&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$400&lt;=$A15)*MOVIMIENTOS!$I$5:$I$400))</f>
-        <v>7535.5</v>
+        <v>745.5</v>
       </c>
       <c r="I15" s="49"/>
       <c r="J15" s="49" t="str">
@@ -12500,7 +12504,7 @@
       </c>
       <c r="H16" s="53" t="n">
         <f aca="false">IF($A16="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$400="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$400&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$400="COMPRA")+(MOVIMIENTOS!$B$5:$B$400="REPROCESO")+(MOVIMIENTOS!$B$5:$B$400="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$400="AJUSTE")*(MOVIMIENTOS!$C$5:$C$400&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$400&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$400&lt;=$A16)*MOVIMIENTOS!$I$5:$I$400)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$400="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$400="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$400="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$400="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$400="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$400="PROCESO")*(MOVIMIENTOS!$C$5:$C$400="Chancho"))+((MOVIMIENTOS!$B$5:$B$400="REGALO")*(MOVIMIENTOS!$C$5:$C$400&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$400="VENTA")*(MOVIMIENTOS!$C$5:$C$400&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$400&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$400&lt;=$A16)*MOVIMIENTOS!$I$5:$I$400))</f>
-        <v>7457.5</v>
+        <v>3577.5</v>
       </c>
       <c r="I16" s="49"/>
       <c r="J16" s="49" t="str">
@@ -12546,7 +12550,7 @@
       </c>
       <c r="H17" s="53" t="n">
         <f aca="false">IF($A17="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$400="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$400&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$400="COMPRA")+(MOVIMIENTOS!$B$5:$B$400="REPROCESO")+(MOVIMIENTOS!$B$5:$B$400="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$400="AJUSTE")*(MOVIMIENTOS!$C$5:$C$400&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$400&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$400&lt;=$A17)*MOVIMIENTOS!$I$5:$I$400)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$400="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$400="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$400="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$400="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$400="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$400="PROCESO")*(MOVIMIENTOS!$C$5:$C$400="Chancho"))+((MOVIMIENTOS!$B$5:$B$400="REGALO")*(MOVIMIENTOS!$C$5:$C$400&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$400="VENTA")*(MOVIMIENTOS!$C$5:$C$400&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$400&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$400&lt;=$A17)*MOVIMIENTOS!$I$5:$I$400))</f>
-        <v>11174</v>
+        <v>3414</v>
       </c>
       <c r="I17" s="49"/>
       <c r="J17" s="49" t="str">
@@ -12592,7 +12596,7 @@
       </c>
       <c r="H18" s="53" t="n">
         <f aca="false">IF($A18="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$400="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$400&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$400="COMPRA")+(MOVIMIENTOS!$B$5:$B$400="REPROCESO")+(MOVIMIENTOS!$B$5:$B$400="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$400="AJUSTE")*(MOVIMIENTOS!$C$5:$C$400&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$400&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$400&lt;=$A18)*MOVIMIENTOS!$I$5:$I$400)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$400="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$400="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$400="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$400="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$400="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$400="PROCESO")*(MOVIMIENTOS!$C$5:$C$400="Chancho"))+((MOVIMIENTOS!$B$5:$B$400="REGALO")*(MOVIMIENTOS!$C$5:$C$400&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$400="VENTA")*(MOVIMIENTOS!$C$5:$C$400&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$400&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$400&lt;=$A18)*MOVIMIENTOS!$I$5:$I$400))</f>
-        <v>7152</v>
+        <v>3563</v>
       </c>
       <c r="I18" s="49"/>
       <c r="J18" s="49" t="str">
@@ -15821,13 +15825,13 @@
       <c r="G109" s="49"/>
       <c r="H109" s="49"/>
       <c r="I109" s="49"/>
-      <c r="J109" s="49" t="str">
+      <c r="J109" s="49" t="n">
         <f aca="false">IF(AND(MOVIMIENTOS!$A109&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A108,MOVIMIENTOS!$A109)=0),COUNT(J$4:J108)+1,"")</f>
-        <v/>
+        <v>11</v>
       </c>
       <c r="K109" s="54" t="n">
         <f aca="false">MOVIMIENTOS!$A109</f>
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="L109" s="49"/>
       <c r="M109" s="49"/>
@@ -15843,9 +15847,9 @@
       <c r="G110" s="49"/>
       <c r="H110" s="49"/>
       <c r="I110" s="49"/>
-      <c r="J110" s="49" t="n">
+      <c r="J110" s="49" t="str">
         <f aca="false">IF(AND(MOVIMIENTOS!$A110&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A109,MOVIMIENTOS!$A110)=0),COUNT(J$4:J109)+1,"")</f>
-        <v>11</v>
+        <v/>
       </c>
       <c r="K110" s="54" t="n">
         <f aca="false">MOVIMIENTOS!$A110</f>
@@ -16217,13 +16221,13 @@
       <c r="G127" s="49"/>
       <c r="H127" s="49"/>
       <c r="I127" s="49"/>
-      <c r="J127" s="49" t="str">
+      <c r="J127" s="49" t="n">
         <f aca="false">IF(AND(MOVIMIENTOS!$A127&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A126,MOVIMIENTOS!$A127)=0),COUNT(J$4:J126)+1,"")</f>
-        <v/>
+        <v>12</v>
       </c>
       <c r="K127" s="54" t="n">
         <f aca="false">MOVIMIENTOS!$A127</f>
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="L127" s="49"/>
       <c r="M127" s="49"/>
@@ -16239,9 +16243,9 @@
       <c r="G128" s="49"/>
       <c r="H128" s="49"/>
       <c r="I128" s="49"/>
-      <c r="J128" s="49" t="n">
+      <c r="J128" s="49" t="str">
         <f aca="false">IF(AND(MOVIMIENTOS!$A128&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A127,MOVIMIENTOS!$A128)=0),COUNT(J$4:J127)+1,"")</f>
-        <v>12</v>
+        <v/>
       </c>
       <c r="K128" s="54" t="n">
         <f aca="false">MOVIMIENTOS!$A128</f>
@@ -16569,13 +16573,13 @@
       <c r="G143" s="49"/>
       <c r="H143" s="49"/>
       <c r="I143" s="49"/>
-      <c r="J143" s="49" t="str">
+      <c r="J143" s="49" t="n">
         <f aca="false">IF(AND(MOVIMIENTOS!$A143&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A142,MOVIMIENTOS!$A143)=0),COUNT(J$4:J142)+1,"")</f>
-        <v/>
+        <v>13</v>
       </c>
       <c r="K143" s="54" t="n">
         <f aca="false">MOVIMIENTOS!$A143</f>
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="L143" s="49"/>
       <c r="M143" s="49"/>
@@ -16591,9 +16595,9 @@
       <c r="G144" s="49"/>
       <c r="H144" s="49"/>
       <c r="I144" s="49"/>
-      <c r="J144" s="49" t="n">
+      <c r="J144" s="49" t="str">
         <f aca="false">IF(AND(MOVIMIENTOS!$A144&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A143,MOVIMIENTOS!$A144)=0),COUNT(J$4:J143)+1,"")</f>
-        <v>13</v>
+        <v/>
       </c>
       <c r="K144" s="54" t="n">
         <f aca="false">MOVIMIENTOS!$A144</f>
@@ -16789,13 +16793,13 @@
       <c r="G153" s="49"/>
       <c r="H153" s="49"/>
       <c r="I153" s="49"/>
-      <c r="J153" s="49" t="str">
+      <c r="J153" s="49" t="n">
         <f aca="false">IF(AND(MOVIMIENTOS!$A153&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A152,MOVIMIENTOS!$A153)=0),COUNT(J$4:J152)+1,"")</f>
-        <v/>
+        <v>14</v>
       </c>
       <c r="K153" s="54" t="n">
         <f aca="false">MOVIMIENTOS!$A153</f>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="L153" s="49"/>
       <c r="M153" s="49"/>
@@ -16817,7 +16821,7 @@
       </c>
       <c r="K154" s="54" t="n">
         <f aca="false">MOVIMIENTOS!$A154</f>
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="L154" s="49"/>
       <c r="M154" s="49"/>
@@ -16833,9 +16837,9 @@
       <c r="G155" s="49"/>
       <c r="H155" s="49"/>
       <c r="I155" s="49"/>
-      <c r="J155" s="49" t="n">
+      <c r="J155" s="49" t="str">
         <f aca="false">IF(AND(MOVIMIENTOS!$A155&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A154,MOVIMIENTOS!$A155)=0),COUNT(J$4:J154)+1,"")</f>
-        <v>14</v>
+        <v/>
       </c>
       <c r="K155" s="54" t="n">
         <f aca="false">MOVIMIENTOS!$A155</f>
@@ -17163,13 +17167,13 @@
       <c r="G170" s="49"/>
       <c r="H170" s="49"/>
       <c r="I170" s="49"/>
-      <c r="J170" s="49" t="str">
+      <c r="J170" s="49" t="n">
         <f aca="false">IF(AND(MOVIMIENTOS!$A170&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A169,MOVIMIENTOS!$A170)=0),COUNT(J$4:J169)+1,"")</f>
-        <v/>
+        <v>15</v>
       </c>
       <c r="K170" s="54" t="n">
         <f aca="false">MOVIMIENTOS!$A170</f>
-        <v>46227</v>
+        <v>46228</v>
       </c>
       <c r="L170" s="49"/>
       <c r="M170" s="49"/>
@@ -17185,9 +17189,9 @@
       <c r="G171" s="49"/>
       <c r="H171" s="49"/>
       <c r="I171" s="49"/>
-      <c r="J171" s="49" t="n">
+      <c r="J171" s="49" t="str">
         <f aca="false">IF(AND(MOVIMIENTOS!$A171&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A170,MOVIMIENTOS!$A171)=0),COUNT(J$4:J170)+1,"")</f>
-        <v>15</v>
+        <v/>
       </c>
       <c r="K171" s="54" t="n">
         <f aca="false">MOVIMIENTOS!$A171</f>
@@ -24149,7 +24153,7 @@
       </c>
       <c r="C54" s="60" t="n">
         <f aca="false">SUMPRODUCT((MOVIMIENTOS!$A$5:$A$400=DATE(2026,7,20))*(MOVIMIENTOS!$B$5:$B$400="COMPRA")*MOVIMIENTOS!$I$5:$I$400)</f>
-        <v>6790</v>
+        <v>4656</v>
       </c>
       <c r="D54" s="60" t="n">
         <f aca="false">SUMPRODUCT((MOVIMIENTOS!$A$5:$A$400=DATE(2026,7,20))*(MOVIMIENTOS!$B$5:$B$400="PROCESO")*MOVIMIENTOS!$I$5:$I$400)</f>
@@ -24161,11 +24165,11 @@
       </c>
       <c r="F54" s="59" t="str">
         <f aca="false">"Selección: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$400=DATE(2026,7,20))*(MOVIMIENTOS!$B$5:$B$400="PROCESO")*(MOVIMIENTOS!$C$5:$C$400&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$400),"#,##0")&amp;" kg  ·  Chancho: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$400=DATE(2026,7,20))*(MOVIMIENTOS!$B$5:$B$400="PROCESO")*(MOVIMIENTOS!$C$5:$C$400="Chancho")*MOVIMIENTOS!$I$5:$I$400),"#,##0")&amp;" kg"&amp;IF(C54&gt;0,"  ·  "&amp;TEXT(D54/C54,"0%")&amp;" del ingreso","")</f>
-        <v>Selección: 4,018 kg  ·  Chancho: 631 kg  ·  68% del ingreso</v>
+        <v>Selección: 4,018 kg  ·  Chancho: 631 kg  ·  100% del ingreso</v>
       </c>
       <c r="G54" s="60" t="n">
-        <f aca="false">N(G62)</f>
-        <v>4667.5</v>
+        <f aca="false">N(G61)</f>
+        <v>2533.5</v>
       </c>
       <c r="H54" s="49"/>
       <c r="I54" s="49"/>
@@ -24355,25 +24359,22 @@
       <c r="T59" s="49"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="62" t="n">
+      <c r="A60" s="52" t="n">
         <v>46223</v>
       </c>
-      <c r="B60" s="63" t="s">
-        <v>92</v>
-      </c>
-      <c r="C60" s="64" t="n">
-        <f aca="false">N(MOVIMIENTOS!$I107)</f>
-        <v>2134</v>
-      </c>
-      <c r="D60" s="64"/>
-      <c r="E60" s="64"/>
-      <c r="F60" s="63" t="str">
-        <f aca="false">TRIM(IF(MOVIMIENTOS!$G107&lt;&gt;"",MOVIMIENTOS!$G107&amp;"  ","")&amp;IF(N(MOVIMIENTOS!$E107)&gt;0,MOVIMIENTOS!$E107&amp;" "&amp;MOVIMIENTOS!$D107&amp;"  ","")&amp;IF(MOVIMIENTOS!$H107&lt;&gt;"",MOVIMIENTOS!$H107,""))</f>
-        <v>22 sacos peso aprox 95 kg/saco</v>
-      </c>
-      <c r="G60" s="64" t="n">
+      <c r="B60" s="61" t="s">
+        <v>114</v>
+      </c>
+      <c r="C60" s="53"/>
+      <c r="D60" s="53"/>
+      <c r="E60" s="53"/>
+      <c r="F60" s="61" t="str">
+        <f aca="false">MOVIMIENTOS!$E107&amp;" jaba(s) movida(s) para completar otras · no resta del Stock Kg"</f>
+        <v>1 jaba(s) movida(s) para completar otras · no resta del Stock Kg</v>
+      </c>
+      <c r="G60" s="53" t="n">
         <f aca="false">N(G59)+N(C60)-N(E60)</f>
-        <v>4667.5</v>
+        <v>2533.5</v>
       </c>
       <c r="H60" s="49"/>
       <c r="I60" s="49"/>
@@ -24394,7 +24395,7 @@
         <v>46223</v>
       </c>
       <c r="B61" s="61" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C61" s="53"/>
       <c r="D61" s="53"/>
@@ -24405,7 +24406,7 @@
       </c>
       <c r="G61" s="53" t="n">
         <f aca="false">N(G60)+N(C61)-N(E61)</f>
-        <v>4667.5</v>
+        <v>2533.5</v>
       </c>
       <c r="H61" s="49"/>
       <c r="I61" s="49"/>
@@ -24422,22 +24423,31 @@
       <c r="T61" s="49"/>
     </row>
     <row r="62" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="52" t="n">
-        <v>46223</v>
-      </c>
-      <c r="B62" s="61" t="s">
-        <v>115</v>
-      </c>
-      <c r="C62" s="53"/>
-      <c r="D62" s="53"/>
-      <c r="E62" s="53"/>
-      <c r="F62" s="61" t="str">
-        <f aca="false">MOVIMIENTOS!$E109&amp;" jaba(s) movida(s) para completar otras · no resta del Stock Kg"</f>
-        <v>1 jaba(s) movida(s) para completar otras · no resta del Stock Kg</v>
-      </c>
-      <c r="G62" s="53" t="n">
-        <f aca="false">N(G61)+N(C62)-N(E62)</f>
-        <v>4667.5</v>
+      <c r="A62" s="58" t="n">
+        <v>46224</v>
+      </c>
+      <c r="B62" s="59" t="s">
+        <v>89</v>
+      </c>
+      <c r="C62" s="60" t="n">
+        <f aca="false">SUMPRODUCT((MOVIMIENTOS!$A$5:$A$400=DATE(2026,7,21))*(MOVIMIENTOS!$B$5:$B$400="COMPRA")*MOVIMIENTOS!$I$5:$I$400)</f>
+        <v>2134</v>
+      </c>
+      <c r="D62" s="60" t="n">
+        <f aca="false">SUMPRODUCT((MOVIMIENTOS!$A$5:$A$400=DATE(2026,7,21))*(MOVIMIENTOS!$B$5:$B$400="PROCESO")*MOVIMIENTOS!$I$5:$I$400)</f>
+        <v>4879</v>
+      </c>
+      <c r="E62" s="60" t="n">
+        <f aca="false">SUMPRODUCT((MOVIMIENTOS!$A$5:$A$400=DATE(2026,7,21))*((MOVIMIENTOS!$B$5:$B$400="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$400="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$400="ENVIO A TOTTUS"))*MOVIMIENTOS!$I$5:$I$400)</f>
+        <v>3260</v>
+      </c>
+      <c r="F62" s="59" t="str">
+        <f aca="false">"Selección: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$400=DATE(2026,7,21))*(MOVIMIENTOS!$B$5:$B$400="PROCESO")*(MOVIMIENTOS!$C$5:$C$400&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$400),"#,##0")&amp;" kg  ·  Chancho: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$400=DATE(2026,7,21))*(MOVIMIENTOS!$B$5:$B$400="PROCESO")*(MOVIMIENTOS!$C$5:$C$400="Chancho")*MOVIMIENTOS!$I$5:$I$400),"#,##0")&amp;" kg"&amp;IF(C62&gt;0,"  ·  "&amp;TEXT(D62/C62,"0%")&amp;" del ingreso","")</f>
+        <v>Selección: 4,200 kg  ·  Chancho: 679 kg  ·  229% del ingreso</v>
+      </c>
+      <c r="G62" s="60" t="n">
+        <f aca="false">N(G72)</f>
+        <v>745.5</v>
       </c>
       <c r="H62" s="49"/>
       <c r="I62" s="49"/>
@@ -24454,31 +24464,25 @@
       <c r="T62" s="49"/>
     </row>
     <row r="63" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="58" t="n">
+      <c r="A63" s="62" t="n">
         <v>46224</v>
       </c>
-      <c r="B63" s="59" t="s">
-        <v>89</v>
-      </c>
-      <c r="C63" s="60" t="n">
-        <f aca="false">SUMPRODUCT((MOVIMIENTOS!$A$5:$A$400=DATE(2026,7,21))*(MOVIMIENTOS!$B$5:$B$400="COMPRA")*MOVIMIENTOS!$I$5:$I$400)</f>
-        <v>6790</v>
-      </c>
-      <c r="D63" s="60" t="n">
-        <f aca="false">SUMPRODUCT((MOVIMIENTOS!$A$5:$A$400=DATE(2026,7,21))*(MOVIMIENTOS!$B$5:$B$400="PROCESO")*MOVIMIENTOS!$I$5:$I$400)</f>
-        <v>4879</v>
-      </c>
-      <c r="E63" s="60" t="n">
-        <f aca="false">SUMPRODUCT((MOVIMIENTOS!$A$5:$A$400=DATE(2026,7,21))*((MOVIMIENTOS!$B$5:$B$400="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$400="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$400="ENVIO A TOTTUS"))*MOVIMIENTOS!$I$5:$I$400)</f>
-        <v>3260</v>
-      </c>
-      <c r="F63" s="59" t="str">
-        <f aca="false">"Selección: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$400=DATE(2026,7,21))*(MOVIMIENTOS!$B$5:$B$400="PROCESO")*(MOVIMIENTOS!$C$5:$C$400&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$400),"#,##0")&amp;" kg  ·  Chancho: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$400=DATE(2026,7,21))*(MOVIMIENTOS!$B$5:$B$400="PROCESO")*(MOVIMIENTOS!$C$5:$C$400="Chancho")*MOVIMIENTOS!$I$5:$I$400),"#,##0")&amp;" kg"&amp;IF(C63&gt;0,"  ·  "&amp;TEXT(D63/C63,"0%")&amp;" del ingreso","")</f>
-        <v>Selección: 4,200 kg  ·  Chancho: 679 kg  ·  72% del ingreso</v>
-      </c>
-      <c r="G63" s="60" t="n">
-        <f aca="false">N(G73)</f>
-        <v>7535.5</v>
+      <c r="B63" s="63" t="s">
+        <v>92</v>
+      </c>
+      <c r="C63" s="64" t="n">
+        <f aca="false">N(MOVIMIENTOS!$I109)</f>
+        <v>2134</v>
+      </c>
+      <c r="D63" s="64"/>
+      <c r="E63" s="64"/>
+      <c r="F63" s="63" t="str">
+        <f aca="false">TRIM(IF(MOVIMIENTOS!$G109&lt;&gt;"",MOVIMIENTOS!$G109&amp;"  ","")&amp;IF(N(MOVIMIENTOS!$E109)&gt;0,MOVIMIENTOS!$E109&amp;" "&amp;MOVIMIENTOS!$D109&amp;"  ","")&amp;IF(MOVIMIENTOS!$H109&lt;&gt;"",MOVIMIENTOS!$H109,""))</f>
+        <v>22 sacos peso aprox 95 kg/saco</v>
+      </c>
+      <c r="G63" s="64" t="n">
+        <f aca="false">N(G61)+N(C63)-N(E63)</f>
+        <v>4667.5</v>
       </c>
       <c r="H63" s="49"/>
       <c r="I63" s="49"/>
@@ -24511,7 +24515,7 @@
         <v>116</v>
       </c>
       <c r="G64" s="67" t="n">
-        <f aca="false">N(G62)</f>
+        <f aca="false">N(G63)</f>
         <v>4667.5</v>
       </c>
       <c r="H64" s="49"/>
@@ -24567,25 +24571,28 @@
       <c r="T65" s="49"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="62" t="n">
+      <c r="A66" s="52" t="n">
         <v>46224</v>
       </c>
-      <c r="B66" s="63" t="s">
-        <v>92</v>
-      </c>
-      <c r="C66" s="64" t="n">
-        <f aca="false">N(MOVIMIENTOS!$I113)</f>
-        <v>6790</v>
-      </c>
-      <c r="D66" s="64"/>
-      <c r="E66" s="64"/>
-      <c r="F66" s="63" t="str">
-        <f aca="false">TRIM(IF(MOVIMIENTOS!$G113&lt;&gt;"",MOVIMIENTOS!$G113&amp;"  ","")&amp;IF(N(MOVIMIENTOS!$E113)&gt;0,MOVIMIENTOS!$E113&amp;" "&amp;MOVIMIENTOS!$D113&amp;"  ","")&amp;IF(MOVIMIENTOS!$H113&lt;&gt;"",MOVIMIENTOS!$H113,""))</f>
-        <v>70 sacos peso aprox 95 kg/saco</v>
-      </c>
-      <c r="G66" s="64" t="n">
+      <c r="B66" s="61" t="s">
+        <v>95</v>
+      </c>
+      <c r="C66" s="53"/>
+      <c r="D66" s="53" t="n">
+        <f aca="false">N(MOVIMIENTOS!$I117)</f>
+        <v>388</v>
+      </c>
+      <c r="E66" s="53" t="n">
+        <f aca="false">N(MOVIMIENTOS!$I117)</f>
+        <v>388</v>
+      </c>
+      <c r="F66" s="61" t="str">
+        <f aca="false">TRIM(IF(MOVIMIENTOS!$G117&lt;&gt;"",MOVIMIENTOS!$G117&amp;"  ","")&amp;IF(N(MOVIMIENTOS!$E117)&gt;0,MOVIMIENTOS!$E117&amp;" "&amp;MOVIMIENTOS!$D117&amp;"  ","")&amp;IF(MOVIMIENTOS!$H117&lt;&gt;"",MOVIMIENTOS!$H117,""))</f>
+        <v>4 sacos</v>
+      </c>
+      <c r="G66" s="53" t="n">
         <f aca="false">N(G65)+N(C66)-N(E66)</f>
-        <v>11166.5</v>
+        <v>3988.5</v>
       </c>
       <c r="H66" s="49"/>
       <c r="I66" s="49"/>
@@ -24606,24 +24613,20 @@
         <v>46224</v>
       </c>
       <c r="B67" s="61" t="s">
-        <v>95</v>
+        <v>23</v>
       </c>
       <c r="C67" s="53"/>
-      <c r="D67" s="53" t="n">
-        <f aca="false">N(MOVIMIENTOS!$I118)</f>
-        <v>388</v>
-      </c>
+      <c r="D67" s="53"/>
       <c r="E67" s="53" t="n">
-        <f aca="false">N(MOVIMIENTOS!$I118)</f>
-        <v>388</v>
-      </c>
-      <c r="F67" s="61" t="str">
-        <f aca="false">TRIM(IF(MOVIMIENTOS!$G118&lt;&gt;"",MOVIMIENTOS!$G118&amp;"  ","")&amp;IF(N(MOVIMIENTOS!$E118)&gt;0,MOVIMIENTOS!$E118&amp;" "&amp;MOVIMIENTOS!$D118&amp;"  ","")&amp;IF(MOVIMIENTOS!$H118&lt;&gt;"",MOVIMIENTOS!$H118,""))</f>
-        <v>4 sacos</v>
+        <f aca="false">N(MOVIMIENTOS!$I118)+N(MOVIMIENTOS!$I119)+N(MOVIMIENTOS!$I120)+N(MOVIMIENTOS!$I121)</f>
+        <v>3260</v>
+      </c>
+      <c r="F67" s="61" t="s">
+        <v>117</v>
       </c>
       <c r="G67" s="53" t="n">
         <f aca="false">N(G66)+N(C67)-N(E67)</f>
-        <v>10778.5</v>
+        <v>728.5</v>
       </c>
       <c r="H67" s="49"/>
       <c r="I67" s="49"/>
@@ -24644,20 +24647,18 @@
         <v>46224</v>
       </c>
       <c r="B68" s="61" t="s">
-        <v>23</v>
+        <v>118</v>
       </c>
       <c r="C68" s="53"/>
       <c r="D68" s="53"/>
-      <c r="E68" s="53" t="n">
-        <f aca="false">N(MOVIMIENTOS!$I119)+N(MOVIMIENTOS!$I120)+N(MOVIMIENTOS!$I121)+N(MOVIMIENTOS!$I122)</f>
-        <v>3260</v>
-      </c>
-      <c r="F68" s="61" t="s">
-        <v>117</v>
+      <c r="E68" s="53"/>
+      <c r="F68" s="61" t="str">
+        <f aca="false">MOVIMIENTOS!$E122&amp;" jabas rechazadas · van a reproceso (merma del día: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$400=MOVIMIENTOS!$A122)*(MOVIMIENTOS!$B$5:$B$400="RECHAZO")*(MOVIMIENTOS!$D$5:$D$400="jabas")*MOVIMIENTOS!$E$5:$E$400*IFERROR(_xlfn.SWITCH(MOVIMIENTOS!$C$5:$C$400,"A",15,"P",18,"C",17,"M",17,0),0))-SUMPRODUCT((MOVIMIENTOS!$A$5:$A$400=MOVIMIENTOS!$A122)*(MOVIMIENTOS!$B$5:$B$400="REPROCESO")*MOVIMIENTOS!$I$5:$I$400),"+#,##0;-#,##0;0")&amp;" kg)"</f>
+        <v>1 jabas rechazadas · van a reproceso (merma del día: +15 kg)</v>
       </c>
       <c r="G68" s="53" t="n">
         <f aca="false">N(G67)+N(C68)-N(E68)</f>
-        <v>7518.5</v>
+        <v>728.5</v>
       </c>
       <c r="H68" s="49"/>
       <c r="I68" s="49"/>
@@ -24678,7 +24679,7 @@
         <v>46224</v>
       </c>
       <c r="B69" s="61" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C69" s="53"/>
       <c r="D69" s="53"/>
@@ -24689,7 +24690,7 @@
       </c>
       <c r="G69" s="53" t="n">
         <f aca="false">N(G68)+N(C69)-N(E69)</f>
-        <v>7518.5</v>
+        <v>728.5</v>
       </c>
       <c r="H69" s="49"/>
       <c r="I69" s="49"/>
@@ -24710,18 +24711,18 @@
         <v>46224</v>
       </c>
       <c r="B70" s="61" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="C70" s="53"/>
       <c r="D70" s="53"/>
       <c r="E70" s="53"/>
       <c r="F70" s="61" t="str">
-        <f aca="false">MOVIMIENTOS!$E124&amp;" jabas rechazadas · van a reproceso (merma del día: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$400=MOVIMIENTOS!$A124)*(MOVIMIENTOS!$B$5:$B$400="RECHAZO")*(MOVIMIENTOS!$D$5:$D$400="jabas")*MOVIMIENTOS!$E$5:$E$400*IFERROR(_xlfn.SWITCH(MOVIMIENTOS!$C$5:$C$400,"A",15,"P",18,"C",17,"M",17,0),0))-SUMPRODUCT((MOVIMIENTOS!$A$5:$A$400=MOVIMIENTOS!$A124)*(MOVIMIENTOS!$B$5:$B$400="REPROCESO")*MOVIMIENTOS!$I$5:$I$400),"+#,##0;-#,##0;0")&amp;" kg)"</f>
-        <v>1 jabas rechazadas · van a reproceso (merma del día: +15 kg)</v>
+        <f aca="false">MOVIMIENTOS!$E124&amp;" jaba(s) movida(s) para completar otras · no resta del Stock Kg"</f>
+        <v>1 jaba(s) movida(s) para completar otras · no resta del Stock Kg</v>
       </c>
       <c r="G70" s="53" t="n">
         <f aca="false">N(G69)+N(C70)-N(E70)</f>
-        <v>7518.5</v>
+        <v>728.5</v>
       </c>
       <c r="H70" s="49"/>
       <c r="I70" s="49"/>
@@ -24742,7 +24743,7 @@
         <v>46224</v>
       </c>
       <c r="B71" s="61" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="C71" s="53"/>
       <c r="D71" s="53"/>
@@ -24753,7 +24754,7 @@
       </c>
       <c r="G71" s="53" t="n">
         <f aca="false">N(G70)+N(C71)-N(E71)</f>
-        <v>7518.5</v>
+        <v>728.5</v>
       </c>
       <c r="H71" s="49"/>
       <c r="I71" s="49"/>
@@ -24774,18 +24775,21 @@
         <v>46224</v>
       </c>
       <c r="B72" s="61" t="s">
-        <v>120</v>
-      </c>
-      <c r="C72" s="53"/>
+        <v>43</v>
+      </c>
+      <c r="C72" s="53" t="n">
+        <f aca="false">N(MOVIMIENTOS!$I126)</f>
+        <v>17</v>
+      </c>
       <c r="D72" s="53"/>
       <c r="E72" s="53"/>
       <c r="F72" s="61" t="str">
-        <f aca="false">MOVIMIENTOS!$E126&amp;" jaba(s) movida(s) para completar otras · no resta del Stock Kg"</f>
-        <v>1 jaba(s) movida(s) para completar otras · no resta del Stock Kg</v>
+        <f aca="false">MOVIMIENTOS!$E126&amp;" kg recuperados (merma del día: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$400=MOVIMIENTOS!$A126)*(MOVIMIENTOS!$B$5:$B$400="RECHAZO")*(MOVIMIENTOS!$D$5:$D$400="jabas")*MOVIMIENTOS!$E$5:$E$400*IFERROR(_xlfn.SWITCH(MOVIMIENTOS!$C$5:$C$400,"A",15,"P",18,"C",17,"M",17,0),0))-SUMPRODUCT((MOVIMIENTOS!$A$5:$A$400=MOVIMIENTOS!$A126)*(MOVIMIENTOS!$B$5:$B$400="REPROCESO")*MOVIMIENTOS!$I$5:$I$400),"+#,##0;-#,##0;0")&amp;" kg)"</f>
+        <v>17 kg recuperados (merma del día: +15 kg)</v>
       </c>
       <c r="G72" s="53" t="n">
         <f aca="false">N(G71)+N(C72)-N(E72)</f>
-        <v>7518.5</v>
+        <v>745.5</v>
       </c>
       <c r="H72" s="49"/>
       <c r="I72" s="49"/>
@@ -24801,26 +24805,32 @@
       <c r="S72" s="49"/>
       <c r="T72" s="49"/>
     </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="52" t="n">
-        <v>46224</v>
-      </c>
-      <c r="B73" s="61" t="s">
-        <v>43</v>
-      </c>
-      <c r="C73" s="53" t="n">
-        <f aca="false">N(MOVIMIENTOS!$I127)</f>
-        <v>17</v>
-      </c>
-      <c r="D73" s="53"/>
-      <c r="E73" s="53"/>
-      <c r="F73" s="61" t="str">
-        <f aca="false">MOVIMIENTOS!$E127&amp;" kg recuperados (merma del día: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$400=MOVIMIENTOS!$A127)*(MOVIMIENTOS!$B$5:$B$400="RECHAZO")*(MOVIMIENTOS!$D$5:$D$400="jabas")*MOVIMIENTOS!$E$5:$E$400*IFERROR(_xlfn.SWITCH(MOVIMIENTOS!$C$5:$C$400,"A",15,"P",18,"C",17,"M",17,0),0))-SUMPRODUCT((MOVIMIENTOS!$A$5:$A$400=MOVIMIENTOS!$A127)*(MOVIMIENTOS!$B$5:$B$400="REPROCESO")*MOVIMIENTOS!$I$5:$I$400),"+#,##0;-#,##0;0")&amp;" kg)"</f>
-        <v>17 kg recuperados (merma del día: +15 kg)</v>
-      </c>
-      <c r="G73" s="53" t="n">
-        <f aca="false">N(G72)+N(C73)-N(E73)</f>
-        <v>7535.5</v>
+    <row r="73" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A73" s="58" t="n">
+        <v>46225</v>
+      </c>
+      <c r="B73" s="59" t="s">
+        <v>89</v>
+      </c>
+      <c r="C73" s="60" t="n">
+        <f aca="false">SUMPRODUCT((MOVIMIENTOS!$A$5:$A$400=DATE(2026,7,22))*(MOVIMIENTOS!$B$5:$B$400="COMPRA")*MOVIMIENTOS!$I$5:$I$400)</f>
+        <v>6790</v>
+      </c>
+      <c r="D73" s="60" t="n">
+        <f aca="false">SUMPRODUCT((MOVIMIENTOS!$A$5:$A$400=DATE(2026,7,22))*(MOVIMIENTOS!$B$5:$B$400="PROCESO")*MOVIMIENTOS!$I$5:$I$400)</f>
+        <v>4025</v>
+      </c>
+      <c r="E73" s="60" t="n">
+        <f aca="false">SUMPRODUCT((MOVIMIENTOS!$A$5:$A$400=DATE(2026,7,22))*((MOVIMIENTOS!$B$5:$B$400="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$400="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$400="ENVIO A TOTTUS"))*MOVIMIENTOS!$I$5:$I$400)</f>
+        <v>3294</v>
+      </c>
+      <c r="F73" s="59" t="str">
+        <f aca="false">"Selección: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$400=DATE(2026,7,22))*(MOVIMIENTOS!$B$5:$B$400="PROCESO")*(MOVIMIENTOS!$C$5:$C$400&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$400),"#,##0")&amp;" kg  ·  Chancho: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$400=DATE(2026,7,22))*(MOVIMIENTOS!$B$5:$B$400="PROCESO")*(MOVIMIENTOS!$C$5:$C$400="Chancho")*MOVIMIENTOS!$I$5:$I$400),"#,##0")&amp;" kg"&amp;IF(C73&gt;0,"  ·  "&amp;TEXT(D73/C73,"0%")&amp;" del ingreso","")</f>
+        <v>Selección: 3,249 kg  ·  Chancho: 776 kg  ·  59% del ingreso</v>
+      </c>
+      <c r="G73" s="60" t="n">
+        <f aca="false">N(G83)</f>
+        <v>3577.5</v>
       </c>
       <c r="H73" s="49"/>
       <c r="I73" s="49"/>
@@ -24837,31 +24847,25 @@
       <c r="T73" s="49"/>
     </row>
     <row r="74" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="58" t="n">
+      <c r="A74" s="62" t="n">
         <v>46225</v>
       </c>
-      <c r="B74" s="59" t="s">
-        <v>89</v>
-      </c>
-      <c r="C74" s="60" t="n">
-        <f aca="false">SUMPRODUCT((MOVIMIENTOS!$A$5:$A$400=DATE(2026,7,22))*(MOVIMIENTOS!$B$5:$B$400="COMPRA")*MOVIMIENTOS!$I$5:$I$400)</f>
-        <v>3880</v>
-      </c>
-      <c r="D74" s="60" t="n">
-        <f aca="false">SUMPRODUCT((MOVIMIENTOS!$A$5:$A$400=DATE(2026,7,22))*(MOVIMIENTOS!$B$5:$B$400="PROCESO")*MOVIMIENTOS!$I$5:$I$400)</f>
-        <v>4025</v>
-      </c>
-      <c r="E74" s="60" t="n">
-        <f aca="false">SUMPRODUCT((MOVIMIENTOS!$A$5:$A$400=DATE(2026,7,22))*((MOVIMIENTOS!$B$5:$B$400="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$400="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$400="ENVIO A TOTTUS"))*MOVIMIENTOS!$I$5:$I$400)</f>
-        <v>3294</v>
-      </c>
-      <c r="F74" s="59" t="str">
-        <f aca="false">"Selección: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$400=DATE(2026,7,22))*(MOVIMIENTOS!$B$5:$B$400="PROCESO")*(MOVIMIENTOS!$C$5:$C$400&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$400),"#,##0")&amp;" kg  ·  Chancho: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$400=DATE(2026,7,22))*(MOVIMIENTOS!$B$5:$B$400="PROCESO")*(MOVIMIENTOS!$C$5:$C$400="Chancho")*MOVIMIENTOS!$I$5:$I$400),"#,##0")&amp;" kg"&amp;IF(C74&gt;0,"  ·  "&amp;TEXT(D74/C74,"0%")&amp;" del ingreso","")</f>
-        <v>Selección: 3,249 kg  ·  Chancho: 776 kg  ·  104% del ingreso</v>
-      </c>
-      <c r="G74" s="60" t="n">
-        <f aca="false">N(G84)</f>
-        <v>7457.5</v>
+      <c r="B74" s="63" t="s">
+        <v>92</v>
+      </c>
+      <c r="C74" s="64" t="n">
+        <f aca="false">N(MOVIMIENTOS!$I127)</f>
+        <v>6790</v>
+      </c>
+      <c r="D74" s="64"/>
+      <c r="E74" s="64"/>
+      <c r="F74" s="63" t="str">
+        <f aca="false">TRIM(IF(MOVIMIENTOS!$G127&lt;&gt;"",MOVIMIENTOS!$G127&amp;"  ","")&amp;IF(N(MOVIMIENTOS!$E127)&gt;0,MOVIMIENTOS!$E127&amp;" "&amp;MOVIMIENTOS!$D127&amp;"  ","")&amp;IF(MOVIMIENTOS!$H127&lt;&gt;"",MOVIMIENTOS!$H127,""))</f>
+        <v>70 sacos peso aprox 95 kg/saco</v>
+      </c>
+      <c r="G74" s="64" t="n">
+        <f aca="false">N(G72)+N(C74)-N(E74)</f>
+        <v>7535.5</v>
       </c>
       <c r="H74" s="49"/>
       <c r="I74" s="49"/>
@@ -24894,7 +24898,7 @@
         <v>121</v>
       </c>
       <c r="G75" s="67" t="n">
-        <f aca="false">N(G73)</f>
+        <f aca="false">N(G74)</f>
         <v>7535.5</v>
       </c>
       <c r="H75" s="49"/>
@@ -25181,26 +25185,32 @@
       <c r="S83" s="49"/>
       <c r="T83" s="49"/>
     </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A84" s="62" t="n">
-        <v>46225</v>
-      </c>
-      <c r="B84" s="63" t="s">
-        <v>92</v>
-      </c>
-      <c r="C84" s="64" t="n">
-        <f aca="false">N(MOVIMIENTOS!$I143)</f>
+    <row r="84" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A84" s="58" t="n">
+        <v>46226</v>
+      </c>
+      <c r="B84" s="59" t="s">
+        <v>89</v>
+      </c>
+      <c r="C84" s="60" t="n">
+        <f aca="false">SUMPRODUCT((MOVIMIENTOS!$A$5:$A$400=DATE(2026,7,23))*(MOVIMIENTOS!$B$5:$B$400="COMPRA")*MOVIMIENTOS!$I$5:$I$400)</f>
         <v>3880</v>
       </c>
-      <c r="D84" s="64"/>
-      <c r="E84" s="64"/>
-      <c r="F84" s="63" t="str">
-        <f aca="false">TRIM(IF(MOVIMIENTOS!$G143&lt;&gt;"",MOVIMIENTOS!$G143&amp;"  ","")&amp;IF(N(MOVIMIENTOS!$E143)&gt;0,MOVIMIENTOS!$E143&amp;" "&amp;MOVIMIENTOS!$D143&amp;"  ","")&amp;IF(MOVIMIENTOS!$H143&lt;&gt;"",MOVIMIENTOS!$H143,""))</f>
-        <v>40 sacos peso aprox 95 kg/saco</v>
-      </c>
-      <c r="G84" s="64" t="n">
-        <f aca="false">N(G83)+N(C84)-N(E84)</f>
-        <v>7457.5</v>
+      <c r="D84" s="60" t="n">
+        <f aca="false">SUMPRODUCT((MOVIMIENTOS!$A$5:$A$400=DATE(2026,7,23))*(MOVIMIENTOS!$B$5:$B$400="PROCESO")*MOVIMIENTOS!$I$5:$I$400)</f>
+        <v>3800.5</v>
+      </c>
+      <c r="E84" s="60" t="n">
+        <f aca="false">SUMPRODUCT((MOVIMIENTOS!$A$5:$A$400=DATE(2026,7,23))*((MOVIMIENTOS!$B$5:$B$400="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$400="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$400="ENVIO A TOTTUS"))*MOVIMIENTOS!$I$5:$I$400)</f>
+        <v>3413</v>
+      </c>
+      <c r="F84" s="59" t="str">
+        <f aca="false">"Selección: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$400=DATE(2026,7,23))*(MOVIMIENTOS!$B$5:$B$400="PROCESO")*(MOVIMIENTOS!$C$5:$C$400&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$400),"#,##0")&amp;" kg  ·  Chancho: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$400=DATE(2026,7,23))*(MOVIMIENTOS!$B$5:$B$400="PROCESO")*(MOVIMIENTOS!$C$5:$C$400="Chancho")*MOVIMIENTOS!$I$5:$I$400),"#,##0")&amp;" kg"&amp;IF(C84&gt;0,"  ·  "&amp;TEXT(D84/C84,"0%")&amp;" del ingreso","")</f>
+        <v>Selección: 3,170 kg  ·  Chancho: 631 kg  ·  98% del ingreso</v>
+      </c>
+      <c r="G84" s="60" t="n">
+        <f aca="false">N(G88)</f>
+        <v>3414</v>
       </c>
       <c r="H84" s="49"/>
       <c r="I84" s="49"/>
@@ -25217,31 +25227,25 @@
       <c r="T84" s="49"/>
     </row>
     <row r="85" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A85" s="58" t="n">
+      <c r="A85" s="62" t="n">
         <v>46226</v>
       </c>
-      <c r="B85" s="59" t="s">
-        <v>89</v>
-      </c>
-      <c r="C85" s="60" t="n">
-        <f aca="false">SUMPRODUCT((MOVIMIENTOS!$A$5:$A$400=DATE(2026,7,23))*(MOVIMIENTOS!$B$5:$B$400="COMPRA")*MOVIMIENTOS!$I$5:$I$400)</f>
-        <v>7760</v>
-      </c>
-      <c r="D85" s="60" t="n">
-        <f aca="false">SUMPRODUCT((MOVIMIENTOS!$A$5:$A$400=DATE(2026,7,23))*(MOVIMIENTOS!$B$5:$B$400="PROCESO")*MOVIMIENTOS!$I$5:$I$400)</f>
-        <v>3800.5</v>
-      </c>
-      <c r="E85" s="60" t="n">
-        <f aca="false">SUMPRODUCT((MOVIMIENTOS!$A$5:$A$400=DATE(2026,7,23))*((MOVIMIENTOS!$B$5:$B$400="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$400="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$400="ENVIO A TOTTUS"))*MOVIMIENTOS!$I$5:$I$400)</f>
-        <v>3413</v>
-      </c>
-      <c r="F85" s="59" t="str">
-        <f aca="false">"Selección: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$400=DATE(2026,7,23))*(MOVIMIENTOS!$B$5:$B$400="PROCESO")*(MOVIMIENTOS!$C$5:$C$400&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$400),"#,##0")&amp;" kg  ·  Chancho: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$400=DATE(2026,7,23))*(MOVIMIENTOS!$B$5:$B$400="PROCESO")*(MOVIMIENTOS!$C$5:$C$400="Chancho")*MOVIMIENTOS!$I$5:$I$400),"#,##0")&amp;" kg"&amp;IF(C85&gt;0,"  ·  "&amp;TEXT(D85/C85,"0%")&amp;" del ingreso","")</f>
-        <v>Selección: 3,170 kg  ·  Chancho: 631 kg  ·  49% del ingreso</v>
-      </c>
-      <c r="G85" s="60" t="n">
-        <f aca="false">N(G90)</f>
-        <v>11174</v>
+      <c r="B85" s="63" t="s">
+        <v>92</v>
+      </c>
+      <c r="C85" s="64" t="n">
+        <f aca="false">N(MOVIMIENTOS!$I143)</f>
+        <v>3880</v>
+      </c>
+      <c r="D85" s="64"/>
+      <c r="E85" s="64"/>
+      <c r="F85" s="63" t="str">
+        <f aca="false">TRIM(IF(MOVIMIENTOS!$G143&lt;&gt;"",MOVIMIENTOS!$G143&amp;"  ","")&amp;IF(N(MOVIMIENTOS!$E143)&gt;0,MOVIMIENTOS!$E143&amp;" "&amp;MOVIMIENTOS!$D143&amp;"  ","")&amp;IF(MOVIMIENTOS!$H143&lt;&gt;"",MOVIMIENTOS!$H143,""))</f>
+        <v>40 sacos peso aprox 95 kg/saco</v>
+      </c>
+      <c r="G85" s="64" t="n">
+        <f aca="false">N(G83)+N(C85)-N(E85)</f>
+        <v>7457.5</v>
       </c>
       <c r="H85" s="49"/>
       <c r="I85" s="49"/>
@@ -25274,7 +25278,7 @@
         <v>124</v>
       </c>
       <c r="G86" s="67" t="n">
-        <f aca="false">N(G84)</f>
+        <f aca="false">N(G85)</f>
         <v>7457.5</v>
       </c>
       <c r="H86" s="49"/>
@@ -25363,26 +25367,32 @@
       <c r="S88" s="49"/>
       <c r="T88" s="49"/>
     </row>
-    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A89" s="62" t="n">
-        <v>46226</v>
-      </c>
-      <c r="B89" s="63" t="s">
-        <v>92</v>
-      </c>
-      <c r="C89" s="64" t="n">
-        <f aca="false">N(MOVIMIENTOS!$I153)</f>
+    <row r="89" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A89" s="58" t="n">
+        <v>46227</v>
+      </c>
+      <c r="B89" s="59" t="s">
+        <v>89</v>
+      </c>
+      <c r="C89" s="60" t="n">
+        <f aca="false">SUMPRODUCT((MOVIMIENTOS!$A$5:$A$400=DATE(2026,7,24))*(MOVIMIENTOS!$B$5:$B$400="COMPRA")*MOVIMIENTOS!$I$5:$I$400)</f>
         <v>4171</v>
       </c>
-      <c r="D89" s="64"/>
-      <c r="E89" s="64"/>
-      <c r="F89" s="63" t="str">
-        <f aca="false">TRIM(IF(MOVIMIENTOS!$G153&lt;&gt;"",MOVIMIENTOS!$G153&amp;"  ","")&amp;IF(N(MOVIMIENTOS!$E153)&gt;0,MOVIMIENTOS!$E153&amp;" "&amp;MOVIMIENTOS!$D153&amp;"  ","")&amp;IF(MOVIMIENTOS!$H153&lt;&gt;"",MOVIMIENTOS!$H153,""))</f>
-        <v>43 sacos EN TOTAL SE COMPRARON 80 SACOS, 43 PROCESARON 24-07 Y 37 PROCESARAN SABADO 25</v>
-      </c>
-      <c r="G89" s="64" t="n">
-        <f aca="false">N(G88)+N(C89)-N(E89)</f>
-        <v>7585</v>
+      <c r="D89" s="60" t="n">
+        <f aca="false">SUMPRODUCT((MOVIMIENTOS!$A$5:$A$400=DATE(2026,7,24))*(MOVIMIENTOS!$B$5:$B$400="PROCESO")*MOVIMIENTOS!$I$5:$I$400)</f>
+        <v>3056</v>
+      </c>
+      <c r="E89" s="60" t="n">
+        <f aca="false">SUMPRODUCT((MOVIMIENTOS!$A$5:$A$400=DATE(2026,7,24))*((MOVIMIENTOS!$B$5:$B$400="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$400="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$400="ENVIO A TOTTUS"))*MOVIMIENTOS!$I$5:$I$400)</f>
+        <v>3461</v>
+      </c>
+      <c r="F89" s="59" t="str">
+        <f aca="false">"Selección: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$400=DATE(2026,7,24))*(MOVIMIENTOS!$B$5:$B$400="PROCESO")*(MOVIMIENTOS!$C$5:$C$400&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$400),"#,##0")&amp;" kg  ·  Chancho: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$400=DATE(2026,7,24))*(MOVIMIENTOS!$B$5:$B$400="PROCESO")*(MOVIMIENTOS!$C$5:$C$400="Chancho")*MOVIMIENTOS!$I$5:$I$400),"#,##0")&amp;" kg"&amp;IF(C89&gt;0,"  ·  "&amp;TEXT(D89/C89,"0%")&amp;" del ingreso","")</f>
+        <v>Selección: 2,474 kg  ·  Chancho: 582 kg  ·  73% del ingreso</v>
+      </c>
+      <c r="G89" s="60" t="n">
+        <f aca="false">N(G100)</f>
+        <v>3563</v>
       </c>
       <c r="H89" s="49"/>
       <c r="I89" s="49"/>
@@ -25400,24 +25410,24 @@
     </row>
     <row r="90" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="62" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B90" s="63" t="s">
         <v>92</v>
       </c>
       <c r="C90" s="64" t="n">
-        <f aca="false">N(MOVIMIENTOS!$I154)</f>
-        <v>3589</v>
+        <f aca="false">N(MOVIMIENTOS!$I153)</f>
+        <v>4171</v>
       </c>
       <c r="D90" s="64"/>
       <c r="E90" s="64"/>
       <c r="F90" s="63" t="str">
-        <f aca="false">TRIM(IF(MOVIMIENTOS!$G154&lt;&gt;"",MOVIMIENTOS!$G154&amp;"  ","")&amp;IF(N(MOVIMIENTOS!$E154)&gt;0,MOVIMIENTOS!$E154&amp;" "&amp;MOVIMIENTOS!$D154&amp;"  ","")&amp;IF(MOVIMIENTOS!$H154&lt;&gt;"",MOVIMIENTOS!$H154,""))</f>
-        <v>37 sacos peso aprox 95 kg/saco</v>
+        <f aca="false">TRIM(IF(MOVIMIENTOS!$G153&lt;&gt;"",MOVIMIENTOS!$G153&amp;"  ","")&amp;IF(N(MOVIMIENTOS!$E153)&gt;0,MOVIMIENTOS!$E153&amp;" "&amp;MOVIMIENTOS!$D153&amp;"  ","")&amp;IF(MOVIMIENTOS!$H153&lt;&gt;"",MOVIMIENTOS!$H153,""))</f>
+        <v>43 sacos EN TOTAL SE COMPRARON 80 SACOS, 43 PROCESARON 24-07 Y 37 PROCESARAN SABADO 25</v>
       </c>
       <c r="G90" s="64" t="n">
-        <f aca="false">N(G89)+N(C90)-N(E90)</f>
-        <v>11174</v>
+        <f aca="false">N(G88)+N(C90)-N(E90)</f>
+        <v>7585</v>
       </c>
       <c r="H90" s="49"/>
       <c r="I90" s="49"/>
@@ -25434,31 +25444,24 @@
       <c r="T90" s="49"/>
     </row>
     <row r="91" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A91" s="58" t="n">
+      <c r="A91" s="65" t="n">
         <v>46227</v>
       </c>
-      <c r="B91" s="59" t="s">
-        <v>89</v>
-      </c>
-      <c r="C91" s="60" t="n">
-        <f aca="false">SUMPRODUCT((MOVIMIENTOS!$A$5:$A$400=DATE(2026,7,24))*(MOVIMIENTOS!$B$5:$B$400="COMPRA")*MOVIMIENTOS!$I$5:$I$400)</f>
-        <v>0</v>
-      </c>
-      <c r="D91" s="60" t="n">
-        <f aca="false">SUMPRODUCT((MOVIMIENTOS!$A$5:$A$400=DATE(2026,7,24))*(MOVIMIENTOS!$B$5:$B$400="PROCESO")*MOVIMIENTOS!$I$5:$I$400)</f>
-        <v>3056</v>
-      </c>
-      <c r="E91" s="60" t="n">
-        <f aca="false">SUMPRODUCT((MOVIMIENTOS!$A$5:$A$400=DATE(2026,7,24))*((MOVIMIENTOS!$B$5:$B$400="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$400="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$400="ENVIO A TOTTUS"))*MOVIMIENTOS!$I$5:$I$400)</f>
-        <v>3461</v>
-      </c>
-      <c r="F91" s="59" t="str">
-        <f aca="false">"Selección: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$400=DATE(2026,7,24))*(MOVIMIENTOS!$B$5:$B$400="PROCESO")*(MOVIMIENTOS!$C$5:$C$400&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$400),"#,##0")&amp;" kg  ·  Chancho: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$400=DATE(2026,7,24))*(MOVIMIENTOS!$B$5:$B$400="PROCESO")*(MOVIMIENTOS!$C$5:$C$400="Chancho")*MOVIMIENTOS!$I$5:$I$400),"#,##0")&amp;" kg"&amp;IF(C91&gt;0,"  ·  "&amp;TEXT(D91/C91,"0%")&amp;" del ingreso","")</f>
-        <v>Selección: 2,474 kg  ·  Chancho: 582 kg</v>
-      </c>
-      <c r="G91" s="60" t="n">
-        <f aca="false">N(G101)</f>
-        <v>7152</v>
+      <c r="B91" s="66" t="s">
+        <v>93</v>
+      </c>
+      <c r="C91" s="67"/>
+      <c r="D91" s="67" t="n">
+        <f aca="false">SUMPRODUCT((MOVIMIENTOS!$A$5:$A$400=DATE(2026,7,24))*(MOVIMIENTOS!$B$5:$B$400="PROCESO")*(MOVIMIENTOS!$C$5:$C$400&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$400)</f>
+        <v>2474</v>
+      </c>
+      <c r="E91" s="67"/>
+      <c r="F91" s="66" t="s">
+        <v>126</v>
+      </c>
+      <c r="G91" s="67" t="n">
+        <f aca="false">N(G90)</f>
+        <v>7585</v>
       </c>
       <c r="H91" s="49"/>
       <c r="I91" s="49"/>
@@ -25475,24 +25478,28 @@
       <c r="T91" s="49"/>
     </row>
     <row r="92" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A92" s="65" t="n">
+      <c r="A92" s="52" t="n">
         <v>46227</v>
       </c>
-      <c r="B92" s="66" t="s">
-        <v>93</v>
-      </c>
-      <c r="C92" s="67"/>
-      <c r="D92" s="67" t="n">
-        <f aca="false">SUMPRODUCT((MOVIMIENTOS!$A$5:$A$400=DATE(2026,7,24))*(MOVIMIENTOS!$B$5:$B$400="PROCESO")*(MOVIMIENTOS!$C$5:$C$400&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$400)</f>
-        <v>2474</v>
-      </c>
-      <c r="E92" s="67"/>
-      <c r="F92" s="66" t="s">
-        <v>126</v>
-      </c>
-      <c r="G92" s="67" t="n">
-        <f aca="false">N(G90)</f>
-        <v>11174</v>
+      <c r="B92" s="61" t="s">
+        <v>95</v>
+      </c>
+      <c r="C92" s="53"/>
+      <c r="D92" s="53" t="n">
+        <f aca="false">N(MOVIMIENTOS!$I158)</f>
+        <v>582</v>
+      </c>
+      <c r="E92" s="53" t="n">
+        <f aca="false">N(MOVIMIENTOS!$I158)</f>
+        <v>582</v>
+      </c>
+      <c r="F92" s="61" t="str">
+        <f aca="false">TRIM(IF(MOVIMIENTOS!$G158&lt;&gt;"",MOVIMIENTOS!$G158&amp;"  ","")&amp;IF(N(MOVIMIENTOS!$E158)&gt;0,MOVIMIENTOS!$E158&amp;" "&amp;MOVIMIENTOS!$D158&amp;"  ","")&amp;IF(MOVIMIENTOS!$H158&lt;&gt;"",MOVIMIENTOS!$H158,""))</f>
+        <v>6 sacos</v>
+      </c>
+      <c r="G92" s="53" t="n">
+        <f aca="false">N(G91)+N(C92)-N(E92)</f>
+        <v>7003</v>
       </c>
       <c r="H92" s="49"/>
       <c r="I92" s="49"/>
@@ -25513,24 +25520,20 @@
         <v>46227</v>
       </c>
       <c r="B93" s="61" t="s">
-        <v>95</v>
+        <v>23</v>
       </c>
       <c r="C93" s="53"/>
-      <c r="D93" s="53" t="n">
-        <f aca="false">N(MOVIMIENTOS!$I159)</f>
-        <v>582</v>
-      </c>
+      <c r="D93" s="53"/>
       <c r="E93" s="53" t="n">
-        <f aca="false">N(MOVIMIENTOS!$I159)</f>
-        <v>582</v>
-      </c>
-      <c r="F93" s="61" t="str">
-        <f aca="false">TRIM(IF(MOVIMIENTOS!$G159&lt;&gt;"",MOVIMIENTOS!$G159&amp;"  ","")&amp;IF(N(MOVIMIENTOS!$E159)&gt;0,MOVIMIENTOS!$E159&amp;" "&amp;MOVIMIENTOS!$D159&amp;"  ","")&amp;IF(MOVIMIENTOS!$H159&lt;&gt;"",MOVIMIENTOS!$H159,""))</f>
-        <v>6 sacos</v>
+        <f aca="false">N(MOVIMIENTOS!$I159)+N(MOVIMIENTOS!$I160)+N(MOVIMIENTOS!$I161)+N(MOVIMIENTOS!$I162)</f>
+        <v>3413</v>
+      </c>
+      <c r="F93" s="61" t="s">
+        <v>127</v>
       </c>
       <c r="G93" s="53" t="n">
         <f aca="false">N(G92)+N(C93)-N(E93)</f>
-        <v>10592</v>
+        <v>3590</v>
       </c>
       <c r="H93" s="49"/>
       <c r="I93" s="49"/>
@@ -25551,20 +25554,18 @@
         <v>46227</v>
       </c>
       <c r="B94" s="61" t="s">
-        <v>23</v>
+        <v>118</v>
       </c>
       <c r="C94" s="53"/>
       <c r="D94" s="53"/>
-      <c r="E94" s="53" t="n">
-        <f aca="false">N(MOVIMIENTOS!$I160)+N(MOVIMIENTOS!$I161)+N(MOVIMIENTOS!$I162)+N(MOVIMIENTOS!$I163)</f>
-        <v>3413</v>
-      </c>
-      <c r="F94" s="61" t="s">
-        <v>127</v>
+      <c r="E94" s="53"/>
+      <c r="F94" s="61" t="str">
+        <f aca="false">MOVIMIENTOS!$E163&amp;" jabas rechazadas · van a reproceso (merma del día: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$400=MOVIMIENTOS!$A163)*(MOVIMIENTOS!$B$5:$B$400="RECHAZO")*(MOVIMIENTOS!$D$5:$D$400="jabas")*MOVIMIENTOS!$E$5:$E$400*IFERROR(_xlfn.SWITCH(MOVIMIENTOS!$C$5:$C$400,"A",15,"P",18,"C",17,"M",17,0),0))-SUMPRODUCT((MOVIMIENTOS!$A$5:$A$400=MOVIMIENTOS!$A163)*(MOVIMIENTOS!$B$5:$B$400="REPROCESO")*MOVIMIENTOS!$I$5:$I$400),"+#,##0;-#,##0;0")&amp;" kg)"</f>
+        <v>1 jabas rechazadas · van a reproceso (merma del día: +11 kg)</v>
       </c>
       <c r="G94" s="53" t="n">
         <f aca="false">N(G93)+N(C94)-N(E94)</f>
-        <v>7179</v>
+        <v>3590</v>
       </c>
       <c r="H94" s="49"/>
       <c r="I94" s="49"/>
@@ -25585,18 +25586,21 @@
         <v>46227</v>
       </c>
       <c r="B95" s="61" t="s">
-        <v>118</v>
-      </c>
-      <c r="C95" s="53"/>
+        <v>43</v>
+      </c>
+      <c r="C95" s="53" t="n">
+        <f aca="false">N(MOVIMIENTOS!$I164)</f>
+        <v>11</v>
+      </c>
       <c r="D95" s="53"/>
       <c r="E95" s="53"/>
       <c r="F95" s="61" t="str">
-        <f aca="false">MOVIMIENTOS!$E164&amp;" jabas rechazadas · van a reproceso (merma del día: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$400=MOVIMIENTOS!$A164)*(MOVIMIENTOS!$B$5:$B$400="RECHAZO")*(MOVIMIENTOS!$D$5:$D$400="jabas")*MOVIMIENTOS!$E$5:$E$400*IFERROR(_xlfn.SWITCH(MOVIMIENTOS!$C$5:$C$400,"A",15,"P",18,"C",17,"M",17,0),0))-SUMPRODUCT((MOVIMIENTOS!$A$5:$A$400=MOVIMIENTOS!$A164)*(MOVIMIENTOS!$B$5:$B$400="REPROCESO")*MOVIMIENTOS!$I$5:$I$400),"+#,##0;-#,##0;0")&amp;" kg)"</f>
-        <v>1 jabas rechazadas · van a reproceso (merma del día: +11 kg)</v>
+        <f aca="false">MOVIMIENTOS!$E164&amp;" kg recuperados (merma del día: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$400=MOVIMIENTOS!$A164)*(MOVIMIENTOS!$B$5:$B$400="RECHAZO")*(MOVIMIENTOS!$D$5:$D$400="jabas")*MOVIMIENTOS!$E$5:$E$400*IFERROR(_xlfn.SWITCH(MOVIMIENTOS!$C$5:$C$400,"A",15,"P",18,"C",17,"M",17,0),0))-SUMPRODUCT((MOVIMIENTOS!$A$5:$A$400=MOVIMIENTOS!$A164)*(MOVIMIENTOS!$B$5:$B$400="REPROCESO")*MOVIMIENTOS!$I$5:$I$400),"+#,##0;-#,##0;0")&amp;" kg)"</f>
+        <v>11 kg recuperados (merma del día: +11 kg)</v>
       </c>
       <c r="G95" s="53" t="n">
         <f aca="false">N(G94)+N(C95)-N(E95)</f>
-        <v>7179</v>
+        <v>3601</v>
       </c>
       <c r="H95" s="49"/>
       <c r="I95" s="49"/>
@@ -25617,21 +25621,18 @@
         <v>46227</v>
       </c>
       <c r="B96" s="61" t="s">
-        <v>43</v>
-      </c>
-      <c r="C96" s="53" t="n">
-        <f aca="false">N(MOVIMIENTOS!$I165)</f>
-        <v>11</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="C96" s="53"/>
       <c r="D96" s="53"/>
       <c r="E96" s="53"/>
       <c r="F96" s="61" t="str">
-        <f aca="false">MOVIMIENTOS!$E165&amp;" kg recuperados (merma del día: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$400=MOVIMIENTOS!$A165)*(MOVIMIENTOS!$B$5:$B$400="RECHAZO")*(MOVIMIENTOS!$D$5:$D$400="jabas")*MOVIMIENTOS!$E$5:$E$400*IFERROR(_xlfn.SWITCH(MOVIMIENTOS!$C$5:$C$400,"A",15,"P",18,"C",17,"M",17,0),0))-SUMPRODUCT((MOVIMIENTOS!$A$5:$A$400=MOVIMIENTOS!$A165)*(MOVIMIENTOS!$B$5:$B$400="REPROCESO")*MOVIMIENTOS!$I$5:$I$400),"+#,##0;-#,##0;0")&amp;" kg)"</f>
-        <v>11 kg recuperados (merma del día: +11 kg)</v>
+        <f aca="false">MOVIMIENTOS!$E165&amp;" jabas rechazadas · van a reproceso (merma del día: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$400=MOVIMIENTOS!$A165)*(MOVIMIENTOS!$B$5:$B$400="RECHAZO")*(MOVIMIENTOS!$D$5:$D$400="jabas")*MOVIMIENTOS!$E$5:$E$400*IFERROR(_xlfn.SWITCH(MOVIMIENTOS!$C$5:$C$400,"A",15,"P",18,"C",17,"M",17,0),0))-SUMPRODUCT((MOVIMIENTOS!$A$5:$A$400=MOVIMIENTOS!$A165)*(MOVIMIENTOS!$B$5:$B$400="REPROCESO")*MOVIMIENTOS!$I$5:$I$400),"+#,##0;-#,##0;0")&amp;" kg)"</f>
+        <v>1 jabas rechazadas · van a reproceso (merma del día: +11 kg)</v>
       </c>
       <c r="G96" s="53" t="n">
         <f aca="false">N(G95)+N(C96)-N(E96)</f>
-        <v>7190</v>
+        <v>3601</v>
       </c>
       <c r="H96" s="49"/>
       <c r="I96" s="49"/>
@@ -25652,18 +25653,21 @@
         <v>46227</v>
       </c>
       <c r="B97" s="61" t="s">
-        <v>119</v>
-      </c>
-      <c r="C97" s="53"/>
+        <v>43</v>
+      </c>
+      <c r="C97" s="53" t="n">
+        <f aca="false">N(MOVIMIENTOS!$I166)</f>
+        <v>10</v>
+      </c>
       <c r="D97" s="53"/>
       <c r="E97" s="53"/>
       <c r="F97" s="61" t="str">
-        <f aca="false">MOVIMIENTOS!$E166&amp;" jabas rechazadas · van a reproceso (merma del día: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$400=MOVIMIENTOS!$A166)*(MOVIMIENTOS!$B$5:$B$400="RECHAZO")*(MOVIMIENTOS!$D$5:$D$400="jabas")*MOVIMIENTOS!$E$5:$E$400*IFERROR(_xlfn.SWITCH(MOVIMIENTOS!$C$5:$C$400,"A",15,"P",18,"C",17,"M",17,0),0))-SUMPRODUCT((MOVIMIENTOS!$A$5:$A$400=MOVIMIENTOS!$A166)*(MOVIMIENTOS!$B$5:$B$400="REPROCESO")*MOVIMIENTOS!$I$5:$I$400),"+#,##0;-#,##0;0")&amp;" kg)"</f>
-        <v>1 jabas rechazadas · van a reproceso (merma del día: +11 kg)</v>
+        <f aca="false">MOVIMIENTOS!$E166&amp;" kg recuperados (merma del día: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$400=MOVIMIENTOS!$A166)*(MOVIMIENTOS!$B$5:$B$400="RECHAZO")*(MOVIMIENTOS!$D$5:$D$400="jabas")*MOVIMIENTOS!$E$5:$E$400*IFERROR(_xlfn.SWITCH(MOVIMIENTOS!$C$5:$C$400,"A",15,"P",18,"C",17,"M",17,0),0))-SUMPRODUCT((MOVIMIENTOS!$A$5:$A$400=MOVIMIENTOS!$A166)*(MOVIMIENTOS!$B$5:$B$400="REPROCESO")*MOVIMIENTOS!$I$5:$I$400),"+#,##0;-#,##0;0")&amp;" kg)"</f>
+        <v>10 kg recuperados (merma del día: +11 kg)</v>
       </c>
       <c r="G97" s="53" t="n">
         <f aca="false">N(G96)+N(C97)-N(E97)</f>
-        <v>7190</v>
+        <v>3611</v>
       </c>
       <c r="H97" s="49"/>
       <c r="I97" s="49"/>
@@ -25684,21 +25688,18 @@
         <v>46227</v>
       </c>
       <c r="B98" s="61" t="s">
-        <v>43</v>
-      </c>
-      <c r="C98" s="53" t="n">
-        <f aca="false">N(MOVIMIENTOS!$I167)</f>
-        <v>10</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="C98" s="53"/>
       <c r="D98" s="53"/>
       <c r="E98" s="53"/>
       <c r="F98" s="61" t="str">
-        <f aca="false">MOVIMIENTOS!$E167&amp;" kg recuperados (merma del día: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$400=MOVIMIENTOS!$A167)*(MOVIMIENTOS!$B$5:$B$400="RECHAZO")*(MOVIMIENTOS!$D$5:$D$400="jabas")*MOVIMIENTOS!$E$5:$E$400*IFERROR(_xlfn.SWITCH(MOVIMIENTOS!$C$5:$C$400,"A",15,"P",18,"C",17,"M",17,0),0))-SUMPRODUCT((MOVIMIENTOS!$A$5:$A$400=MOVIMIENTOS!$A167)*(MOVIMIENTOS!$B$5:$B$400="REPROCESO")*MOVIMIENTOS!$I$5:$I$400),"+#,##0;-#,##0;0")&amp;" kg)"</f>
-        <v>10 kg recuperados (merma del día: +11 kg)</v>
+        <f aca="false">TRIM(IF(MOVIMIENTOS!$G167&lt;&gt;"",MOVIMIENTOS!$G167&amp;"  ","")&amp;IF(N(MOVIMIENTOS!$E167)&gt;0,MOVIMIENTOS!$E167&amp;" "&amp;MOVIMIENTOS!$D167&amp;"  ","")&amp;IF(MOVIMIENTOS!$H167&lt;&gt;"",MOVIMIENTOS!$H167,""))</f>
+        <v>TCK002-729 9 sacos</v>
       </c>
       <c r="G98" s="53" t="n">
         <f aca="false">N(G97)+N(C98)-N(E98)</f>
-        <v>7200</v>
+        <v>3611</v>
       </c>
       <c r="H98" s="49"/>
       <c r="I98" s="49"/>
@@ -25726,11 +25727,11 @@
       <c r="E99" s="53"/>
       <c r="F99" s="61" t="str">
         <f aca="false">TRIM(IF(MOVIMIENTOS!$G168&lt;&gt;"",MOVIMIENTOS!$G168&amp;"  ","")&amp;IF(N(MOVIMIENTOS!$E168)&gt;0,MOVIMIENTOS!$E168&amp;" "&amp;MOVIMIENTOS!$D168&amp;"  ","")&amp;IF(MOVIMIENTOS!$H168&lt;&gt;"",MOVIMIENTOS!$H168,""))</f>
-        <v>TCK002-729 9 sacos</v>
+        <v>TCK002-734 1 sacos</v>
       </c>
       <c r="G99" s="53" t="n">
         <f aca="false">N(G98)+N(C99)-N(E99)</f>
-        <v>7200</v>
+        <v>3611</v>
       </c>
       <c r="H99" s="49"/>
       <c r="I99" s="49"/>
@@ -25751,18 +25752,18 @@
         <v>46227</v>
       </c>
       <c r="B100" s="61" t="s">
-        <v>28</v>
+        <v>128</v>
       </c>
       <c r="C100" s="53"/>
       <c r="D100" s="53"/>
-      <c r="E100" s="53"/>
-      <c r="F100" s="61" t="str">
-        <f aca="false">TRIM(IF(MOVIMIENTOS!$G169&lt;&gt;"",MOVIMIENTOS!$G169&amp;"  ","")&amp;IF(N(MOVIMIENTOS!$E169)&gt;0,MOVIMIENTOS!$E169&amp;" "&amp;MOVIMIENTOS!$D169&amp;"  ","")&amp;IF(MOVIMIENTOS!$H169&lt;&gt;"",MOVIMIENTOS!$H169,""))</f>
-        <v>TCK002-734 1 sacos</v>
-      </c>
+      <c r="E100" s="53" t="n">
+        <f aca="false">N(MOVIMIENTOS!$I169)</f>
+        <v>48</v>
+      </c>
+      <c r="F100" s="61"/>
       <c r="G100" s="53" t="n">
         <f aca="false">N(G99)+N(C100)-N(E100)</f>
-        <v>7200</v>
+        <v>3563</v>
       </c>
       <c r="H100" s="49"/>
       <c r="I100" s="49"/>
@@ -25779,22 +25780,31 @@
       <c r="T100" s="49"/>
     </row>
     <row r="101" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A101" s="52" t="n">
-        <v>46227</v>
-      </c>
-      <c r="B101" s="61" t="s">
-        <v>128</v>
-      </c>
-      <c r="C101" s="53"/>
-      <c r="D101" s="53"/>
-      <c r="E101" s="53" t="n">
-        <f aca="false">N(MOVIMIENTOS!$I170)</f>
-        <v>48</v>
-      </c>
-      <c r="F101" s="61"/>
-      <c r="G101" s="53" t="n">
-        <f aca="false">N(G100)+N(C101)-N(E101)</f>
-        <v>7152</v>
+      <c r="A101" s="58" t="n">
+        <v>46228</v>
+      </c>
+      <c r="B101" s="59" t="s">
+        <v>89</v>
+      </c>
+      <c r="C101" s="60" t="n">
+        <f aca="false">SUMPRODUCT((MOVIMIENTOS!$A$5:$A$400=DATE(2026,7,25))*(MOVIMIENTOS!$B$5:$B$400="COMPRA")*MOVIMIENTOS!$I$5:$I$400)</f>
+        <v>3589</v>
+      </c>
+      <c r="D101" s="60" t="n">
+        <f aca="false">SUMPRODUCT((MOVIMIENTOS!$A$5:$A$400=DATE(2026,7,25))*(MOVIMIENTOS!$B$5:$B$400="PROCESO")*MOVIMIENTOS!$I$5:$I$400)</f>
+        <v>4813.5</v>
+      </c>
+      <c r="E101" s="60" t="n">
+        <f aca="false">SUMPRODUCT((MOVIMIENTOS!$A$5:$A$400=DATE(2026,7,25))*((MOVIMIENTOS!$B$5:$B$400="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$400="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$400="ENVIO A TOTTUS"))*MOVIMIENTOS!$I$5:$I$400)</f>
+        <v>3168</v>
+      </c>
+      <c r="F101" s="59" t="str">
+        <f aca="false">"Selección: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$400=DATE(2026,7,25))*(MOVIMIENTOS!$B$5:$B$400="PROCESO")*(MOVIMIENTOS!$C$5:$C$400&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$400),"#,##0")&amp;" kg  ·  Chancho: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$400=DATE(2026,7,25))*(MOVIMIENTOS!$B$5:$B$400="PROCESO")*(MOVIMIENTOS!$C$5:$C$400="Chancho")*MOVIMIENTOS!$I$5:$I$400),"#,##0")&amp;" kg"&amp;IF(C101&gt;0,"  ·  "&amp;TEXT(D101/C101,"0%")&amp;" del ingreso","")</f>
+        <v>Selección: 3,892 kg  ·  Chancho: 922 kg  ·  134% del ingreso</v>
+      </c>
+      <c r="G101" s="60" t="n">
+        <f aca="false">N(G105)</f>
+        <v>3062.5</v>
       </c>
       <c r="H101" s="49"/>
       <c r="I101" s="49"/>
@@ -25811,31 +25821,25 @@
       <c r="T101" s="49"/>
     </row>
     <row r="102" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A102" s="58" t="n">
+      <c r="A102" s="62" t="n">
         <v>46228</v>
       </c>
-      <c r="B102" s="59" t="s">
-        <v>89</v>
-      </c>
-      <c r="C102" s="60" t="n">
-        <f aca="false">SUMPRODUCT((MOVIMIENTOS!$A$5:$A$400=DATE(2026,7,25))*(MOVIMIENTOS!$B$5:$B$400="COMPRA")*MOVIMIENTOS!$I$5:$I$400)</f>
-        <v>0</v>
-      </c>
-      <c r="D102" s="60" t="n">
-        <f aca="false">SUMPRODUCT((MOVIMIENTOS!$A$5:$A$400=DATE(2026,7,25))*(MOVIMIENTOS!$B$5:$B$400="PROCESO")*MOVIMIENTOS!$I$5:$I$400)</f>
-        <v>4813.5</v>
-      </c>
-      <c r="E102" s="60" t="n">
-        <f aca="false">SUMPRODUCT((MOVIMIENTOS!$A$5:$A$400=DATE(2026,7,25))*((MOVIMIENTOS!$B$5:$B$400="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$400="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$400="ENVIO A TOTTUS"))*MOVIMIENTOS!$I$5:$I$400)</f>
-        <v>3168</v>
-      </c>
-      <c r="F102" s="59" t="str">
-        <f aca="false">"Selección: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$400=DATE(2026,7,25))*(MOVIMIENTOS!$B$5:$B$400="PROCESO")*(MOVIMIENTOS!$C$5:$C$400&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$400),"#,##0")&amp;" kg  ·  Chancho: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$400=DATE(2026,7,25))*(MOVIMIENTOS!$B$5:$B$400="PROCESO")*(MOVIMIENTOS!$C$5:$C$400="Chancho")*MOVIMIENTOS!$I$5:$I$400),"#,##0")&amp;" kg"&amp;IF(C102&gt;0,"  ·  "&amp;TEXT(D102/C102,"0%")&amp;" del ingreso","")</f>
-        <v>Selección: 3,892 kg  ·  Chancho: 922 kg</v>
-      </c>
-      <c r="G102" s="60" t="n">
-        <f aca="false">N(G105)</f>
-        <v>3062.5</v>
+      <c r="B102" s="63" t="s">
+        <v>92</v>
+      </c>
+      <c r="C102" s="64" t="n">
+        <f aca="false">N(MOVIMIENTOS!$I170)</f>
+        <v>3589</v>
+      </c>
+      <c r="D102" s="64"/>
+      <c r="E102" s="64"/>
+      <c r="F102" s="63" t="str">
+        <f aca="false">TRIM(IF(MOVIMIENTOS!$G170&lt;&gt;"",MOVIMIENTOS!$G170&amp;"  ","")&amp;IF(N(MOVIMIENTOS!$E170)&gt;0,MOVIMIENTOS!$E170&amp;" "&amp;MOVIMIENTOS!$D170&amp;"  ","")&amp;IF(MOVIMIENTOS!$H170&lt;&gt;"",MOVIMIENTOS!$H170,""))</f>
+        <v>37 sacos peso aprox 95 kg/saco</v>
+      </c>
+      <c r="G102" s="64" t="n">
+        <f aca="false">N(G100)+N(C102)-N(E102)</f>
+        <v>7152</v>
       </c>
       <c r="H102" s="49"/>
       <c r="I102" s="49"/>
@@ -25868,7 +25872,7 @@
         <v>129</v>
       </c>
       <c r="G103" s="53" t="n">
-        <f aca="false">N(G101)+N(C103)-N(E103)</f>
+        <f aca="false">N(G102)+N(C103)-N(E103)</f>
         <v>3984</v>
       </c>
       <c r="H103" s="49"/>
@@ -33142,7 +33146,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AW34"/>
+  <dimension ref="A1:AY34"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11"/>
@@ -33163,13 +33167,13 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="33" min="33" style="0" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="35" min="35" style="0" width="11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="38" min="36" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="39" min="39" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="40" min="40" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="41" min="41" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="46" min="43" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="47" min="47" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="48" min="48" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="49" min="49" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="40" min="39" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="41" min="41" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="42" min="42" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="47" min="44" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="49" min="48" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="50" min="50" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="51" min="51" style="0" width="9"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33228,15 +33232,17 @@
       <c r="AM4" s="76"/>
       <c r="AN4" s="76"/>
       <c r="AO4" s="76"/>
-      <c r="AQ4" s="76" t="s">
+      <c r="AP4" s="76"/>
+      <c r="AR4" s="76" t="s">
         <v>156</v>
       </c>
-      <c r="AR4" s="76"/>
       <c r="AS4" s="76"/>
       <c r="AT4" s="76"/>
       <c r="AU4" s="76"/>
       <c r="AV4" s="76"/>
       <c r="AW4" s="76"/>
+      <c r="AX4" s="76"/>
+      <c r="AY4" s="76"/>
     </row>
     <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="77" t="s">
@@ -33354,30 +33360,36 @@
         <v>191</v>
       </c>
       <c r="AN5" s="78" t="s">
+        <v>192</v>
+      </c>
+      <c r="AO5" s="78" t="s">
         <v>187</v>
       </c>
-      <c r="AO5" s="77" t="s">
+      <c r="AP5" s="77" t="s">
         <v>188</v>
       </c>
-      <c r="AQ5" s="77" t="s">
+      <c r="AR5" s="77" t="s">
         <v>158</v>
       </c>
-      <c r="AR5" s="78" t="s">
+      <c r="AS5" s="78" t="s">
         <v>160</v>
       </c>
-      <c r="AS5" s="78" t="s">
+      <c r="AT5" s="78" t="s">
         <v>189</v>
       </c>
-      <c r="AT5" s="78" t="s">
+      <c r="AU5" s="78" t="s">
         <v>190</v>
       </c>
-      <c r="AU5" s="79" t="s">
+      <c r="AV5" s="79" t="s">
         <v>191</v>
       </c>
-      <c r="AV5" s="78" t="s">
+      <c r="AW5" s="78" t="s">
+        <v>192</v>
+      </c>
+      <c r="AX5" s="78" t="s">
         <v>187</v>
       </c>
-      <c r="AW5" s="77" t="s">
+      <c r="AY5" s="77" t="s">
         <v>188</v>
       </c>
     </row>
@@ -33386,10 +33398,10 @@
         <v>46208</v>
       </c>
       <c r="B6" s="81" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C6" s="81" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D6" s="82" t="n">
         <f aca="false">SUMIFS(MOVIMIENTOS!$E:$E,MOVIMIENTOS!$A:$A,$A6,MOVIMIENTOS!$B:$B,"COMPRA")</f>
@@ -33532,38 +33544,46 @@
         <v>0</v>
       </c>
       <c r="AN6" s="83" t="n">
+        <f aca="false">AA6</f>
+        <v>0</v>
+      </c>
+      <c r="AO6" s="83" t="n">
         <f aca="false">AF6</f>
         <v>0</v>
       </c>
-      <c r="AO6" s="84" t="n">
+      <c r="AP6" s="84" t="n">
         <f aca="false">AG6</f>
         <v>0</v>
       </c>
-      <c r="AQ6" s="82" t="s">
-        <v>193</v>
-      </c>
-      <c r="AR6" s="83" t="n">
-        <f aca="false">SUMIF($C$6:$C$33,$AQ6,$E$6:$E$33)</f>
-        <v>0</v>
+      <c r="AR6" s="82" t="s">
+        <v>194</v>
       </c>
       <c r="AS6" s="83" t="n">
-        <f aca="false">SUMIF($C$6:$C$33,$AQ6,$K$6:$K$33)</f>
+        <f aca="false">SUMIF($C$6:$C$33,$AR6,$E$6:$E$33)</f>
         <v>0</v>
       </c>
       <c r="AT6" s="83" t="n">
-        <f aca="false">SUMIF($C$6:$C$33,$AQ6,$T$6:$T$33)</f>
-        <v>0</v>
-      </c>
-      <c r="AU6" s="86" t="n">
-        <f aca="false">SUMIF($C$6:$C$33,$AQ6,$Z$6:$Z$33)</f>
-        <v>0</v>
-      </c>
-      <c r="AV6" s="83" t="n">
-        <f aca="false">SUMIF($C$6:$C$33,$AQ6,$AF$6:$AF$33)</f>
-        <v>0</v>
-      </c>
-      <c r="AW6" s="84" t="n">
-        <f aca="false">IF(AR6=0,0,ROUND(AV6/AR6*100,1))</f>
+        <f aca="false">SUMIF($C$6:$C$33,$AR6,$K$6:$K$33)</f>
+        <v>0</v>
+      </c>
+      <c r="AU6" s="83" t="n">
+        <f aca="false">SUMIF($C$6:$C$33,$AR6,$T$6:$T$33)</f>
+        <v>0</v>
+      </c>
+      <c r="AV6" s="86" t="n">
+        <f aca="false">SUMIF($C$6:$C$33,$AR6,$Z$6:$Z$33)</f>
+        <v>0</v>
+      </c>
+      <c r="AW6" s="83" t="n">
+        <f aca="false">SUMIF($C$6:$C$33,$AR6,$AA$6:$AA$33)</f>
+        <v>0</v>
+      </c>
+      <c r="AX6" s="83" t="n">
+        <f aca="false">SUMIF($C$6:$C$33,$AR6,$AF$6:$AF$33)</f>
+        <v>0</v>
+      </c>
+      <c r="AY6" s="84" t="n">
+        <f aca="false">IF(AS6=0,0,ROUND(AX6/AS6*100,1))</f>
         <v>0</v>
       </c>
     </row>
@@ -33572,10 +33592,10 @@
         <v>46209</v>
       </c>
       <c r="B7" s="81" t="s">
+        <v>195</v>
+      </c>
+      <c r="C7" s="81" t="s">
         <v>194</v>
-      </c>
-      <c r="C7" s="81" t="s">
-        <v>193</v>
       </c>
       <c r="D7" s="82" t="n">
         <f aca="false">SUMIFS(MOVIMIENTOS!$E:$E,MOVIMIENTOS!$A:$A,$A7,MOVIMIENTOS!$B:$B,"COMPRA")</f>
@@ -33718,38 +33738,46 @@
         <v>0</v>
       </c>
       <c r="AN7" s="83" t="n">
+        <f aca="false">AA7</f>
+        <v>0</v>
+      </c>
+      <c r="AO7" s="83" t="n">
         <f aca="false">AF7</f>
         <v>0</v>
       </c>
-      <c r="AO7" s="84" t="n">
+      <c r="AP7" s="84" t="n">
         <f aca="false">AG7</f>
         <v>0</v>
       </c>
-      <c r="AQ7" s="82" t="s">
-        <v>195</v>
-      </c>
-      <c r="AR7" s="83" t="n">
-        <f aca="false">SUMIF($C$6:$C$33,$AQ7,$E$6:$E$33)</f>
+      <c r="AR7" s="82" t="s">
+        <v>196</v>
+      </c>
+      <c r="AS7" s="83" t="n">
+        <f aca="false">SUMIF($C$6:$C$33,$AR7,$E$6:$E$33)</f>
         <v>27936</v>
       </c>
-      <c r="AS7" s="83" t="n">
-        <f aca="false">SUMIF($C$6:$C$33,$AQ7,$K$6:$K$33)</f>
+      <c r="AT7" s="83" t="n">
+        <f aca="false">SUMIF($C$6:$C$33,$AR7,$K$6:$K$33)</f>
         <v>23556</v>
       </c>
-      <c r="AT7" s="83" t="n">
-        <f aca="false">SUMIF($C$6:$C$33,$AQ7,$T$6:$T$33)</f>
+      <c r="AU7" s="83" t="n">
+        <f aca="false">SUMIF($C$6:$C$33,$AR7,$T$6:$T$33)</f>
         <v>21410</v>
       </c>
-      <c r="AU7" s="86" t="n">
-        <f aca="false">SUMIF($C$6:$C$33,$AQ7,$Z$6:$Z$33)</f>
+      <c r="AV7" s="86" t="n">
+        <f aca="false">SUMIF($C$6:$C$33,$AR7,$Z$6:$Z$33)</f>
         <v>45</v>
       </c>
-      <c r="AV7" s="83" t="n">
-        <f aca="false">SUMIF($C$6:$C$33,$AQ7,$AF$6:$AF$33)</f>
+      <c r="AW7" s="83" t="n">
+        <f aca="false">SUMIF($C$6:$C$33,$AR7,$AA$6:$AA$33)</f>
+        <v>4365</v>
+      </c>
+      <c r="AX7" s="83" t="n">
+        <f aca="false">SUMIF($C$6:$C$33,$AR7,$AF$6:$AF$33)</f>
         <v>15</v>
       </c>
-      <c r="AW7" s="84" t="n">
-        <f aca="false">IF(AR7=0,0,ROUND(AV7/AR7*100,1))</f>
+      <c r="AY7" s="84" t="n">
+        <f aca="false">IF(AS7=0,0,ROUND(AX7/AS7*100,1))</f>
         <v>0.1</v>
       </c>
     </row>
@@ -33758,10 +33786,10 @@
         <v>46210</v>
       </c>
       <c r="B8" s="81" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C8" s="81" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D8" s="82" t="n">
         <f aca="false">SUMIFS(MOVIMIENTOS!$E:$E,MOVIMIENTOS!$A:$A,$A8,MOVIMIENTOS!$B:$B,"COMPRA")</f>
@@ -33904,38 +33932,46 @@
         <v>0</v>
       </c>
       <c r="AN8" s="83" t="n">
+        <f aca="false">AA8</f>
+        <v>0</v>
+      </c>
+      <c r="AO8" s="83" t="n">
         <f aca="false">AF8</f>
         <v>0</v>
       </c>
-      <c r="AO8" s="84" t="n">
+      <c r="AP8" s="84" t="n">
         <f aca="false">AG8</f>
         <v>0</v>
       </c>
-      <c r="AQ8" s="82" t="s">
-        <v>197</v>
-      </c>
-      <c r="AR8" s="83" t="n">
-        <f aca="false">SUMIF($C$6:$C$33,$AQ8,$E$6:$E$33)</f>
+      <c r="AR8" s="82" t="s">
+        <v>198</v>
+      </c>
+      <c r="AS8" s="83" t="n">
+        <f aca="false">SUMIF($C$6:$C$33,$AR8,$E$6:$E$33)</f>
         <v>26869</v>
       </c>
-      <c r="AS8" s="83" t="n">
-        <f aca="false">SUMIF($C$6:$C$33,$AQ8,$K$6:$K$33)</f>
+      <c r="AT8" s="83" t="n">
+        <f aca="false">SUMIF($C$6:$C$33,$AR8,$K$6:$K$33)</f>
         <v>22181</v>
       </c>
-      <c r="AT8" s="83" t="n">
-        <f aca="false">SUMIF($C$6:$C$33,$AQ8,$T$6:$T$33)</f>
+      <c r="AU8" s="83" t="n">
+        <f aca="false">SUMIF($C$6:$C$33,$AR8,$T$6:$T$33)</f>
         <v>21773</v>
       </c>
-      <c r="AU8" s="86" t="n">
-        <f aca="false">SUMIF($C$6:$C$33,$AQ8,$Z$6:$Z$33)</f>
+      <c r="AV8" s="86" t="n">
+        <f aca="false">SUMIF($C$6:$C$33,$AR8,$Z$6:$Z$33)</f>
         <v>46.5</v>
       </c>
-      <c r="AV8" s="83" t="n">
-        <f aca="false">SUMIF($C$6:$C$33,$AQ8,$AF$6:$AF$33)</f>
+      <c r="AW8" s="83" t="n">
+        <f aca="false">SUMIF($C$6:$C$33,$AR8,$AA$6:$AA$33)</f>
+        <v>4510.5</v>
+      </c>
+      <c r="AX8" s="83" t="n">
+        <f aca="false">SUMIF($C$6:$C$33,$AR8,$AF$6:$AF$33)</f>
         <v>177.5</v>
       </c>
-      <c r="AW8" s="84" t="n">
-        <f aca="false">IF(AR8=0,0,ROUND(AV8/AR8*100,1))</f>
+      <c r="AY8" s="84" t="n">
+        <f aca="false">IF(AS8=0,0,ROUND(AX8/AS8*100,1))</f>
         <v>0.7</v>
       </c>
     </row>
@@ -33944,10 +33980,10 @@
         <v>46211</v>
       </c>
       <c r="B9" s="81" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C9" s="81" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D9" s="82" t="n">
         <f aca="false">SUMIFS(MOVIMIENTOS!$E:$E,MOVIMIENTOS!$A:$A,$A9,MOVIMIENTOS!$B:$B,"COMPRA")</f>
@@ -34090,38 +34126,46 @@
         <v>0</v>
       </c>
       <c r="AN9" s="83" t="n">
+        <f aca="false">AA9</f>
+        <v>0</v>
+      </c>
+      <c r="AO9" s="83" t="n">
         <f aca="false">AF9</f>
         <v>0</v>
       </c>
-      <c r="AO9" s="84" t="n">
+      <c r="AP9" s="84" t="n">
         <f aca="false">AG9</f>
         <v>0</v>
       </c>
-      <c r="AQ9" s="82" t="s">
-        <v>199</v>
-      </c>
-      <c r="AR9" s="83" t="n">
-        <f aca="false">SUMIF($C$6:$C$33,$AQ9,$E$6:$E$33)</f>
+      <c r="AR9" s="82" t="s">
+        <v>200</v>
+      </c>
+      <c r="AS9" s="83" t="n">
+        <f aca="false">SUMIF($C$6:$C$33,$AR9,$E$6:$E$33)</f>
         <v>19610</v>
       </c>
-      <c r="AS9" s="83" t="n">
-        <f aca="false">SUMIF($C$6:$C$33,$AQ9,$K$6:$K$33)</f>
+      <c r="AT9" s="83" t="n">
+        <f aca="false">SUMIF($C$6:$C$33,$AR9,$K$6:$K$33)</f>
         <v>15227</v>
       </c>
-      <c r="AT9" s="83" t="n">
-        <f aca="false">SUMIF($C$6:$C$33,$AQ9,$T$6:$T$33)</f>
+      <c r="AU9" s="83" t="n">
+        <f aca="false">SUMIF($C$6:$C$33,$AR9,$T$6:$T$33)</f>
         <v>15626</v>
       </c>
-      <c r="AU9" s="86" t="n">
-        <f aca="false">SUMIF($C$6:$C$33,$AQ9,$Z$6:$Z$33)</f>
+      <c r="AV9" s="86" t="n">
+        <f aca="false">SUMIF($C$6:$C$33,$AR9,$Z$6:$Z$33)</f>
         <v>42.5</v>
       </c>
-      <c r="AV9" s="83" t="n">
-        <f aca="false">SUMIF($C$6:$C$33,$AQ9,$AF$6:$AF$33)</f>
+      <c r="AW9" s="83" t="n">
+        <f aca="false">SUMIF($C$6:$C$33,$AR9,$AA$6:$AA$33)</f>
+        <v>4122.5</v>
+      </c>
+      <c r="AX9" s="83" t="n">
+        <f aca="false">SUMIF($C$6:$C$33,$AR9,$AF$6:$AF$33)</f>
         <v>260.5</v>
       </c>
-      <c r="AW9" s="84" t="n">
-        <f aca="false">IF(AR9=0,0,ROUND(AV9/AR9*100,1))</f>
+      <c r="AY9" s="84" t="n">
+        <f aca="false">IF(AS9=0,0,ROUND(AX9/AS9*100,1))</f>
         <v>1.3</v>
       </c>
     </row>
@@ -34130,10 +34174,10 @@
         <v>46212</v>
       </c>
       <c r="B10" s="81" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C10" s="81" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D10" s="82" t="n">
         <f aca="false">SUMIFS(MOVIMIENTOS!$E:$E,MOVIMIENTOS!$A:$A,$A10,MOVIMIENTOS!$B:$B,"COMPRA")</f>
@@ -34276,38 +34320,46 @@
         <v>0</v>
       </c>
       <c r="AN10" s="83" t="n">
+        <f aca="false">AA10</f>
+        <v>0</v>
+      </c>
+      <c r="AO10" s="83" t="n">
         <f aca="false">AF10</f>
         <v>0</v>
       </c>
-      <c r="AO10" s="84" t="n">
+      <c r="AP10" s="84" t="n">
         <f aca="false">AG10</f>
         <v>0</v>
       </c>
-      <c r="AQ10" s="87" t="s">
-        <v>201</v>
-      </c>
-      <c r="AR10" s="88" t="n">
-        <f aca="false">SUM(AR6:AR9)</f>
-        <v>74415</v>
+      <c r="AR10" s="87" t="s">
+        <v>202</v>
       </c>
       <c r="AS10" s="88" t="n">
         <f aca="false">SUM(AS6:AS9)</f>
-        <v>60964</v>
+        <v>74415</v>
       </c>
       <c r="AT10" s="88" t="n">
         <f aca="false">SUM(AT6:AT9)</f>
-        <v>58809</v>
+        <v>60964</v>
       </c>
       <c r="AU10" s="88" t="n">
         <f aca="false">SUM(AU6:AU9)</f>
-        <v>134</v>
+        <v>58809</v>
       </c>
       <c r="AV10" s="88" t="n">
         <f aca="false">SUM(AV6:AV9)</f>
+        <v>134</v>
+      </c>
+      <c r="AW10" s="88" t="n">
+        <f aca="false">SUM(AW6:AW9)</f>
+        <v>12998</v>
+      </c>
+      <c r="AX10" s="88" t="n">
+        <f aca="false">SUM(AX6:AX9)</f>
         <v>453</v>
       </c>
-      <c r="AW10" s="84" t="n">
-        <f aca="false">IF(AR10=0,0,ROUND(AV10/AR10*100,1))</f>
+      <c r="AY10" s="84" t="n">
+        <f aca="false">IF(AS10=0,0,ROUND(AX10/AS10*100,1))</f>
         <v>0.6</v>
       </c>
     </row>
@@ -34316,10 +34368,10 @@
         <v>46213</v>
       </c>
       <c r="B11" s="81" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C11" s="81" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D11" s="82" t="n">
         <f aca="false">SUMIFS(MOVIMIENTOS!$E:$E,MOVIMIENTOS!$A:$A,$A11,MOVIMIENTOS!$B:$B,"COMPRA")</f>
@@ -34462,10 +34514,14 @@
         <v>0</v>
       </c>
       <c r="AN11" s="83" t="n">
+        <f aca="false">AA11</f>
+        <v>0</v>
+      </c>
+      <c r="AO11" s="83" t="n">
         <f aca="false">AF11</f>
         <v>0</v>
       </c>
-      <c r="AO11" s="84" t="n">
+      <c r="AP11" s="84" t="n">
         <f aca="false">AG11</f>
         <v>0</v>
       </c>
@@ -34475,10 +34531,10 @@
         <v>46214</v>
       </c>
       <c r="B12" s="81" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C12" s="81" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D12" s="82" t="n">
         <f aca="false">SUMIFS(MOVIMIENTOS!$E:$E,MOVIMIENTOS!$A:$A,$A12,MOVIMIENTOS!$B:$B,"COMPRA")</f>
@@ -34621,10 +34677,14 @@
         <v>0</v>
       </c>
       <c r="AN12" s="83" t="n">
+        <f aca="false">AA12</f>
+        <v>0</v>
+      </c>
+      <c r="AO12" s="83" t="n">
         <f aca="false">AF12</f>
         <v>0</v>
       </c>
-      <c r="AO12" s="84" t="n">
+      <c r="AP12" s="84" t="n">
         <f aca="false">AG12</f>
         <v>0</v>
       </c>
@@ -34634,10 +34694,10 @@
         <v>46215</v>
       </c>
       <c r="B13" s="81" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C13" s="81" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D13" s="82" t="n">
         <f aca="false">SUMIFS(MOVIMIENTOS!$E:$E,MOVIMIENTOS!$A:$A,$A13,MOVIMIENTOS!$B:$B,"COMPRA")</f>
@@ -34780,10 +34840,14 @@
         <v>6</v>
       </c>
       <c r="AN13" s="83" t="n">
+        <f aca="false">AA13</f>
+        <v>582</v>
+      </c>
+      <c r="AO13" s="83" t="n">
         <f aca="false">AF13</f>
         <v>-47</v>
       </c>
-      <c r="AO13" s="84" t="n">
+      <c r="AP13" s="84" t="n">
         <f aca="false">AG13</f>
         <v>-1.6</v>
       </c>
@@ -34793,10 +34857,10 @@
         <v>46216</v>
       </c>
       <c r="B14" s="81" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C14" s="81" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D14" s="82" t="n">
         <f aca="false">SUMIFS(MOVIMIENTOS!$E:$E,MOVIMIENTOS!$A:$A,$A14,MOVIMIENTOS!$B:$B,"COMPRA")</f>
@@ -34939,10 +35003,14 @@
         <v>2</v>
       </c>
       <c r="AN14" s="83" t="n">
+        <f aca="false">AA14</f>
+        <v>194</v>
+      </c>
+      <c r="AO14" s="83" t="n">
         <f aca="false">AF14</f>
         <v>-191</v>
       </c>
-      <c r="AO14" s="84" t="n">
+      <c r="AP14" s="84" t="n">
         <f aca="false">AG14</f>
         <v>-4.9</v>
       </c>
@@ -34952,10 +35020,10 @@
         <v>46217</v>
       </c>
       <c r="B15" s="81" t="s">
+        <v>197</v>
+      </c>
+      <c r="C15" s="81" t="s">
         <v>196</v>
-      </c>
-      <c r="C15" s="81" t="s">
-        <v>195</v>
       </c>
       <c r="D15" s="82" t="n">
         <f aca="false">SUMIFS(MOVIMIENTOS!$E:$E,MOVIMIENTOS!$A:$A,$A15,MOVIMIENTOS!$B:$B,"COMPRA")</f>
@@ -35098,10 +35166,14 @@
         <v>7</v>
       </c>
       <c r="AN15" s="83" t="n">
+        <f aca="false">AA15</f>
+        <v>679</v>
+      </c>
+      <c r="AO15" s="83" t="n">
         <f aca="false">AF15</f>
         <v>67</v>
       </c>
-      <c r="AO15" s="84" t="n">
+      <c r="AP15" s="84" t="n">
         <f aca="false">AG15</f>
         <v>1.7</v>
       </c>
@@ -35111,10 +35183,10 @@
         <v>46218</v>
       </c>
       <c r="B16" s="81" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C16" s="81" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D16" s="82" t="n">
         <f aca="false">SUMIFS(MOVIMIENTOS!$E:$E,MOVIMIENTOS!$A:$A,$A16,MOVIMIENTOS!$B:$B,"COMPRA")</f>
@@ -35257,10 +35329,14 @@
         <v>5</v>
       </c>
       <c r="AN16" s="83" t="n">
+        <f aca="false">AA16</f>
+        <v>485</v>
+      </c>
+      <c r="AO16" s="83" t="n">
         <f aca="false">AF16</f>
         <v>46</v>
       </c>
-      <c r="AO16" s="84" t="n">
+      <c r="AP16" s="84" t="n">
         <f aca="false">AG16</f>
         <v>1.2</v>
       </c>
@@ -35270,10 +35346,10 @@
         <v>46219</v>
       </c>
       <c r="B17" s="81" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C17" s="81" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D17" s="82" t="n">
         <f aca="false">SUMIFS(MOVIMIENTOS!$E:$E,MOVIMIENTOS!$A:$A,$A17,MOVIMIENTOS!$B:$B,"COMPRA")</f>
@@ -35416,10 +35492,14 @@
         <v>4</v>
       </c>
       <c r="AN17" s="83" t="n">
+        <f aca="false">AA17</f>
+        <v>388</v>
+      </c>
+      <c r="AO17" s="83" t="n">
         <f aca="false">AF17</f>
         <v>98</v>
       </c>
-      <c r="AO17" s="84" t="n">
+      <c r="AP17" s="84" t="n">
         <f aca="false">AG17</f>
         <v>2.5</v>
       </c>
@@ -35429,10 +35509,10 @@
         <v>46220</v>
       </c>
       <c r="B18" s="81" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C18" s="81" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D18" s="82" t="n">
         <f aca="false">SUMIFS(MOVIMIENTOS!$E:$E,MOVIMIENTOS!$A:$A,$A18,MOVIMIENTOS!$B:$B,"COMPRA")</f>
@@ -35575,10 +35655,14 @@
         <v>11</v>
       </c>
       <c r="AN18" s="83" t="n">
+        <f aca="false">AA18</f>
+        <v>1067</v>
+      </c>
+      <c r="AO18" s="83" t="n">
         <f aca="false">AF18</f>
         <v>136</v>
       </c>
-      <c r="AO18" s="84" t="n">
+      <c r="AP18" s="84" t="n">
         <f aca="false">AG18</f>
         <v>2.2</v>
       </c>
@@ -35588,10 +35672,10 @@
         <v>46221</v>
       </c>
       <c r="B19" s="81" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C19" s="81" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D19" s="82" t="n">
         <f aca="false">SUMIFS(MOVIMIENTOS!$E:$E,MOVIMIENTOS!$A:$A,$A19,MOVIMIENTOS!$B:$B,"COMPRA")</f>
@@ -35734,10 +35818,14 @@
         <v>10</v>
       </c>
       <c r="AN19" s="83" t="n">
+        <f aca="false">AA19</f>
+        <v>970</v>
+      </c>
+      <c r="AO19" s="83" t="n">
         <f aca="false">AF19</f>
         <v>-94</v>
       </c>
-      <c r="AO19" s="84" t="n">
+      <c r="AP19" s="84" t="n">
         <f aca="false">AG19</f>
         <v>-2.9</v>
       </c>
@@ -35747,10 +35835,10 @@
         <v>46222</v>
       </c>
       <c r="B20" s="81" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C20" s="81" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D20" s="82" t="n">
         <f aca="false">SUMIFS(MOVIMIENTOS!$E:$E,MOVIMIENTOS!$A:$A,$A20,MOVIMIENTOS!$B:$B,"COMPRA")</f>
@@ -35893,10 +35981,14 @@
         <v>3</v>
       </c>
       <c r="AN20" s="83" t="n">
+        <f aca="false">AA20</f>
+        <v>291</v>
+      </c>
+      <c r="AO20" s="83" t="n">
         <f aca="false">AF20</f>
         <v>180</v>
       </c>
-      <c r="AO20" s="84" t="n">
+      <c r="AP20" s="84" t="n">
         <f aca="false">AG20</f>
         <v>10.9</v>
       </c>
@@ -35906,18 +35998,18 @@
         <v>46223</v>
       </c>
       <c r="B21" s="81" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C21" s="81" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D21" s="82" t="n">
         <f aca="false">SUMIFS(MOVIMIENTOS!$E:$E,MOVIMIENTOS!$A:$A,$A21,MOVIMIENTOS!$B:$B,"COMPRA")</f>
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="E21" s="83" t="n">
         <f aca="false">SUMIFS(MOVIMIENTOS!$F:$F,MOVIMIENTOS!$A:$A,$A21,MOVIMIENTOS!$B:$B,"COMPRA")</f>
-        <v>6790</v>
+        <v>4656</v>
       </c>
       <c r="F21" s="82" t="n">
         <f aca="false">SUMIFS(MOVIMIENTOS!$E:$E,MOVIMIENTOS!$A:$A,$A21,MOVIMIENTOS!$B:$B,"PROCESO",MOVIMIENTOS!$C:$C,"A")</f>
@@ -36025,11 +36117,11 @@
       </c>
       <c r="AF21" s="83" t="n">
         <f aca="false">E21-(K21+AA21)</f>
-        <v>2141.5</v>
+        <v>7.5</v>
       </c>
       <c r="AG21" s="84" t="n">
         <f aca="false">IF(E21=0,0,ROUND(AF21/E21*100,1))</f>
-        <v>31.5</v>
+        <v>0.2</v>
       </c>
       <c r="AI21" s="85" t="n">
         <f aca="false">A21</f>
@@ -36037,7 +36129,7 @@
       </c>
       <c r="AJ21" s="83" t="n">
         <f aca="false">E21</f>
-        <v>6790</v>
+        <v>4656</v>
       </c>
       <c r="AK21" s="83" t="n">
         <f aca="false">K21</f>
@@ -36052,12 +36144,16 @@
         <v>6.5</v>
       </c>
       <c r="AN21" s="83" t="n">
+        <f aca="false">AA21</f>
+        <v>630.5</v>
+      </c>
+      <c r="AO21" s="83" t="n">
         <f aca="false">AF21</f>
-        <v>2141.5</v>
-      </c>
-      <c r="AO21" s="84" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AP21" s="84" t="n">
         <f aca="false">AG21</f>
-        <v>31.5</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36065,18 +36161,18 @@
         <v>46224</v>
       </c>
       <c r="B22" s="81" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C22" s="81" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D22" s="82" t="n">
         <f aca="false">SUMIFS(MOVIMIENTOS!$E:$E,MOVIMIENTOS!$A:$A,$A22,MOVIMIENTOS!$B:$B,"COMPRA")</f>
-        <v>70</v>
+        <v>22</v>
       </c>
       <c r="E22" s="83" t="n">
         <f aca="false">SUMIFS(MOVIMIENTOS!$F:$F,MOVIMIENTOS!$A:$A,$A22,MOVIMIENTOS!$B:$B,"COMPRA")</f>
-        <v>6790</v>
+        <v>2134</v>
       </c>
       <c r="F22" s="82" t="n">
         <f aca="false">SUMIFS(MOVIMIENTOS!$E:$E,MOVIMIENTOS!$A:$A,$A22,MOVIMIENTOS!$B:$B,"PROCESO",MOVIMIENTOS!$C:$C,"A")</f>
@@ -36184,11 +36280,11 @@
       </c>
       <c r="AF22" s="83" t="n">
         <f aca="false">E22-(K22+AA22)</f>
-        <v>1911</v>
+        <v>-2745</v>
       </c>
       <c r="AG22" s="84" t="n">
         <f aca="false">IF(E22=0,0,ROUND(AF22/E22*100,1))</f>
-        <v>28.1</v>
+        <v>-128.6</v>
       </c>
       <c r="AI22" s="85" t="n">
         <f aca="false">A22</f>
@@ -36196,7 +36292,7 @@
       </c>
       <c r="AJ22" s="83" t="n">
         <f aca="false">E22</f>
-        <v>6790</v>
+        <v>2134</v>
       </c>
       <c r="AK22" s="83" t="n">
         <f aca="false">K22</f>
@@ -36211,12 +36307,16 @@
         <v>7</v>
       </c>
       <c r="AN22" s="83" t="n">
+        <f aca="false">AA22</f>
+        <v>679</v>
+      </c>
+      <c r="AO22" s="83" t="n">
         <f aca="false">AF22</f>
-        <v>1911</v>
-      </c>
-      <c r="AO22" s="84" t="n">
+        <v>-2745</v>
+      </c>
+      <c r="AP22" s="84" t="n">
         <f aca="false">AG22</f>
-        <v>28.1</v>
+        <v>-128.6</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36224,18 +36324,18 @@
         <v>46225</v>
       </c>
       <c r="B23" s="81" t="s">
+        <v>199</v>
+      </c>
+      <c r="C23" s="81" t="s">
         <v>198</v>
-      </c>
-      <c r="C23" s="81" t="s">
-        <v>197</v>
       </c>
       <c r="D23" s="82" t="n">
         <f aca="false">SUMIFS(MOVIMIENTOS!$E:$E,MOVIMIENTOS!$A:$A,$A23,MOVIMIENTOS!$B:$B,"COMPRA")</f>
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="E23" s="83" t="n">
         <f aca="false">SUMIFS(MOVIMIENTOS!$F:$F,MOVIMIENTOS!$A:$A,$A23,MOVIMIENTOS!$B:$B,"COMPRA")</f>
-        <v>3880</v>
+        <v>6790</v>
       </c>
       <c r="F23" s="82" t="n">
         <f aca="false">SUMIFS(MOVIMIENTOS!$E:$E,MOVIMIENTOS!$A:$A,$A23,MOVIMIENTOS!$B:$B,"PROCESO",MOVIMIENTOS!$C:$C,"A")</f>
@@ -36343,11 +36443,11 @@
       </c>
       <c r="AF23" s="83" t="n">
         <f aca="false">E23-(K23+AA23)</f>
-        <v>-145</v>
+        <v>2765</v>
       </c>
       <c r="AG23" s="84" t="n">
         <f aca="false">IF(E23=0,0,ROUND(AF23/E23*100,1))</f>
-        <v>-3.7</v>
+        <v>40.7</v>
       </c>
       <c r="AI23" s="85" t="n">
         <f aca="false">A23</f>
@@ -36355,7 +36455,7 @@
       </c>
       <c r="AJ23" s="83" t="n">
         <f aca="false">E23</f>
-        <v>3880</v>
+        <v>6790</v>
       </c>
       <c r="AK23" s="83" t="n">
         <f aca="false">K23</f>
@@ -36370,12 +36470,16 @@
         <v>8</v>
       </c>
       <c r="AN23" s="83" t="n">
+        <f aca="false">AA23</f>
+        <v>776</v>
+      </c>
+      <c r="AO23" s="83" t="n">
         <f aca="false">AF23</f>
-        <v>-145</v>
-      </c>
-      <c r="AO23" s="84" t="n">
+        <v>2765</v>
+      </c>
+      <c r="AP23" s="84" t="n">
         <f aca="false">AG23</f>
-        <v>-3.7</v>
+        <v>40.7</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36383,18 +36487,18 @@
         <v>46226</v>
       </c>
       <c r="B24" s="81" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C24" s="81" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D24" s="82" t="n">
         <f aca="false">SUMIFS(MOVIMIENTOS!$E:$E,MOVIMIENTOS!$A:$A,$A24,MOVIMIENTOS!$B:$B,"COMPRA")</f>
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="E24" s="83" t="n">
         <f aca="false">SUMIFS(MOVIMIENTOS!$F:$F,MOVIMIENTOS!$A:$A,$A24,MOVIMIENTOS!$B:$B,"COMPRA")</f>
-        <v>7760</v>
+        <v>3880</v>
       </c>
       <c r="F24" s="82" t="n">
         <f aca="false">SUMIFS(MOVIMIENTOS!$E:$E,MOVIMIENTOS!$A:$A,$A24,MOVIMIENTOS!$B:$B,"PROCESO",MOVIMIENTOS!$C:$C,"A")</f>
@@ -36502,11 +36606,11 @@
       </c>
       <c r="AF24" s="83" t="n">
         <f aca="false">E24-(K24+AA24)</f>
-        <v>3959.5</v>
+        <v>79.5</v>
       </c>
       <c r="AG24" s="84" t="n">
         <f aca="false">IF(E24=0,0,ROUND(AF24/E24*100,1))</f>
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="AI24" s="85" t="n">
         <f aca="false">A24</f>
@@ -36514,7 +36618,7 @@
       </c>
       <c r="AJ24" s="83" t="n">
         <f aca="false">E24</f>
-        <v>7760</v>
+        <v>3880</v>
       </c>
       <c r="AK24" s="83" t="n">
         <f aca="false">K24</f>
@@ -36529,12 +36633,16 @@
         <v>6.5</v>
       </c>
       <c r="AN24" s="83" t="n">
+        <f aca="false">AA24</f>
+        <v>630.5</v>
+      </c>
+      <c r="AO24" s="83" t="n">
         <f aca="false">AF24</f>
-        <v>3959.5</v>
-      </c>
-      <c r="AO24" s="84" t="n">
+        <v>79.5</v>
+      </c>
+      <c r="AP24" s="84" t="n">
         <f aca="false">AG24</f>
-        <v>51</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36542,18 +36650,18 @@
         <v>46227</v>
       </c>
       <c r="B25" s="81" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C25" s="81" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D25" s="82" t="n">
         <f aca="false">SUMIFS(MOVIMIENTOS!$E:$E,MOVIMIENTOS!$A:$A,$A25,MOVIMIENTOS!$B:$B,"COMPRA")</f>
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="E25" s="83" t="n">
         <f aca="false">SUMIFS(MOVIMIENTOS!$F:$F,MOVIMIENTOS!$A:$A,$A25,MOVIMIENTOS!$B:$B,"COMPRA")</f>
-        <v>0</v>
+        <v>4171</v>
       </c>
       <c r="F25" s="82" t="n">
         <f aca="false">SUMIFS(MOVIMIENTOS!$E:$E,MOVIMIENTOS!$A:$A,$A25,MOVIMIENTOS!$B:$B,"PROCESO",MOVIMIENTOS!$C:$C,"A")</f>
@@ -36661,11 +36769,11 @@
       </c>
       <c r="AF25" s="83" t="n">
         <f aca="false">E25-(K25+AA25)</f>
-        <v>-3056</v>
+        <v>1115</v>
       </c>
       <c r="AG25" s="84" t="n">
         <f aca="false">IF(E25=0,0,ROUND(AF25/E25*100,1))</f>
-        <v>0</v>
+        <v>26.7</v>
       </c>
       <c r="AI25" s="85" t="n">
         <f aca="false">A25</f>
@@ -36673,7 +36781,7 @@
       </c>
       <c r="AJ25" s="83" t="n">
         <f aca="false">E25</f>
-        <v>0</v>
+        <v>4171</v>
       </c>
       <c r="AK25" s="83" t="n">
         <f aca="false">K25</f>
@@ -36688,12 +36796,16 @@
         <v>6</v>
       </c>
       <c r="AN25" s="83" t="n">
+        <f aca="false">AA25</f>
+        <v>582</v>
+      </c>
+      <c r="AO25" s="83" t="n">
         <f aca="false">AF25</f>
-        <v>-3056</v>
-      </c>
-      <c r="AO25" s="84" t="n">
+        <v>1115</v>
+      </c>
+      <c r="AP25" s="84" t="n">
         <f aca="false">AG25</f>
-        <v>0</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36701,18 +36813,18 @@
         <v>46228</v>
       </c>
       <c r="B26" s="81" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C26" s="81" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D26" s="82" t="n">
         <f aca="false">SUMIFS(MOVIMIENTOS!$E:$E,MOVIMIENTOS!$A:$A,$A26,MOVIMIENTOS!$B:$B,"COMPRA")</f>
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="E26" s="83" t="n">
         <f aca="false">SUMIFS(MOVIMIENTOS!$F:$F,MOVIMIENTOS!$A:$A,$A26,MOVIMIENTOS!$B:$B,"COMPRA")</f>
-        <v>0</v>
+        <v>3589</v>
       </c>
       <c r="F26" s="82" t="n">
         <f aca="false">SUMIFS(MOVIMIENTOS!$E:$E,MOVIMIENTOS!$A:$A,$A26,MOVIMIENTOS!$B:$B,"PROCESO",MOVIMIENTOS!$C:$C,"A")</f>
@@ -36820,11 +36932,11 @@
       </c>
       <c r="AF26" s="83" t="n">
         <f aca="false">E26-(K26+AA26)</f>
-        <v>-4813.5</v>
+        <v>-1224.5</v>
       </c>
       <c r="AG26" s="84" t="n">
         <f aca="false">IF(E26=0,0,ROUND(AF26/E26*100,1))</f>
-        <v>0</v>
+        <v>-34.1</v>
       </c>
       <c r="AI26" s="85" t="n">
         <f aca="false">A26</f>
@@ -36832,7 +36944,7 @@
       </c>
       <c r="AJ26" s="83" t="n">
         <f aca="false">E26</f>
-        <v>0</v>
+        <v>3589</v>
       </c>
       <c r="AK26" s="83" t="n">
         <f aca="false">K26</f>
@@ -36847,12 +36959,16 @@
         <v>9.5</v>
       </c>
       <c r="AN26" s="83" t="n">
+        <f aca="false">AA26</f>
+        <v>921.5</v>
+      </c>
+      <c r="AO26" s="83" t="n">
         <f aca="false">AF26</f>
-        <v>-4813.5</v>
-      </c>
-      <c r="AO26" s="84" t="n">
+        <v>-1224.5</v>
+      </c>
+      <c r="AP26" s="84" t="n">
         <f aca="false">AG26</f>
-        <v>0</v>
+        <v>-34.1</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36860,10 +36976,10 @@
         <v>46229</v>
       </c>
       <c r="B27" s="81" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C27" s="81" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D27" s="82" t="n">
         <f aca="false">SUMIFS(MOVIMIENTOS!$E:$E,MOVIMIENTOS!$A:$A,$A27,MOVIMIENTOS!$B:$B,"COMPRA")</f>
@@ -37006,10 +37122,14 @@
         <v>0</v>
       </c>
       <c r="AN27" s="83" t="n">
+        <f aca="false">AA27</f>
+        <v>0</v>
+      </c>
+      <c r="AO27" s="83" t="n">
         <f aca="false">AF27</f>
         <v>0</v>
       </c>
-      <c r="AO27" s="84" t="n">
+      <c r="AP27" s="84" t="n">
         <f aca="false">AG27</f>
         <v>0</v>
       </c>
@@ -37019,10 +37139,10 @@
         <v>46230</v>
       </c>
       <c r="B28" s="81" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C28" s="81" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D28" s="82" t="n">
         <f aca="false">SUMIFS(MOVIMIENTOS!$E:$E,MOVIMIENTOS!$A:$A,$A28,MOVIMIENTOS!$B:$B,"COMPRA")</f>
@@ -37165,10 +37285,14 @@
         <v>8.5</v>
       </c>
       <c r="AN28" s="83" t="n">
+        <f aca="false">AA28</f>
+        <v>824.5</v>
+      </c>
+      <c r="AO28" s="83" t="n">
         <f aca="false">AF28</f>
         <v>330.5</v>
       </c>
-      <c r="AO28" s="84" t="n">
+      <c r="AP28" s="84" t="n">
         <f aca="false">AG28</f>
         <v>7.4</v>
       </c>
@@ -37178,10 +37302,10 @@
         <v>46231</v>
       </c>
       <c r="B29" s="81" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C29" s="81" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D29" s="82" t="n">
         <f aca="false">SUMIFS(MOVIMIENTOS!$E:$E,MOVIMIENTOS!$A:$A,$A29,MOVIMIENTOS!$B:$B,"COMPRA")</f>
@@ -37324,10 +37448,14 @@
         <v>14.5</v>
       </c>
       <c r="AN29" s="83" t="n">
+        <f aca="false">AA29</f>
+        <v>1406.5</v>
+      </c>
+      <c r="AO29" s="83" t="n">
         <f aca="false">AF29</f>
         <v>175.5</v>
       </c>
-      <c r="AO29" s="84" t="n">
+      <c r="AP29" s="84" t="n">
         <f aca="false">AG29</f>
         <v>3.2</v>
       </c>
@@ -37337,10 +37465,10 @@
         <v>46232</v>
       </c>
       <c r="B30" s="81" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C30" s="81" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D30" s="82" t="n">
         <f aca="false">SUMIFS(MOVIMIENTOS!$E:$E,MOVIMIENTOS!$A:$A,$A30,MOVIMIENTOS!$B:$B,"COMPRA")</f>
@@ -37483,10 +37611,14 @@
         <v>0</v>
       </c>
       <c r="AN30" s="83" t="n">
+        <f aca="false">AA30</f>
+        <v>0</v>
+      </c>
+      <c r="AO30" s="83" t="n">
         <f aca="false">AF30</f>
         <v>0</v>
       </c>
-      <c r="AO30" s="84" t="n">
+      <c r="AP30" s="84" t="n">
         <f aca="false">AG30</f>
         <v>0</v>
       </c>
@@ -37496,10 +37628,10 @@
         <v>46233</v>
       </c>
       <c r="B31" s="81" t="s">
+        <v>201</v>
+      </c>
+      <c r="C31" s="81" t="s">
         <v>200</v>
-      </c>
-      <c r="C31" s="81" t="s">
-        <v>199</v>
       </c>
       <c r="D31" s="82" t="n">
         <f aca="false">SUMIFS(MOVIMIENTOS!$E:$E,MOVIMIENTOS!$A:$A,$A31,MOVIMIENTOS!$B:$B,"COMPRA")</f>
@@ -37642,10 +37774,14 @@
         <v>5</v>
       </c>
       <c r="AN31" s="83" t="n">
+        <f aca="false">AA31</f>
+        <v>485</v>
+      </c>
+      <c r="AO31" s="83" t="n">
         <f aca="false">AF31</f>
         <v>-78</v>
       </c>
-      <c r="AO31" s="84" t="n">
+      <c r="AP31" s="84" t="n">
         <f aca="false">AG31</f>
         <v>-2.7</v>
       </c>
@@ -37655,10 +37791,10 @@
         <v>46234</v>
       </c>
       <c r="B32" s="81" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C32" s="81" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D32" s="82" t="n">
         <f aca="false">SUMIFS(MOVIMIENTOS!$E:$E,MOVIMIENTOS!$A:$A,$A32,MOVIMIENTOS!$B:$B,"COMPRA")</f>
@@ -37801,10 +37937,14 @@
         <v>14.5</v>
       </c>
       <c r="AN32" s="83" t="n">
+        <f aca="false">AA32</f>
+        <v>1406.5</v>
+      </c>
+      <c r="AO32" s="83" t="n">
         <f aca="false">AF32</f>
         <v>-167.5</v>
       </c>
-      <c r="AO32" s="84" t="n">
+      <c r="AP32" s="84" t="n">
         <f aca="false">AG32</f>
         <v>-2.5</v>
       </c>
@@ -37814,10 +37954,10 @@
         <v>46235</v>
       </c>
       <c r="B33" s="81" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C33" s="81" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D33" s="82" t="n">
         <f aca="false">SUMIFS(MOVIMIENTOS!$E:$E,MOVIMIENTOS!$A:$A,$A33,MOVIMIENTOS!$B:$B,"COMPRA")</f>
@@ -37960,17 +38100,21 @@
         <v>0</v>
       </c>
       <c r="AN33" s="83" t="n">
+        <f aca="false">AA33</f>
+        <v>0</v>
+      </c>
+      <c r="AO33" s="83" t="n">
         <f aca="false">AF33</f>
         <v>0</v>
       </c>
-      <c r="AO33" s="84" t="n">
+      <c r="AP33" s="84" t="n">
         <f aca="false">AG33</f>
         <v>0</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AI34" s="87" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AJ34" s="88" t="n">
         <f aca="false">SUM(AJ6:AJ33)</f>
@@ -37990,9 +38134,13 @@
       </c>
       <c r="AN34" s="88" t="n">
         <f aca="false">SUM(AN6:AN33)</f>
+        <v>12998</v>
+      </c>
+      <c r="AO34" s="88" t="n">
+        <f aca="false">SUM(AO6:AO33)</f>
         <v>453</v>
       </c>
-      <c r="AO34" s="84" t="n">
+      <c r="AP34" s="84" t="n">
         <f aca="false">IF(AJ34=0,0,ROUND(SUM($AF$6:$AF$33)/AJ34*100,1))</f>
         <v>0.6</v>
       </c>
@@ -38005,8 +38153,8 @@
     <mergeCell ref="U4:Y4"/>
     <mergeCell ref="Z4:AE4"/>
     <mergeCell ref="AF4:AG4"/>
-    <mergeCell ref="AI4:AO4"/>
-    <mergeCell ref="AQ4:AW4"/>
+    <mergeCell ref="AI4:AP4"/>
+    <mergeCell ref="AR4:AY4"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/PROCESO DE PLANTA.xlsx
+++ b/PROCESO DE PLANTA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mirianmartinez/Desktop/Agro Pacayales/GESTION COSTOS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BD1288F-57F7-1E43-95B7-A21290CF862A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94200E4D-6ED3-C547-8511-139048B5D936}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4320" yWindow="600" windowWidth="24480" windowHeight="17400" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4320" yWindow="600" windowWidth="24480" windowHeight="17400" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MOVIMIENTOS" sheetId="1" r:id="rId1"/>
@@ -22,9 +22,9 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'BALANCE SEMANAL'!$A$5:$AG$33</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">KARDEX!$A$5:$G$137</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">MOVIMIENTOS!$A$4:$H$421</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">MOVIMIENTOS!$A$4:$H$425</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -77,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1575" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1679" uniqueCount="247">
   <si>
     <t>AGRO PACAYALES · PLANTA CAMOTE 2026  |  MOVIMIENTOS — registra aquí un evento por fila</t>
   </si>
@@ -221,12 +221,6 @@
   </si>
   <si>
     <t>3006</t>
-  </si>
-  <si>
-    <t>S/T</t>
-  </si>
-  <si>
-    <t>POR REGULARIZAR</t>
   </si>
   <si>
     <t>DEVOLUCIÓN</t>
@@ -847,6 +841,24 @@
   </si>
   <si>
     <t>TCK002-745</t>
+  </si>
+  <si>
+    <t>Ticket Pendiente</t>
+  </si>
+  <si>
+    <t>PENDIENTE</t>
+  </si>
+  <si>
+    <t>CAMPOS PROPIOS</t>
+  </si>
+  <si>
+    <t>CASAS_2026</t>
+  </si>
+  <si>
+    <t>SE COMPRÓ 103 SACOS</t>
+  </si>
+  <si>
+    <t>saldo de los 103 quedan aún 33 sacos</t>
   </si>
 </sst>
 </file>
@@ -2008,7 +2020,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O434"/>
+  <dimension ref="A1:O438"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -5805,10 +5817,10 @@
         <v>970</v>
       </c>
       <c r="G138" s="18" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="H138" s="18" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="I138">
         <f t="shared" si="2"/>
@@ -5847,7 +5859,7 @@
         <v>46225</v>
       </c>
       <c r="B140" s="33" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C140" s="33" t="s">
         <v>13</v>
@@ -5864,7 +5876,7 @@
       </c>
       <c r="G140" s="33"/>
       <c r="H140" s="33" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="I140">
         <f t="shared" si="2"/>
@@ -5920,7 +5932,7 @@
       </c>
       <c r="G142" s="27"/>
       <c r="H142" s="27" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="I142">
         <f t="shared" si="2"/>
@@ -6112,7 +6124,7 @@
         <v>1005</v>
       </c>
       <c r="G149" s="15" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H149" s="15"/>
       <c r="I149">
@@ -6141,7 +6153,7 @@
         <v>198</v>
       </c>
       <c r="G150" s="15" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H150" s="15"/>
       <c r="I150">
@@ -6170,7 +6182,7 @@
         <v>204</v>
       </c>
       <c r="G151" s="15" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H151" s="15"/>
       <c r="I151">
@@ -6199,7 +6211,7 @@
         <v>2006</v>
       </c>
       <c r="G152" s="15" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H152" s="15"/>
       <c r="I152">
@@ -6229,7 +6241,7 @@
       </c>
       <c r="G153" s="9"/>
       <c r="H153" s="9" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I153">
         <f t="shared" si="2"/>
@@ -6392,7 +6404,7 @@
         <v>1005</v>
       </c>
       <c r="G159" s="15" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H159" s="15"/>
       <c r="I159">
@@ -6421,7 +6433,7 @@
         <v>198</v>
       </c>
       <c r="G160" s="15" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H160" s="15"/>
       <c r="I160">
@@ -6450,7 +6462,7 @@
         <v>204</v>
       </c>
       <c r="G161" s="15" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H161" s="15"/>
       <c r="I161">
@@ -6479,7 +6491,7 @@
         <v>2006</v>
       </c>
       <c r="G162" s="15" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H162" s="15"/>
       <c r="I162">
@@ -6616,7 +6628,7 @@
         <v>873</v>
       </c>
       <c r="G167" s="18" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H167" s="18"/>
       <c r="I167">
@@ -6645,7 +6657,7 @@
         <v>97</v>
       </c>
       <c r="G168" s="18" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H168" s="18"/>
       <c r="I168">
@@ -6658,10 +6670,10 @@
         <v>46227</v>
       </c>
       <c r="B169" s="36" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C169" s="36" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D169" s="36" t="s">
         <v>44</v>
@@ -6675,7 +6687,7 @@
       </c>
       <c r="G169" s="36"/>
       <c r="H169" s="36" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I169">
         <f t="shared" si="2"/>
@@ -6849,7 +6861,7 @@
       </c>
       <c r="G175" s="12"/>
       <c r="H175" s="12" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I175">
         <f t="shared" si="2"/>
@@ -7072,7 +7084,7 @@
       </c>
       <c r="G183" s="9"/>
       <c r="H183" s="9" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="I183">
         <f t="shared" si="2"/>
@@ -7322,7 +7334,7 @@
         <v>1552</v>
       </c>
       <c r="G192" s="18" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H192" s="18"/>
       <c r="I192">
@@ -7351,7 +7363,7 @@
         <v>679</v>
       </c>
       <c r="G193" s="18" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="H193" s="18"/>
       <c r="I193">
@@ -7379,9 +7391,11 @@
         <f>IF($B194="","",IF($D194="kg",N($E194),IF($D194="sacos",N($E194)*97,IF($D194="jabas",N($E194)*IFERROR(VLOOKUP($C194,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
         <v>194</v>
       </c>
-      <c r="G194" s="18"/>
+      <c r="G194" s="18" t="s">
+        <v>63</v>
+      </c>
       <c r="H194" s="38" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="I194">
         <f t="shared" si="2"/>
@@ -7859,7 +7873,7 @@
         <v>970</v>
       </c>
       <c r="G211" s="18" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H211" s="18"/>
       <c r="I211">
@@ -7889,7 +7903,7 @@
       </c>
       <c r="G212" s="9"/>
       <c r="H212" s="9" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="I212">
         <f t="shared" si="3"/>
@@ -8195,7 +8209,7 @@
       </c>
       <c r="G223" s="9"/>
       <c r="H223" s="9" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I223">
         <f t="shared" si="3"/>
@@ -8480,7 +8494,7 @@
         <v>776</v>
       </c>
       <c r="G233" s="18" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H233" s="18"/>
       <c r="I233">
@@ -8510,7 +8524,7 @@
       </c>
       <c r="G234" s="18"/>
       <c r="H234" s="18" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="235" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8555,7 +8569,7 @@
       </c>
       <c r="G236" s="40"/>
       <c r="H236" s="40" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="I236">
         <f t="shared" ref="I236:I245" si="4">N($F236)</f>
@@ -8883,10 +8897,10 @@
         <v>485</v>
       </c>
       <c r="G248" s="18" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H248" s="40" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K248" s="42"/>
     </row>
@@ -8911,7 +8925,7 @@
         <v>485</v>
       </c>
       <c r="G249" s="18" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H249" s="40"/>
     </row>
@@ -8934,7 +8948,7 @@
       </c>
       <c r="G250" s="40"/>
       <c r="H250" s="40" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="I250">
         <f t="shared" ref="I250:I259" si="5">N($F250)</f>
@@ -9254,10 +9268,10 @@
         <v>1164</v>
       </c>
       <c r="G262" s="18" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H262" s="46" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="263" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -9265,7 +9279,7 @@
         <v>46237</v>
       </c>
       <c r="B263" s="44" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C263" s="44" t="s">
         <v>22</v>
@@ -9281,7 +9295,7 @@
       </c>
       <c r="G263" s="46"/>
       <c r="H263" s="46" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="264" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -9405,7 +9419,7 @@
         <v>46237</v>
       </c>
       <c r="B268" s="40" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C268" s="40" t="s">
         <v>11</v>
@@ -9422,7 +9436,7 @@
       </c>
       <c r="G268" s="40"/>
       <c r="H268" s="40" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="I268">
         <f t="shared" si="6"/>
@@ -9448,7 +9462,7 @@
       </c>
       <c r="G269" s="40"/>
       <c r="H269" s="40" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="I269">
         <f t="shared" si="6"/>
@@ -9727,7 +9741,7 @@
       </c>
       <c r="G279" s="40"/>
       <c r="H279" s="40" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="I279">
         <f t="shared" si="6"/>
@@ -10006,7 +10020,7 @@
         <v>194</v>
       </c>
       <c r="G289" s="40" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H289" s="40"/>
       <c r="I289">
@@ -10035,7 +10049,7 @@
         <v>194</v>
       </c>
       <c r="G290" s="40" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="H290" s="40"/>
       <c r="I290">
@@ -10064,10 +10078,10 @@
         <v>1455</v>
       </c>
       <c r="G291" s="40" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="H291" s="40" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="I291">
         <f t="shared" si="6"/>
@@ -10094,9 +10108,11 @@
         <f>IF($B292="","",IF($D292="kg",N($E292),IF($D292="sacos",N($E292)*97,IF($D292="jabas",N($E292)*IFERROR(VLOOKUP($C292,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
         <v>97</v>
       </c>
-      <c r="G292" s="40"/>
+      <c r="G292" s="40" t="s">
+        <v>63</v>
+      </c>
       <c r="H292" s="40" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="I292">
         <f t="shared" si="6"/>
@@ -10166,7 +10182,7 @@
       </c>
       <c r="G295" s="40"/>
       <c r="H295" s="40" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="I295">
         <f t="shared" ref="I295:I314" si="7">N($F295)</f>
@@ -10445,7 +10461,7 @@
         <v>1649</v>
       </c>
       <c r="G305" s="40" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H305" s="40"/>
       <c r="I305">
@@ -10474,10 +10490,10 @@
         <v>582</v>
       </c>
       <c r="G306" s="40" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="H306" s="40" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I306">
         <f t="shared" si="7"/>
@@ -10504,7 +10520,7 @@
       </c>
       <c r="G307" s="40"/>
       <c r="H307" s="52" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="I307">
         <f t="shared" si="7"/>
@@ -10817,7 +10833,7 @@
         <v>388</v>
       </c>
       <c r="G319" s="40" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H319" s="40"/>
     </row>
@@ -10841,7 +10857,7 @@
       </c>
       <c r="G320" s="40"/>
       <c r="H320" s="40" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="I320">
         <f t="shared" ref="I320:I351" si="8">N($F320)</f>
@@ -11119,9 +11135,11 @@
         <f>IF($B330="","",IF($D330="kg",N($E330),IF($D330="sacos",N($E330)*97,IF($D330="jabas",N($E330)*IFERROR(VLOOKUP($C330,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
         <v>48.5</v>
       </c>
-      <c r="G330" s="40"/>
+      <c r="G330" s="40" t="s">
+        <v>242</v>
+      </c>
       <c r="H330" s="40" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I330">
         <f t="shared" si="8"/>
@@ -11148,7 +11166,7 @@
       </c>
       <c r="G331" s="40"/>
       <c r="H331" s="40" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="I331">
         <f t="shared" si="8"/>
@@ -11427,10 +11445,10 @@
         <v>873</v>
       </c>
       <c r="G341" s="40" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="H341" s="40" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="I341">
         <f t="shared" si="8"/>
@@ -11457,7 +11475,7 @@
       </c>
       <c r="G342" s="40"/>
       <c r="H342" s="40" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="I342">
         <f t="shared" si="8"/>
@@ -11736,558 +11754,883 @@
         <v>1067</v>
       </c>
       <c r="G352" s="40" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="H352" s="40" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="I352">
-        <f t="shared" ref="I352:I382" si="9">N($F352)</f>
+        <f t="shared" ref="I352:I386" si="9">N($F352)</f>
         <v>1067</v>
       </c>
     </row>
     <row r="353" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A353" s="39"/>
-      <c r="B353" s="40"/>
-      <c r="C353" s="40"/>
-      <c r="D353" s="40"/>
-      <c r="E353" s="41"/>
-      <c r="F353" s="41" t="str">
+      <c r="A353" s="39">
+        <v>46245</v>
+      </c>
+      <c r="B353" s="40" t="s">
+        <v>34</v>
+      </c>
+      <c r="C353" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D353" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="E353" s="16">
+        <v>1</v>
+      </c>
+      <c r="F353" s="16">
         <f>IF($B353="","",IF($D353="kg",N($E353),IF($D353="sacos",N($E353)*97,IF($D353="jabas",N($E353)*IFERROR(VLOOKUP($C353,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
-        <v/>
+        <v>15</v>
       </c>
       <c r="G353" s="40"/>
       <c r="H353" s="40"/>
-      <c r="I353">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
     </row>
     <row r="354" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A354" s="39"/>
-      <c r="B354" s="40"/>
+      <c r="A354" s="39">
+        <v>46245</v>
+      </c>
+      <c r="B354" s="40" t="s">
+        <v>243</v>
+      </c>
       <c r="C354" s="40"/>
-      <c r="D354" s="40"/>
-      <c r="E354" s="41"/>
-      <c r="F354" s="41" t="str">
-        <f>IF($B354="","",IF($D354="kg",N($E354),IF($D354="sacos",N($E354)*97,IF($D354="jabas",N($E354)*IFERROR(VLOOKUP($C354,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
-        <v/>
+      <c r="D354" s="40" t="s">
+        <v>16</v>
+      </c>
+      <c r="E354" s="41">
+        <v>8</v>
+      </c>
+      <c r="F354" s="41">
+        <v>633</v>
       </c>
       <c r="G354" s="40"/>
-      <c r="H354" s="40"/>
-      <c r="I354">
-        <f t="shared" si="9"/>
-        <v>0</v>
+      <c r="H354" s="40" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="355" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A355" s="39"/>
-      <c r="B355" s="40"/>
-      <c r="C355" s="40"/>
-      <c r="D355" s="40"/>
-      <c r="E355" s="41"/>
-      <c r="F355" s="41" t="str">
+      <c r="A355" s="39">
+        <v>46245</v>
+      </c>
+      <c r="B355" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C355" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D355" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E355" s="13">
+        <v>37</v>
+      </c>
+      <c r="F355" s="13">
         <f>IF($B355="","",IF($D355="kg",N($E355),IF($D355="sacos",N($E355)*97,IF($D355="jabas",N($E355)*IFERROR(VLOOKUP($C355,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
-        <v/>
+        <v>629</v>
       </c>
       <c r="G355" s="40"/>
       <c r="H355" s="40"/>
-      <c r="I355">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
     </row>
     <row r="356" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A356" s="39"/>
-      <c r="B356" s="40"/>
-      <c r="C356" s="40"/>
-      <c r="D356" s="40"/>
-      <c r="E356" s="41"/>
-      <c r="F356" s="41" t="str">
+      <c r="A356" s="39">
+        <v>46245</v>
+      </c>
+      <c r="B356" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C356" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D356" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="E356" s="16">
+        <v>67</v>
+      </c>
+      <c r="F356" s="16">
         <f>IF($B356="","",IF($D356="kg",N($E356),IF($D356="sacos",N($E356)*97,IF($D356="jabas",N($E356)*IFERROR(VLOOKUP($C356,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
-        <v/>
-      </c>
-      <c r="G356" s="40"/>
+        <v>1005</v>
+      </c>
+      <c r="G356" s="79">
+        <v>3069</v>
+      </c>
       <c r="H356" s="40"/>
       <c r="I356">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="357" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A357" s="39"/>
-      <c r="B357" s="40"/>
-      <c r="C357" s="40"/>
-      <c r="D357" s="40"/>
-      <c r="E357" s="41"/>
-      <c r="F357" s="41" t="str">
+      <c r="A357" s="39">
+        <v>46245</v>
+      </c>
+      <c r="B357" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C357" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D357" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="E357" s="16">
+        <v>11</v>
+      </c>
+      <c r="F357" s="16">
         <f>IF($B357="","",IF($D357="kg",N($E357),IF($D357="sacos",N($E357)*97,IF($D357="jabas",N($E357)*IFERROR(VLOOKUP($C357,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
-        <v/>
-      </c>
-      <c r="G357" s="40"/>
+        <v>198</v>
+      </c>
+      <c r="G357" s="79">
+        <v>3069</v>
+      </c>
       <c r="H357" s="40"/>
       <c r="I357">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>198</v>
       </c>
     </row>
     <row r="358" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A358" s="39"/>
-      <c r="B358" s="40"/>
-      <c r="C358" s="40"/>
-      <c r="D358" s="40"/>
-      <c r="E358" s="41"/>
-      <c r="F358" s="41" t="str">
+      <c r="A358" s="39">
+        <v>46245</v>
+      </c>
+      <c r="B358" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C358" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="D358" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="E358" s="16">
+        <v>9</v>
+      </c>
+      <c r="F358" s="16">
         <f>IF($B358="","",IF($D358="kg",N($E358),IF($D358="sacos",N($E358)*97,IF($D358="jabas",N($E358)*IFERROR(VLOOKUP($C358,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
-        <v/>
-      </c>
-      <c r="G358" s="40"/>
+        <v>153</v>
+      </c>
+      <c r="G358" s="79">
+        <v>3069</v>
+      </c>
       <c r="H358" s="40"/>
       <c r="I358">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>153</v>
       </c>
     </row>
     <row r="359" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A359" s="39"/>
-      <c r="B359" s="40"/>
-      <c r="C359" s="40"/>
-      <c r="D359" s="40"/>
-      <c r="E359" s="41"/>
-      <c r="F359" s="41" t="str">
+      <c r="A359" s="39">
+        <v>46245</v>
+      </c>
+      <c r="B359" s="44" t="s">
+        <v>23</v>
+      </c>
+      <c r="C359" s="44" t="s">
+        <v>13</v>
+      </c>
+      <c r="D359" s="44" t="s">
+        <v>12</v>
+      </c>
+      <c r="E359" s="45">
+        <v>99</v>
+      </c>
+      <c r="F359" s="45">
         <f>IF($B359="","",IF($D359="kg",N($E359),IF($D359="sacos",N($E359)*97,IF($D359="jabas",N($E359)*IFERROR(VLOOKUP($C359,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
-        <v/>
-      </c>
-      <c r="G359" s="40"/>
+        <v>1683</v>
+      </c>
+      <c r="G359" s="79">
+        <v>3069</v>
+      </c>
       <c r="H359" s="40"/>
       <c r="I359">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="360" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A360" s="39"/>
-      <c r="B360" s="40"/>
-      <c r="C360" s="40"/>
-      <c r="D360" s="40"/>
-      <c r="E360" s="41"/>
-      <c r="F360" s="41" t="str">
+      <c r="A360" s="39">
+        <v>46245</v>
+      </c>
+      <c r="B360" s="40" t="s">
+        <v>28</v>
+      </c>
+      <c r="C360" s="40" t="s">
+        <v>15</v>
+      </c>
+      <c r="D360" s="40" t="s">
+        <v>16</v>
+      </c>
+      <c r="E360" s="41">
+        <v>10.5</v>
+      </c>
+      <c r="F360" s="41">
         <f>IF($B360="","",IF($D360="kg",N($E360),IF($D360="sacos",N($E360)*97,IF($D360="jabas",N($E360)*IFERROR(VLOOKUP($C360,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
-        <v/>
-      </c>
-      <c r="G360" s="40"/>
-      <c r="H360" s="40"/>
+        <v>1018.5</v>
+      </c>
+      <c r="G360" s="40" t="s">
+        <v>242</v>
+      </c>
+      <c r="H360" s="40" t="s">
+        <v>241</v>
+      </c>
       <c r="I360">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1018.5</v>
       </c>
     </row>
     <row r="361" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A361" s="39"/>
-      <c r="B361" s="40"/>
+      <c r="A361" s="39">
+        <v>46246</v>
+      </c>
+      <c r="B361" s="40" t="s">
+        <v>243</v>
+      </c>
       <c r="C361" s="40"/>
-      <c r="D361" s="40"/>
-      <c r="E361" s="41"/>
-      <c r="F361" s="41" t="str">
+      <c r="D361" s="40" t="s">
+        <v>16</v>
+      </c>
+      <c r="E361" s="41">
+        <v>8</v>
+      </c>
+      <c r="F361" s="41">
         <f>IF($B361="","",IF($D361="kg",N($E361),IF($D361="sacos",N($E361)*97,IF($D361="jabas",N($E361)*IFERROR(VLOOKUP($C361,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
-        <v/>
+        <v>776</v>
       </c>
       <c r="G361" s="40"/>
-      <c r="H361" s="40"/>
+      <c r="H361" s="40" t="s">
+        <v>244</v>
+      </c>
       <c r="I361">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>776</v>
       </c>
     </row>
     <row r="362" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A362" s="39"/>
-      <c r="B362" s="40"/>
-      <c r="C362" s="40"/>
-      <c r="D362" s="40"/>
-      <c r="E362" s="41"/>
-      <c r="F362" s="41" t="str">
+      <c r="A362" s="39">
+        <v>46246</v>
+      </c>
+      <c r="B362" s="40" t="s">
+        <v>20</v>
+      </c>
+      <c r="C362" s="40" t="s">
+        <v>11</v>
+      </c>
+      <c r="D362" s="40" t="s">
+        <v>12</v>
+      </c>
+      <c r="E362" s="41">
+        <v>7</v>
+      </c>
+      <c r="F362" s="41">
         <f>IF($B362="","",IF($D362="kg",N($E362),IF($D362="sacos",N($E362)*97,IF($D362="jabas",N($E362)*IFERROR(VLOOKUP($C362,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
-        <v/>
+        <v>105</v>
       </c>
       <c r="G362" s="40"/>
-      <c r="H362" s="40"/>
+      <c r="H362" s="40" t="s">
+        <v>244</v>
+      </c>
       <c r="I362">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>105</v>
       </c>
     </row>
     <row r="363" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A363" s="39"/>
-      <c r="B363" s="40"/>
-      <c r="C363" s="40"/>
-      <c r="D363" s="40"/>
-      <c r="E363" s="41"/>
-      <c r="F363" s="41" t="str">
+      <c r="A363" s="39">
+        <v>46246</v>
+      </c>
+      <c r="B363" s="40" t="s">
+        <v>20</v>
+      </c>
+      <c r="C363" s="40" t="s">
+        <v>13</v>
+      </c>
+      <c r="D363" s="40" t="s">
+        <v>12</v>
+      </c>
+      <c r="E363" s="41">
+        <v>32</v>
+      </c>
+      <c r="F363" s="41">
         <f>IF($B363="","",IF($D363="kg",N($E363),IF($D363="sacos",N($E363)*97,IF($D363="jabas",N($E363)*IFERROR(VLOOKUP($C363,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
-        <v/>
+        <v>544</v>
       </c>
       <c r="G363" s="40"/>
-      <c r="H363" s="40"/>
+      <c r="H363" s="40" t="s">
+        <v>244</v>
+      </c>
       <c r="I363">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>544</v>
       </c>
     </row>
     <row r="364" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A364" s="39"/>
-      <c r="B364" s="40"/>
-      <c r="C364" s="40"/>
-      <c r="D364" s="40"/>
-      <c r="E364" s="41"/>
-      <c r="F364" s="41" t="str">
+      <c r="A364" s="39">
+        <v>46246</v>
+      </c>
+      <c r="B364" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C364" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D364" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="E364" s="13">
+        <v>3</v>
+      </c>
+      <c r="F364" s="13">
         <f>IF($B364="","",IF($D364="kg",N($E364),IF($D364="sacos",N($E364)*97,IF($D364="jabas",N($E364)*IFERROR(VLOOKUP($C364,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
-        <v/>
+        <v>291</v>
       </c>
       <c r="G364" s="40"/>
-      <c r="H364" s="40"/>
-      <c r="I364">
-        <f t="shared" si="9"/>
-        <v>0</v>
+      <c r="H364" s="40" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="365" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A365" s="39"/>
-      <c r="B365" s="40"/>
+      <c r="A365" s="39">
+        <v>46246</v>
+      </c>
+      <c r="B365" s="40" t="s">
+        <v>17</v>
+      </c>
       <c r="C365" s="40"/>
-      <c r="D365" s="40"/>
-      <c r="E365" s="41"/>
-      <c r="F365" s="41" t="str">
+      <c r="D365" s="40" t="s">
+        <v>16</v>
+      </c>
+      <c r="E365" s="41">
+        <v>25</v>
+      </c>
+      <c r="F365" s="41">
         <f>IF($B365="","",IF($D365="kg",N($E365),IF($D365="sacos",N($E365)*97,IF($D365="jabas",N($E365)*IFERROR(VLOOKUP($C365,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
-        <v/>
+        <v>2425</v>
       </c>
       <c r="G365" s="40"/>
-      <c r="H365" s="40"/>
+      <c r="H365" s="40" t="s">
+        <v>245</v>
+      </c>
       <c r="I365">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>2425</v>
       </c>
     </row>
     <row r="366" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A366" s="39"/>
-      <c r="B366" s="40"/>
-      <c r="C366" s="40"/>
-      <c r="D366" s="40"/>
-      <c r="E366" s="41"/>
-      <c r="F366" s="41" t="str">
+      <c r="A366" s="39">
+        <v>46246</v>
+      </c>
+      <c r="B366" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C366" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="D366" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E366" s="13">
+        <v>60</v>
+      </c>
+      <c r="F366" s="41">
         <f>IF($B366="","",IF($D366="kg",N($E366),IF($D366="sacos",N($E366)*97,IF($D366="jabas",N($E366)*IFERROR(VLOOKUP($C366,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
-        <v/>
+        <v>900</v>
       </c>
       <c r="G366" s="40"/>
       <c r="H366" s="40"/>
       <c r="I366">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>900</v>
       </c>
     </row>
     <row r="367" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A367" s="39"/>
-      <c r="B367" s="40"/>
-      <c r="C367" s="40"/>
-      <c r="D367" s="40"/>
-      <c r="E367" s="41"/>
-      <c r="F367" s="41" t="str">
+      <c r="A367" s="39">
+        <v>46246</v>
+      </c>
+      <c r="B367" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C367" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D367" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E367" s="13">
+        <v>8</v>
+      </c>
+      <c r="F367" s="41">
         <f>IF($B367="","",IF($D367="kg",N($E367),IF($D367="sacos",N($E367)*97,IF($D367="jabas",N($E367)*IFERROR(VLOOKUP($C367,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
-        <v/>
+        <v>144</v>
       </c>
       <c r="G367" s="40"/>
       <c r="H367" s="40"/>
       <c r="I367">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>144</v>
       </c>
     </row>
     <row r="368" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A368" s="39"/>
-      <c r="B368" s="40"/>
-      <c r="C368" s="40"/>
-      <c r="D368" s="40"/>
-      <c r="E368" s="41"/>
-      <c r="F368" s="41" t="str">
+      <c r="A368" s="39">
+        <v>46246</v>
+      </c>
+      <c r="B368" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C368" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D368" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E368" s="13">
+        <v>11</v>
+      </c>
+      <c r="F368" s="41">
         <f>IF($B368="","",IF($D368="kg",N($E368),IF($D368="sacos",N($E368)*97,IF($D368="jabas",N($E368)*IFERROR(VLOOKUP($C368,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
-        <v/>
+        <v>187</v>
       </c>
       <c r="G368" s="40"/>
       <c r="H368" s="40"/>
       <c r="I368">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>187</v>
       </c>
     </row>
     <row r="369" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A369" s="39"/>
-      <c r="B369" s="40"/>
-      <c r="C369" s="40"/>
-      <c r="D369" s="40"/>
-      <c r="E369" s="41"/>
-      <c r="F369" s="41" t="str">
+      <c r="A369" s="39">
+        <v>46246</v>
+      </c>
+      <c r="B369" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C369" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D369" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E369" s="13">
+        <v>86</v>
+      </c>
+      <c r="F369" s="41">
         <f>IF($B369="","",IF($D369="kg",N($E369),IF($D369="sacos",N($E369)*97,IF($D369="jabas",N($E369)*IFERROR(VLOOKUP($C369,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
-        <v/>
+        <v>1462</v>
       </c>
       <c r="G369" s="40"/>
       <c r="H369" s="40"/>
       <c r="I369">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="370" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A370" s="39"/>
-      <c r="B370" s="40"/>
-      <c r="C370" s="40"/>
-      <c r="D370" s="40"/>
-      <c r="E370" s="41"/>
-      <c r="F370" s="41" t="str">
+      <c r="A370" s="39">
+        <v>46246</v>
+      </c>
+      <c r="B370" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C370" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D370" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="E370" s="13">
+        <v>2</v>
+      </c>
+      <c r="F370" s="41">
         <f>IF($B370="","",IF($D370="kg",N($E370),IF($D370="sacos",N($E370)*97,IF($D370="jabas",N($E370)*IFERROR(VLOOKUP($C370,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
-        <v/>
+        <v>194</v>
       </c>
       <c r="G370" s="40"/>
       <c r="H370" s="40"/>
       <c r="I370">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>194</v>
       </c>
     </row>
     <row r="371" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A371" s="39"/>
-      <c r="B371" s="40"/>
-      <c r="C371" s="40"/>
-      <c r="D371" s="40"/>
-      <c r="E371" s="41"/>
-      <c r="F371" s="41" t="str">
+      <c r="A371" s="39">
+        <v>46246</v>
+      </c>
+      <c r="B371" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C371" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D371" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="E371" s="16">
+        <v>67</v>
+      </c>
+      <c r="F371" s="41">
         <f>IF($B371="","",IF($D371="kg",N($E371),IF($D371="sacos",N($E371)*97,IF($D371="jabas",N($E371)*IFERROR(VLOOKUP($C371,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
-        <v/>
-      </c>
-      <c r="G371" s="40"/>
+        <v>1005</v>
+      </c>
+      <c r="G371" s="40">
+        <v>3074</v>
+      </c>
       <c r="H371" s="40"/>
       <c r="I371">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="372" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A372" s="39"/>
-      <c r="B372" s="40"/>
-      <c r="C372" s="40"/>
-      <c r="D372" s="40"/>
-      <c r="E372" s="41"/>
-      <c r="F372" s="41" t="str">
+      <c r="A372" s="39">
+        <v>46246</v>
+      </c>
+      <c r="B372" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C372" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D372" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="E372" s="16">
+        <v>8</v>
+      </c>
+      <c r="F372" s="41">
         <f>IF($B372="","",IF($D372="kg",N($E372),IF($D372="sacos",N($E372)*97,IF($D372="jabas",N($E372)*IFERROR(VLOOKUP($C372,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
-        <v/>
+        <v>144</v>
       </c>
       <c r="G372" s="40"/>
       <c r="H372" s="40"/>
       <c r="I372">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>144</v>
       </c>
     </row>
     <row r="373" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A373" s="39"/>
-      <c r="B373" s="40"/>
-      <c r="C373" s="40"/>
-      <c r="D373" s="40"/>
-      <c r="E373" s="41"/>
-      <c r="F373" s="41" t="str">
+      <c r="A373" s="39">
+        <v>46246</v>
+      </c>
+      <c r="B373" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C373" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="D373" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="E373" s="16">
+        <v>11</v>
+      </c>
+      <c r="F373" s="41">
         <f>IF($B373="","",IF($D373="kg",N($E373),IF($D373="sacos",N($E373)*97,IF($D373="jabas",N($E373)*IFERROR(VLOOKUP($C373,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
-        <v/>
+        <v>187</v>
       </c>
       <c r="G373" s="40"/>
       <c r="H373" s="40"/>
       <c r="I373">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>187</v>
       </c>
     </row>
     <row r="374" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A374" s="39"/>
-      <c r="B374" s="40"/>
-      <c r="C374" s="40"/>
-      <c r="D374" s="40"/>
-      <c r="E374" s="41"/>
-      <c r="F374" s="41" t="str">
+      <c r="A374" s="39">
+        <v>46246</v>
+      </c>
+      <c r="B374" s="44" t="s">
+        <v>23</v>
+      </c>
+      <c r="C374" s="44" t="s">
+        <v>13</v>
+      </c>
+      <c r="D374" s="44" t="s">
+        <v>12</v>
+      </c>
+      <c r="E374" s="45">
+        <v>118</v>
+      </c>
+      <c r="F374" s="41">
         <f>IF($B374="","",IF($D374="kg",N($E374),IF($D374="sacos",N($E374)*97,IF($D374="jabas",N($E374)*IFERROR(VLOOKUP($C374,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
-        <v/>
+        <v>2006</v>
       </c>
       <c r="G374" s="40"/>
       <c r="H374" s="40"/>
       <c r="I374">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>2006</v>
       </c>
     </row>
     <row r="375" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A375" s="39"/>
-      <c r="B375" s="40"/>
+      <c r="A375" s="39">
+        <v>46247</v>
+      </c>
+      <c r="B375" s="40" t="s">
+        <v>17</v>
+      </c>
       <c r="C375" s="40"/>
-      <c r="D375" s="40"/>
-      <c r="E375" s="41"/>
-      <c r="F375" s="41" t="str">
+      <c r="D375" s="40" t="s">
+        <v>16</v>
+      </c>
+      <c r="E375" s="41">
+        <v>45</v>
+      </c>
+      <c r="F375" s="41">
         <f>IF($B375="","",IF($D375="kg",N($E375),IF($D375="sacos",N($E375)*97,IF($D375="jabas",N($E375)*IFERROR(VLOOKUP($C375,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
-        <v/>
+        <v>4365</v>
       </c>
       <c r="G375" s="40"/>
-      <c r="H375" s="40"/>
+      <c r="H375" s="40" t="s">
+        <v>246</v>
+      </c>
       <c r="I375">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>4365</v>
       </c>
     </row>
     <row r="376" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A376" s="39"/>
-      <c r="B376" s="40"/>
-      <c r="C376" s="40"/>
-      <c r="D376" s="40"/>
-      <c r="E376" s="41"/>
-      <c r="F376" s="41" t="str">
+      <c r="A376" s="39">
+        <v>46247</v>
+      </c>
+      <c r="B376" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C376" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="D376" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E376" s="13">
+        <v>67</v>
+      </c>
+      <c r="F376" s="41">
         <f>IF($B376="","",IF($D376="kg",N($E376),IF($D376="sacos",N($E376)*97,IF($D376="jabas",N($E376)*IFERROR(VLOOKUP($C376,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
-        <v/>
+        <v>1005</v>
       </c>
       <c r="G376" s="40"/>
       <c r="H376" s="40"/>
       <c r="I376">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="377" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A377" s="39"/>
-      <c r="B377" s="40"/>
-      <c r="C377" s="40"/>
-      <c r="D377" s="40"/>
-      <c r="E377" s="41"/>
-      <c r="F377" s="41" t="str">
+      <c r="A377" s="39">
+        <v>46247</v>
+      </c>
+      <c r="B377" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C377" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D377" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E377" s="13">
+        <v>11</v>
+      </c>
+      <c r="F377" s="41">
         <f>IF($B377="","",IF($D377="kg",N($E377),IF($D377="sacos",N($E377)*97,IF($D377="jabas",N($E377)*IFERROR(VLOOKUP($C377,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
-        <v/>
+        <v>198</v>
       </c>
       <c r="G377" s="40"/>
       <c r="H377" s="40"/>
       <c r="I377">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>198</v>
       </c>
     </row>
     <row r="378" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A378" s="39"/>
-      <c r="B378" s="40"/>
-      <c r="C378" s="40"/>
-      <c r="D378" s="40"/>
-      <c r="E378" s="41"/>
-      <c r="F378" s="41" t="str">
+      <c r="A378" s="39">
+        <v>46247</v>
+      </c>
+      <c r="B378" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C378" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D378" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E378" s="13">
+        <v>12</v>
+      </c>
+      <c r="F378" s="41">
         <f>IF($B378="","",IF($D378="kg",N($E378),IF($D378="sacos",N($E378)*97,IF($D378="jabas",N($E378)*IFERROR(VLOOKUP($C378,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
-        <v/>
+        <v>204</v>
       </c>
       <c r="G378" s="40"/>
       <c r="H378" s="40"/>
       <c r="I378">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>204</v>
       </c>
     </row>
     <row r="379" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A379" s="39"/>
-      <c r="B379" s="40"/>
-      <c r="C379" s="40"/>
-      <c r="D379" s="40"/>
-      <c r="E379" s="41"/>
-      <c r="F379" s="41" t="str">
+      <c r="A379" s="39">
+        <v>46247</v>
+      </c>
+      <c r="B379" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C379" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D379" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E379" s="13">
+        <v>118</v>
+      </c>
+      <c r="F379" s="41">
         <f>IF($B379="","",IF($D379="kg",N($E379),IF($D379="sacos",N($E379)*97,IF($D379="jabas",N($E379)*IFERROR(VLOOKUP($C379,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
-        <v/>
+        <v>2006</v>
       </c>
       <c r="G379" s="40"/>
       <c r="H379" s="40"/>
       <c r="I379">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>2006</v>
       </c>
     </row>
     <row r="380" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A380" s="39"/>
-      <c r="B380" s="40"/>
-      <c r="C380" s="40"/>
-      <c r="D380" s="40"/>
-      <c r="E380" s="41"/>
-      <c r="F380" s="41" t="str">
+      <c r="A380" s="39">
+        <v>46247</v>
+      </c>
+      <c r="B380" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C380" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D380" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="E380" s="13">
+        <v>3</v>
+      </c>
+      <c r="F380" s="41">
         <f>IF($B380="","",IF($D380="kg",N($E380),IF($D380="sacos",N($E380)*97,IF($D380="jabas",N($E380)*IFERROR(VLOOKUP($C380,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
-        <v/>
+        <v>291</v>
       </c>
       <c r="G380" s="40"/>
       <c r="H380" s="40"/>
       <c r="I380">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>291</v>
       </c>
     </row>
     <row r="381" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A381" s="39"/>
-      <c r="B381" s="40"/>
-      <c r="C381" s="40"/>
-      <c r="D381" s="40"/>
-      <c r="E381" s="41"/>
-      <c r="F381" s="41" t="str">
+      <c r="A381" s="39">
+        <v>46247</v>
+      </c>
+      <c r="B381" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C381" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D381" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="E381" s="13">
+        <v>67</v>
+      </c>
+      <c r="F381" s="41">
         <f>IF($B381="","",IF($D381="kg",N($E381),IF($D381="sacos",N($E381)*97,IF($D381="jabas",N($E381)*IFERROR(VLOOKUP($C381,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
-        <v/>
-      </c>
-      <c r="G381" s="40"/>
+        <v>1005</v>
+      </c>
+      <c r="G381" s="40">
+        <v>3078</v>
+      </c>
       <c r="H381" s="40"/>
       <c r="I381">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="382" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A382" s="39"/>
-      <c r="B382" s="40"/>
-      <c r="C382" s="40"/>
-      <c r="D382" s="40"/>
-      <c r="E382" s="41"/>
-      <c r="F382" s="41" t="str">
+      <c r="A382" s="39">
+        <v>46247</v>
+      </c>
+      <c r="B382" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C382" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D382" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="E382" s="13">
+        <v>11</v>
+      </c>
+      <c r="F382" s="41">
         <f>IF($B382="","",IF($D382="kg",N($E382),IF($D382="sacos",N($E382)*97,IF($D382="jabas",N($E382)*IFERROR(VLOOKUP($C382,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
-        <v/>
+        <v>198</v>
       </c>
       <c r="G382" s="40"/>
       <c r="H382" s="40"/>
       <c r="I382">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>198</v>
       </c>
     </row>
     <row r="383" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A383" s="39"/>
-      <c r="B383" s="40"/>
-      <c r="C383" s="40"/>
-      <c r="D383" s="40"/>
-      <c r="E383" s="41"/>
-      <c r="F383" s="41" t="str">
+      <c r="A383" s="39">
+        <v>46247</v>
+      </c>
+      <c r="B383" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C383" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="D383" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="E383" s="13">
+        <v>12</v>
+      </c>
+      <c r="F383" s="41">
         <f>IF($B383="","",IF($D383="kg",N($E383),IF($D383="sacos",N($E383)*97,IF($D383="jabas",N($E383)*IFERROR(VLOOKUP($C383,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
-        <v/>
+        <v>204</v>
       </c>
       <c r="G383" s="40"/>
       <c r="H383" s="40"/>
       <c r="I383">
-        <f t="shared" ref="I383:I414" si="10">N($F383)</f>
-        <v>0</v>
+        <f t="shared" si="9"/>
+        <v>204</v>
       </c>
     </row>
     <row r="384" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A384" s="39"/>
-      <c r="B384" s="40"/>
-      <c r="C384" s="40"/>
-      <c r="D384" s="40"/>
-      <c r="E384" s="41"/>
-      <c r="F384" s="41" t="str">
+      <c r="A384" s="39">
+        <v>46247</v>
+      </c>
+      <c r="B384" s="44" t="s">
+        <v>23</v>
+      </c>
+      <c r="C384" s="44" t="s">
+        <v>13</v>
+      </c>
+      <c r="D384" s="44" t="s">
+        <v>12</v>
+      </c>
+      <c r="E384" s="13">
+        <v>118</v>
+      </c>
+      <c r="F384" s="41">
         <f>IF($B384="","",IF($D384="kg",N($E384),IF($D384="sacos",N($E384)*97,IF($D384="jabas",N($E384)*IFERROR(VLOOKUP($C384,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
-        <v/>
+        <v>2006</v>
       </c>
       <c r="G384" s="40"/>
       <c r="H384" s="40"/>
       <c r="I384">
-        <f t="shared" si="10"/>
-        <v>0</v>
+        <f t="shared" si="9"/>
+        <v>2006</v>
       </c>
     </row>
     <row r="385" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -12303,7 +12646,7 @@
       <c r="G385" s="40"/>
       <c r="H385" s="40"/>
       <c r="I385">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
@@ -12320,7 +12663,7 @@
       <c r="G386" s="40"/>
       <c r="H386" s="40"/>
       <c r="I386">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
@@ -12337,7 +12680,7 @@
       <c r="G387" s="40"/>
       <c r="H387" s="40"/>
       <c r="I387">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="I387:I418" si="10">N($F387)</f>
         <v>0</v>
       </c>
     </row>
@@ -12813,7 +13156,7 @@
       <c r="G415" s="40"/>
       <c r="H415" s="40"/>
       <c r="I415">
-        <f t="shared" ref="I415:I434" si="11">N($F415)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
@@ -12830,7 +13173,7 @@
       <c r="G416" s="40"/>
       <c r="H416" s="40"/>
       <c r="I416">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
@@ -12847,7 +13190,7 @@
       <c r="G417" s="40"/>
       <c r="H417" s="40"/>
       <c r="I417">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
@@ -12864,7 +13207,7 @@
       <c r="G418" s="40"/>
       <c r="H418" s="40"/>
       <c r="I418">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
@@ -12881,7 +13224,7 @@
       <c r="G419" s="40"/>
       <c r="H419" s="40"/>
       <c r="I419">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="I419:I438" si="11">N($F419)</f>
         <v>0</v>
       </c>
     </row>
@@ -12919,7 +13262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="422" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A422" s="39"/>
       <c r="B422" s="40"/>
       <c r="C422" s="40"/>
@@ -12943,7 +13286,7 @@
       <c r="D423" s="40"/>
       <c r="E423" s="41"/>
       <c r="F423" s="41" t="str">
-        <f>IF($B423="","",IF($D423="kg",N($E423),IF($D423="sacos",N($E423)*95,IF($D423="jabas",N($E423)*IFERROR(VLOOKUP($C423,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
+        <f>IF($B423="","",IF($D423="kg",N($E423),IF($D423="sacos",N($E423)*97,IF($D423="jabas",N($E423)*IFERROR(VLOOKUP($C423,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
         <v/>
       </c>
       <c r="G423" s="40"/>
@@ -12960,7 +13303,7 @@
       <c r="D424" s="40"/>
       <c r="E424" s="41"/>
       <c r="F424" s="41" t="str">
-        <f>IF($B424="","",IF($D424="kg",N($E424),IF($D424="sacos",N($E424)*95,IF($D424="jabas",N($E424)*IFERROR(VLOOKUP($C424,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
+        <f>IF($B424="","",IF($D424="kg",N($E424),IF($D424="sacos",N($E424)*97,IF($D424="jabas",N($E424)*IFERROR(VLOOKUP($C424,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
         <v/>
       </c>
       <c r="G424" s="40"/>
@@ -12977,7 +13320,7 @@
       <c r="D425" s="40"/>
       <c r="E425" s="41"/>
       <c r="F425" s="41" t="str">
-        <f>IF($B425="","",IF($D425="kg",N($E425),IF($D425="sacos",N($E425)*95,IF($D425="jabas",N($E425)*IFERROR(VLOOKUP($C425,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
+        <f>IF($B425="","",IF($D425="kg",N($E425),IF($D425="sacos",N($E425)*97,IF($D425="jabas",N($E425)*IFERROR(VLOOKUP($C425,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
         <v/>
       </c>
       <c r="G425" s="40"/>
@@ -12987,14 +13330,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="426" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A426" s="39"/>
       <c r="B426" s="40"/>
       <c r="C426" s="40"/>
       <c r="D426" s="40"/>
       <c r="E426" s="41"/>
       <c r="F426" s="41" t="str">
-        <f>IF($B426="","",IF($D426="kg",N($E426),IF($D426="sacos",N($E426)*95,IF($D426="jabas",N($E426)*IFERROR(VLOOKUP($C426,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
+        <f>IF($B426="","",IF($D426="kg",N($E426),IF($D426="sacos",N($E426)*97,IF($D426="jabas",N($E426)*IFERROR(VLOOKUP($C426,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
         <v/>
       </c>
       <c r="G426" s="40"/>
@@ -13140,13 +13483,81 @@
         <v>0</v>
       </c>
     </row>
+    <row r="435" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A435" s="39"/>
+      <c r="B435" s="40"/>
+      <c r="C435" s="40"/>
+      <c r="D435" s="40"/>
+      <c r="E435" s="41"/>
+      <c r="F435" s="41" t="str">
+        <f>IF($B435="","",IF($D435="kg",N($E435),IF($D435="sacos",N($E435)*95,IF($D435="jabas",N($E435)*IFERROR(VLOOKUP($C435,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
+        <v/>
+      </c>
+      <c r="G435" s="40"/>
+      <c r="H435" s="40"/>
+      <c r="I435">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="436" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A436" s="39"/>
+      <c r="B436" s="40"/>
+      <c r="C436" s="40"/>
+      <c r="D436" s="40"/>
+      <c r="E436" s="41"/>
+      <c r="F436" s="41" t="str">
+        <f>IF($B436="","",IF($D436="kg",N($E436),IF($D436="sacos",N($E436)*95,IF($D436="jabas",N($E436)*IFERROR(VLOOKUP($C436,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
+        <v/>
+      </c>
+      <c r="G436" s="40"/>
+      <c r="H436" s="40"/>
+      <c r="I436">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="437" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A437" s="39"/>
+      <c r="B437" s="40"/>
+      <c r="C437" s="40"/>
+      <c r="D437" s="40"/>
+      <c r="E437" s="41"/>
+      <c r="F437" s="41" t="str">
+        <f>IF($B437="","",IF($D437="kg",N($E437),IF($D437="sacos",N($E437)*95,IF($D437="jabas",N($E437)*IFERROR(VLOOKUP($C437,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
+        <v/>
+      </c>
+      <c r="G437" s="40"/>
+      <c r="H437" s="40"/>
+      <c r="I437">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="438" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A438" s="39"/>
+      <c r="B438" s="40"/>
+      <c r="C438" s="40"/>
+      <c r="D438" s="40"/>
+      <c r="E438" s="41"/>
+      <c r="F438" s="41" t="str">
+        <f>IF($B438="","",IF($D438="kg",N($E438),IF($D438="sacos",N($E438)*95,IF($D438="jabas",N($E438)*IFERROR(VLOOKUP($C438,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
+        <v/>
+      </c>
+      <c r="G438" s="40"/>
+      <c r="H438" s="40"/>
+      <c r="I438">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:H421" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A4:H425" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="2">
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:H434">
+  <conditionalFormatting sqref="A5:H438">
     <cfRule type="expression" dxfId="14" priority="3">
       <formula>$B5="COMPRA"</formula>
     </cfRule>
@@ -13187,7 +13598,7 @@
       <formula>$B5="SALDO INICIAL"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E5:H434">
+  <conditionalFormatting sqref="E5:H438">
     <cfRule type="expression" dxfId="1" priority="2">
       <formula>ISNUMBER(SEARCH("FALTA",$H5))</formula>
     </cfRule>
@@ -13216,7 +13627,7 @@
   <sheetData>
     <row r="1" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="88" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B1" s="87"/>
       <c r="C1" s="87"/>
@@ -13234,7 +13645,7 @@
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="86" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B2" s="87"/>
       <c r="C2" s="87"/>
@@ -13271,25 +13682,25 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>99</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>101</v>
       </c>
       <c r="I4" s="54"/>
       <c r="J4" s="54"/>
@@ -13304,23 +13715,23 @@
         <v>46214</v>
       </c>
       <c r="B5" s="56">
-        <f>IF($A5="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A5)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A5)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A5)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A5)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A5)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A5)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A5)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A5)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A5="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A5)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A5)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A5)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A5)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A5)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A5)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A5)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A5)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>2</v>
       </c>
       <c r="C5" s="56">
-        <f>IF($A5="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A5)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A5)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A5)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A5)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A5)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A5)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A5)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A5)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A5="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A5)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A5)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A5)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A5)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A5)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A5)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A5)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A5)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>0</v>
       </c>
       <c r="D5" s="56">
-        <f>IF($A5="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A5)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A5)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A5)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A5)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A5)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A5)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A5)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A5)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A5="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A5)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A5)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A5)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A5)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A5)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A5)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A5)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A5)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>0</v>
       </c>
       <c r="E5" s="56">
-        <f>IF($A5="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A5)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A5)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A5)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A5)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A5)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A5)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A5)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A5)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A5="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A5)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A5)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A5)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A5)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A5)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A5)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A5)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A5)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>8</v>
       </c>
       <c r="F5" s="56">
-        <f>IF($A5="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A5)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A5)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A5)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A5)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A5)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A5)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A5="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A5)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A5)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A5)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A5)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A5)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A5)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>20</v>
       </c>
       <c r="G5" s="56">
@@ -13328,7 +13739,7 @@
         <v>10</v>
       </c>
       <c r="H5" s="56">
-        <f>IF($A5="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$421="COMPRA")+(MOVIMIENTOS!$B$5:$B$421="REPROCESO")+(MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A5)*MOVIMIENTOS!$I$5:$I$421)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$421="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$421="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho"))+((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A5)*MOVIMIENTOS!$I$5:$I$421))</f>
+        <f>IF($A5="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$425="COMPRA")+(MOVIMIENTOS!$B$5:$B$425="REPROCESO")+(MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A5)*MOVIMIENTOS!$I$5:$I$425)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$425="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho"))+((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A5)*MOVIMIENTOS!$I$5:$I$425))</f>
         <v>166</v>
       </c>
       <c r="I5" s="54"/>
@@ -13350,23 +13761,23 @@
         <v>46215</v>
       </c>
       <c r="B6" s="56">
-        <f>IF($A6="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A6)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A6)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A6)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A6)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A6)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A6)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A6)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A6)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A6="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A6)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A6)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A6)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A6)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A6)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A6)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A6)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A6)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>-6</v>
       </c>
       <c r="C6" s="56">
-        <f>IF($A6="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A6)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A6)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A6)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A6)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A6)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A6)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A6)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A6)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A6="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A6)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A6)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A6)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A6)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A6)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A6)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A6)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A6)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>0</v>
       </c>
       <c r="D6" s="56">
-        <f>IF($A6="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A6)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A6)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A6)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A6)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A6)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A6)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A6)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A6)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A6="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A6)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A6)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A6)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A6)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A6)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A6)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A6)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A6)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>0</v>
       </c>
       <c r="E6" s="56">
-        <f>IF($A6="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A6)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A6)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A6)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A6)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A6)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A6)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A6)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A6)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A6="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A6)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A6)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A6)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A6)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A6)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A6)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A6)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A6)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>30</v>
       </c>
       <c r="F6" s="56">
-        <f>IF($A6="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A6)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A6)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A6)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A6)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A6)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A6)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A6="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A6)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A6)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A6)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A6)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A6)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A6)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>26</v>
       </c>
       <c r="G6" s="56">
@@ -13374,7 +13785,7 @@
         <v>24</v>
       </c>
       <c r="H6" s="56">
-        <f>IF($A6="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$421="COMPRA")+(MOVIMIENTOS!$B$5:$B$421="REPROCESO")+(MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A6)*MOVIMIENTOS!$I$5:$I$421)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$421="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$421="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho"))+((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A6)*MOVIMIENTOS!$I$5:$I$421))</f>
+        <f>IF($A6="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$425="COMPRA")+(MOVIMIENTOS!$B$5:$B$425="REPROCESO")+(MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A6)*MOVIMIENTOS!$I$5:$I$425)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$425="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho"))+((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A6)*MOVIMIENTOS!$I$5:$I$425))</f>
         <v>373</v>
       </c>
       <c r="I6" s="54"/>
@@ -13396,23 +13807,23 @@
         <v>46216</v>
       </c>
       <c r="B7" s="56">
-        <f>IF($A7="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A7)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A7)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A7)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A7)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A7)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A7)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A7)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A7)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A7="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A7)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A7)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A7)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A7)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A7)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A7)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A7)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A7)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>34</v>
       </c>
       <c r="C7" s="56">
-        <f>IF($A7="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A7)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A7)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A7)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A7)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A7)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A7)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A7)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A7)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A7="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A7)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A7)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A7)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A7)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A7)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A7)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A7)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A7)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>0</v>
       </c>
       <c r="D7" s="56">
-        <f>IF($A7="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A7)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A7)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A7)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A7)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A7)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A7)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A7)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A7)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A7="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A7)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A7)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A7)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A7)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A7)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A7)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A7)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A7)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>0</v>
       </c>
       <c r="E7" s="56">
-        <f>IF($A7="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A7)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A7)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A7)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A7)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A7)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A7)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A7)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A7)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A7="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A7)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A7)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A7)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A7)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A7)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A7)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A7)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A7)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>43</v>
       </c>
       <c r="F7" s="56">
-        <f>IF($A7="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A7)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A7)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A7)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A7)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A7)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A7)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A7="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A7)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A7)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A7)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A7)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A7)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A7)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>28</v>
       </c>
       <c r="G7" s="56">
@@ -13420,7 +13831,7 @@
         <v>77</v>
       </c>
       <c r="H7" s="56">
-        <f>IF($A7="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$421="COMPRA")+(MOVIMIENTOS!$B$5:$B$421="REPROCESO")+(MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A7)*MOVIMIENTOS!$I$5:$I$421)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$421="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$421="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho"))+((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A7)*MOVIMIENTOS!$I$5:$I$421))</f>
+        <f>IF($A7="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$425="COMPRA")+(MOVIMIENTOS!$B$5:$B$425="REPROCESO")+(MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A7)*MOVIMIENTOS!$I$5:$I$425)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$425="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho"))+((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A7)*MOVIMIENTOS!$I$5:$I$425))</f>
         <v>1003</v>
       </c>
       <c r="I7" s="54"/>
@@ -13442,23 +13853,23 @@
         <v>46217</v>
       </c>
       <c r="B8" s="56">
-        <f>IF($A8="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A8)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A8)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A8)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A8)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A8)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A8)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A8)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A8)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A8="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A8)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A8)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A8)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A8)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A8)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A8)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A8)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A8)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>12</v>
       </c>
       <c r="C8" s="56">
-        <f>IF($A8="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A8)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A8)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A8)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A8)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A8)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A8)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A8)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A8)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A8="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A8)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A8)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A8)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A8)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A8)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A8)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A8)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A8)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>0</v>
       </c>
       <c r="D8" s="56">
-        <f>IF($A8="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A8)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A8)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A8)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A8)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A8)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A8)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A8)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A8)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A8="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A8)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A8)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A8)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A8)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A8)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A8)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A8)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A8)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>0</v>
       </c>
       <c r="E8" s="56">
-        <f>IF($A8="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A8)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A8)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A8)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A8)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A8)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A8)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A8)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A8)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A8="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A8)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A8)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A8)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A8)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A8)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A8)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A8)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A8)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>48</v>
       </c>
       <c r="F8" s="56">
-        <f>IF($A8="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A8)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A8)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A8)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A8)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A8)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A8)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A8="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A8)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A8)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A8)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A8)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A8)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A8)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>35</v>
       </c>
       <c r="G8" s="56">
@@ -13466,7 +13877,7 @@
         <v>60</v>
       </c>
       <c r="H8" s="56">
-        <f>IF($A8="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$421="COMPRA")+(MOVIMIENTOS!$B$5:$B$421="REPROCESO")+(MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A8)*MOVIMIENTOS!$I$5:$I$421)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$421="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$421="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho"))+((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A8)*MOVIMIENTOS!$I$5:$I$421))</f>
+        <f>IF($A8="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$425="COMPRA")+(MOVIMIENTOS!$B$5:$B$425="REPROCESO")+(MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A8)*MOVIMIENTOS!$I$5:$I$425)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$425="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho"))+((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A8)*MOVIMIENTOS!$I$5:$I$425))</f>
         <v>825</v>
       </c>
       <c r="I8" s="54"/>
@@ -13488,23 +13899,23 @@
         <v>46218</v>
       </c>
       <c r="B9" s="56">
-        <f>IF($A9="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A9)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A9)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A9)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A9)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A9)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A9)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A9)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A9)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A9="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A9)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A9)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A9)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A9)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A9)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A9)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A9)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A9)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>24</v>
       </c>
       <c r="C9" s="56">
-        <f>IF($A9="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A9)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A9)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A9)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A9)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A9)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A9)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A9)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A9)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A9="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A9)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A9)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A9)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A9)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A9)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A9)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A9)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A9)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>11</v>
       </c>
       <c r="D9" s="56">
-        <f>IF($A9="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A9)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A9)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A9)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A9)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A9)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A9)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A9)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A9)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A9="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A9)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A9)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A9)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A9)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A9)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A9)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A9)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A9)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>12</v>
       </c>
       <c r="E9" s="56">
-        <f>IF($A9="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A9)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A9)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A9)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A9)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A9)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A9)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A9)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A9)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A9="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A9)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A9)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A9)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A9)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A9)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A9)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A9)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A9)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>36</v>
       </c>
       <c r="F9" s="56">
-        <f>IF($A9="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A9)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A9)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A9)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A9)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A9)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A9)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A9="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A9)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A9)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A9)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A9)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A9)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A9)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>5</v>
       </c>
       <c r="G9" s="56">
@@ -13512,7 +13923,7 @@
         <v>83</v>
       </c>
       <c r="H9" s="56">
-        <f>IF($A9="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$421="COMPRA")+(MOVIMIENTOS!$B$5:$B$421="REPROCESO")+(MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A9)*MOVIMIENTOS!$I$5:$I$421)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$421="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$421="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho"))+((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A9)*MOVIMIENTOS!$I$5:$I$421))</f>
+        <f>IF($A9="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$425="COMPRA")+(MOVIMIENTOS!$B$5:$B$425="REPROCESO")+(MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A9)*MOVIMIENTOS!$I$5:$I$425)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$425="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho"))+((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A9)*MOVIMIENTOS!$I$5:$I$425))</f>
         <v>1249</v>
       </c>
       <c r="I9" s="54"/>
@@ -13534,23 +13945,23 @@
         <v>46219</v>
       </c>
       <c r="B10" s="56">
-        <f>IF($A10="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A10)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A10)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A10)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A10)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A10)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A10)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A10)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A10)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A10="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A10)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A10)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A10)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A10)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A10)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A10)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A10)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A10)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>29</v>
       </c>
       <c r="C10" s="56">
-        <f>IF($A10="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A10)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A10)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A10)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A10)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A10)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A10)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A10)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A10)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A10="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A10)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A10)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A10)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A10)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A10)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A10)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A10)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A10)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>11</v>
       </c>
       <c r="D10" s="56">
-        <f>IF($A10="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A10)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A10)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A10)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A10)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A10)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A10)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A10)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A10)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A10="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A10)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A10)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A10)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A10)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A10)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A10)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A10)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A10)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>12</v>
       </c>
       <c r="E10" s="56">
-        <f>IF($A10="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A10)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A10)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A10)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A10)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A10)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A10)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A10)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A10)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A10="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A10)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A10)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A10)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A10)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A10)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A10)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A10)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A10)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>37</v>
       </c>
       <c r="F10" s="56">
-        <f>IF($A10="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A10)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A10)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A10)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A10)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A10)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A10)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A10="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A10)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A10)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A10)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A10)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A10)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A10)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>9</v>
       </c>
       <c r="G10" s="56">
@@ -13558,7 +13969,7 @@
         <v>89</v>
       </c>
       <c r="H10" s="56">
-        <f>IF($A10="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$421="COMPRA")+(MOVIMIENTOS!$B$5:$B$421="REPROCESO")+(MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A10)*MOVIMIENTOS!$I$5:$I$421)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$421="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$421="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho"))+((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A10)*MOVIMIENTOS!$I$5:$I$421))</f>
+        <f>IF($A10="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$425="COMPRA")+(MOVIMIENTOS!$B$5:$B$425="REPROCESO")+(MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A10)*MOVIMIENTOS!$I$5:$I$425)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$425="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho"))+((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A10)*MOVIMIENTOS!$I$5:$I$425))</f>
         <v>1439</v>
       </c>
       <c r="I10" s="54"/>
@@ -13580,23 +13991,23 @@
         <v>46220</v>
       </c>
       <c r="B11" s="56">
-        <f>IF($A11="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A11)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A11)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A11)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A11)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A11)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A11)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A11)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A11)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A11="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A11)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A11)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A11)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A11)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A11)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A11)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A11)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A11)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>65</v>
       </c>
       <c r="C11" s="56">
-        <f>IF($A11="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A11)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A11)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A11)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A11)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A11)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A11)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A11)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A11)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A11="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A11)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A11)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A11)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A11)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A11)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A11)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A11)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A11)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>4</v>
       </c>
       <c r="D11" s="56">
-        <f>IF($A11="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A11)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A11)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A11)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A11)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A11)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A11)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A11)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A11)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A11="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A11)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A11)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A11)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A11)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A11)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A11)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A11)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A11)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>9</v>
       </c>
       <c r="E11" s="56">
-        <f>IF($A11="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A11)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A11)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A11)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A11)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A11)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A11)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A11)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A11)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A11="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A11)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A11)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A11)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A11)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A11)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A11)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A11)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A11)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>115</v>
       </c>
       <c r="F11" s="56">
-        <f>IF($A11="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A11)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A11)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A11)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A11)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A11)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A11)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A11="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A11)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A11)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A11)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A11)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A11)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A11)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>5</v>
       </c>
       <c r="G11" s="56">
@@ -13604,7 +14015,7 @@
         <v>193</v>
       </c>
       <c r="H11" s="56">
-        <f>IF($A11="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$421="COMPRA")+(MOVIMIENTOS!$B$5:$B$421="REPROCESO")+(MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A11)*MOVIMIENTOS!$I$5:$I$421)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$421="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$421="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho"))+((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A11)*MOVIMIENTOS!$I$5:$I$421))</f>
+        <f>IF($A11="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$425="COMPRA")+(MOVIMIENTOS!$B$5:$B$425="REPROCESO")+(MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A11)*MOVIMIENTOS!$I$5:$I$425)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$425="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho"))+((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A11)*MOVIMIENTOS!$I$5:$I$425))</f>
         <v>3264</v>
       </c>
       <c r="I11" s="54"/>
@@ -13626,23 +14037,23 @@
         <v>46221</v>
       </c>
       <c r="B12" s="56">
-        <f>IF($A12="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A12)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A12)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A12)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A12)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A12)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A12)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A12)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A12)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A12="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A12)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A12)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A12)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A12)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A12)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A12)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A12)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A12)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>64</v>
       </c>
       <c r="C12" s="56">
-        <f>IF($A12="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A12)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A12)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A12)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A12)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A12)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A12)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A12)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A12)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A12="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A12)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A12)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A12)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A12)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A12)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A12)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A12)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A12)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>11</v>
       </c>
       <c r="D12" s="56">
-        <f>IF($A12="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A12)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A12)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A12)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A12)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A12)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A12)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A12)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A12)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A12="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A12)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A12)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A12)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A12)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A12)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A12)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A12)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A12)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>12</v>
       </c>
       <c r="E12" s="56">
-        <f>IF($A12="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A12)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A12)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A12)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A12)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A12)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A12)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A12)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A12)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A12="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A12)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A12)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A12)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A12)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A12)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A12)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A12)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A12)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>55</v>
       </c>
       <c r="F12" s="56">
-        <f>IF($A12="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A12)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A12)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A12)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A12)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A12)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A12)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A12="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A12)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A12)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A12)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A12)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A12)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A12)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>15</v>
       </c>
       <c r="G12" s="56">
@@ -13650,7 +14061,7 @@
         <v>142</v>
       </c>
       <c r="H12" s="56">
-        <f>IF($A12="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$421="COMPRA")+(MOVIMIENTOS!$B$5:$B$421="REPROCESO")+(MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A12)*MOVIMIENTOS!$I$5:$I$421)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$421="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$421="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho"))+((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A12)*MOVIMIENTOS!$I$5:$I$421))</f>
+        <f>IF($A12="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$425="COMPRA")+(MOVIMIENTOS!$B$5:$B$425="REPROCESO")+(MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A12)*MOVIMIENTOS!$I$5:$I$425)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$425="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho"))+((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A12)*MOVIMIENTOS!$I$5:$I$425))</f>
         <v>2327</v>
       </c>
       <c r="I12" s="54"/>
@@ -13672,23 +14083,23 @@
         <v>46222</v>
       </c>
       <c r="B13" s="56">
-        <f>IF($A13="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A13)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A13)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A13)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A13)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A13)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A13)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A13)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A13)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A13="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A13)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A13)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A13)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A13)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A13)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A13)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A13)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A13)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>37</v>
       </c>
       <c r="C13" s="56">
-        <f>IF($A13="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A13)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A13)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A13)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A13)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A13)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A13)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A13)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A13)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A13="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A13)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A13)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A13)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A13)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A13)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A13)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A13)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A13)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>0</v>
       </c>
       <c r="D13" s="56">
-        <f>IF($A13="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A13)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A13)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A13)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A13)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A13)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A13)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A13)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A13)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A13="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A13)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A13)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A13)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A13)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A13)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A13)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A13)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A13)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>0</v>
       </c>
       <c r="E13" s="56">
-        <f>IF($A13="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A13)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A13)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A13)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A13)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A13)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A13)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A13)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A13)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A13="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A13)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A13)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A13)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A13)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A13)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A13)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A13)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A13)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>61</v>
       </c>
       <c r="F13" s="56">
-        <f>IF($A13="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A13)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A13)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A13)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A13)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A13)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A13)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A13="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A13)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A13)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A13)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A13)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A13)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A13)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>18</v>
       </c>
       <c r="G13" s="56">
@@ -13696,7 +14107,7 @@
         <v>98</v>
       </c>
       <c r="H13" s="56">
-        <f>IF($A13="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$421="COMPRA")+(MOVIMIENTOS!$B$5:$B$421="REPROCESO")+(MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A13)*MOVIMIENTOS!$I$5:$I$421)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$421="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$421="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho"))+((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A13)*MOVIMIENTOS!$I$5:$I$421))</f>
+        <f>IF($A13="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$425="COMPRA")+(MOVIMIENTOS!$B$5:$B$425="REPROCESO")+(MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A13)*MOVIMIENTOS!$I$5:$I$425)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$425="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho"))+((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A13)*MOVIMIENTOS!$I$5:$I$425))</f>
         <v>1802</v>
       </c>
       <c r="I13" s="54"/>
@@ -13718,23 +14129,23 @@
         <v>46223</v>
       </c>
       <c r="B14" s="56">
-        <f>IF($A14="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A14)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A14)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A14)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A14)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A14)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A14)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A14)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A14)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A14="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A14)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A14)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A14)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A14)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A14)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A14)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A14)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A14)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>38</v>
       </c>
       <c r="C14" s="56">
-        <f>IF($A14="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A14)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A14)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A14)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A14)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A14)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A14)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A14)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A14)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A14="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A14)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A14)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A14)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A14)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A14)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A14)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A14)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A14)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>11</v>
       </c>
       <c r="D14" s="56">
-        <f>IF($A14="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A14)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A14)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A14)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A14)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A14)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A14)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A14)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A14)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A14="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A14)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A14)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A14)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A14)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A14)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A14)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A14)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A14)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>10</v>
       </c>
       <c r="E14" s="56">
-        <f>IF($A14="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A14)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A14)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A14)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A14)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A14)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A14)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A14)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A14)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A14="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A14)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A14)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A14)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A14)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A14)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A14)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A14)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A14)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>79</v>
       </c>
       <c r="F14" s="56">
-        <f>IF($A14="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A14)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A14)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A14)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A14)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A14)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A14)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A14="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A14)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A14)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A14)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A14)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A14)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A14)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>6.5</v>
       </c>
       <c r="G14" s="56">
@@ -13742,7 +14153,7 @@
         <v>138</v>
       </c>
       <c r="H14" s="56">
-        <f>IF($A14="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$421="COMPRA")+(MOVIMIENTOS!$B$5:$B$421="REPROCESO")+(MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A14)*MOVIMIENTOS!$I$5:$I$421)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$421="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$421="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho"))+((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A14)*MOVIMIENTOS!$I$5:$I$421))</f>
+        <f>IF($A14="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$425="COMPRA")+(MOVIMIENTOS!$B$5:$B$425="REPROCESO")+(MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A14)*MOVIMIENTOS!$I$5:$I$425)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$425="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho"))+((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A14)*MOVIMIENTOS!$I$5:$I$425))</f>
         <v>2533.5</v>
       </c>
       <c r="I14" s="54"/>
@@ -13764,23 +14175,23 @@
         <v>46224</v>
       </c>
       <c r="B15" s="56">
-        <f>IF($A15="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A15)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A15)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A15)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A15)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A15)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A15)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A15)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A15)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A15="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A15)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A15)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A15)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A15)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A15)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A15)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A15)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A15)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>60</v>
       </c>
       <c r="C15" s="56">
-        <f>IF($A15="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A15)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A15)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A15)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A15)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A15)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A15)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A15)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A15)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A15="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A15)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A15)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A15)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A15)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A15)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A15)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A15)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A15)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>11</v>
       </c>
       <c r="D15" s="56">
-        <f>IF($A15="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A15)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A15)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A15)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A15)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A15)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A15)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A15)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A15)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A15="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A15)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A15)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A15)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A15)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A15)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A15)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A15)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A15)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>12</v>
       </c>
       <c r="E15" s="56">
-        <f>IF($A15="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A15)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A15)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A15)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A15)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A15)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A15)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A15)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A15)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A15="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A15)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A15)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A15)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A15)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A15)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A15)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A15)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A15)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>111</v>
       </c>
       <c r="F15" s="56">
-        <f>IF($A15="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A15)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A15)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A15)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A15)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A15)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A15)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A15="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A15)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A15)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A15)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A15)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A15)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A15)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>13.5</v>
       </c>
       <c r="G15" s="56">
@@ -13788,7 +14199,7 @@
         <v>194</v>
       </c>
       <c r="H15" s="56">
-        <f>IF($A15="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$421="COMPRA")+(MOVIMIENTOS!$B$5:$B$421="REPROCESO")+(MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A15)*MOVIMIENTOS!$I$5:$I$421)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$421="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$421="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho"))+((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A15)*MOVIMIENTOS!$I$5:$I$421))</f>
+        <f>IF($A15="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$425="COMPRA")+(MOVIMIENTOS!$B$5:$B$425="REPROCESO")+(MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A15)*MOVIMIENTOS!$I$5:$I$425)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$425="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho"))+((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A15)*MOVIMIENTOS!$I$5:$I$425))</f>
         <v>745.5</v>
       </c>
       <c r="I15" s="54"/>
@@ -13810,23 +14221,23 @@
         <v>46225</v>
       </c>
       <c r="B16" s="56">
-        <f>IF($A16="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A16)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A16)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A16)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A16)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A16)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A16)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A16)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A16)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A16="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A16)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A16)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A16)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A16)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A16)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A16)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A16)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A16)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>56</v>
       </c>
       <c r="C16" s="56">
-        <f>IF($A16="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A16)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A16)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A16)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A16)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A16)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A16)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A16)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A16)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A16="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A16)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A16)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A16)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A16)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A16)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A16)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A16)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A16)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>11</v>
       </c>
       <c r="D16" s="56">
-        <f>IF($A16="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A16)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A16)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A16)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A16)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A16)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A16)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A16)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A16)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A16="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A16)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A16)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A16)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A16)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A16)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A16)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A16)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A16)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>12</v>
       </c>
       <c r="E16" s="56">
-        <f>IF($A16="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A16)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A16)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A16)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A16)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A16)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A16)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A16)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A16)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A16="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A16)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A16)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A16)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A16)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A16)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A16)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A16)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A16)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>120</v>
       </c>
       <c r="F16" s="56">
-        <f>IF($A16="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A16)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A16)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A16)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A16)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A16)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A16)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A16="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A16)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A16)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A16)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A16)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A16)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A16)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>11.5</v>
       </c>
       <c r="G16" s="56">
@@ -13834,7 +14245,7 @@
         <v>199</v>
       </c>
       <c r="H16" s="56">
-        <f>IF($A16="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$421="COMPRA")+(MOVIMIENTOS!$B$5:$B$421="REPROCESO")+(MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A16)*MOVIMIENTOS!$I$5:$I$421)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$421="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$421="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho"))+((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A16)*MOVIMIENTOS!$I$5:$I$421))</f>
+        <f>IF($A16="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$425="COMPRA")+(MOVIMIENTOS!$B$5:$B$425="REPROCESO")+(MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A16)*MOVIMIENTOS!$I$5:$I$425)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$425="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho"))+((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A16)*MOVIMIENTOS!$I$5:$I$425))</f>
         <v>3577.5</v>
       </c>
       <c r="I16" s="54"/>
@@ -13856,23 +14267,23 @@
         <v>46226</v>
       </c>
       <c r="B17" s="56">
-        <f>IF($A17="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A17)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A17)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A17)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A17)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A17)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A17)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A17)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A17)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A17="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A17)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A17)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A17)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A17)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A17)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A17)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A17)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A17)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>67</v>
       </c>
       <c r="C17" s="56">
-        <f>IF($A17="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A17)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A17)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A17)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A17)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A17)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A17)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A17)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A17)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A17="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A17)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A17)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A17)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A17)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A17)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A17)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A17)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A17)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>11</v>
       </c>
       <c r="D17" s="56">
-        <f>IF($A17="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A17)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A17)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A17)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A17)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A17)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A17)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A17)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A17)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A17="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A17)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A17)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A17)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A17)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A17)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A17)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A17)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A17)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>12</v>
       </c>
       <c r="E17" s="56">
-        <f>IF($A17="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A17)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A17)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A17)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A17)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A17)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A17)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A17)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A17)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A17="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A17)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A17)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A17)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A17)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A17)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A17)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A17)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A17)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>96</v>
       </c>
       <c r="F17" s="56">
-        <f>IF($A17="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A17)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A17)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A17)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A17)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A17)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A17)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A17="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A17)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A17)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A17)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A17)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A17)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A17)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>18</v>
       </c>
       <c r="G17" s="56">
@@ -13880,7 +14291,7 @@
         <v>186</v>
       </c>
       <c r="H17" s="56">
-        <f>IF($A17="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$421="COMPRA")+(MOVIMIENTOS!$B$5:$B$421="REPROCESO")+(MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A17)*MOVIMIENTOS!$I$5:$I$421)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$421="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$421="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho"))+((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A17)*MOVIMIENTOS!$I$5:$I$421))</f>
+        <f>IF($A17="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$425="COMPRA")+(MOVIMIENTOS!$B$5:$B$425="REPROCESO")+(MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A17)*MOVIMIENTOS!$I$5:$I$425)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$425="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho"))+((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A17)*MOVIMIENTOS!$I$5:$I$425))</f>
         <v>3414</v>
       </c>
       <c r="I17" s="54"/>
@@ -13902,23 +14313,23 @@
         <v>46227</v>
       </c>
       <c r="B18" s="56">
-        <f>IF($A18="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A18)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A18)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A18)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A18)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A18)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A18)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A18)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A18)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A18="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A18)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A18)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A18)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A18)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A18)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A18)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A18)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A18)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>48</v>
       </c>
       <c r="C18" s="56">
-        <f>IF($A18="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A18)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A18)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A18)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A18)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A18)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A18)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A18)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A18)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A18="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A18)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A18)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A18)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A18)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A18)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A18)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A18)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A18)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>3</v>
       </c>
       <c r="D18" s="56">
-        <f>IF($A18="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A18)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A18)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A18)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A18)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A18)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A18)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A18)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A18)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A18="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A18)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A18)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A18)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A18)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A18)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A18)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A18)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A18)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>5</v>
       </c>
       <c r="E18" s="56">
-        <f>IF($A18="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A18)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A18)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A18)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A18)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A18)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A18)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A18)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A18)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A18="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A18)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A18)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A18)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A18)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A18)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A18)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A18)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A18)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>73</v>
       </c>
       <c r="F18" s="56">
-        <f>IF($A18="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A18)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A18)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A18)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A18)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A18)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A18)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A18="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A18)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A18)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A18)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A18)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A18)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A18)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>14</v>
       </c>
       <c r="G18" s="56">
@@ -13926,7 +14337,7 @@
         <v>129</v>
       </c>
       <c r="H18" s="56">
-        <f>IF($A18="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$421="COMPRA")+(MOVIMIENTOS!$B$5:$B$421="REPROCESO")+(MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A18)*MOVIMIENTOS!$I$5:$I$421)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$421="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$421="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho"))+((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A18)*MOVIMIENTOS!$I$5:$I$421))</f>
+        <f>IF($A18="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$425="COMPRA")+(MOVIMIENTOS!$B$5:$B$425="REPROCESO")+(MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A18)*MOVIMIENTOS!$I$5:$I$425)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$425="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho"))+((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A18)*MOVIMIENTOS!$I$5:$I$425))</f>
         <v>3563</v>
       </c>
       <c r="I18" s="54"/>
@@ -13948,23 +14359,23 @@
         <v>46228</v>
       </c>
       <c r="B19" s="56">
-        <f>IF($A19="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A19)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A19)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A19)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A19)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A19)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A19)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A19)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A19)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A19="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A19)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A19)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A19)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A19)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A19)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A19)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A19)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A19)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>77</v>
       </c>
       <c r="C19" s="56">
-        <f>IF($A19="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A19)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A19)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A19)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A19)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A19)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A19)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A19)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A19)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A19="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A19)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A19)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A19)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A19)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A19)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A19)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A19)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A19)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>20</v>
       </c>
       <c r="D19" s="56">
-        <f>IF($A19="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A19)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A19)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A19)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A19)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A19)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A19)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A19)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A19)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A19="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A19)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A19)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A19)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A19)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A19)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A19)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A19)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A19)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>12</v>
       </c>
       <c r="E19" s="56">
-        <f>IF($A19="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A19)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A19)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A19)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A19)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A19)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A19)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A19)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A19)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A19="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A19)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A19)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A19)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A19)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A19)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A19)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A19)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A19)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>65</v>
       </c>
       <c r="F19" s="56">
-        <f>IF($A19="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A19)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A19)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A19)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A19)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A19)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A19)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A19="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A19)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A19)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A19)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A19)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A19)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A19)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>23.5</v>
       </c>
       <c r="G19" s="56">
@@ -13972,7 +14383,7 @@
         <v>174</v>
       </c>
       <c r="H19" s="56">
-        <f>IF($A19="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$421="COMPRA")+(MOVIMIENTOS!$B$5:$B$421="REPROCESO")+(MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A19)*MOVIMIENTOS!$I$5:$I$421)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$421="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$421="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho"))+((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A19)*MOVIMIENTOS!$I$5:$I$421))</f>
+        <f>IF($A19="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$425="COMPRA")+(MOVIMIENTOS!$B$5:$B$425="REPROCESO")+(MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A19)*MOVIMIENTOS!$I$5:$I$425)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$425="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho"))+((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A19)*MOVIMIENTOS!$I$5:$I$425))</f>
         <v>3062.5</v>
       </c>
       <c r="I19" s="54"/>
@@ -13994,23 +14405,23 @@
         <v>46229</v>
       </c>
       <c r="B20" s="56">
-        <f>IF($A20="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A20)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A20)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A20)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A20)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A20)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A20)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A20)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A20)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A20="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A20)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A20)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A20)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A20)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A20)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A20)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A20)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A20)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>10</v>
       </c>
       <c r="C20" s="56">
-        <f>IF($A20="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A20)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A20)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A20)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A20)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A20)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A20)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A20)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A20)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A20="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A20)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A20)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A20)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A20)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A20)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A20)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A20)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A20)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>9</v>
       </c>
       <c r="D20" s="56">
-        <f>IF($A20="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A20)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A20)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A20)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A20)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A20)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A20)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A20)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A20)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A20="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A20)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A20)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A20)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A20)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A20)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A20)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A20)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A20)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>0</v>
       </c>
       <c r="E20" s="56">
-        <f>IF($A20="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A20)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A20)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A20)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A20)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A20)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A20)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A20)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A20)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A20="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A20)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A20)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A20)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A20)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A20)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A20)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A20)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A20)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>65</v>
       </c>
       <c r="F20" s="56">
-        <f>IF($A20="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A20)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A20)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A20)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A20)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A20)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A20)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A20="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A20)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A20)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A20)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A20)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A20)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A20)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>23.5</v>
       </c>
       <c r="G20" s="56">
@@ -14018,7 +14429,7 @@
         <v>84</v>
       </c>
       <c r="H20" s="56">
-        <f>IF($A20="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$421="COMPRA")+(MOVIMIENTOS!$B$5:$B$421="REPROCESO")+(MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A20)*MOVIMIENTOS!$I$5:$I$421)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$421="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$421="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho"))+((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A20)*MOVIMIENTOS!$I$5:$I$421))</f>
+        <f>IF($A20="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$425="COMPRA")+(MOVIMIENTOS!$B$5:$B$425="REPROCESO")+(MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A20)*MOVIMIENTOS!$I$5:$I$425)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$425="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho"))+((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A20)*MOVIMIENTOS!$I$5:$I$425))</f>
         <v>1655.5</v>
       </c>
       <c r="I20" s="54"/>
@@ -14040,23 +14451,23 @@
         <v>46230</v>
       </c>
       <c r="B21" s="56">
-        <f>IF($A21="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A21)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A21)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A21)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A21)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A21)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A21)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A21)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A21)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A21="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A21)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A21)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A21)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A21)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A21)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A21)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A21)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A21)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>40</v>
       </c>
       <c r="C21" s="56">
-        <f>IF($A21="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A21)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A21)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A21)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A21)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A21)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A21)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A21)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A21)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A21="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A21)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A21)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A21)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A21)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A21)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A21)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A21)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A21)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>11</v>
       </c>
       <c r="D21" s="56">
-        <f>IF($A21="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A21)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A21)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A21)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A21)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A21)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A21)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A21)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A21)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A21="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A21)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A21)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A21)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A21)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A21)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A21)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A21)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A21)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>10</v>
       </c>
       <c r="E21" s="56">
-        <f>IF($A21="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A21)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A21)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A21)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A21)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A21)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A21)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A21)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A21)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A21="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A21)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A21)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A21)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A21)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A21)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A21)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A21)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A21)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>142</v>
       </c>
       <c r="F21" s="56">
-        <f>IF($A21="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A21)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A21)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A21)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A21)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A21)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A21)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A21="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A21)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A21)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A21)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A21)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A21)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A21)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>7</v>
       </c>
       <c r="G21" s="56">
@@ -14064,7 +14475,7 @@
         <v>203</v>
       </c>
       <c r="H21" s="56">
-        <f>IF($A21="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$421="COMPRA")+(MOVIMIENTOS!$B$5:$B$421="REPROCESO")+(MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A21)*MOVIMIENTOS!$I$5:$I$421)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$421="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$421="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho"))+((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A21)*MOVIMIENTOS!$I$5:$I$421))</f>
+        <f>IF($A21="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$425="COMPRA")+(MOVIMIENTOS!$B$5:$B$425="REPROCESO")+(MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A21)*MOVIMIENTOS!$I$5:$I$425)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$425="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho"))+((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A21)*MOVIMIENTOS!$I$5:$I$425))</f>
         <v>3958</v>
       </c>
       <c r="I21" s="54"/>
@@ -14086,23 +14497,23 @@
         <v>46231</v>
       </c>
       <c r="B22" s="56">
-        <f>IF($A22="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A22)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A22)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A22)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A22)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A22)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A22)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A22)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A22)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A22="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A22)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A22)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A22)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A22)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A22)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A22)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A22)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A22)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>106</v>
       </c>
       <c r="C22" s="56">
-        <f>IF($A22="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A22)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A22)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A22)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A22)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A22)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A22)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A22)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A22)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A22="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A22)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A22)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A22)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A22)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A22)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A22)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A22)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A22)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>4</v>
       </c>
       <c r="D22" s="56">
-        <f>IF($A22="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A22)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A22)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A22)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A22)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A22)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A22)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A22)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A22)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A22="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A22)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A22)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A22)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A22)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A22)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A22)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A22)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A22)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>12</v>
       </c>
       <c r="E22" s="56">
-        <f>IF($A22="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A22)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A22)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A22)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A22)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A22)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A22)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A22)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A22)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A22="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A22)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A22)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A22)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A22)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A22)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A22)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A22)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A22)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>118</v>
       </c>
       <c r="F22" s="56">
-        <f>IF($A22="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A22)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A22)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A22)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A22)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A22)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A22)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A22="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A22)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A22)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A22)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A22)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A22)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A22)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>21.5</v>
       </c>
       <c r="G22" s="56">
@@ -14110,7 +14521,7 @@
         <v>240</v>
       </c>
       <c r="H22" s="56">
-        <f>IF($A22="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$421="COMPRA")+(MOVIMIENTOS!$B$5:$B$421="REPROCESO")+(MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A22)*MOVIMIENTOS!$I$5:$I$421)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$421="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$421="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho"))+((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A22)*MOVIMIENTOS!$I$5:$I$421))</f>
+        <f>IF($A22="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$425="COMPRA")+(MOVIMIENTOS!$B$5:$B$425="REPROCESO")+(MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A22)*MOVIMIENTOS!$I$5:$I$425)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$425="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho"))+((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A22)*MOVIMIENTOS!$I$5:$I$425))</f>
         <v>4623.5</v>
       </c>
       <c r="I22" s="54"/>
@@ -14132,23 +14543,23 @@
         <v>46232</v>
       </c>
       <c r="B23" s="56">
-        <f>IF($A23="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A23)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A23)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A23)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A23)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A23)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A23)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A23)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A23)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A23="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A23)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A23)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A23)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A23)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A23)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A23)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A23)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A23)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>39</v>
       </c>
       <c r="C23" s="56">
-        <f>IF($A23="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A23)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A23)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A23)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A23)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A23)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A23)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A23)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A23)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A23="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A23)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A23)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A23)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A23)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A23)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A23)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A23)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A23)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>0</v>
       </c>
       <c r="D23" s="56">
-        <f>IF($A23="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A23)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A23)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A23)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A23)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A23)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A23)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A23)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A23)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A23="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A23)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A23)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A23)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A23)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A23)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A23)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A23)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A23)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>0</v>
       </c>
       <c r="E23" s="56">
-        <f>IF($A23="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A23)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A23)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A23)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A23)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A23)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A23)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A23)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A23)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A23="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A23)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A23)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A23)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A23)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A23)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A23)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A23)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A23)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>29</v>
       </c>
       <c r="F23" s="56">
-        <f>IF($A23="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A23)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A23)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A23)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A23)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A23)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A23)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A23="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A23)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A23)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A23)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A23)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A23)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A23)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>11.5</v>
       </c>
       <c r="G23" s="56">
@@ -14156,7 +14567,7 @@
         <v>68</v>
       </c>
       <c r="H23" s="56">
-        <f>IF($A23="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$421="COMPRA")+(MOVIMIENTOS!$B$5:$B$421="REPROCESO")+(MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A23)*MOVIMIENTOS!$I$5:$I$421)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$421="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$421="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho"))+((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A23)*MOVIMIENTOS!$I$5:$I$421))</f>
+        <f>IF($A23="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$425="COMPRA")+(MOVIMIENTOS!$B$5:$B$425="REPROCESO")+(MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A23)*MOVIMIENTOS!$I$5:$I$425)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$425="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho"))+((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A23)*MOVIMIENTOS!$I$5:$I$425))</f>
         <v>1829.5</v>
       </c>
       <c r="I23" s="54"/>
@@ -14178,23 +14589,23 @@
         <v>46233</v>
       </c>
       <c r="B24" s="56">
-        <f>IF($A24="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A24)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A24)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A24)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A24)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A24)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A24)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A24)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A24)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A24="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A24)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A24)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A24)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A24)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A24)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A24)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A24)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A24)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>18</v>
       </c>
       <c r="C24" s="56">
-        <f>IF($A24="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A24)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A24)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A24)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A24)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A24)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A24)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A24)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A24)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A24="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A24)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A24)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A24)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A24)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A24)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A24)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A24)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A24)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>0</v>
       </c>
       <c r="D24" s="56">
-        <f>IF($A24="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A24)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A24)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A24)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A24)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A24)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A24)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A24)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A24)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A24="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A24)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A24)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A24)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A24)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A24)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A24)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A24)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A24)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>0</v>
       </c>
       <c r="E24" s="56">
-        <f>IF($A24="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A24)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A24)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A24)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A24)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A24)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A24)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A24)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A24)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A24="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A24)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A24)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A24)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A24)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A24)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A24)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A24)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A24)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>0</v>
       </c>
       <c r="F24" s="56">
-        <f>IF($A24="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A24)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A24)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A24)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A24)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A24)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A24)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A24="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A24)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A24)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A24)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A24)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A24)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A24)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>16.5</v>
       </c>
       <c r="G24" s="56">
@@ -14202,7 +14613,7 @@
         <v>18</v>
       </c>
       <c r="H24" s="56">
-        <f>IF($A24="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$421="COMPRA")+(MOVIMIENTOS!$B$5:$B$421="REPROCESO")+(MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A24)*MOVIMIENTOS!$I$5:$I$421)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$421="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$421="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho"))+((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A24)*MOVIMIENTOS!$I$5:$I$421))</f>
+        <f>IF($A24="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$425="COMPRA")+(MOVIMIENTOS!$B$5:$B$425="REPROCESO")+(MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A24)*MOVIMIENTOS!$I$5:$I$425)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$425="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho"))+((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A24)*MOVIMIENTOS!$I$5:$I$425))</f>
         <v>960.5</v>
       </c>
       <c r="I24" s="54"/>
@@ -14224,23 +14635,23 @@
         <v>46234</v>
       </c>
       <c r="B25" s="56">
-        <f>IF($A25="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A25)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A25)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A25)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A25)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A25)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A25)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A25)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A25)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A25="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A25)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A25)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A25)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A25)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A25)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A25)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A25)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A25)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>88</v>
       </c>
       <c r="C25" s="56">
-        <f>IF($A25="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A25)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A25)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A25)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A25)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A25)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A25)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A25)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A25)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A25="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A25)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A25)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A25)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A25)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A25)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A25)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A25)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A25)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>0</v>
       </c>
       <c r="D25" s="56">
-        <f>IF($A25="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A25)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A25)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A25)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A25)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A25)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A25)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A25)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A25)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A25="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A25)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A25)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A25)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A25)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A25)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A25)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A25)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A25)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>0</v>
       </c>
       <c r="E25" s="56">
-        <f>IF($A25="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A25)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A25)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A25)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A25)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A25)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A25)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A25)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A25)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A25="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A25)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A25)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A25)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A25)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A25)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A25)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A25)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A25)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>64</v>
       </c>
       <c r="F25" s="56">
-        <f>IF($A25="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A25)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A25)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A25)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A25)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A25)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A25)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A25="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A25)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A25)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A25)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A25)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A25)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A25)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>23</v>
       </c>
       <c r="G25" s="56">
@@ -14248,7 +14659,7 @@
         <v>152</v>
       </c>
       <c r="H25" s="56">
-        <f>IF($A25="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$421="COMPRA")+(MOVIMIENTOS!$B$5:$B$421="REPROCESO")+(MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A25)*MOVIMIENTOS!$I$5:$I$421)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$421="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$421="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho"))+((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A25)*MOVIMIENTOS!$I$5:$I$421))</f>
+        <f>IF($A25="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$425="COMPRA")+(MOVIMIENTOS!$B$5:$B$425="REPROCESO")+(MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A25)*MOVIMIENTOS!$I$5:$I$425)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$425="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho"))+((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A25)*MOVIMIENTOS!$I$5:$I$425))</f>
         <v>2931</v>
       </c>
       <c r="I25" s="54"/>
@@ -14270,23 +14681,23 @@
         <v>46235</v>
       </c>
       <c r="B26" s="56">
-        <f>IF($A26="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A26)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A26)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A26)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A26)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A26)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A26)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A26)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A26)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A26="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A26)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A26)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A26)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A26)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A26)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A26)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A26)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A26)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>67</v>
       </c>
       <c r="C26" s="56">
-        <f>IF($A26="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A26)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A26)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A26)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A26)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A26)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A26)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A26)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A26)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A26="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A26)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A26)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A26)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A26)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A26)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A26)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A26)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A26)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>8</v>
       </c>
       <c r="D26" s="56">
-        <f>IF($A26="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A26)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A26)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A26)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A26)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A26)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A26)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A26)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A26)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A26="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A26)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A26)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A26)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A26)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A26)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A26)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A26)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A26)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>0</v>
       </c>
       <c r="E26" s="56">
-        <f>IF($A26="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A26)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A26)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A26)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A26)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A26)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A26)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A26)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A26)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A26="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A26)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A26)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A26)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A26)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A26)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A26)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A26)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A26)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>54</v>
       </c>
       <c r="F26" s="56">
-        <f>IF($A26="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A26)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A26)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A26)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A26)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A26)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A26)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A26="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A26)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A26)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A26)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A26)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A26)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A26)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>26</v>
       </c>
       <c r="G26" s="56">
@@ -14294,7 +14705,7 @@
         <v>129</v>
       </c>
       <c r="H26" s="56">
-        <f>IF($A26="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$421="COMPRA")+(MOVIMIENTOS!$B$5:$B$421="REPROCESO")+(MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A26)*MOVIMIENTOS!$I$5:$I$421)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$421="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$421="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho"))+((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A26)*MOVIMIENTOS!$I$5:$I$421))</f>
+        <f>IF($A26="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$425="COMPRA")+(MOVIMIENTOS!$B$5:$B$425="REPROCESO")+(MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A26)*MOVIMIENTOS!$I$5:$I$425)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$425="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho"))+((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A26)*MOVIMIENTOS!$I$5:$I$425))</f>
         <v>2716</v>
       </c>
       <c r="I26" s="54"/>
@@ -14316,23 +14727,23 @@
         <v>46236</v>
       </c>
       <c r="B27" s="56">
-        <f>IF($A27="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A27)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A27)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A27)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A27)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A27)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A27)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A27)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A27)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A27="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A27)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A27)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A27)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A27)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A27)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A27)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A27)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A27)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>98</v>
       </c>
       <c r="C27" s="56">
-        <f>IF($A27="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A27)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A27)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A27)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A27)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A27)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A27)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A27)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A27)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A27="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A27)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A27)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A27)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A27)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A27)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A27)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A27)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A27)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>11</v>
       </c>
       <c r="D27" s="56">
-        <f>IF($A27="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A27)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A27)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A27)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A27)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A27)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A27)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A27)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A27)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A27="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A27)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A27)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A27)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A27)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A27)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A27)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A27)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A27)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>11</v>
       </c>
       <c r="E27" s="56">
-        <f>IF($A27="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A27)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A27)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A27)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A27)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A27)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A27)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A27)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A27)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A27="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A27)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A27)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A27)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A27)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A27)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A27)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A27)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A27)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>174</v>
       </c>
       <c r="F27" s="56">
-        <f>IF($A27="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A27)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A27)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A27)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A27)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A27)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A27)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A27="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A27)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A27)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A27)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A27)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A27)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A27)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>19.5</v>
       </c>
       <c r="G27" s="56">
@@ -14340,7 +14751,7 @@
         <v>294</v>
       </c>
       <c r="H27" s="56">
-        <f>IF($A27="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$421="COMPRA")+(MOVIMIENTOS!$B$5:$B$421="REPROCESO")+(MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A27)*MOVIMIENTOS!$I$5:$I$421)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$421="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$421="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho"))+((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A27)*MOVIMIENTOS!$I$5:$I$421))</f>
+        <f>IF($A27="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$425="COMPRA")+(MOVIMIENTOS!$B$5:$B$425="REPROCESO")+(MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A27)*MOVIMIENTOS!$I$5:$I$425)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$425="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho"))+((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A27)*MOVIMIENTOS!$I$5:$I$425))</f>
         <v>5712.320000000007</v>
       </c>
       <c r="I27" s="54"/>
@@ -14362,23 +14773,23 @@
         <v>46237</v>
       </c>
       <c r="B28" s="56">
-        <f>IF($A28="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A28)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A28)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A28)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A28)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A28)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A28)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A28)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A28)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A28="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A28)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A28)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A28)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A28)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A28)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A28)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A28)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A28)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>51</v>
       </c>
       <c r="C28" s="56">
-        <f>IF($A28="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A28)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A28)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A28)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A28)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A28)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A28)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A28)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A28)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A28="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A28)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A28)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A28)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A28)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A28)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A28)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A28)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A28)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>0</v>
       </c>
       <c r="D28" s="56">
-        <f>IF($A28="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A28)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A28)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A28)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A28)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A28)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A28)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A28)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A28)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A28="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A28)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A28)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A28)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A28)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A28)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A28)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A28)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A28)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>0</v>
       </c>
       <c r="E28" s="56">
-        <f>IF($A28="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A28)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A28)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A28)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A28)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A28)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A28)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A28)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A28)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A28="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A28)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A28)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A28)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A28)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A28)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A28)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A28)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A28)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>56</v>
       </c>
       <c r="F28" s="56">
-        <f>IF($A28="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A28)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A28)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A28)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A28)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A28)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A28)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A28="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A28)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A28)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A28)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A28)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A28)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A28)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>19.5</v>
       </c>
       <c r="G28" s="56">
@@ -14386,7 +14797,7 @@
         <v>107</v>
       </c>
       <c r="H28" s="56">
-        <f>IF($A28="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$421="COMPRA")+(MOVIMIENTOS!$B$5:$B$421="REPROCESO")+(MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A28)*MOVIMIENTOS!$I$5:$I$421)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$421="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$421="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho"))+((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A28)*MOVIMIENTOS!$I$5:$I$421))</f>
+        <f>IF($A28="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$425="COMPRA")+(MOVIMIENTOS!$B$5:$B$425="REPROCESO")+(MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A28)*MOVIMIENTOS!$I$5:$I$425)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$425="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho"))+((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A28)*MOVIMIENTOS!$I$5:$I$425))</f>
         <v>2599.320000000007</v>
       </c>
       <c r="I28" s="54"/>
@@ -14408,23 +14819,23 @@
         <v>46238</v>
       </c>
       <c r="B29" s="56">
-        <f>IF($A29="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A29)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A29)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A29)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A29)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A29)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A29)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A29)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A29)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A29="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A29)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A29)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A29)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A29)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A29)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A29)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A29)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A29)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>21</v>
       </c>
       <c r="C29" s="56">
-        <f>IF($A29="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A29)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A29)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A29)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A29)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A29)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A29)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A29)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A29)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A29="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A29)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A29)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A29)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A29)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A29)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A29)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A29)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A29)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>0</v>
       </c>
       <c r="D29" s="56">
-        <f>IF($A29="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A29)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A29)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A29)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A29)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A29)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A29)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A29)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A29)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A29="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A29)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A29)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A29)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A29)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A29)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A29)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A29)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A29)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>0</v>
       </c>
       <c r="E29" s="56">
-        <f>IF($A29="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A29)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A29)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A29)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A29)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A29)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A29)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A29)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A29)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A29="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A29)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A29)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A29)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A29)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A29)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A29)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A29)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A29)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>16</v>
       </c>
       <c r="F29" s="56">
-        <f>IF($A29="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A29)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A29)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A29)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A29)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A29)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A29)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A29="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A29)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A29)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A29)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A29)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A29)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A29)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>31.5</v>
       </c>
       <c r="G29" s="56">
@@ -14432,7 +14843,7 @@
         <v>37</v>
       </c>
       <c r="H29" s="56">
-        <f>IF($A29="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$421="COMPRA")+(MOVIMIENTOS!$B$5:$B$421="REPROCESO")+(MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A29)*MOVIMIENTOS!$I$5:$I$421)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$421="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$421="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho"))+((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A29)*MOVIMIENTOS!$I$5:$I$421))</f>
+        <f>IF($A29="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$425="COMPRA")+(MOVIMIENTOS!$B$5:$B$425="REPROCESO")+(MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A29)*MOVIMIENTOS!$I$5:$I$425)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$425="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho"))+((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A29)*MOVIMIENTOS!$I$5:$I$425))</f>
         <v>1472.320000000007</v>
       </c>
       <c r="I29" s="54"/>
@@ -14454,23 +14865,23 @@
         <v>46239</v>
       </c>
       <c r="B30" s="56">
-        <f>IF($A30="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A30)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A30)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A30)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A30)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A30)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A30)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A30)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A30)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A30="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A30)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A30)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A30)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A30)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A30)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A30)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A30)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A30)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>50</v>
       </c>
       <c r="C30" s="56">
-        <f>IF($A30="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A30)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A30)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A30)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A30)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A30)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A30)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A30)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A30)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A30="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A30)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A30)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A30)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A30)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A30)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A30)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A30)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A30)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>11</v>
       </c>
       <c r="D30" s="56">
-        <f>IF($A30="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A30)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A30)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A30)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A30)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A30)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A30)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A30)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A30)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A30="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A30)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A30)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A30)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A30)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A30)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A30)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A30)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A30)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>12</v>
       </c>
       <c r="E30" s="56">
-        <f>IF($A30="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A30)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A30)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A30)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A30)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A30)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A30)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A30)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A30)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A30="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A30)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A30)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A30)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A30)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A30)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A30)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A30)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A30)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>65</v>
       </c>
       <c r="F30" s="56">
-        <f>IF($A30="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A30)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A30)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A30)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A30)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A30)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A30)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A30="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A30)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A30)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A30)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A30)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A30)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A30)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>17</v>
       </c>
       <c r="G30" s="56">
@@ -14478,7 +14889,7 @@
         <v>138</v>
       </c>
       <c r="H30" s="56">
-        <f>IF($A30="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$421="COMPRA")+(MOVIMIENTOS!$B$5:$B$421="REPROCESO")+(MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A30)*MOVIMIENTOS!$I$5:$I$421)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$421="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$421="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho"))+((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A30)*MOVIMIENTOS!$I$5:$I$421))</f>
+        <f>IF($A30="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$425="COMPRA")+(MOVIMIENTOS!$B$5:$B$425="REPROCESO")+(MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A30)*MOVIMIENTOS!$I$5:$I$425)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$425="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho"))+((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A30)*MOVIMIENTOS!$I$5:$I$425))</f>
         <v>2824.820000000007</v>
       </c>
       <c r="I30" s="54"/>
@@ -14500,23 +14911,23 @@
         <v>46240</v>
       </c>
       <c r="B31" s="56">
-        <f>IF($A31="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A31)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A31)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A31)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A31)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A31)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A31)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A31)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A31)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A31="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A31)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A31)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A31)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A31)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A31)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A31)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A31)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A31)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>62</v>
       </c>
       <c r="C31" s="56">
-        <f>IF($A31="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A31)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A31)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A31)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A31)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A31)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A31)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A31)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A31)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A31="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A31)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A31)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A31)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A31)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A31)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A31)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A31)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A31)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>11</v>
       </c>
       <c r="D31" s="56">
-        <f>IF($A31="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A31)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A31)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A31)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A31)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A31)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A31)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A31)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A31)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A31="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A31)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A31)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A31)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A31)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A31)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A31)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A31)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A31)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>12</v>
       </c>
       <c r="E31" s="56">
-        <f>IF($A31="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A31)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A31)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A31)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A31)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A31)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A31)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A31)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A31)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A31="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A31)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A31)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A31)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A31)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A31)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A31)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A31)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A31)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>94</v>
       </c>
       <c r="F31" s="56">
-        <f>IF($A31="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A31)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A31)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A31)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A31)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A31)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A31)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A31="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A31)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A31)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A31)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A31)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A31)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A31)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>6.5</v>
       </c>
       <c r="G31" s="56">
@@ -14524,7 +14935,7 @@
         <v>179</v>
       </c>
       <c r="H31" s="56">
-        <f>IF($A31="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$421="COMPRA")+(MOVIMIENTOS!$B$5:$B$421="REPROCESO")+(MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A31)*MOVIMIENTOS!$I$5:$I$421)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$421="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$421="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho"))+((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A31)*MOVIMIENTOS!$I$5:$I$421))</f>
+        <f>IF($A31="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$425="COMPRA")+(MOVIMIENTOS!$B$5:$B$425="REPROCESO")+(MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A31)*MOVIMIENTOS!$I$5:$I$425)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$425="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho"))+((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A31)*MOVIMIENTOS!$I$5:$I$425))</f>
         <v>3437.320000000007</v>
       </c>
       <c r="I31" s="54"/>
@@ -14546,23 +14957,23 @@
         <v>46241</v>
       </c>
       <c r="B32" s="56">
-        <f>IF($A32="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A32)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A32)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A32)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A32)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A32)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A32)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A32)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A32)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A32="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A32)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A32)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A32)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A32)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A32)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A32)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A32)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A32)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>12</v>
       </c>
       <c r="C32" s="56">
-        <f>IF($A32="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A32)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A32)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A32)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A32)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A32)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A32)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A32)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A32)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A32="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A32)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A32)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A32)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A32)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A32)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A32)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A32)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A32)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>0</v>
       </c>
       <c r="D32" s="56">
-        <f>IF($A32="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A32)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A32)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A32)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A32)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A32)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A32)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A32)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A32)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A32="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A32)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A32)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A32)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A32)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A32)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A32)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A32)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A32)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>0</v>
       </c>
       <c r="E32" s="56">
-        <f>IF($A32="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A32)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A32)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A32)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A32)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A32)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A32)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A32)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A32)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A32="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A32)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A32)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A32)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A32)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A32)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A32)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A32)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A32)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>13</v>
       </c>
       <c r="F32" s="56">
-        <f>IF($A32="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A32)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A32)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A32)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A32)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A32)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A32)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A32="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A32)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A32)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A32)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A32)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A32)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A32)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>4.5</v>
       </c>
       <c r="G32" s="56">
@@ -14570,7 +14981,7 @@
         <v>25</v>
       </c>
       <c r="H32" s="56">
-        <f>IF($A32="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$421="COMPRA")+(MOVIMIENTOS!$B$5:$B$421="REPROCESO")+(MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A32)*MOVIMIENTOS!$I$5:$I$421)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$421="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$421="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho"))+((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A32)*MOVIMIENTOS!$I$5:$I$421))</f>
+        <f>IF($A32="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$425="COMPRA")+(MOVIMIENTOS!$B$5:$B$425="REPROCESO")+(MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A32)*MOVIMIENTOS!$I$5:$I$425)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$425="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho"))+((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A32)*MOVIMIENTOS!$I$5:$I$425))</f>
         <v>800.32000000000698</v>
       </c>
       <c r="I32" s="54"/>
@@ -14592,23 +15003,23 @@
         <v>46242</v>
       </c>
       <c r="B33" s="56">
-        <f>IF($A33="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A33)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A33)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A33)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A33)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A33)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A33)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A33)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A33)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A33="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A33)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A33)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A33)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A33)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A33)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A33)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A33)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A33)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>0</v>
       </c>
       <c r="C33" s="56">
-        <f>IF($A33="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A33)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A33)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A33)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A33)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A33)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A33)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A33)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A33)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A33="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A33)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A33)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A33)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A33)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A33)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A33)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A33)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A33)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>0</v>
       </c>
       <c r="D33" s="56">
-        <f>IF($A33="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A33)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A33)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A33)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A33)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A33)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A33)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A33)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A33)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A33="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A33)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A33)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A33)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A33)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A33)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A33)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A33)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A33)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>0</v>
       </c>
       <c r="E33" s="56">
-        <f>IF($A33="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A33)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A33)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A33)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A33)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A33)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A33)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A33)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A33)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A33="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A33)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A33)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A33)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A33)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A33)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A33)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A33)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A33)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>4</v>
       </c>
       <c r="F33" s="56">
-        <f>IF($A33="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A33)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A33)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A33)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A33)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A33)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A33)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A33="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A33)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A33)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A33)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A33)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A33)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A33)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>9.5</v>
       </c>
       <c r="G33" s="56">
@@ -14616,7 +15027,7 @@
         <v>4</v>
       </c>
       <c r="H33" s="56">
-        <f>IF($A33="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$421="COMPRA")+(MOVIMIENTOS!$B$5:$B$421="REPROCESO")+(MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A33)*MOVIMIENTOS!$I$5:$I$421)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$421="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$421="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho"))+((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A33)*MOVIMIENTOS!$I$5:$I$421))</f>
+        <f>IF($A33="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$425="COMPRA")+(MOVIMIENTOS!$B$5:$B$425="REPROCESO")+(MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A33)*MOVIMIENTOS!$I$5:$I$425)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$425="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho"))+((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A33)*MOVIMIENTOS!$I$5:$I$425))</f>
         <v>345.82000000000698</v>
       </c>
       <c r="I33" s="54"/>
@@ -14638,23 +15049,23 @@
         <v>46243</v>
       </c>
       <c r="B34" s="56">
-        <f>IF($A34="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A34)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A34)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A34)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A34)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A34)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A34)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A34)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A34)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A34="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A34)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A34)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A34)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A34)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A34)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A34)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A34)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A34)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>7</v>
       </c>
       <c r="C34" s="56">
-        <f>IF($A34="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A34)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A34)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A34)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A34)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A34)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A34)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A34)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A34)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A34="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A34)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A34)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A34)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A34)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A34)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A34)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A34)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A34)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>0</v>
       </c>
       <c r="D34" s="56">
-        <f>IF($A34="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A34)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A34)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A34)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A34)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A34)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A34)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A34)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A34)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A34="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A34)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A34)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A34)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A34)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A34)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A34)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A34)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A34)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>0</v>
       </c>
       <c r="E34" s="56">
-        <f>IF($A34="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A34)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A34)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A34)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A34)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A34)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A34)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A34)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A34)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A34="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A34)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A34)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A34)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A34)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A34)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A34)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A34)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A34)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>48</v>
       </c>
       <c r="F34" s="56">
-        <f>IF($A34="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A34)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A34)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A34)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A34)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A34)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A34)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A34="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A34)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A34)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A34)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A34)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A34)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A34)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>9</v>
       </c>
       <c r="G34" s="56">
@@ -14662,7 +15073,7 @@
         <v>55</v>
       </c>
       <c r="H34" s="56">
-        <f>IF($A34="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$421="COMPRA")+(MOVIMIENTOS!$B$5:$B$421="REPROCESO")+(MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A34)*MOVIMIENTOS!$I$5:$I$421)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$421="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$421="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho"))+((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A34)*MOVIMIENTOS!$I$5:$I$421))</f>
+        <f>IF($A34="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$425="COMPRA")+(MOVIMIENTOS!$B$5:$B$425="REPROCESO")+(MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A34)*MOVIMIENTOS!$I$5:$I$425)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$425="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho"))+((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A34)*MOVIMIENTOS!$I$5:$I$425))</f>
         <v>1013.320000000007</v>
       </c>
       <c r="I34" s="54"/>
@@ -14684,23 +15095,23 @@
         <v>46244</v>
       </c>
       <c r="B35" s="56">
-        <f>IF($A35="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A35)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A35)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A35)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A35)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A35)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A35)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A35)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A35)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A35="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A35)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A35)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A35)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A35)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A35)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A35)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A35)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A35)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>68</v>
       </c>
       <c r="C35" s="56">
-        <f>IF($A35="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A35)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A35)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A35)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A35)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A35)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A35)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A35)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A35)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A35="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A35)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A35)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A35)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A35)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A35)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A35)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A35)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A35)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>11</v>
       </c>
       <c r="D35" s="56">
-        <f>IF($A35="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A35)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A35)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A35)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A35)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A35)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A35)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A35)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A35)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A35="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A35)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A35)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A35)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A35)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A35)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A35)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A35)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A35)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>9</v>
       </c>
       <c r="E35" s="56">
-        <f>IF($A35="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A35)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A35)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A35)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A35)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A35)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A35)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A35)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A35)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A35="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A35)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A35)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A35)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A35)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A35)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A35)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A35)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A35)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>62</v>
       </c>
       <c r="F35" s="56">
-        <f>IF($A35="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A35)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A35)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A35)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A35)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A35)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A35)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A35="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A35)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A35)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A35)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A35)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A35)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A35)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v>10.5</v>
       </c>
       <c r="G35" s="56">
@@ -14708,7 +15119,7 @@
         <v>150</v>
       </c>
       <c r="H35" s="56">
-        <f>IF($A35="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$421="COMPRA")+(MOVIMIENTOS!$B$5:$B$421="REPROCESO")+(MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A35)*MOVIMIENTOS!$I$5:$I$421)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$421="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$421="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho"))+((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A35)*MOVIMIENTOS!$I$5:$I$421))</f>
+        <f>IF($A35="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$425="COMPRA")+(MOVIMIENTOS!$B$5:$B$425="REPROCESO")+(MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A35)*MOVIMIENTOS!$I$5:$I$425)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$425="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho"))+((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A35)*MOVIMIENTOS!$I$5:$I$425))</f>
         <v>2469.820000000007</v>
       </c>
       <c r="I35" s="54"/>
@@ -14725,37 +15136,37 @@
       <c r="N35" s="54"/>
     </row>
     <row r="36" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="55" t="str">
+      <c r="A36" s="55">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="B36" s="56" t="str">
-        <f>IF($A36="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A36)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A36)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A36)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A36)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A36)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A36)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A36)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A36)*MOVIMIENTOS!$E$5:$E$421))</f>
-        <v/>
-      </c>
-      <c r="C36" s="56" t="str">
-        <f>IF($A36="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A36)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A36)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A36)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A36)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A36)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A36)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A36)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A36)*MOVIMIENTOS!$E$5:$E$421))</f>
-        <v/>
-      </c>
-      <c r="D36" s="56" t="str">
-        <f>IF($A36="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A36)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A36)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A36)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A36)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A36)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A36)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A36)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A36)*MOVIMIENTOS!$E$5:$E$421))</f>
-        <v/>
-      </c>
-      <c r="E36" s="56" t="str">
-        <f>IF($A36="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A36)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A36)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A36)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A36)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A36)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A36)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A36)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A36)*MOVIMIENTOS!$E$5:$E$421))</f>
-        <v/>
-      </c>
-      <c r="F36" s="56" t="str">
-        <f>IF($A36="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A36)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A36)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A36)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A36)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A36)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A36)*MOVIMIENTOS!$E$5:$E$421))</f>
-        <v/>
-      </c>
-      <c r="G36" s="56" t="str">
+        <v>46245</v>
+      </c>
+      <c r="B36" s="56">
+        <f>IF($A36="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A36)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A36)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A36)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A36)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A36)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A36)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A36)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A36)*MOVIMIENTOS!$E$5:$E$425))</f>
+        <v>0</v>
+      </c>
+      <c r="C36" s="56">
+        <f>IF($A36="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A36)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A36)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A36)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A36)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A36)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A36)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A36)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A36)*MOVIMIENTOS!$E$5:$E$425))</f>
+        <v>0</v>
+      </c>
+      <c r="D36" s="56">
+        <f>IF($A36="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A36)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A36)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A36)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A36)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A36)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A36)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A36)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A36)*MOVIMIENTOS!$E$5:$E$425))</f>
+        <v>0</v>
+      </c>
+      <c r="E36" s="56">
+        <f>IF($A36="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A36)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A36)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A36)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A36)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A36)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A36)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A36)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A36)*MOVIMIENTOS!$E$5:$E$425))</f>
+        <v>0</v>
+      </c>
+      <c r="F36" s="56">
+        <f>IF($A36="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A36)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A36)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A36)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A36)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A36)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A36)*MOVIMIENTOS!$E$5:$E$425))</f>
+        <v>0</v>
+      </c>
+      <c r="G36" s="56">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="H36" s="56" t="str">
-        <f>IF($A36="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$421="COMPRA")+(MOVIMIENTOS!$B$5:$B$421="REPROCESO")+(MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A36)*MOVIMIENTOS!$I$5:$I$421)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$421="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$421="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho"))+((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A36)*MOVIMIENTOS!$I$5:$I$421))</f>
-        <v/>
+        <v>0</v>
+      </c>
+      <c r="H36" s="56">
+        <f>IF($A36="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$425="COMPRA")+(MOVIMIENTOS!$B$5:$B$425="REPROCESO")+(MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A36)*MOVIMIENTOS!$I$5:$I$425)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$425="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho"))+((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A36)*MOVIMIENTOS!$I$5:$I$425))</f>
+        <v>-569.17999999999302</v>
       </c>
       <c r="I36" s="54"/>
       <c r="J36" s="54" t="str">
@@ -14771,37 +15182,37 @@
       <c r="N36" s="54"/>
     </row>
     <row r="37" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="55" t="str">
+      <c r="A37" s="55">
         <f t="shared" ref="A37:A69" si="2">IFERROR(INDEX(K$5:K$400,MATCH(ROW()-4,J$5:J$400,0)),"")</f>
-        <v/>
-      </c>
-      <c r="B37" s="56" t="str">
-        <f>IF($A37="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A37)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A37)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A37)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A37)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A37)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A37)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A37)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A37)*MOVIMIENTOS!$E$5:$E$421))</f>
-        <v/>
-      </c>
-      <c r="C37" s="56" t="str">
-        <f>IF($A37="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A37)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A37)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A37)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A37)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A37)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A37)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A37)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A37)*MOVIMIENTOS!$E$5:$E$421))</f>
-        <v/>
-      </c>
-      <c r="D37" s="56" t="str">
-        <f>IF($A37="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A37)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A37)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A37)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A37)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A37)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A37)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A37)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A37)*MOVIMIENTOS!$E$5:$E$421))</f>
-        <v/>
-      </c>
-      <c r="E37" s="56" t="str">
-        <f>IF($A37="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A37)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A37)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A37)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A37)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A37)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A37)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A37)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A37)*MOVIMIENTOS!$E$5:$E$421))</f>
-        <v/>
-      </c>
-      <c r="F37" s="56" t="str">
-        <f>IF($A37="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A37)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A37)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A37)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A37)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A37)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A37)*MOVIMIENTOS!$E$5:$E$421))</f>
-        <v/>
-      </c>
-      <c r="G37" s="56" t="str">
+        <v>46246</v>
+      </c>
+      <c r="B37" s="56">
+        <f>IF($A37="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A37)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A37)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A37)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A37)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A37)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A37)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A37)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A37)*MOVIMIENTOS!$E$5:$E$425))</f>
+        <v>0</v>
+      </c>
+      <c r="C37" s="56">
+        <f>IF($A37="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A37)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A37)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A37)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A37)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A37)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A37)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A37)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A37)*MOVIMIENTOS!$E$5:$E$425))</f>
+        <v>0</v>
+      </c>
+      <c r="D37" s="56">
+        <f>IF($A37="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A37)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A37)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A37)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A37)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A37)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A37)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A37)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A37)*MOVIMIENTOS!$E$5:$E$425))</f>
+        <v>0</v>
+      </c>
+      <c r="E37" s="56">
+        <f>IF($A37="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A37)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A37)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A37)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A37)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A37)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A37)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A37)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A37)*MOVIMIENTOS!$E$5:$E$425))</f>
+        <v>0</v>
+      </c>
+      <c r="F37" s="56">
+        <f>IF($A37="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A37)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A37)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A37)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A37)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A37)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A37)*MOVIMIENTOS!$E$5:$E$425))</f>
+        <v>5</v>
+      </c>
+      <c r="G37" s="56">
         <f t="shared" ref="G37:G69" si="3">IF($A37="","",SUM(B37:E37))</f>
-        <v/>
-      </c>
-      <c r="H37" s="56" t="str">
-        <f>IF($A37="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$421="COMPRA")+(MOVIMIENTOS!$B$5:$B$421="REPROCESO")+(MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A37)*MOVIMIENTOS!$I$5:$I$421)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$421="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$421="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho"))+((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A37)*MOVIMIENTOS!$I$5:$I$421))</f>
-        <v/>
+        <v>0</v>
+      </c>
+      <c r="H37" s="56">
+        <f>IF($A37="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$425="COMPRA")+(MOVIMIENTOS!$B$5:$B$425="REPROCESO")+(MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A37)*MOVIMIENTOS!$I$5:$I$425)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$425="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho"))+((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A37)*MOVIMIENTOS!$I$5:$I$425))</f>
+        <v>-1680.179999999993</v>
       </c>
       <c r="I37" s="54"/>
       <c r="J37" s="54" t="str">
@@ -14817,37 +15228,37 @@
       <c r="N37" s="54"/>
     </row>
     <row r="38" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="55" t="str">
+      <c r="A38" s="55">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="B38" s="56" t="str">
-        <f>IF($A38="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A38)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A38)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A38)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A38)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A38)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A38)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A38)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A38)*MOVIMIENTOS!$E$5:$E$421))</f>
-        <v/>
-      </c>
-      <c r="C38" s="56" t="str">
-        <f>IF($A38="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A38)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A38)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A38)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A38)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A38)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A38)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A38)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A38)*MOVIMIENTOS!$E$5:$E$421))</f>
-        <v/>
-      </c>
-      <c r="D38" s="56" t="str">
-        <f>IF($A38="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A38)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A38)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A38)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A38)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A38)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A38)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A38)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A38)*MOVIMIENTOS!$E$5:$E$421))</f>
-        <v/>
-      </c>
-      <c r="E38" s="56" t="str">
-        <f>IF($A38="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A38)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A38)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A38)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A38)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A38)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A38)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A38)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A38)*MOVIMIENTOS!$E$5:$E$421))</f>
-        <v/>
-      </c>
-      <c r="F38" s="56" t="str">
-        <f>IF($A38="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A38)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A38)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A38)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A38)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A38)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A38)*MOVIMIENTOS!$E$5:$E$421))</f>
-        <v/>
-      </c>
-      <c r="G38" s="56" t="str">
+        <v>46247</v>
+      </c>
+      <c r="B38" s="56">
+        <f>IF($A38="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A38)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A38)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A38)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A38)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A38)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A38)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A38)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A38)*MOVIMIENTOS!$E$5:$E$425))</f>
+        <v>0</v>
+      </c>
+      <c r="C38" s="56">
+        <f>IF($A38="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A38)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A38)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A38)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A38)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A38)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A38)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A38)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A38)*MOVIMIENTOS!$E$5:$E$425))</f>
+        <v>0</v>
+      </c>
+      <c r="D38" s="56">
+        <f>IF($A38="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A38)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A38)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A38)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A38)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A38)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A38)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A38)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A38)*MOVIMIENTOS!$E$5:$E$425))</f>
+        <v>0</v>
+      </c>
+      <c r="E38" s="56">
+        <f>IF($A38="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A38)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A38)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A38)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A38)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A38)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A38)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A38)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A38)*MOVIMIENTOS!$E$5:$E$425))</f>
+        <v>0</v>
+      </c>
+      <c r="F38" s="56">
+        <f>IF($A38="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A38)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A38)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A38)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A38)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A38)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A38)*MOVIMIENTOS!$E$5:$E$425))</f>
+        <v>8</v>
+      </c>
+      <c r="G38" s="56">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="H38" s="56" t="str">
-        <f>IF($A38="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$421="COMPRA")+(MOVIMIENTOS!$B$5:$B$421="REPROCESO")+(MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A38)*MOVIMIENTOS!$I$5:$I$421)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$421="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$421="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho"))+((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A38)*MOVIMIENTOS!$I$5:$I$421))</f>
-        <v/>
+        <v>0</v>
+      </c>
+      <c r="H38" s="56">
+        <f>IF($A38="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$425="COMPRA")+(MOVIMIENTOS!$B$5:$B$425="REPROCESO")+(MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A38)*MOVIMIENTOS!$I$5:$I$425)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$425="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho"))+((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A38)*MOVIMIENTOS!$I$5:$I$425))</f>
+        <v>-1019.179999999993</v>
       </c>
       <c r="I38" s="54"/>
       <c r="J38" s="54" t="str">
@@ -14868,23 +15279,23 @@
         <v/>
       </c>
       <c r="B39" s="56" t="str">
-        <f>IF($A39="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A39)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A39)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A39)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A39)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A39)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A39)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A39)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A39)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A39="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A39)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A39)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A39)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A39)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A39)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A39)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A39)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A39)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="C39" s="56" t="str">
-        <f>IF($A39="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A39)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A39)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A39)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A39)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A39)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A39)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A39)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A39)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A39="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A39)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A39)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A39)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A39)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A39)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A39)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A39)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A39)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="D39" s="56" t="str">
-        <f>IF($A39="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A39)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A39)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A39)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A39)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A39)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A39)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A39)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A39)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A39="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A39)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A39)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A39)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A39)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A39)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A39)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A39)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A39)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="E39" s="56" t="str">
-        <f>IF($A39="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A39)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A39)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A39)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A39)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A39)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A39)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A39)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A39)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A39="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A39)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A39)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A39)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A39)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A39)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A39)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A39)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A39)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="F39" s="56" t="str">
-        <f>IF($A39="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A39)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A39)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A39)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A39)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A39)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A39)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A39="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A39)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A39)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A39)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A39)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A39)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A39)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="G39" s="56" t="str">
@@ -14892,7 +15303,7 @@
         <v/>
       </c>
       <c r="H39" s="56" t="str">
-        <f>IF($A39="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$421="COMPRA")+(MOVIMIENTOS!$B$5:$B$421="REPROCESO")+(MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A39)*MOVIMIENTOS!$I$5:$I$421)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$421="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$421="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho"))+((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A39)*MOVIMIENTOS!$I$5:$I$421))</f>
+        <f>IF($A39="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$425="COMPRA")+(MOVIMIENTOS!$B$5:$B$425="REPROCESO")+(MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A39)*MOVIMIENTOS!$I$5:$I$425)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$425="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho"))+((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A39)*MOVIMIENTOS!$I$5:$I$425))</f>
         <v/>
       </c>
       <c r="I39" s="54"/>
@@ -14914,23 +15325,23 @@
         <v/>
       </c>
       <c r="B40" s="56" t="str">
-        <f>IF($A40="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A40)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A40)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A40)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A40)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A40)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A40)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A40)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A40)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A40="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A40)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A40)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A40)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A40)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A40)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A40)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A40)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A40)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="C40" s="56" t="str">
-        <f>IF($A40="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A40)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A40)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A40)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A40)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A40)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A40)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A40)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A40)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A40="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A40)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A40)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A40)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A40)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A40)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A40)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A40)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A40)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="D40" s="56" t="str">
-        <f>IF($A40="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A40)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A40)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A40)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A40)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A40)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A40)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A40)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A40)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A40="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A40)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A40)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A40)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A40)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A40)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A40)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A40)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A40)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="E40" s="56" t="str">
-        <f>IF($A40="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A40)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A40)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A40)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A40)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A40)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A40)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A40)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A40)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A40="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A40)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A40)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A40)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A40)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A40)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A40)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A40)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A40)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="F40" s="56" t="str">
-        <f>IF($A40="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A40)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A40)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A40)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A40)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A40)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A40)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A40="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A40)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A40)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A40)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A40)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A40)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A40)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="G40" s="56" t="str">
@@ -14938,7 +15349,7 @@
         <v/>
       </c>
       <c r="H40" s="56" t="str">
-        <f>IF($A40="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$421="COMPRA")+(MOVIMIENTOS!$B$5:$B$421="REPROCESO")+(MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A40)*MOVIMIENTOS!$I$5:$I$421)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$421="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$421="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho"))+((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A40)*MOVIMIENTOS!$I$5:$I$421))</f>
+        <f>IF($A40="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$425="COMPRA")+(MOVIMIENTOS!$B$5:$B$425="REPROCESO")+(MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A40)*MOVIMIENTOS!$I$5:$I$425)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$425="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho"))+((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A40)*MOVIMIENTOS!$I$5:$I$425))</f>
         <v/>
       </c>
       <c r="I40" s="54"/>
@@ -14960,23 +15371,23 @@
         <v/>
       </c>
       <c r="B41" s="56" t="str">
-        <f>IF($A41="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A41)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A41)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A41)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A41)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A41)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A41)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A41)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A41)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A41="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A41)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A41)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A41)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A41)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A41)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A41)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A41)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A41)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="C41" s="56" t="str">
-        <f>IF($A41="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A41)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A41)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A41)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A41)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A41)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A41)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A41)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A41)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A41="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A41)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A41)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A41)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A41)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A41)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A41)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A41)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A41)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="D41" s="56" t="str">
-        <f>IF($A41="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A41)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A41)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A41)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A41)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A41)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A41)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A41)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A41)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A41="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A41)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A41)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A41)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A41)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A41)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A41)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A41)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A41)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="E41" s="56" t="str">
-        <f>IF($A41="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A41)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A41)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A41)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A41)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A41)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A41)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A41)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A41)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A41="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A41)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A41)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A41)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A41)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A41)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A41)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A41)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A41)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="F41" s="56" t="str">
-        <f>IF($A41="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A41)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A41)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A41)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A41)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A41)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A41)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A41="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A41)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A41)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A41)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A41)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A41)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A41)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="G41" s="56" t="str">
@@ -14984,7 +15395,7 @@
         <v/>
       </c>
       <c r="H41" s="56" t="str">
-        <f>IF($A41="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$421="COMPRA")+(MOVIMIENTOS!$B$5:$B$421="REPROCESO")+(MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A41)*MOVIMIENTOS!$I$5:$I$421)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$421="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$421="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho"))+((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A41)*MOVIMIENTOS!$I$5:$I$421))</f>
+        <f>IF($A41="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$425="COMPRA")+(MOVIMIENTOS!$B$5:$B$425="REPROCESO")+(MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A41)*MOVIMIENTOS!$I$5:$I$425)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$425="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho"))+((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A41)*MOVIMIENTOS!$I$5:$I$425))</f>
         <v/>
       </c>
       <c r="I41" s="54"/>
@@ -15006,23 +15417,23 @@
         <v/>
       </c>
       <c r="B42" s="56" t="str">
-        <f>IF($A42="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A42)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A42)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A42)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A42)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A42)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A42)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A42)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A42)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A42="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A42)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A42)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A42)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A42)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A42)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A42)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A42)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A42)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="C42" s="56" t="str">
-        <f>IF($A42="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A42)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A42)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A42)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A42)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A42)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A42)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A42)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A42)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A42="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A42)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A42)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A42)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A42)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A42)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A42)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A42)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A42)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="D42" s="56" t="str">
-        <f>IF($A42="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A42)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A42)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A42)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A42)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A42)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A42)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A42)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A42)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A42="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A42)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A42)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A42)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A42)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A42)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A42)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A42)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A42)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="E42" s="56" t="str">
-        <f>IF($A42="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A42)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A42)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A42)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A42)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A42)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A42)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A42)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A42)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A42="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A42)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A42)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A42)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A42)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A42)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A42)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A42)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A42)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="F42" s="56" t="str">
-        <f>IF($A42="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A42)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A42)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A42)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A42)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A42)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A42)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A42="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A42)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A42)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A42)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A42)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A42)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A42)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="G42" s="56" t="str">
@@ -15030,7 +15441,7 @@
         <v/>
       </c>
       <c r="H42" s="56" t="str">
-        <f>IF($A42="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$421="COMPRA")+(MOVIMIENTOS!$B$5:$B$421="REPROCESO")+(MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A42)*MOVIMIENTOS!$I$5:$I$421)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$421="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$421="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho"))+((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A42)*MOVIMIENTOS!$I$5:$I$421))</f>
+        <f>IF($A42="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$425="COMPRA")+(MOVIMIENTOS!$B$5:$B$425="REPROCESO")+(MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A42)*MOVIMIENTOS!$I$5:$I$425)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$425="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho"))+((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A42)*MOVIMIENTOS!$I$5:$I$425))</f>
         <v/>
       </c>
       <c r="I42" s="54"/>
@@ -15052,23 +15463,23 @@
         <v/>
       </c>
       <c r="B43" s="56" t="str">
-        <f>IF($A43="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A43)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A43)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A43)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A43)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A43)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A43)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A43)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A43)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A43="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A43)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A43)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A43)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A43)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A43)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A43)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A43)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A43)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="C43" s="56" t="str">
-        <f>IF($A43="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A43)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A43)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A43)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A43)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A43)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A43)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A43)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A43)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A43="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A43)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A43)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A43)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A43)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A43)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A43)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A43)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A43)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="D43" s="56" t="str">
-        <f>IF($A43="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A43)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A43)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A43)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A43)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A43)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A43)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A43)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A43)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A43="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A43)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A43)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A43)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A43)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A43)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A43)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A43)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A43)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="E43" s="56" t="str">
-        <f>IF($A43="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A43)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A43)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A43)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A43)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A43)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A43)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A43)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A43)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A43="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A43)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A43)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A43)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A43)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A43)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A43)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A43)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A43)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="F43" s="56" t="str">
-        <f>IF($A43="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A43)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A43)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A43)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A43)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A43)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A43)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A43="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A43)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A43)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A43)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A43)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A43)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A43)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="G43" s="56" t="str">
@@ -15076,7 +15487,7 @@
         <v/>
       </c>
       <c r="H43" s="56" t="str">
-        <f>IF($A43="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$421="COMPRA")+(MOVIMIENTOS!$B$5:$B$421="REPROCESO")+(MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A43)*MOVIMIENTOS!$I$5:$I$421)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$421="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$421="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho"))+((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A43)*MOVIMIENTOS!$I$5:$I$421))</f>
+        <f>IF($A43="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$425="COMPRA")+(MOVIMIENTOS!$B$5:$B$425="REPROCESO")+(MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A43)*MOVIMIENTOS!$I$5:$I$425)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$425="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho"))+((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A43)*MOVIMIENTOS!$I$5:$I$425))</f>
         <v/>
       </c>
       <c r="I43" s="54"/>
@@ -15098,23 +15509,23 @@
         <v/>
       </c>
       <c r="B44" s="56" t="str">
-        <f>IF($A44="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A44)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A44)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A44)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A44)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A44)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A44)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A44)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A44)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A44="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A44)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A44)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A44)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A44)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A44)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A44)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A44)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A44)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="C44" s="56" t="str">
-        <f>IF($A44="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A44)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A44)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A44)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A44)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A44)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A44)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A44)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A44)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A44="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A44)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A44)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A44)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A44)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A44)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A44)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A44)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A44)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="D44" s="56" t="str">
-        <f>IF($A44="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A44)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A44)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A44)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A44)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A44)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A44)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A44)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A44)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A44="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A44)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A44)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A44)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A44)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A44)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A44)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A44)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A44)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="E44" s="56" t="str">
-        <f>IF($A44="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A44)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A44)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A44)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A44)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A44)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A44)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A44)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A44)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A44="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A44)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A44)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A44)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A44)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A44)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A44)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A44)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A44)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="F44" s="56" t="str">
-        <f>IF($A44="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A44)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A44)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A44)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A44)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A44)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A44)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A44="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A44)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A44)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A44)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A44)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A44)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A44)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="G44" s="56" t="str">
@@ -15122,7 +15533,7 @@
         <v/>
       </c>
       <c r="H44" s="56" t="str">
-        <f>IF($A44="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$421="COMPRA")+(MOVIMIENTOS!$B$5:$B$421="REPROCESO")+(MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A44)*MOVIMIENTOS!$I$5:$I$421)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$421="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$421="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho"))+((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A44)*MOVIMIENTOS!$I$5:$I$421))</f>
+        <f>IF($A44="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$425="COMPRA")+(MOVIMIENTOS!$B$5:$B$425="REPROCESO")+(MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A44)*MOVIMIENTOS!$I$5:$I$425)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$425="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho"))+((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A44)*MOVIMIENTOS!$I$5:$I$425))</f>
         <v/>
       </c>
       <c r="I44" s="54"/>
@@ -15144,23 +15555,23 @@
         <v/>
       </c>
       <c r="B45" s="56" t="str">
-        <f>IF($A45="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A45)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A45)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A45)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A45)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A45)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A45)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A45)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A45)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A45="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A45)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A45)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A45)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A45)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A45)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A45)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A45)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A45)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="C45" s="56" t="str">
-        <f>IF($A45="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A45)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A45)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A45)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A45)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A45)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A45)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A45)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A45)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A45="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A45)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A45)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A45)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A45)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A45)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A45)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A45)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A45)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="D45" s="56" t="str">
-        <f>IF($A45="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A45)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A45)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A45)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A45)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A45)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A45)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A45)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A45)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A45="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A45)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A45)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A45)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A45)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A45)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A45)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A45)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A45)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="E45" s="56" t="str">
-        <f>IF($A45="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A45)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A45)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A45)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A45)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A45)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A45)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A45)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A45)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A45="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A45)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A45)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A45)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A45)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A45)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A45)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A45)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A45)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="F45" s="56" t="str">
-        <f>IF($A45="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A45)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A45)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A45)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A45)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A45)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A45)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A45="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A45)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A45)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A45)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A45)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A45)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A45)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="G45" s="56" t="str">
@@ -15168,7 +15579,7 @@
         <v/>
       </c>
       <c r="H45" s="56" t="str">
-        <f>IF($A45="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$421="COMPRA")+(MOVIMIENTOS!$B$5:$B$421="REPROCESO")+(MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A45)*MOVIMIENTOS!$I$5:$I$421)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$421="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$421="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho"))+((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A45)*MOVIMIENTOS!$I$5:$I$421))</f>
+        <f>IF($A45="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$425="COMPRA")+(MOVIMIENTOS!$B$5:$B$425="REPROCESO")+(MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A45)*MOVIMIENTOS!$I$5:$I$425)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$425="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho"))+((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A45)*MOVIMIENTOS!$I$5:$I$425))</f>
         <v/>
       </c>
       <c r="I45" s="54"/>
@@ -15190,23 +15601,23 @@
         <v/>
       </c>
       <c r="B46" s="56" t="str">
-        <f>IF($A46="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A46)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A46)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A46)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A46)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A46)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A46)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A46)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A46)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A46="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A46)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A46)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A46)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A46)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A46)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A46)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A46)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A46)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="C46" s="56" t="str">
-        <f>IF($A46="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A46)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A46)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A46)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A46)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A46)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A46)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A46)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A46)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A46="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A46)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A46)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A46)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A46)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A46)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A46)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A46)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A46)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="D46" s="56" t="str">
-        <f>IF($A46="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A46)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A46)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A46)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A46)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A46)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A46)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A46)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A46)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A46="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A46)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A46)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A46)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A46)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A46)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A46)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A46)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A46)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="E46" s="56" t="str">
-        <f>IF($A46="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A46)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A46)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A46)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A46)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A46)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A46)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A46)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A46)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A46="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A46)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A46)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A46)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A46)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A46)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A46)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A46)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A46)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="F46" s="56" t="str">
-        <f>IF($A46="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A46)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A46)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A46)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A46)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A46)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A46)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A46="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A46)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A46)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A46)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A46)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A46)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A46)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="G46" s="56" t="str">
@@ -15214,7 +15625,7 @@
         <v/>
       </c>
       <c r="H46" s="56" t="str">
-        <f>IF($A46="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$421="COMPRA")+(MOVIMIENTOS!$B$5:$B$421="REPROCESO")+(MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A46)*MOVIMIENTOS!$I$5:$I$421)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$421="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$421="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho"))+((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A46)*MOVIMIENTOS!$I$5:$I$421))</f>
+        <f>IF($A46="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$425="COMPRA")+(MOVIMIENTOS!$B$5:$B$425="REPROCESO")+(MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A46)*MOVIMIENTOS!$I$5:$I$425)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$425="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho"))+((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A46)*MOVIMIENTOS!$I$5:$I$425))</f>
         <v/>
       </c>
       <c r="I46" s="54"/>
@@ -15236,23 +15647,23 @@
         <v/>
       </c>
       <c r="B47" s="56" t="str">
-        <f>IF($A47="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A47)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A47)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A47)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A47)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A47)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A47)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A47)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A47)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A47="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A47)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A47)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A47)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A47)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A47)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A47)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A47)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A47)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="C47" s="56" t="str">
-        <f>IF($A47="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A47)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A47)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A47)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A47)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A47)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A47)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A47)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A47)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A47="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A47)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A47)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A47)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A47)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A47)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A47)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A47)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A47)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="D47" s="56" t="str">
-        <f>IF($A47="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A47)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A47)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A47)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A47)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A47)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A47)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A47)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A47)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A47="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A47)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A47)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A47)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A47)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A47)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A47)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A47)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A47)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="E47" s="56" t="str">
-        <f>IF($A47="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A47)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A47)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A47)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A47)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A47)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A47)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A47)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A47)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A47="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A47)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A47)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A47)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A47)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A47)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A47)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A47)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A47)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="F47" s="56" t="str">
-        <f>IF($A47="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A47)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A47)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A47)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A47)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A47)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A47)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A47="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A47)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A47)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A47)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A47)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A47)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A47)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="G47" s="56" t="str">
@@ -15260,7 +15671,7 @@
         <v/>
       </c>
       <c r="H47" s="56" t="str">
-        <f>IF($A47="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$421="COMPRA")+(MOVIMIENTOS!$B$5:$B$421="REPROCESO")+(MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A47)*MOVIMIENTOS!$I$5:$I$421)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$421="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$421="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho"))+((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A47)*MOVIMIENTOS!$I$5:$I$421))</f>
+        <f>IF($A47="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$425="COMPRA")+(MOVIMIENTOS!$B$5:$B$425="REPROCESO")+(MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A47)*MOVIMIENTOS!$I$5:$I$425)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$425="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho"))+((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A47)*MOVIMIENTOS!$I$5:$I$425))</f>
         <v/>
       </c>
       <c r="I47" s="54"/>
@@ -15282,23 +15693,23 @@
         <v/>
       </c>
       <c r="B48" s="56" t="str">
-        <f>IF($A48="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A48)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A48)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A48)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A48)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A48)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A48)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A48)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A48)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A48="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A48)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A48)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A48)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A48)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A48)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A48)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A48)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A48)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="C48" s="56" t="str">
-        <f>IF($A48="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A48)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A48)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A48)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A48)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A48)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A48)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A48)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A48)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A48="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A48)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A48)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A48)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A48)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A48)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A48)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A48)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A48)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="D48" s="56" t="str">
-        <f>IF($A48="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A48)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A48)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A48)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A48)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A48)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A48)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A48)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A48)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A48="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A48)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A48)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A48)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A48)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A48)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A48)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A48)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A48)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="E48" s="56" t="str">
-        <f>IF($A48="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A48)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A48)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A48)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A48)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A48)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A48)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A48)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A48)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A48="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A48)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A48)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A48)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A48)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A48)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A48)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A48)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A48)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="F48" s="56" t="str">
-        <f>IF($A48="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A48)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A48)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A48)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A48)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A48)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A48)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A48="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A48)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A48)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A48)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A48)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A48)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A48)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="G48" s="56" t="str">
@@ -15306,7 +15717,7 @@
         <v/>
       </c>
       <c r="H48" s="56" t="str">
-        <f>IF($A48="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$421="COMPRA")+(MOVIMIENTOS!$B$5:$B$421="REPROCESO")+(MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A48)*MOVIMIENTOS!$I$5:$I$421)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$421="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$421="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho"))+((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A48)*MOVIMIENTOS!$I$5:$I$421))</f>
+        <f>IF($A48="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$425="COMPRA")+(MOVIMIENTOS!$B$5:$B$425="REPROCESO")+(MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A48)*MOVIMIENTOS!$I$5:$I$425)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$425="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho"))+((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A48)*MOVIMIENTOS!$I$5:$I$425))</f>
         <v/>
       </c>
       <c r="I48" s="54"/>
@@ -15328,23 +15739,23 @@
         <v/>
       </c>
       <c r="B49" s="56" t="str">
-        <f>IF($A49="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A49)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A49)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A49)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A49)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A49)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A49)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A49)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A49)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A49="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A49)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A49)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A49)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A49)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A49)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A49)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A49)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A49)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="C49" s="56" t="str">
-        <f>IF($A49="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A49)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A49)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A49)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A49)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A49)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A49)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A49)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A49)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A49="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A49)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A49)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A49)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A49)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A49)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A49)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A49)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A49)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="D49" s="56" t="str">
-        <f>IF($A49="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A49)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A49)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A49)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A49)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A49)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A49)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A49)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A49)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A49="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A49)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A49)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A49)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A49)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A49)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A49)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A49)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A49)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="E49" s="56" t="str">
-        <f>IF($A49="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A49)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A49)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A49)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A49)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A49)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A49)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A49)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A49)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A49="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A49)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A49)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A49)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A49)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A49)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A49)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A49)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A49)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="F49" s="56" t="str">
-        <f>IF($A49="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A49)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A49)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A49)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A49)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A49)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A49)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A49="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A49)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A49)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A49)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A49)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A49)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A49)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="G49" s="56" t="str">
@@ -15352,7 +15763,7 @@
         <v/>
       </c>
       <c r="H49" s="56" t="str">
-        <f>IF($A49="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$421="COMPRA")+(MOVIMIENTOS!$B$5:$B$421="REPROCESO")+(MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A49)*MOVIMIENTOS!$I$5:$I$421)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$421="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$421="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho"))+((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A49)*MOVIMIENTOS!$I$5:$I$421))</f>
+        <f>IF($A49="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$425="COMPRA")+(MOVIMIENTOS!$B$5:$B$425="REPROCESO")+(MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A49)*MOVIMIENTOS!$I$5:$I$425)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$425="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho"))+((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A49)*MOVIMIENTOS!$I$5:$I$425))</f>
         <v/>
       </c>
       <c r="I49" s="54"/>
@@ -15374,23 +15785,23 @@
         <v/>
       </c>
       <c r="B50" s="56" t="str">
-        <f>IF($A50="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A50)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A50)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A50)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A50)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A50)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A50)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A50)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A50)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A50="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A50)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A50)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A50)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A50)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A50)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A50)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A50)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A50)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="C50" s="56" t="str">
-        <f>IF($A50="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A50)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A50)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A50)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A50)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A50)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A50)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A50)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A50)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A50="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A50)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A50)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A50)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A50)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A50)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A50)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A50)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A50)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="D50" s="56" t="str">
-        <f>IF($A50="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A50)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A50)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A50)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A50)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A50)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A50)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A50)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A50)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A50="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A50)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A50)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A50)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A50)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A50)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A50)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A50)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A50)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="E50" s="56" t="str">
-        <f>IF($A50="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A50)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A50)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A50)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A50)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A50)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A50)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A50)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A50)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A50="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A50)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A50)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A50)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A50)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A50)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A50)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A50)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A50)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="F50" s="56" t="str">
-        <f>IF($A50="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A50)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A50)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A50)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A50)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A50)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A50)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A50="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A50)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A50)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A50)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A50)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A50)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A50)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="G50" s="56" t="str">
@@ -15398,7 +15809,7 @@
         <v/>
       </c>
       <c r="H50" s="56" t="str">
-        <f>IF($A50="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$421="COMPRA")+(MOVIMIENTOS!$B$5:$B$421="REPROCESO")+(MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A50)*MOVIMIENTOS!$I$5:$I$421)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$421="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$421="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho"))+((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A50)*MOVIMIENTOS!$I$5:$I$421))</f>
+        <f>IF($A50="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$425="COMPRA")+(MOVIMIENTOS!$B$5:$B$425="REPROCESO")+(MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A50)*MOVIMIENTOS!$I$5:$I$425)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$425="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho"))+((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A50)*MOVIMIENTOS!$I$5:$I$425))</f>
         <v/>
       </c>
       <c r="I50" s="54"/>
@@ -15420,23 +15831,23 @@
         <v/>
       </c>
       <c r="B51" s="56" t="str">
-        <f>IF($A51="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A51)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A51)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A51)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A51)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A51)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A51)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A51)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A51)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A51="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A51)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A51)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A51)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A51)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A51)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A51)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A51)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A51)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="C51" s="56" t="str">
-        <f>IF($A51="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A51)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A51)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A51)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A51)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A51)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A51)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A51)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A51)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A51="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A51)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A51)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A51)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A51)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A51)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A51)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A51)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A51)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="D51" s="56" t="str">
-        <f>IF($A51="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A51)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A51)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A51)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A51)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A51)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A51)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A51)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A51)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A51="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A51)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A51)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A51)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A51)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A51)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A51)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A51)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A51)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="E51" s="56" t="str">
-        <f>IF($A51="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A51)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A51)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A51)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A51)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A51)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A51)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A51)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A51)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A51="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A51)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A51)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A51)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A51)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A51)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A51)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A51)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A51)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="F51" s="56" t="str">
-        <f>IF($A51="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A51)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A51)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A51)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A51)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A51)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A51)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A51="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A51)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A51)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A51)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A51)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A51)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A51)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="G51" s="56" t="str">
@@ -15444,7 +15855,7 @@
         <v/>
       </c>
       <c r="H51" s="56" t="str">
-        <f>IF($A51="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$421="COMPRA")+(MOVIMIENTOS!$B$5:$B$421="REPROCESO")+(MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A51)*MOVIMIENTOS!$I$5:$I$421)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$421="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$421="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho"))+((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A51)*MOVIMIENTOS!$I$5:$I$421))</f>
+        <f>IF($A51="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$425="COMPRA")+(MOVIMIENTOS!$B$5:$B$425="REPROCESO")+(MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A51)*MOVIMIENTOS!$I$5:$I$425)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$425="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho"))+((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A51)*MOVIMIENTOS!$I$5:$I$425))</f>
         <v/>
       </c>
       <c r="I51" s="54"/>
@@ -15466,23 +15877,23 @@
         <v/>
       </c>
       <c r="B52" s="56" t="str">
-        <f>IF($A52="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A52)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A52)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A52)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A52)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A52)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A52)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A52)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A52)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A52="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A52)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A52)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A52)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A52)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A52)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A52)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A52)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A52)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="C52" s="56" t="str">
-        <f>IF($A52="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A52)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A52)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A52)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A52)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A52)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A52)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A52)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A52)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A52="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A52)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A52)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A52)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A52)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A52)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A52)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A52)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A52)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="D52" s="56" t="str">
-        <f>IF($A52="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A52)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A52)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A52)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A52)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A52)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A52)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A52)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A52)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A52="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A52)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A52)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A52)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A52)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A52)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A52)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A52)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A52)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="E52" s="56" t="str">
-        <f>IF($A52="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A52)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A52)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A52)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A52)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A52)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A52)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A52)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A52)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A52="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A52)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A52)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A52)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A52)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A52)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A52)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A52)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A52)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="F52" s="56" t="str">
-        <f>IF($A52="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A52)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A52)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A52)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A52)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A52)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A52)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A52="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A52)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A52)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A52)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A52)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A52)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A52)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="G52" s="56" t="str">
@@ -15490,7 +15901,7 @@
         <v/>
       </c>
       <c r="H52" s="56" t="str">
-        <f>IF($A52="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$421="COMPRA")+(MOVIMIENTOS!$B$5:$B$421="REPROCESO")+(MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A52)*MOVIMIENTOS!$I$5:$I$421)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$421="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$421="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho"))+((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A52)*MOVIMIENTOS!$I$5:$I$421))</f>
+        <f>IF($A52="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$425="COMPRA")+(MOVIMIENTOS!$B$5:$B$425="REPROCESO")+(MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A52)*MOVIMIENTOS!$I$5:$I$425)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$425="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho"))+((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A52)*MOVIMIENTOS!$I$5:$I$425))</f>
         <v/>
       </c>
       <c r="I52" s="54"/>
@@ -15512,23 +15923,23 @@
         <v/>
       </c>
       <c r="B53" s="56" t="str">
-        <f>IF($A53="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A53)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A53)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A53)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A53)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A53)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A53)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A53)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A53)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A53="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A53)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A53)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A53)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A53)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A53)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A53)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A53)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A53)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="C53" s="56" t="str">
-        <f>IF($A53="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A53)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A53)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A53)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A53)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A53)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A53)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A53)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A53)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A53="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A53)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A53)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A53)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A53)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A53)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A53)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A53)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A53)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="D53" s="56" t="str">
-        <f>IF($A53="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A53)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A53)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A53)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A53)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A53)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A53)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A53)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A53)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A53="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A53)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A53)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A53)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A53)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A53)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A53)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A53)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A53)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="E53" s="56" t="str">
-        <f>IF($A53="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A53)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A53)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A53)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A53)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A53)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A53)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A53)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A53)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A53="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A53)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A53)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A53)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A53)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A53)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A53)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A53)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A53)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="F53" s="56" t="str">
-        <f>IF($A53="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A53)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A53)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A53)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A53)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A53)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A53)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A53="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A53)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A53)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A53)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A53)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A53)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A53)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="G53" s="56" t="str">
@@ -15536,7 +15947,7 @@
         <v/>
       </c>
       <c r="H53" s="56" t="str">
-        <f>IF($A53="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$421="COMPRA")+(MOVIMIENTOS!$B$5:$B$421="REPROCESO")+(MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A53)*MOVIMIENTOS!$I$5:$I$421)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$421="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$421="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho"))+((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A53)*MOVIMIENTOS!$I$5:$I$421))</f>
+        <f>IF($A53="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$425="COMPRA")+(MOVIMIENTOS!$B$5:$B$425="REPROCESO")+(MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A53)*MOVIMIENTOS!$I$5:$I$425)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$425="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho"))+((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A53)*MOVIMIENTOS!$I$5:$I$425))</f>
         <v/>
       </c>
       <c r="I53" s="54"/>
@@ -15558,23 +15969,23 @@
         <v/>
       </c>
       <c r="B54" s="56" t="str">
-        <f>IF($A54="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A54)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A54)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A54)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A54)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A54)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A54)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A54)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A54)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A54="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A54)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A54)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A54)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A54)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A54)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A54)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A54)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A54)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="C54" s="56" t="str">
-        <f>IF($A54="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A54)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A54)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A54)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A54)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A54)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A54)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A54)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A54)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A54="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A54)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A54)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A54)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A54)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A54)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A54)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A54)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A54)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="D54" s="56" t="str">
-        <f>IF($A54="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A54)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A54)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A54)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A54)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A54)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A54)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A54)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A54)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A54="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A54)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A54)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A54)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A54)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A54)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A54)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A54)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A54)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="E54" s="56" t="str">
-        <f>IF($A54="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A54)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A54)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A54)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A54)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A54)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A54)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A54)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A54)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A54="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A54)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A54)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A54)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A54)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A54)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A54)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A54)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A54)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="F54" s="56" t="str">
-        <f>IF($A54="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A54)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A54)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A54)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A54)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A54)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A54)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A54="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A54)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A54)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A54)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A54)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A54)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A54)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="G54" s="56" t="str">
@@ -15582,7 +15993,7 @@
         <v/>
       </c>
       <c r="H54" s="56" t="str">
-        <f>IF($A54="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$421="COMPRA")+(MOVIMIENTOS!$B$5:$B$421="REPROCESO")+(MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A54)*MOVIMIENTOS!$I$5:$I$421)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$421="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$421="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho"))+((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A54)*MOVIMIENTOS!$I$5:$I$421))</f>
+        <f>IF($A54="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$425="COMPRA")+(MOVIMIENTOS!$B$5:$B$425="REPROCESO")+(MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A54)*MOVIMIENTOS!$I$5:$I$425)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$425="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho"))+((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A54)*MOVIMIENTOS!$I$5:$I$425))</f>
         <v/>
       </c>
       <c r="I54" s="54"/>
@@ -15604,23 +16015,23 @@
         <v/>
       </c>
       <c r="B55" s="56" t="str">
-        <f>IF($A55="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A55)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A55)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A55)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A55)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A55)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A55)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A55)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A55)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A55="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A55)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A55)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A55)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A55)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A55)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A55)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A55)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A55)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="C55" s="56" t="str">
-        <f>IF($A55="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A55)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A55)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A55)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A55)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A55)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A55)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A55)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A55)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A55="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A55)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A55)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A55)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A55)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A55)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A55)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A55)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A55)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="D55" s="56" t="str">
-        <f>IF($A55="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A55)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A55)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A55)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A55)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A55)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A55)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A55)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A55)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A55="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A55)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A55)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A55)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A55)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A55)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A55)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A55)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A55)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="E55" s="56" t="str">
-        <f>IF($A55="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A55)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A55)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A55)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A55)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A55)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A55)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A55)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A55)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A55="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A55)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A55)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A55)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A55)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A55)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A55)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A55)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A55)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="F55" s="56" t="str">
-        <f>IF($A55="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A55)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A55)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A55)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A55)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A55)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A55)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A55="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A55)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A55)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A55)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A55)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A55)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A55)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="G55" s="56" t="str">
@@ -15628,7 +16039,7 @@
         <v/>
       </c>
       <c r="H55" s="56" t="str">
-        <f>IF($A55="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$421="COMPRA")+(MOVIMIENTOS!$B$5:$B$421="REPROCESO")+(MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A55)*MOVIMIENTOS!$I$5:$I$421)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$421="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$421="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho"))+((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A55)*MOVIMIENTOS!$I$5:$I$421))</f>
+        <f>IF($A55="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$425="COMPRA")+(MOVIMIENTOS!$B$5:$B$425="REPROCESO")+(MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A55)*MOVIMIENTOS!$I$5:$I$425)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$425="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho"))+((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A55)*MOVIMIENTOS!$I$5:$I$425))</f>
         <v/>
       </c>
       <c r="I55" s="54"/>
@@ -15650,23 +16061,23 @@
         <v/>
       </c>
       <c r="B56" s="56" t="str">
-        <f>IF($A56="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A56)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A56)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A56)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A56)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A56)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A56)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A56)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A56)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A56="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A56)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A56)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A56)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A56)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A56)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A56)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A56)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A56)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="C56" s="56" t="str">
-        <f>IF($A56="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A56)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A56)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A56)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A56)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A56)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A56)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A56)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A56)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A56="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A56)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A56)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A56)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A56)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A56)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A56)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A56)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A56)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="D56" s="56" t="str">
-        <f>IF($A56="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A56)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A56)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A56)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A56)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A56)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A56)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A56)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A56)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A56="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A56)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A56)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A56)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A56)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A56)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A56)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A56)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A56)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="E56" s="56" t="str">
-        <f>IF($A56="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A56)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A56)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A56)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A56)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A56)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A56)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A56)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A56)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A56="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A56)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A56)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A56)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A56)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A56)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A56)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A56)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A56)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="F56" s="56" t="str">
-        <f>IF($A56="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A56)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A56)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A56)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A56)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A56)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A56)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A56="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A56)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A56)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A56)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A56)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A56)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A56)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="G56" s="56" t="str">
@@ -15674,7 +16085,7 @@
         <v/>
       </c>
       <c r="H56" s="56" t="str">
-        <f>IF($A56="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$421="COMPRA")+(MOVIMIENTOS!$B$5:$B$421="REPROCESO")+(MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A56)*MOVIMIENTOS!$I$5:$I$421)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$421="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$421="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho"))+((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A56)*MOVIMIENTOS!$I$5:$I$421))</f>
+        <f>IF($A56="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$425="COMPRA")+(MOVIMIENTOS!$B$5:$B$425="REPROCESO")+(MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A56)*MOVIMIENTOS!$I$5:$I$425)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$425="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho"))+((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A56)*MOVIMIENTOS!$I$5:$I$425))</f>
         <v/>
       </c>
       <c r="I56" s="54"/>
@@ -15696,23 +16107,23 @@
         <v/>
       </c>
       <c r="B57" s="56" t="str">
-        <f>IF($A57="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A57)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A57)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A57)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A57)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A57)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A57)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A57)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A57)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A57="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A57)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A57)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A57)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A57)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A57)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A57)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A57)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A57)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="C57" s="56" t="str">
-        <f>IF($A57="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A57)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A57)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A57)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A57)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A57)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A57)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A57)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A57)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A57="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A57)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A57)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A57)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A57)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A57)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A57)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A57)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A57)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="D57" s="56" t="str">
-        <f>IF($A57="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A57)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A57)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A57)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A57)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A57)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A57)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A57)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A57)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A57="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A57)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A57)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A57)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A57)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A57)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A57)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A57)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A57)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="E57" s="56" t="str">
-        <f>IF($A57="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A57)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A57)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A57)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A57)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A57)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A57)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A57)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A57)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A57="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A57)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A57)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A57)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A57)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A57)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A57)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A57)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A57)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="F57" s="56" t="str">
-        <f>IF($A57="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A57)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A57)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A57)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A57)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A57)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A57)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A57="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A57)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A57)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A57)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A57)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A57)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A57)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="G57" s="56" t="str">
@@ -15720,7 +16131,7 @@
         <v/>
       </c>
       <c r="H57" s="56" t="str">
-        <f>IF($A57="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$421="COMPRA")+(MOVIMIENTOS!$B$5:$B$421="REPROCESO")+(MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A57)*MOVIMIENTOS!$I$5:$I$421)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$421="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$421="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho"))+((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A57)*MOVIMIENTOS!$I$5:$I$421))</f>
+        <f>IF($A57="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$425="COMPRA")+(MOVIMIENTOS!$B$5:$B$425="REPROCESO")+(MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A57)*MOVIMIENTOS!$I$5:$I$425)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$425="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho"))+((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A57)*MOVIMIENTOS!$I$5:$I$425))</f>
         <v/>
       </c>
       <c r="I57" s="54"/>
@@ -15742,23 +16153,23 @@
         <v/>
       </c>
       <c r="B58" s="56" t="str">
-        <f>IF($A58="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A58)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A58)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A58)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A58)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A58)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A58)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A58)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A58)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A58="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A58)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A58)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A58)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A58)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A58)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A58)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A58)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A58)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="C58" s="56" t="str">
-        <f>IF($A58="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A58)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A58)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A58)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A58)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A58)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A58)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A58)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A58)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A58="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A58)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A58)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A58)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A58)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A58)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A58)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A58)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A58)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="D58" s="56" t="str">
-        <f>IF($A58="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A58)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A58)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A58)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A58)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A58)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A58)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A58)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A58)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A58="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A58)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A58)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A58)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A58)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A58)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A58)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A58)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A58)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="E58" s="56" t="str">
-        <f>IF($A58="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A58)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A58)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A58)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A58)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A58)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A58)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A58)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A58)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A58="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A58)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A58)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A58)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A58)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A58)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A58)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A58)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A58)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="F58" s="56" t="str">
-        <f>IF($A58="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A58)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A58)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A58)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A58)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A58)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A58)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A58="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A58)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A58)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A58)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A58)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A58)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A58)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="G58" s="56" t="str">
@@ -15766,7 +16177,7 @@
         <v/>
       </c>
       <c r="H58" s="56" t="str">
-        <f>IF($A58="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$421="COMPRA")+(MOVIMIENTOS!$B$5:$B$421="REPROCESO")+(MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A58)*MOVIMIENTOS!$I$5:$I$421)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$421="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$421="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho"))+((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A58)*MOVIMIENTOS!$I$5:$I$421))</f>
+        <f>IF($A58="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$425="COMPRA")+(MOVIMIENTOS!$B$5:$B$425="REPROCESO")+(MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A58)*MOVIMIENTOS!$I$5:$I$425)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$425="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho"))+((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A58)*MOVIMIENTOS!$I$5:$I$425))</f>
         <v/>
       </c>
       <c r="I58" s="54"/>
@@ -15788,23 +16199,23 @@
         <v/>
       </c>
       <c r="B59" s="56" t="str">
-        <f>IF($A59="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A59)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A59)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A59)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A59)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A59)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A59)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A59)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A59)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A59="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A59)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A59)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A59)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A59)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A59)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A59)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A59)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A59)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="C59" s="56" t="str">
-        <f>IF($A59="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A59)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A59)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A59)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A59)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A59)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A59)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A59)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A59)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A59="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A59)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A59)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A59)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A59)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A59)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A59)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A59)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A59)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="D59" s="56" t="str">
-        <f>IF($A59="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A59)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A59)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A59)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A59)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A59)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A59)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A59)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A59)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A59="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A59)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A59)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A59)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A59)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A59)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A59)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A59)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A59)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="E59" s="56" t="str">
-        <f>IF($A59="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A59)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A59)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A59)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A59)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A59)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A59)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A59)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A59)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A59="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A59)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A59)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A59)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A59)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A59)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A59)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A59)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A59)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="F59" s="56" t="str">
-        <f>IF($A59="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A59)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A59)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A59)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A59)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A59)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A59)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A59="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A59)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A59)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A59)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A59)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A59)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A59)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="G59" s="56" t="str">
@@ -15812,7 +16223,7 @@
         <v/>
       </c>
       <c r="H59" s="56" t="str">
-        <f>IF($A59="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$421="COMPRA")+(MOVIMIENTOS!$B$5:$B$421="REPROCESO")+(MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A59)*MOVIMIENTOS!$I$5:$I$421)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$421="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$421="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho"))+((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A59)*MOVIMIENTOS!$I$5:$I$421))</f>
+        <f>IF($A59="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$425="COMPRA")+(MOVIMIENTOS!$B$5:$B$425="REPROCESO")+(MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A59)*MOVIMIENTOS!$I$5:$I$425)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$425="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho"))+((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A59)*MOVIMIENTOS!$I$5:$I$425))</f>
         <v/>
       </c>
       <c r="I59" s="54"/>
@@ -15834,23 +16245,23 @@
         <v/>
       </c>
       <c r="B60" s="56" t="str">
-        <f>IF($A60="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A60)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A60)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A60)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A60)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A60)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A60)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A60)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A60)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A60="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A60)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A60)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A60)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A60)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A60)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A60)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A60)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A60)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="C60" s="56" t="str">
-        <f>IF($A60="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A60)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A60)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A60)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A60)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A60)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A60)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A60)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A60)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A60="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A60)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A60)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A60)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A60)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A60)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A60)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A60)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A60)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="D60" s="56" t="str">
-        <f>IF($A60="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A60)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A60)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A60)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A60)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A60)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A60)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A60)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A60)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A60="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A60)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A60)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A60)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A60)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A60)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A60)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A60)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A60)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="E60" s="56" t="str">
-        <f>IF($A60="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A60)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A60)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A60)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A60)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A60)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A60)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A60)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A60)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A60="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A60)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A60)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A60)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A60)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A60)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A60)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A60)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A60)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="F60" s="56" t="str">
-        <f>IF($A60="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A60)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A60)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A60)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A60)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A60)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A60)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A60="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A60)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A60)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A60)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A60)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A60)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A60)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="G60" s="56" t="str">
@@ -15858,7 +16269,7 @@
         <v/>
       </c>
       <c r="H60" s="56" t="str">
-        <f>IF($A60="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$421="COMPRA")+(MOVIMIENTOS!$B$5:$B$421="REPROCESO")+(MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A60)*MOVIMIENTOS!$I$5:$I$421)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$421="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$421="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho"))+((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A60)*MOVIMIENTOS!$I$5:$I$421))</f>
+        <f>IF($A60="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$425="COMPRA")+(MOVIMIENTOS!$B$5:$B$425="REPROCESO")+(MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A60)*MOVIMIENTOS!$I$5:$I$425)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$425="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho"))+((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A60)*MOVIMIENTOS!$I$5:$I$425))</f>
         <v/>
       </c>
       <c r="I60" s="54"/>
@@ -15880,23 +16291,23 @@
         <v/>
       </c>
       <c r="B61" s="56" t="str">
-        <f>IF($A61="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A61)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A61)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A61)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A61)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A61)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A61)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A61)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A61)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A61="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A61)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A61)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A61)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A61)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A61)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A61)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A61)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A61)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="C61" s="56" t="str">
-        <f>IF($A61="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A61)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A61)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A61)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A61)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A61)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A61)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A61)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A61)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A61="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A61)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A61)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A61)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A61)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A61)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A61)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A61)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A61)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="D61" s="56" t="str">
-        <f>IF($A61="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A61)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A61)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A61)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A61)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A61)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A61)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A61)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A61)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A61="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A61)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A61)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A61)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A61)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A61)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A61)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A61)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A61)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="E61" s="56" t="str">
-        <f>IF($A61="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A61)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A61)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A61)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A61)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A61)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A61)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A61)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A61)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A61="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A61)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A61)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A61)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A61)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A61)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A61)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A61)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A61)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="F61" s="56" t="str">
-        <f>IF($A61="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A61)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A61)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A61)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A61)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A61)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A61)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A61="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A61)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A61)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A61)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A61)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A61)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A61)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="G61" s="56" t="str">
@@ -15904,7 +16315,7 @@
         <v/>
       </c>
       <c r="H61" s="56" t="str">
-        <f>IF($A61="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$421="COMPRA")+(MOVIMIENTOS!$B$5:$B$421="REPROCESO")+(MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A61)*MOVIMIENTOS!$I$5:$I$421)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$421="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$421="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho"))+((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A61)*MOVIMIENTOS!$I$5:$I$421))</f>
+        <f>IF($A61="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$425="COMPRA")+(MOVIMIENTOS!$B$5:$B$425="REPROCESO")+(MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A61)*MOVIMIENTOS!$I$5:$I$425)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$425="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho"))+((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A61)*MOVIMIENTOS!$I$5:$I$425))</f>
         <v/>
       </c>
       <c r="I61" s="54"/>
@@ -15926,23 +16337,23 @@
         <v/>
       </c>
       <c r="B62" s="56" t="str">
-        <f>IF($A62="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A62)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A62)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A62)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A62)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A62)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A62)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A62)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A62)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A62="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A62)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A62)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A62)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A62)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A62)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A62)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A62)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A62)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="C62" s="56" t="str">
-        <f>IF($A62="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A62)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A62)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A62)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A62)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A62)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A62)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A62)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A62)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A62="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A62)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A62)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A62)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A62)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A62)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A62)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A62)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A62)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="D62" s="56" t="str">
-        <f>IF($A62="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A62)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A62)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A62)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A62)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A62)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A62)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A62)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A62)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A62="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A62)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A62)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A62)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A62)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A62)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A62)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A62)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A62)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="E62" s="56" t="str">
-        <f>IF($A62="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A62)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A62)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A62)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A62)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A62)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A62)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A62)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A62)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A62="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A62)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A62)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A62)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A62)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A62)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A62)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A62)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A62)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="F62" s="56" t="str">
-        <f>IF($A62="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A62)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A62)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A62)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A62)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A62)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A62)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A62="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A62)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A62)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A62)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A62)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A62)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A62)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="G62" s="56" t="str">
@@ -15950,7 +16361,7 @@
         <v/>
       </c>
       <c r="H62" s="56" t="str">
-        <f>IF($A62="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$421="COMPRA")+(MOVIMIENTOS!$B$5:$B$421="REPROCESO")+(MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A62)*MOVIMIENTOS!$I$5:$I$421)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$421="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$421="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho"))+((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A62)*MOVIMIENTOS!$I$5:$I$421))</f>
+        <f>IF($A62="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$425="COMPRA")+(MOVIMIENTOS!$B$5:$B$425="REPROCESO")+(MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A62)*MOVIMIENTOS!$I$5:$I$425)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$425="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho"))+((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A62)*MOVIMIENTOS!$I$5:$I$425))</f>
         <v/>
       </c>
       <c r="I62" s="54"/>
@@ -15972,23 +16383,23 @@
         <v/>
       </c>
       <c r="B63" s="56" t="str">
-        <f>IF($A63="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A63)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A63)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A63)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A63)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A63)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A63)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A63)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A63)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A63="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A63)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A63)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A63)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A63)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A63)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A63)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A63)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A63)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="C63" s="56" t="str">
-        <f>IF($A63="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A63)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A63)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A63)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A63)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A63)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A63)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A63)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A63)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A63="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A63)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A63)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A63)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A63)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A63)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A63)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A63)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A63)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="D63" s="56" t="str">
-        <f>IF($A63="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A63)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A63)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A63)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A63)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A63)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A63)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A63)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A63)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A63="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A63)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A63)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A63)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A63)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A63)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A63)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A63)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A63)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="E63" s="56" t="str">
-        <f>IF($A63="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A63)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A63)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A63)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A63)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A63)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A63)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A63)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A63)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A63="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A63)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A63)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A63)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A63)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A63)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A63)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A63)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A63)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="F63" s="56" t="str">
-        <f>IF($A63="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A63)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A63)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A63)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A63)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A63)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A63)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A63="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A63)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A63)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A63)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A63)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A63)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A63)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="G63" s="56" t="str">
@@ -15996,7 +16407,7 @@
         <v/>
       </c>
       <c r="H63" s="56" t="str">
-        <f>IF($A63="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$421="COMPRA")+(MOVIMIENTOS!$B$5:$B$421="REPROCESO")+(MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A63)*MOVIMIENTOS!$I$5:$I$421)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$421="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$421="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho"))+((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A63)*MOVIMIENTOS!$I$5:$I$421))</f>
+        <f>IF($A63="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$425="COMPRA")+(MOVIMIENTOS!$B$5:$B$425="REPROCESO")+(MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A63)*MOVIMIENTOS!$I$5:$I$425)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$425="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho"))+((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A63)*MOVIMIENTOS!$I$5:$I$425))</f>
         <v/>
       </c>
       <c r="I63" s="54"/>
@@ -16018,23 +16429,23 @@
         <v/>
       </c>
       <c r="B64" s="56" t="str">
-        <f>IF($A64="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A64)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A64)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A64)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A64)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A64)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A64)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A64)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A64)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A64="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A64)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A64)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A64)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A64)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A64)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A64)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A64)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A64)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="C64" s="56" t="str">
-        <f>IF($A64="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A64)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A64)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A64)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A64)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A64)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A64)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A64)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A64)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A64="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A64)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A64)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A64)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A64)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A64)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A64)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A64)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A64)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="D64" s="56" t="str">
-        <f>IF($A64="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A64)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A64)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A64)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A64)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A64)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A64)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A64)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A64)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A64="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A64)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A64)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A64)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A64)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A64)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A64)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A64)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A64)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="E64" s="56" t="str">
-        <f>IF($A64="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A64)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A64)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A64)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A64)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A64)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A64)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A64)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A64)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A64="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A64)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A64)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A64)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A64)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A64)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A64)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A64)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A64)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="F64" s="56" t="str">
-        <f>IF($A64="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A64)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A64)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A64)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A64)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A64)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A64)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A64="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A64)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A64)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A64)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A64)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A64)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A64)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="G64" s="56" t="str">
@@ -16042,7 +16453,7 @@
         <v/>
       </c>
       <c r="H64" s="56" t="str">
-        <f>IF($A64="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$421="COMPRA")+(MOVIMIENTOS!$B$5:$B$421="REPROCESO")+(MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A64)*MOVIMIENTOS!$I$5:$I$421)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$421="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$421="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho"))+((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A64)*MOVIMIENTOS!$I$5:$I$421))</f>
+        <f>IF($A64="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$425="COMPRA")+(MOVIMIENTOS!$B$5:$B$425="REPROCESO")+(MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A64)*MOVIMIENTOS!$I$5:$I$425)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$425="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho"))+((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A64)*MOVIMIENTOS!$I$5:$I$425))</f>
         <v/>
       </c>
       <c r="I64" s="54"/>
@@ -16064,23 +16475,23 @@
         <v/>
       </c>
       <c r="B65" s="56" t="str">
-        <f>IF($A65="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A65)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A65)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A65)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A65)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A65)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A65)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A65)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A65)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A65="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A65)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A65)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A65)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A65)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A65)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A65)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A65)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A65)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="C65" s="56" t="str">
-        <f>IF($A65="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A65)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A65)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A65)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A65)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A65)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A65)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A65)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A65)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A65="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A65)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A65)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A65)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A65)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A65)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A65)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A65)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A65)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="D65" s="56" t="str">
-        <f>IF($A65="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A65)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A65)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A65)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A65)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A65)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A65)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A65)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A65)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A65="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A65)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A65)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A65)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A65)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A65)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A65)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A65)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A65)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="E65" s="56" t="str">
-        <f>IF($A65="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A65)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A65)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A65)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A65)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A65)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A65)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A65)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A65)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A65="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A65)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A65)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A65)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A65)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A65)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A65)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A65)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A65)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="F65" s="56" t="str">
-        <f>IF($A65="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A65)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A65)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A65)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A65)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A65)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A65)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A65="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A65)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A65)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A65)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A65)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A65)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A65)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="G65" s="56" t="str">
@@ -16088,7 +16499,7 @@
         <v/>
       </c>
       <c r="H65" s="56" t="str">
-        <f>IF($A65="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$421="COMPRA")+(MOVIMIENTOS!$B$5:$B$421="REPROCESO")+(MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A65)*MOVIMIENTOS!$I$5:$I$421)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$421="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$421="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho"))+((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A65)*MOVIMIENTOS!$I$5:$I$421))</f>
+        <f>IF($A65="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$425="COMPRA")+(MOVIMIENTOS!$B$5:$B$425="REPROCESO")+(MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A65)*MOVIMIENTOS!$I$5:$I$425)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$425="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho"))+((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A65)*MOVIMIENTOS!$I$5:$I$425))</f>
         <v/>
       </c>
       <c r="I65" s="54"/>
@@ -16110,23 +16521,23 @@
         <v/>
       </c>
       <c r="B66" s="56" t="str">
-        <f>IF($A66="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A66)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A66)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A66)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A66)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A66)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A66)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A66)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A66)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A66="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A66)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A66)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A66)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A66)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A66)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A66)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A66)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A66)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="C66" s="56" t="str">
-        <f>IF($A66="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A66)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A66)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A66)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A66)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A66)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A66)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A66)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A66)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A66="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A66)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A66)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A66)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A66)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A66)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A66)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A66)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A66)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="D66" s="56" t="str">
-        <f>IF($A66="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A66)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A66)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A66)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A66)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A66)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A66)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A66)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A66)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A66="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A66)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A66)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A66)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A66)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A66)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A66)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A66)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A66)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="E66" s="56" t="str">
-        <f>IF($A66="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A66)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A66)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A66)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A66)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A66)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A66)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A66)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A66)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A66="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A66)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A66)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A66)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A66)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A66)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A66)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A66)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A66)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="F66" s="56" t="str">
-        <f>IF($A66="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A66)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A66)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A66)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A66)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A66)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A66)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A66="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A66)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A66)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A66)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A66)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A66)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A66)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="G66" s="56" t="str">
@@ -16134,7 +16545,7 @@
         <v/>
       </c>
       <c r="H66" s="56" t="str">
-        <f>IF($A66="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$421="COMPRA")+(MOVIMIENTOS!$B$5:$B$421="REPROCESO")+(MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A66)*MOVIMIENTOS!$I$5:$I$421)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$421="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$421="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho"))+((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A66)*MOVIMIENTOS!$I$5:$I$421))</f>
+        <f>IF($A66="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$425="COMPRA")+(MOVIMIENTOS!$B$5:$B$425="REPROCESO")+(MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A66)*MOVIMIENTOS!$I$5:$I$425)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$425="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho"))+((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A66)*MOVIMIENTOS!$I$5:$I$425))</f>
         <v/>
       </c>
       <c r="I66" s="54"/>
@@ -16156,23 +16567,23 @@
         <v/>
       </c>
       <c r="B67" s="56" t="str">
-        <f>IF($A67="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A67)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A67)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A67)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A67)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A67)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A67)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A67)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A67)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A67="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A67)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A67)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A67)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A67)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A67)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A67)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A67)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A67)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="C67" s="56" t="str">
-        <f>IF($A67="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A67)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A67)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A67)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A67)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A67)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A67)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A67)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A67)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A67="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A67)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A67)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A67)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A67)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A67)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A67)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A67)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A67)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="D67" s="56" t="str">
-        <f>IF($A67="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A67)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A67)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A67)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A67)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A67)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A67)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A67)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A67)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A67="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A67)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A67)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A67)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A67)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A67)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A67)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A67)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A67)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="E67" s="56" t="str">
-        <f>IF($A67="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A67)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A67)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A67)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A67)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A67)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A67)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A67)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A67)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A67="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A67)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A67)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A67)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A67)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A67)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A67)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A67)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A67)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="F67" s="56" t="str">
-        <f>IF($A67="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A67)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A67)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A67)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A67)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A67)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A67)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A67="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A67)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A67)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A67)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A67)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A67)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A67)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="G67" s="56" t="str">
@@ -16180,7 +16591,7 @@
         <v/>
       </c>
       <c r="H67" s="56" t="str">
-        <f>IF($A67="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$421="COMPRA")+(MOVIMIENTOS!$B$5:$B$421="REPROCESO")+(MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A67)*MOVIMIENTOS!$I$5:$I$421)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$421="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$421="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho"))+((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A67)*MOVIMIENTOS!$I$5:$I$421))</f>
+        <f>IF($A67="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$425="COMPRA")+(MOVIMIENTOS!$B$5:$B$425="REPROCESO")+(MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A67)*MOVIMIENTOS!$I$5:$I$425)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$425="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho"))+((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A67)*MOVIMIENTOS!$I$5:$I$425))</f>
         <v/>
       </c>
       <c r="I67" s="54"/>
@@ -16202,23 +16613,23 @@
         <v/>
       </c>
       <c r="B68" s="56" t="str">
-        <f>IF($A68="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A68)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A68)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A68)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A68)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A68)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A68)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A68)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A68)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A68="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A68)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A68)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A68)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A68)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A68)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A68)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A68)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A68)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="C68" s="56" t="str">
-        <f>IF($A68="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A68)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A68)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A68)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A68)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A68)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A68)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A68)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A68)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A68="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A68)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A68)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A68)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A68)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A68)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A68)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A68)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A68)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="D68" s="56" t="str">
-        <f>IF($A68="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A68)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A68)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A68)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A68)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A68)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A68)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A68)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A68)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A68="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A68)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A68)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A68)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A68)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A68)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A68)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A68)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A68)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="E68" s="56" t="str">
-        <f>IF($A68="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A68)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A68)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A68)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A68)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A68)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A68)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A68)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A68)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A68="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A68)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A68)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A68)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A68)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A68)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A68)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A68)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A68)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="F68" s="56" t="str">
-        <f>IF($A68="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A68)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A68)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A68)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A68)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A68)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A68)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A68="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A68)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A68)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A68)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A68)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A68)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A68)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="G68" s="56" t="str">
@@ -16226,7 +16637,7 @@
         <v/>
       </c>
       <c r="H68" s="56" t="str">
-        <f>IF($A68="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$421="COMPRA")+(MOVIMIENTOS!$B$5:$B$421="REPROCESO")+(MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A68)*MOVIMIENTOS!$I$5:$I$421)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$421="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$421="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho"))+((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A68)*MOVIMIENTOS!$I$5:$I$421))</f>
+        <f>IF($A68="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$425="COMPRA")+(MOVIMIENTOS!$B$5:$B$425="REPROCESO")+(MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A68)*MOVIMIENTOS!$I$5:$I$425)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$425="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho"))+((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A68)*MOVIMIENTOS!$I$5:$I$425))</f>
         <v/>
       </c>
       <c r="I68" s="54"/>
@@ -16248,23 +16659,23 @@
         <v/>
       </c>
       <c r="B69" s="56" t="str">
-        <f>IF($A69="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A69)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A69)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A69)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A69)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A69)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A69)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A69)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="A")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A69)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A69="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A69)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A69)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A69)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A69)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A69)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A69)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A69)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A69)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="C69" s="56" t="str">
-        <f>IF($A69="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A69)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A69)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A69)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A69)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A69)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A69)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A69)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="P")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A69)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A69="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A69)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A69)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A69)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A69)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A69)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A69)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A69)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A69)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="D69" s="56" t="str">
-        <f>IF($A69="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A69)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A69)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A69)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A69)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A69)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A69)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A69)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="C")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A69)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A69="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A69)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A69)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A69)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A69)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A69)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A69)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A69)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A69)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="E69" s="56" t="str">
-        <f>IF($A69="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A69)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A69)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A69)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A69)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A69)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A69)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A69)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="M")*(MOVIMIENTOS!$D$5:$D$421="jabas")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A69)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A69="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A69)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A69)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A69)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A69)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A69)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A69)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A69)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A69)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="F69" s="56" t="str">
-        <f>IF($A69="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A69)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A69)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A69)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A69)*MOVIMIENTOS!$E$5:$E$421)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A69)*MOVIMIENTOS!$E$5:$E$421)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*(MOVIMIENTOS!$D$5:$D$421="sacos")*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A69)*MOVIMIENTOS!$E$5:$E$421))</f>
+        <f>IF($A69="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A69)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A69)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A69)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A69)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A69)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A69)*MOVIMIENTOS!$E$5:$E$425))</f>
         <v/>
       </c>
       <c r="G69" s="56" t="str">
@@ -16272,7 +16683,7 @@
         <v/>
       </c>
       <c r="H69" s="56" t="str">
-        <f>IF($A69="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$421="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$421="COMPRA")+(MOVIMIENTOS!$B$5:$B$421="REPROCESO")+(MOVIMIENTOS!$B$5:$B$421="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$421="AJUSTE")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A69)*MOVIMIENTOS!$I$5:$I$421)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$421="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$421="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho"))+((MOVIMIENTOS!$B$5:$B$421="REGALO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$421="VENTA")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$421&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$421&lt;=$A69)*MOVIMIENTOS!$I$5:$I$421))</f>
+        <f>IF($A69="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$425="COMPRA")+(MOVIMIENTOS!$B$5:$B$425="REPROCESO")+(MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A69)*MOVIMIENTOS!$I$5:$I$425)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$425="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho"))+((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A69)*MOVIMIENTOS!$I$5:$I$425))</f>
         <v/>
       </c>
       <c r="I69" s="54"/>
@@ -22056,13 +22467,13 @@
       <c r="G332" s="54"/>
       <c r="H332" s="54"/>
       <c r="I332" s="54"/>
-      <c r="J332" s="54" t="str">
-        <f>IF(AND(MOVIMIENTOS!$A353&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A352,MOVIMIENTOS!$A353)=0),COUNT(J$4:J331)+1,"")</f>
-        <v/>
+      <c r="J332" s="54">
+        <f>IF(AND(MOVIMIENTOS!$A356&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A352,MOVIMIENTOS!$A356)=0),COUNT(J$4:J331)+1,"")</f>
+        <v>32</v>
       </c>
       <c r="K332" s="57">
-        <f>MOVIMIENTOS!$A353</f>
-        <v>0</v>
+        <f>MOVIMIENTOS!$A356</f>
+        <v>46245</v>
       </c>
       <c r="L332" s="54"/>
       <c r="M332" s="54"/>
@@ -22079,12 +22490,12 @@
       <c r="H333" s="54"/>
       <c r="I333" s="54"/>
       <c r="J333" s="54" t="str">
-        <f>IF(AND(MOVIMIENTOS!$A354&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A353,MOVIMIENTOS!$A354)=0),COUNT(J$4:J332)+1,"")</f>
+        <f>IF(AND(MOVIMIENTOS!$A357&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A356,MOVIMIENTOS!$A357)=0),COUNT(J$4:J332)+1,"")</f>
         <v/>
       </c>
       <c r="K333" s="57">
-        <f>MOVIMIENTOS!$A354</f>
-        <v>0</v>
+        <f>MOVIMIENTOS!$A357</f>
+        <v>46245</v>
       </c>
       <c r="L333" s="54"/>
       <c r="M333" s="54"/>
@@ -22101,12 +22512,12 @@
       <c r="H334" s="54"/>
       <c r="I334" s="54"/>
       <c r="J334" s="54" t="str">
-        <f>IF(AND(MOVIMIENTOS!$A355&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A354,MOVIMIENTOS!$A355)=0),COUNT(J$4:J333)+1,"")</f>
+        <f>IF(AND(MOVIMIENTOS!$A358&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A357,MOVIMIENTOS!$A358)=0),COUNT(J$4:J333)+1,"")</f>
         <v/>
       </c>
       <c r="K334" s="57">
-        <f>MOVIMIENTOS!$A355</f>
-        <v>0</v>
+        <f>MOVIMIENTOS!$A358</f>
+        <v>46245</v>
       </c>
       <c r="L334" s="54"/>
       <c r="M334" s="54"/>
@@ -22123,12 +22534,12 @@
       <c r="H335" s="54"/>
       <c r="I335" s="54"/>
       <c r="J335" s="54" t="str">
-        <f>IF(AND(MOVIMIENTOS!$A356&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A355,MOVIMIENTOS!$A356)=0),COUNT(J$4:J334)+1,"")</f>
+        <f>IF(AND(MOVIMIENTOS!$A359&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A358,MOVIMIENTOS!$A359)=0),COUNT(J$4:J334)+1,"")</f>
         <v/>
       </c>
       <c r="K335" s="57">
-        <f>MOVIMIENTOS!$A356</f>
-        <v>0</v>
+        <f>MOVIMIENTOS!$A359</f>
+        <v>46245</v>
       </c>
       <c r="L335" s="54"/>
       <c r="M335" s="54"/>
@@ -22145,12 +22556,12 @@
       <c r="H336" s="54"/>
       <c r="I336" s="54"/>
       <c r="J336" s="54" t="str">
-        <f>IF(AND(MOVIMIENTOS!$A357&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A356,MOVIMIENTOS!$A357)=0),COUNT(J$4:J335)+1,"")</f>
+        <f>IF(AND(MOVIMIENTOS!$A360&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A359,MOVIMIENTOS!$A360)=0),COUNT(J$4:J335)+1,"")</f>
         <v/>
       </c>
       <c r="K336" s="57">
-        <f>MOVIMIENTOS!$A357</f>
-        <v>0</v>
+        <f>MOVIMIENTOS!$A360</f>
+        <v>46245</v>
       </c>
       <c r="L336" s="54"/>
       <c r="M336" s="54"/>
@@ -22166,13 +22577,13 @@
       <c r="G337" s="54"/>
       <c r="H337" s="54"/>
       <c r="I337" s="54"/>
-      <c r="J337" s="54" t="str">
-        <f>IF(AND(MOVIMIENTOS!$A358&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A357,MOVIMIENTOS!$A358)=0),COUNT(J$4:J336)+1,"")</f>
-        <v/>
+      <c r="J337" s="54">
+        <f>IF(AND(MOVIMIENTOS!$A361&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A360,MOVIMIENTOS!$A361)=0),COUNT(J$4:J336)+1,"")</f>
+        <v>33</v>
       </c>
       <c r="K337" s="57">
-        <f>MOVIMIENTOS!$A358</f>
-        <v>0</v>
+        <f>MOVIMIENTOS!$A361</f>
+        <v>46246</v>
       </c>
       <c r="L337" s="54"/>
       <c r="M337" s="54"/>
@@ -22189,12 +22600,12 @@
       <c r="H338" s="54"/>
       <c r="I338" s="54"/>
       <c r="J338" s="54" t="str">
-        <f>IF(AND(MOVIMIENTOS!$A359&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A358,MOVIMIENTOS!$A359)=0),COUNT(J$4:J337)+1,"")</f>
+        <f>IF(AND(MOVIMIENTOS!$A362&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A361,MOVIMIENTOS!$A362)=0),COUNT(J$4:J337)+1,"")</f>
         <v/>
       </c>
       <c r="K338" s="57">
-        <f>MOVIMIENTOS!$A359</f>
-        <v>0</v>
+        <f>MOVIMIENTOS!$A362</f>
+        <v>46246</v>
       </c>
       <c r="L338" s="54"/>
       <c r="M338" s="54"/>
@@ -22211,12 +22622,12 @@
       <c r="H339" s="54"/>
       <c r="I339" s="54"/>
       <c r="J339" s="54" t="str">
-        <f>IF(AND(MOVIMIENTOS!$A360&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A359,MOVIMIENTOS!$A360)=0),COUNT(J$4:J338)+1,"")</f>
+        <f>IF(AND(MOVIMIENTOS!$A363&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A362,MOVIMIENTOS!$A363)=0),COUNT(J$4:J338)+1,"")</f>
         <v/>
       </c>
       <c r="K339" s="57">
-        <f>MOVIMIENTOS!$A360</f>
-        <v>0</v>
+        <f>MOVIMIENTOS!$A363</f>
+        <v>46246</v>
       </c>
       <c r="L339" s="54"/>
       <c r="M339" s="54"/>
@@ -22233,12 +22644,12 @@
       <c r="H340" s="54"/>
       <c r="I340" s="54"/>
       <c r="J340" s="54" t="str">
-        <f>IF(AND(MOVIMIENTOS!$A361&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A360,MOVIMIENTOS!$A361)=0),COUNT(J$4:J339)+1,"")</f>
+        <f>IF(AND(MOVIMIENTOS!$A365&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A363,MOVIMIENTOS!$A365)=0),COUNT(J$4:J339)+1,"")</f>
         <v/>
       </c>
       <c r="K340" s="57">
-        <f>MOVIMIENTOS!$A361</f>
-        <v>0</v>
+        <f>MOVIMIENTOS!$A365</f>
+        <v>46246</v>
       </c>
       <c r="L340" s="54"/>
       <c r="M340" s="54"/>
@@ -22255,12 +22666,12 @@
       <c r="H341" s="54"/>
       <c r="I341" s="54"/>
       <c r="J341" s="54" t="str">
-        <f>IF(AND(MOVIMIENTOS!$A362&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A361,MOVIMIENTOS!$A362)=0),COUNT(J$4:J340)+1,"")</f>
+        <f>IF(AND(MOVIMIENTOS!$A366&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A365,MOVIMIENTOS!$A366)=0),COUNT(J$4:J340)+1,"")</f>
         <v/>
       </c>
       <c r="K341" s="57">
-        <f>MOVIMIENTOS!$A362</f>
-        <v>0</v>
+        <f>MOVIMIENTOS!$A366</f>
+        <v>46246</v>
       </c>
       <c r="L341" s="54"/>
       <c r="M341" s="54"/>
@@ -22277,12 +22688,12 @@
       <c r="H342" s="54"/>
       <c r="I342" s="54"/>
       <c r="J342" s="54" t="str">
-        <f>IF(AND(MOVIMIENTOS!$A363&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A362,MOVIMIENTOS!$A363)=0),COUNT(J$4:J341)+1,"")</f>
+        <f>IF(AND(MOVIMIENTOS!$A367&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A366,MOVIMIENTOS!$A367)=0),COUNT(J$4:J341)+1,"")</f>
         <v/>
       </c>
       <c r="K342" s="57">
-        <f>MOVIMIENTOS!$A363</f>
-        <v>0</v>
+        <f>MOVIMIENTOS!$A367</f>
+        <v>46246</v>
       </c>
       <c r="L342" s="54"/>
       <c r="M342" s="54"/>
@@ -22299,12 +22710,12 @@
       <c r="H343" s="54"/>
       <c r="I343" s="54"/>
       <c r="J343" s="54" t="str">
-        <f>IF(AND(MOVIMIENTOS!$A364&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A363,MOVIMIENTOS!$A364)=0),COUNT(J$4:J342)+1,"")</f>
+        <f>IF(AND(MOVIMIENTOS!$A368&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A367,MOVIMIENTOS!$A368)=0),COUNT(J$4:J342)+1,"")</f>
         <v/>
       </c>
       <c r="K343" s="57">
-        <f>MOVIMIENTOS!$A364</f>
-        <v>0</v>
+        <f>MOVIMIENTOS!$A368</f>
+        <v>46246</v>
       </c>
       <c r="L343" s="54"/>
       <c r="M343" s="54"/>
@@ -22321,12 +22732,12 @@
       <c r="H344" s="54"/>
       <c r="I344" s="54"/>
       <c r="J344" s="54" t="str">
-        <f>IF(AND(MOVIMIENTOS!$A365&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A364,MOVIMIENTOS!$A365)=0),COUNT(J$4:J343)+1,"")</f>
+        <f>IF(AND(MOVIMIENTOS!$A369&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A368,MOVIMIENTOS!$A369)=0),COUNT(J$4:J343)+1,"")</f>
         <v/>
       </c>
       <c r="K344" s="57">
-        <f>MOVIMIENTOS!$A365</f>
-        <v>0</v>
+        <f>MOVIMIENTOS!$A369</f>
+        <v>46246</v>
       </c>
       <c r="L344" s="54"/>
       <c r="M344" s="54"/>
@@ -22343,12 +22754,12 @@
       <c r="H345" s="54"/>
       <c r="I345" s="54"/>
       <c r="J345" s="54" t="str">
-        <f>IF(AND(MOVIMIENTOS!$A366&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A365,MOVIMIENTOS!$A366)=0),COUNT(J$4:J344)+1,"")</f>
+        <f>IF(AND(MOVIMIENTOS!$A370&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A369,MOVIMIENTOS!$A370)=0),COUNT(J$4:J344)+1,"")</f>
         <v/>
       </c>
       <c r="K345" s="57">
-        <f>MOVIMIENTOS!$A366</f>
-        <v>0</v>
+        <f>MOVIMIENTOS!$A370</f>
+        <v>46246</v>
       </c>
       <c r="L345" s="54"/>
       <c r="M345" s="54"/>
@@ -22365,12 +22776,12 @@
       <c r="H346" s="54"/>
       <c r="I346" s="54"/>
       <c r="J346" s="54" t="str">
-        <f>IF(AND(MOVIMIENTOS!$A367&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A366,MOVIMIENTOS!$A367)=0),COUNT(J$4:J345)+1,"")</f>
+        <f>IF(AND(MOVIMIENTOS!$A371&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A370,MOVIMIENTOS!$A371)=0),COUNT(J$4:J345)+1,"")</f>
         <v/>
       </c>
       <c r="K346" s="57">
-        <f>MOVIMIENTOS!$A367</f>
-        <v>0</v>
+        <f>MOVIMIENTOS!$A371</f>
+        <v>46246</v>
       </c>
       <c r="L346" s="54"/>
       <c r="M346" s="54"/>
@@ -22387,12 +22798,12 @@
       <c r="H347" s="54"/>
       <c r="I347" s="54"/>
       <c r="J347" s="54" t="str">
-        <f>IF(AND(MOVIMIENTOS!$A368&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A367,MOVIMIENTOS!$A368)=0),COUNT(J$4:J346)+1,"")</f>
+        <f>IF(AND(MOVIMIENTOS!$A372&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A371,MOVIMIENTOS!$A372)=0),COUNT(J$4:J346)+1,"")</f>
         <v/>
       </c>
       <c r="K347" s="57">
-        <f>MOVIMIENTOS!$A368</f>
-        <v>0</v>
+        <f>MOVIMIENTOS!$A372</f>
+        <v>46246</v>
       </c>
       <c r="L347" s="54"/>
       <c r="M347" s="54"/>
@@ -22409,12 +22820,12 @@
       <c r="H348" s="54"/>
       <c r="I348" s="54"/>
       <c r="J348" s="54" t="str">
-        <f>IF(AND(MOVIMIENTOS!$A369&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A368,MOVIMIENTOS!$A369)=0),COUNT(J$4:J347)+1,"")</f>
+        <f>IF(AND(MOVIMIENTOS!$A373&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A372,MOVIMIENTOS!$A373)=0),COUNT(J$4:J347)+1,"")</f>
         <v/>
       </c>
       <c r="K348" s="57">
-        <f>MOVIMIENTOS!$A369</f>
-        <v>0</v>
+        <f>MOVIMIENTOS!$A373</f>
+        <v>46246</v>
       </c>
       <c r="L348" s="54"/>
       <c r="M348" s="54"/>
@@ -22431,12 +22842,12 @@
       <c r="H349" s="54"/>
       <c r="I349" s="54"/>
       <c r="J349" s="54" t="str">
-        <f>IF(AND(MOVIMIENTOS!$A370&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A369,MOVIMIENTOS!$A370)=0),COUNT(J$4:J348)+1,"")</f>
+        <f>IF(AND(MOVIMIENTOS!$A374&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A373,MOVIMIENTOS!$A374)=0),COUNT(J$4:J348)+1,"")</f>
         <v/>
       </c>
       <c r="K349" s="57">
-        <f>MOVIMIENTOS!$A370</f>
-        <v>0</v>
+        <f>MOVIMIENTOS!$A374</f>
+        <v>46246</v>
       </c>
       <c r="L349" s="54"/>
       <c r="M349" s="54"/>
@@ -22452,13 +22863,13 @@
       <c r="G350" s="54"/>
       <c r="H350" s="54"/>
       <c r="I350" s="54"/>
-      <c r="J350" s="54" t="str">
-        <f>IF(AND(MOVIMIENTOS!$A371&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A370,MOVIMIENTOS!$A371)=0),COUNT(J$4:J349)+1,"")</f>
-        <v/>
+      <c r="J350" s="54">
+        <f>IF(AND(MOVIMIENTOS!$A375&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A374,MOVIMIENTOS!$A375)=0),COUNT(J$4:J349)+1,"")</f>
+        <v>34</v>
       </c>
       <c r="K350" s="57">
-        <f>MOVIMIENTOS!$A371</f>
-        <v>0</v>
+        <f>MOVIMIENTOS!$A375</f>
+        <v>46247</v>
       </c>
       <c r="L350" s="54"/>
       <c r="M350" s="54"/>
@@ -22475,12 +22886,12 @@
       <c r="H351" s="54"/>
       <c r="I351" s="54"/>
       <c r="J351" s="54" t="str">
-        <f>IF(AND(MOVIMIENTOS!$A372&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A371,MOVIMIENTOS!$A372)=0),COUNT(J$4:J350)+1,"")</f>
+        <f>IF(AND(MOVIMIENTOS!$A376&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A375,MOVIMIENTOS!$A376)=0),COUNT(J$4:J350)+1,"")</f>
         <v/>
       </c>
       <c r="K351" s="57">
-        <f>MOVIMIENTOS!$A372</f>
-        <v>0</v>
+        <f>MOVIMIENTOS!$A376</f>
+        <v>46247</v>
       </c>
       <c r="L351" s="54"/>
       <c r="M351" s="54"/>
@@ -22497,12 +22908,12 @@
       <c r="H352" s="54"/>
       <c r="I352" s="54"/>
       <c r="J352" s="54" t="str">
-        <f>IF(AND(MOVIMIENTOS!$A373&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A372,MOVIMIENTOS!$A373)=0),COUNT(J$4:J351)+1,"")</f>
+        <f>IF(AND(MOVIMIENTOS!$A377&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A376,MOVIMIENTOS!$A377)=0),COUNT(J$4:J351)+1,"")</f>
         <v/>
       </c>
       <c r="K352" s="57">
-        <f>MOVIMIENTOS!$A373</f>
-        <v>0</v>
+        <f>MOVIMIENTOS!$A377</f>
+        <v>46247</v>
       </c>
       <c r="L352" s="54"/>
       <c r="M352" s="54"/>
@@ -22519,12 +22930,12 @@
       <c r="H353" s="54"/>
       <c r="I353" s="54"/>
       <c r="J353" s="54" t="str">
-        <f>IF(AND(MOVIMIENTOS!$A374&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A373,MOVIMIENTOS!$A374)=0),COUNT(J$4:J352)+1,"")</f>
+        <f>IF(AND(MOVIMIENTOS!$A378&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A377,MOVIMIENTOS!$A378)=0),COUNT(J$4:J352)+1,"")</f>
         <v/>
       </c>
       <c r="K353" s="57">
-        <f>MOVIMIENTOS!$A374</f>
-        <v>0</v>
+        <f>MOVIMIENTOS!$A378</f>
+        <v>46247</v>
       </c>
       <c r="L353" s="54"/>
       <c r="M353" s="54"/>
@@ -22541,12 +22952,12 @@
       <c r="H354" s="54"/>
       <c r="I354" s="54"/>
       <c r="J354" s="54" t="str">
-        <f>IF(AND(MOVIMIENTOS!$A375&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A374,MOVIMIENTOS!$A375)=0),COUNT(J$4:J353)+1,"")</f>
+        <f>IF(AND(MOVIMIENTOS!$A379&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A378,MOVIMIENTOS!$A379)=0),COUNT(J$4:J353)+1,"")</f>
         <v/>
       </c>
       <c r="K354" s="57">
-        <f>MOVIMIENTOS!$A375</f>
-        <v>0</v>
+        <f>MOVIMIENTOS!$A379</f>
+        <v>46247</v>
       </c>
       <c r="L354" s="54"/>
       <c r="M354" s="54"/>
@@ -22563,12 +22974,12 @@
       <c r="H355" s="54"/>
       <c r="I355" s="54"/>
       <c r="J355" s="54" t="str">
-        <f>IF(AND(MOVIMIENTOS!$A376&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A375,MOVIMIENTOS!$A376)=0),COUNT(J$4:J354)+1,"")</f>
+        <f>IF(AND(MOVIMIENTOS!$A380&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A379,MOVIMIENTOS!$A380)=0),COUNT(J$4:J354)+1,"")</f>
         <v/>
       </c>
       <c r="K355" s="57">
-        <f>MOVIMIENTOS!$A376</f>
-        <v>0</v>
+        <f>MOVIMIENTOS!$A380</f>
+        <v>46247</v>
       </c>
       <c r="L355" s="54"/>
       <c r="M355" s="54"/>
@@ -22585,12 +22996,12 @@
       <c r="H356" s="54"/>
       <c r="I356" s="54"/>
       <c r="J356" s="54" t="str">
-        <f>IF(AND(MOVIMIENTOS!$A377&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A376,MOVIMIENTOS!$A377)=0),COUNT(J$4:J355)+1,"")</f>
+        <f>IF(AND(MOVIMIENTOS!$A381&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A380,MOVIMIENTOS!$A381)=0),COUNT(J$4:J355)+1,"")</f>
         <v/>
       </c>
       <c r="K356" s="57">
-        <f>MOVIMIENTOS!$A377</f>
-        <v>0</v>
+        <f>MOVIMIENTOS!$A381</f>
+        <v>46247</v>
       </c>
       <c r="L356" s="54"/>
       <c r="M356" s="54"/>
@@ -22607,12 +23018,12 @@
       <c r="H357" s="54"/>
       <c r="I357" s="54"/>
       <c r="J357" s="54" t="str">
-        <f>IF(AND(MOVIMIENTOS!$A378&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A377,MOVIMIENTOS!$A378)=0),COUNT(J$4:J356)+1,"")</f>
+        <f>IF(AND(MOVIMIENTOS!$A382&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A381,MOVIMIENTOS!$A382)=0),COUNT(J$4:J356)+1,"")</f>
         <v/>
       </c>
       <c r="K357" s="57">
-        <f>MOVIMIENTOS!$A378</f>
-        <v>0</v>
+        <f>MOVIMIENTOS!$A382</f>
+        <v>46247</v>
       </c>
       <c r="L357" s="54"/>
       <c r="M357" s="54"/>
@@ -22629,12 +23040,12 @@
       <c r="H358" s="54"/>
       <c r="I358" s="54"/>
       <c r="J358" s="54" t="str">
-        <f>IF(AND(MOVIMIENTOS!$A379&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A378,MOVIMIENTOS!$A379)=0),COUNT(J$4:J357)+1,"")</f>
+        <f>IF(AND(MOVIMIENTOS!$A383&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A382,MOVIMIENTOS!$A383)=0),COUNT(J$4:J357)+1,"")</f>
         <v/>
       </c>
       <c r="K358" s="57">
-        <f>MOVIMIENTOS!$A379</f>
-        <v>0</v>
+        <f>MOVIMIENTOS!$A383</f>
+        <v>46247</v>
       </c>
       <c r="L358" s="54"/>
       <c r="M358" s="54"/>
@@ -22651,12 +23062,12 @@
       <c r="H359" s="54"/>
       <c r="I359" s="54"/>
       <c r="J359" s="54" t="str">
-        <f>IF(AND(MOVIMIENTOS!$A380&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A379,MOVIMIENTOS!$A380)=0),COUNT(J$4:J358)+1,"")</f>
+        <f>IF(AND(MOVIMIENTOS!$A384&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A383,MOVIMIENTOS!$A384)=0),COUNT(J$4:J358)+1,"")</f>
         <v/>
       </c>
       <c r="K359" s="57">
-        <f>MOVIMIENTOS!$A380</f>
-        <v>0</v>
+        <f>MOVIMIENTOS!$A384</f>
+        <v>46247</v>
       </c>
       <c r="L359" s="54"/>
       <c r="M359" s="54"/>
@@ -22673,11 +23084,11 @@
       <c r="H360" s="54"/>
       <c r="I360" s="54"/>
       <c r="J360" s="54" t="str">
-        <f>IF(AND(MOVIMIENTOS!$A381&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A380,MOVIMIENTOS!$A381)=0),COUNT(J$4:J359)+1,"")</f>
+        <f>IF(AND(MOVIMIENTOS!$A385&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A384,MOVIMIENTOS!$A385)=0),COUNT(J$4:J359)+1,"")</f>
         <v/>
       </c>
       <c r="K360" s="57">
-        <f>MOVIMIENTOS!$A381</f>
+        <f>MOVIMIENTOS!$A385</f>
         <v>0</v>
       </c>
       <c r="L360" s="54"/>
@@ -22695,11 +23106,11 @@
       <c r="H361" s="54"/>
       <c r="I361" s="54"/>
       <c r="J361" s="54" t="str">
-        <f>IF(AND(MOVIMIENTOS!$A382&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A381,MOVIMIENTOS!$A382)=0),COUNT(J$4:J360)+1,"")</f>
+        <f>IF(AND(MOVIMIENTOS!$A386&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A385,MOVIMIENTOS!$A386)=0),COUNT(J$4:J360)+1,"")</f>
         <v/>
       </c>
       <c r="K361" s="57">
-        <f>MOVIMIENTOS!$A382</f>
+        <f>MOVIMIENTOS!$A386</f>
         <v>0</v>
       </c>
       <c r="L361" s="54"/>
@@ -22717,11 +23128,11 @@
       <c r="H362" s="54"/>
       <c r="I362" s="54"/>
       <c r="J362" s="54" t="str">
-        <f>IF(AND(MOVIMIENTOS!$A383&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A382,MOVIMIENTOS!$A383)=0),COUNT(J$4:J361)+1,"")</f>
+        <f>IF(AND(MOVIMIENTOS!$A387&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A386,MOVIMIENTOS!$A387)=0),COUNT(J$4:J361)+1,"")</f>
         <v/>
       </c>
       <c r="K362" s="57">
-        <f>MOVIMIENTOS!$A383</f>
+        <f>MOVIMIENTOS!$A387</f>
         <v>0</v>
       </c>
       <c r="L362" s="54"/>
@@ -22739,11 +23150,11 @@
       <c r="H363" s="54"/>
       <c r="I363" s="54"/>
       <c r="J363" s="54" t="str">
-        <f>IF(AND(MOVIMIENTOS!$A384&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A383,MOVIMIENTOS!$A384)=0),COUNT(J$4:J362)+1,"")</f>
+        <f>IF(AND(MOVIMIENTOS!$A388&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A387,MOVIMIENTOS!$A388)=0),COUNT(J$4:J362)+1,"")</f>
         <v/>
       </c>
       <c r="K363" s="57">
-        <f>MOVIMIENTOS!$A384</f>
+        <f>MOVIMIENTOS!$A388</f>
         <v>0</v>
       </c>
       <c r="L363" s="54"/>
@@ -22761,11 +23172,11 @@
       <c r="H364" s="54"/>
       <c r="I364" s="54"/>
       <c r="J364" s="54" t="str">
-        <f>IF(AND(MOVIMIENTOS!$A385&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A384,MOVIMIENTOS!$A385)=0),COUNT(J$4:J363)+1,"")</f>
+        <f>IF(AND(MOVIMIENTOS!$A389&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A388,MOVIMIENTOS!$A389)=0),COUNT(J$4:J363)+1,"")</f>
         <v/>
       </c>
       <c r="K364" s="57">
-        <f>MOVIMIENTOS!$A385</f>
+        <f>MOVIMIENTOS!$A389</f>
         <v>0</v>
       </c>
       <c r="L364" s="54"/>
@@ -22783,11 +23194,11 @@
       <c r="H365" s="54"/>
       <c r="I365" s="54"/>
       <c r="J365" s="54" t="str">
-        <f>IF(AND(MOVIMIENTOS!$A386&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A385,MOVIMIENTOS!$A386)=0),COUNT(J$4:J364)+1,"")</f>
+        <f>IF(AND(MOVIMIENTOS!$A390&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A389,MOVIMIENTOS!$A390)=0),COUNT(J$4:J364)+1,"")</f>
         <v/>
       </c>
       <c r="K365" s="57">
-        <f>MOVIMIENTOS!$A386</f>
+        <f>MOVIMIENTOS!$A390</f>
         <v>0</v>
       </c>
       <c r="L365" s="54"/>
@@ -22805,11 +23216,11 @@
       <c r="H366" s="54"/>
       <c r="I366" s="54"/>
       <c r="J366" s="54" t="str">
-        <f>IF(AND(MOVIMIENTOS!$A387&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A386,MOVIMIENTOS!$A387)=0),COUNT(J$4:J365)+1,"")</f>
+        <f>IF(AND(MOVIMIENTOS!$A391&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A390,MOVIMIENTOS!$A391)=0),COUNT(J$4:J365)+1,"")</f>
         <v/>
       </c>
       <c r="K366" s="57">
-        <f>MOVIMIENTOS!$A387</f>
+        <f>MOVIMIENTOS!$A391</f>
         <v>0</v>
       </c>
       <c r="L366" s="54"/>
@@ -22827,11 +23238,11 @@
       <c r="H367" s="54"/>
       <c r="I367" s="54"/>
       <c r="J367" s="54" t="str">
-        <f>IF(AND(MOVIMIENTOS!$A388&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A387,MOVIMIENTOS!$A388)=0),COUNT(J$4:J366)+1,"")</f>
+        <f>IF(AND(MOVIMIENTOS!$A392&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A391,MOVIMIENTOS!$A392)=0),COUNT(J$4:J366)+1,"")</f>
         <v/>
       </c>
       <c r="K367" s="57">
-        <f>MOVIMIENTOS!$A388</f>
+        <f>MOVIMIENTOS!$A392</f>
         <v>0</v>
       </c>
       <c r="L367" s="54"/>
@@ -22849,11 +23260,11 @@
       <c r="H368" s="54"/>
       <c r="I368" s="54"/>
       <c r="J368" s="54" t="str">
-        <f>IF(AND(MOVIMIENTOS!$A389&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A388,MOVIMIENTOS!$A389)=0),COUNT(J$4:J367)+1,"")</f>
+        <f>IF(AND(MOVIMIENTOS!$A393&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A392,MOVIMIENTOS!$A393)=0),COUNT(J$4:J367)+1,"")</f>
         <v/>
       </c>
       <c r="K368" s="57">
-        <f>MOVIMIENTOS!$A389</f>
+        <f>MOVIMIENTOS!$A393</f>
         <v>0</v>
       </c>
       <c r="L368" s="54"/>
@@ -22871,11 +23282,11 @@
       <c r="H369" s="54"/>
       <c r="I369" s="54"/>
       <c r="J369" s="54" t="str">
-        <f>IF(AND(MOVIMIENTOS!$A390&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A389,MOVIMIENTOS!$A390)=0),COUNT(J$4:J368)+1,"")</f>
+        <f>IF(AND(MOVIMIENTOS!$A394&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A393,MOVIMIENTOS!$A394)=0),COUNT(J$4:J368)+1,"")</f>
         <v/>
       </c>
       <c r="K369" s="57">
-        <f>MOVIMIENTOS!$A390</f>
+        <f>MOVIMIENTOS!$A394</f>
         <v>0</v>
       </c>
       <c r="L369" s="54"/>
@@ -22893,11 +23304,11 @@
       <c r="H370" s="54"/>
       <c r="I370" s="54"/>
       <c r="J370" s="54" t="str">
-        <f>IF(AND(MOVIMIENTOS!$A391&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A390,MOVIMIENTOS!$A391)=0),COUNT(J$4:J369)+1,"")</f>
+        <f>IF(AND(MOVIMIENTOS!$A395&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A394,MOVIMIENTOS!$A395)=0),COUNT(J$4:J369)+1,"")</f>
         <v/>
       </c>
       <c r="K370" s="57">
-        <f>MOVIMIENTOS!$A391</f>
+        <f>MOVIMIENTOS!$A395</f>
         <v>0</v>
       </c>
       <c r="L370" s="54"/>
@@ -22915,11 +23326,11 @@
       <c r="H371" s="54"/>
       <c r="I371" s="54"/>
       <c r="J371" s="54" t="str">
-        <f>IF(AND(MOVIMIENTOS!$A392&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A391,MOVIMIENTOS!$A392)=0),COUNT(J$4:J370)+1,"")</f>
+        <f>IF(AND(MOVIMIENTOS!$A396&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A395,MOVIMIENTOS!$A396)=0),COUNT(J$4:J370)+1,"")</f>
         <v/>
       </c>
       <c r="K371" s="57">
-        <f>MOVIMIENTOS!$A392</f>
+        <f>MOVIMIENTOS!$A396</f>
         <v>0</v>
       </c>
       <c r="L371" s="54"/>
@@ -22937,11 +23348,11 @@
       <c r="H372" s="54"/>
       <c r="I372" s="54"/>
       <c r="J372" s="54" t="str">
-        <f>IF(AND(MOVIMIENTOS!$A393&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A392,MOVIMIENTOS!$A393)=0),COUNT(J$4:J371)+1,"")</f>
+        <f>IF(AND(MOVIMIENTOS!$A397&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A396,MOVIMIENTOS!$A397)=0),COUNT(J$4:J371)+1,"")</f>
         <v/>
       </c>
       <c r="K372" s="57">
-        <f>MOVIMIENTOS!$A393</f>
+        <f>MOVIMIENTOS!$A397</f>
         <v>0</v>
       </c>
       <c r="L372" s="54"/>
@@ -22959,11 +23370,11 @@
       <c r="H373" s="54"/>
       <c r="I373" s="54"/>
       <c r="J373" s="54" t="str">
-        <f>IF(AND(MOVIMIENTOS!$A394&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A393,MOVIMIENTOS!$A394)=0),COUNT(J$4:J372)+1,"")</f>
+        <f>IF(AND(MOVIMIENTOS!$A398&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A397,MOVIMIENTOS!$A398)=0),COUNT(J$4:J372)+1,"")</f>
         <v/>
       </c>
       <c r="K373" s="57">
-        <f>MOVIMIENTOS!$A394</f>
+        <f>MOVIMIENTOS!$A398</f>
         <v>0</v>
       </c>
       <c r="L373" s="54"/>
@@ -22981,11 +23392,11 @@
       <c r="H374" s="54"/>
       <c r="I374" s="54"/>
       <c r="J374" s="54" t="str">
-        <f>IF(AND(MOVIMIENTOS!$A395&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A394,MOVIMIENTOS!$A395)=0),COUNT(J$4:J373)+1,"")</f>
+        <f>IF(AND(MOVIMIENTOS!$A399&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A398,MOVIMIENTOS!$A399)=0),COUNT(J$4:J373)+1,"")</f>
         <v/>
       </c>
       <c r="K374" s="57">
-        <f>MOVIMIENTOS!$A395</f>
+        <f>MOVIMIENTOS!$A399</f>
         <v>0</v>
       </c>
       <c r="L374" s="54"/>
@@ -23003,11 +23414,11 @@
       <c r="H375" s="54"/>
       <c r="I375" s="54"/>
       <c r="J375" s="54" t="str">
-        <f>IF(AND(MOVIMIENTOS!$A396&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A395,MOVIMIENTOS!$A396)=0),COUNT(J$4:J374)+1,"")</f>
+        <f>IF(AND(MOVIMIENTOS!$A400&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A399,MOVIMIENTOS!$A400)=0),COUNT(J$4:J374)+1,"")</f>
         <v/>
       </c>
       <c r="K375" s="57">
-        <f>MOVIMIENTOS!$A396</f>
+        <f>MOVIMIENTOS!$A400</f>
         <v>0</v>
       </c>
       <c r="L375" s="54"/>
@@ -23025,11 +23436,11 @@
       <c r="H376" s="54"/>
       <c r="I376" s="54"/>
       <c r="J376" s="54" t="str">
-        <f>IF(AND(MOVIMIENTOS!$A397&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A396,MOVIMIENTOS!$A397)=0),COUNT(J$4:J375)+1,"")</f>
+        <f>IF(AND(MOVIMIENTOS!$A401&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A400,MOVIMIENTOS!$A401)=0),COUNT(J$4:J375)+1,"")</f>
         <v/>
       </c>
       <c r="K376" s="57">
-        <f>MOVIMIENTOS!$A397</f>
+        <f>MOVIMIENTOS!$A401</f>
         <v>0</v>
       </c>
       <c r="L376" s="54"/>
@@ -23047,11 +23458,11 @@
       <c r="H377" s="54"/>
       <c r="I377" s="54"/>
       <c r="J377" s="54" t="str">
-        <f>IF(AND(MOVIMIENTOS!$A398&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A397,MOVIMIENTOS!$A398)=0),COUNT(J$4:J376)+1,"")</f>
+        <f>IF(AND(MOVIMIENTOS!$A402&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A401,MOVIMIENTOS!$A402)=0),COUNT(J$4:J376)+1,"")</f>
         <v/>
       </c>
       <c r="K377" s="57">
-        <f>MOVIMIENTOS!$A398</f>
+        <f>MOVIMIENTOS!$A402</f>
         <v>0</v>
       </c>
       <c r="L377" s="54"/>
@@ -23069,11 +23480,11 @@
       <c r="H378" s="54"/>
       <c r="I378" s="54"/>
       <c r="J378" s="54" t="str">
-        <f>IF(AND(MOVIMIENTOS!$A399&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A398,MOVIMIENTOS!$A399)=0),COUNT(J$4:J377)+1,"")</f>
+        <f>IF(AND(MOVIMIENTOS!$A403&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A402,MOVIMIENTOS!$A403)=0),COUNT(J$4:J377)+1,"")</f>
         <v/>
       </c>
       <c r="K378" s="57">
-        <f>MOVIMIENTOS!$A399</f>
+        <f>MOVIMIENTOS!$A403</f>
         <v>0</v>
       </c>
       <c r="L378" s="54"/>
@@ -23091,11 +23502,11 @@
       <c r="H379" s="54"/>
       <c r="I379" s="54"/>
       <c r="J379" s="54" t="str">
-        <f>IF(AND(MOVIMIENTOS!$A400&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A399,MOVIMIENTOS!$A400)=0),COUNT(J$4:J378)+1,"")</f>
+        <f>IF(AND(MOVIMIENTOS!$A404&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A403,MOVIMIENTOS!$A404)=0),COUNT(J$4:J378)+1,"")</f>
         <v/>
       </c>
       <c r="K379" s="57">
-        <f>MOVIMIENTOS!$A400</f>
+        <f>MOVIMIENTOS!$A404</f>
         <v>0</v>
       </c>
       <c r="L379" s="54"/>
@@ -23113,11 +23524,11 @@
       <c r="H380" s="54"/>
       <c r="I380" s="54"/>
       <c r="J380" s="54" t="str">
-        <f>IF(AND(MOVIMIENTOS!$A401&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A400,MOVIMIENTOS!$A401)=0),COUNT(J$4:J379)+1,"")</f>
+        <f>IF(AND(MOVIMIENTOS!$A405&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A404,MOVIMIENTOS!$A405)=0),COUNT(J$4:J379)+1,"")</f>
         <v/>
       </c>
       <c r="K380" s="57">
-        <f>MOVIMIENTOS!$A401</f>
+        <f>MOVIMIENTOS!$A405</f>
         <v>0</v>
       </c>
       <c r="L380" s="54"/>
@@ -23135,11 +23546,11 @@
       <c r="H381" s="54"/>
       <c r="I381" s="54"/>
       <c r="J381" s="54" t="str">
-        <f>IF(AND(MOVIMIENTOS!$A402&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A401,MOVIMIENTOS!$A402)=0),COUNT(J$4:J380)+1,"")</f>
+        <f>IF(AND(MOVIMIENTOS!$A406&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A405,MOVIMIENTOS!$A406)=0),COUNT(J$4:J380)+1,"")</f>
         <v/>
       </c>
       <c r="K381" s="57">
-        <f>MOVIMIENTOS!$A402</f>
+        <f>MOVIMIENTOS!$A406</f>
         <v>0</v>
       </c>
       <c r="L381" s="54"/>
@@ -23157,11 +23568,11 @@
       <c r="H382" s="54"/>
       <c r="I382" s="54"/>
       <c r="J382" s="54" t="str">
-        <f>IF(AND(MOVIMIENTOS!$A403&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A402,MOVIMIENTOS!$A403)=0),COUNT(J$4:J381)+1,"")</f>
+        <f>IF(AND(MOVIMIENTOS!$A407&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A406,MOVIMIENTOS!$A407)=0),COUNT(J$4:J381)+1,"")</f>
         <v/>
       </c>
       <c r="K382" s="57">
-        <f>MOVIMIENTOS!$A403</f>
+        <f>MOVIMIENTOS!$A407</f>
         <v>0</v>
       </c>
       <c r="L382" s="54"/>
@@ -23179,11 +23590,11 @@
       <c r="H383" s="54"/>
       <c r="I383" s="54"/>
       <c r="J383" s="54" t="str">
-        <f>IF(AND(MOVIMIENTOS!$A404&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A403,MOVIMIENTOS!$A404)=0),COUNT(J$4:J382)+1,"")</f>
+        <f>IF(AND(MOVIMIENTOS!$A408&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A407,MOVIMIENTOS!$A408)=0),COUNT(J$4:J382)+1,"")</f>
         <v/>
       </c>
       <c r="K383" s="57">
-        <f>MOVIMIENTOS!$A404</f>
+        <f>MOVIMIENTOS!$A408</f>
         <v>0</v>
       </c>
       <c r="L383" s="54"/>
@@ -23201,11 +23612,11 @@
       <c r="H384" s="54"/>
       <c r="I384" s="54"/>
       <c r="J384" s="54" t="str">
-        <f>IF(AND(MOVIMIENTOS!$A405&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A404,MOVIMIENTOS!$A405)=0),COUNT(J$4:J383)+1,"")</f>
+        <f>IF(AND(MOVIMIENTOS!$A409&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A408,MOVIMIENTOS!$A409)=0),COUNT(J$4:J383)+1,"")</f>
         <v/>
       </c>
       <c r="K384" s="57">
-        <f>MOVIMIENTOS!$A405</f>
+        <f>MOVIMIENTOS!$A409</f>
         <v>0</v>
       </c>
       <c r="L384" s="54"/>
@@ -23223,11 +23634,11 @@
       <c r="H385" s="54"/>
       <c r="I385" s="54"/>
       <c r="J385" s="54" t="str">
-        <f>IF(AND(MOVIMIENTOS!$A406&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A405,MOVIMIENTOS!$A406)=0),COUNT(J$4:J384)+1,"")</f>
+        <f>IF(AND(MOVIMIENTOS!$A410&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A409,MOVIMIENTOS!$A410)=0),COUNT(J$4:J384)+1,"")</f>
         <v/>
       </c>
       <c r="K385" s="57">
-        <f>MOVIMIENTOS!$A406</f>
+        <f>MOVIMIENTOS!$A410</f>
         <v>0</v>
       </c>
       <c r="L385" s="54"/>
@@ -23245,11 +23656,11 @@
       <c r="H386" s="54"/>
       <c r="I386" s="54"/>
       <c r="J386" s="54" t="str">
-        <f>IF(AND(MOVIMIENTOS!$A407&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A406,MOVIMIENTOS!$A407)=0),COUNT(J$4:J385)+1,"")</f>
+        <f>IF(AND(MOVIMIENTOS!$A411&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A410,MOVIMIENTOS!$A411)=0),COUNT(J$4:J385)+1,"")</f>
         <v/>
       </c>
       <c r="K386" s="57">
-        <f>MOVIMIENTOS!$A407</f>
+        <f>MOVIMIENTOS!$A411</f>
         <v>0</v>
       </c>
       <c r="L386" s="54"/>
@@ -23267,11 +23678,11 @@
       <c r="H387" s="54"/>
       <c r="I387" s="54"/>
       <c r="J387" s="54" t="str">
-        <f>IF(AND(MOVIMIENTOS!$A408&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A407,MOVIMIENTOS!$A408)=0),COUNT(J$4:J386)+1,"")</f>
+        <f>IF(AND(MOVIMIENTOS!$A412&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A411,MOVIMIENTOS!$A412)=0),COUNT(J$4:J386)+1,"")</f>
         <v/>
       </c>
       <c r="K387" s="57">
-        <f>MOVIMIENTOS!$A408</f>
+        <f>MOVIMIENTOS!$A412</f>
         <v>0</v>
       </c>
       <c r="L387" s="54"/>
@@ -23289,11 +23700,11 @@
       <c r="H388" s="54"/>
       <c r="I388" s="54"/>
       <c r="J388" s="54" t="str">
-        <f>IF(AND(MOVIMIENTOS!$A409&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A408,MOVIMIENTOS!$A409)=0),COUNT(J$4:J387)+1,"")</f>
+        <f>IF(AND(MOVIMIENTOS!$A413&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A412,MOVIMIENTOS!$A413)=0),COUNT(J$4:J387)+1,"")</f>
         <v/>
       </c>
       <c r="K388" s="57">
-        <f>MOVIMIENTOS!$A409</f>
+        <f>MOVIMIENTOS!$A413</f>
         <v>0</v>
       </c>
       <c r="L388" s="54"/>
@@ -23311,11 +23722,11 @@
       <c r="H389" s="54"/>
       <c r="I389" s="54"/>
       <c r="J389" s="54" t="str">
-        <f>IF(AND(MOVIMIENTOS!$A410&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A409,MOVIMIENTOS!$A410)=0),COUNT(J$4:J388)+1,"")</f>
+        <f>IF(AND(MOVIMIENTOS!$A414&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A413,MOVIMIENTOS!$A414)=0),COUNT(J$4:J388)+1,"")</f>
         <v/>
       </c>
       <c r="K389" s="57">
-        <f>MOVIMIENTOS!$A410</f>
+        <f>MOVIMIENTOS!$A414</f>
         <v>0</v>
       </c>
       <c r="L389" s="54"/>
@@ -23333,11 +23744,11 @@
       <c r="H390" s="54"/>
       <c r="I390" s="54"/>
       <c r="J390" s="54" t="str">
-        <f>IF(AND(MOVIMIENTOS!$A411&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A410,MOVIMIENTOS!$A411)=0),COUNT(J$4:J389)+1,"")</f>
+        <f>IF(AND(MOVIMIENTOS!$A415&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A414,MOVIMIENTOS!$A415)=0),COUNT(J$4:J389)+1,"")</f>
         <v/>
       </c>
       <c r="K390" s="57">
-        <f>MOVIMIENTOS!$A411</f>
+        <f>MOVIMIENTOS!$A415</f>
         <v>0</v>
       </c>
       <c r="L390" s="54"/>
@@ -23355,11 +23766,11 @@
       <c r="H391" s="54"/>
       <c r="I391" s="54"/>
       <c r="J391" s="54" t="str">
-        <f>IF(AND(MOVIMIENTOS!$A412&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A411,MOVIMIENTOS!$A412)=0),COUNT(J$4:J390)+1,"")</f>
+        <f>IF(AND(MOVIMIENTOS!$A416&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A415,MOVIMIENTOS!$A416)=0),COUNT(J$4:J390)+1,"")</f>
         <v/>
       </c>
       <c r="K391" s="57">
-        <f>MOVIMIENTOS!$A412</f>
+        <f>MOVIMIENTOS!$A416</f>
         <v>0</v>
       </c>
       <c r="L391" s="54"/>
@@ -23377,11 +23788,11 @@
       <c r="H392" s="54"/>
       <c r="I392" s="54"/>
       <c r="J392" s="54" t="str">
-        <f>IF(AND(MOVIMIENTOS!$A413&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A412,MOVIMIENTOS!$A413)=0),COUNT(J$4:J391)+1,"")</f>
+        <f>IF(AND(MOVIMIENTOS!$A417&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A416,MOVIMIENTOS!$A417)=0),COUNT(J$4:J391)+1,"")</f>
         <v/>
       </c>
       <c r="K392" s="57">
-        <f>MOVIMIENTOS!$A413</f>
+        <f>MOVIMIENTOS!$A417</f>
         <v>0</v>
       </c>
       <c r="L392" s="54"/>
@@ -23399,11 +23810,11 @@
       <c r="H393" s="54"/>
       <c r="I393" s="54"/>
       <c r="J393" s="54" t="str">
-        <f>IF(AND(MOVIMIENTOS!$A414&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A413,MOVIMIENTOS!$A414)=0),COUNT(J$4:J392)+1,"")</f>
+        <f>IF(AND(MOVIMIENTOS!$A418&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A417,MOVIMIENTOS!$A418)=0),COUNT(J$4:J392)+1,"")</f>
         <v/>
       </c>
       <c r="K393" s="57">
-        <f>MOVIMIENTOS!$A414</f>
+        <f>MOVIMIENTOS!$A418</f>
         <v>0</v>
       </c>
       <c r="L393" s="54"/>
@@ -23421,11 +23832,11 @@
       <c r="H394" s="54"/>
       <c r="I394" s="54"/>
       <c r="J394" s="54" t="str">
-        <f>IF(AND(MOVIMIENTOS!$A415&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A414,MOVIMIENTOS!$A415)=0),COUNT(J$4:J393)+1,"")</f>
+        <f>IF(AND(MOVIMIENTOS!$A419&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A418,MOVIMIENTOS!$A419)=0),COUNT(J$4:J393)+1,"")</f>
         <v/>
       </c>
       <c r="K394" s="57">
-        <f>MOVIMIENTOS!$A415</f>
+        <f>MOVIMIENTOS!$A419</f>
         <v>0</v>
       </c>
       <c r="L394" s="54"/>
@@ -23443,11 +23854,11 @@
       <c r="H395" s="54"/>
       <c r="I395" s="54"/>
       <c r="J395" s="54" t="str">
-        <f>IF(AND(MOVIMIENTOS!$A416&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A415,MOVIMIENTOS!$A416)=0),COUNT(J$4:J394)+1,"")</f>
+        <f>IF(AND(MOVIMIENTOS!$A420&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A419,MOVIMIENTOS!$A420)=0),COUNT(J$4:J394)+1,"")</f>
         <v/>
       </c>
       <c r="K395" s="57">
-        <f>MOVIMIENTOS!$A416</f>
+        <f>MOVIMIENTOS!$A420</f>
         <v>0</v>
       </c>
       <c r="L395" s="54"/>
@@ -23465,11 +23876,11 @@
       <c r="H396" s="54"/>
       <c r="I396" s="54"/>
       <c r="J396" s="54" t="str">
-        <f>IF(AND(MOVIMIENTOS!$A417&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A416,MOVIMIENTOS!$A417)=0),COUNT(J$4:J395)+1,"")</f>
+        <f>IF(AND(MOVIMIENTOS!$A421&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A420,MOVIMIENTOS!$A421)=0),COUNT(J$4:J395)+1,"")</f>
         <v/>
       </c>
       <c r="K396" s="57">
-        <f>MOVIMIENTOS!$A417</f>
+        <f>MOVIMIENTOS!$A421</f>
         <v>0</v>
       </c>
       <c r="L396" s="54"/>
@@ -23487,11 +23898,11 @@
       <c r="H397" s="54"/>
       <c r="I397" s="54"/>
       <c r="J397" s="54" t="str">
-        <f>IF(AND(MOVIMIENTOS!$A418&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A417,MOVIMIENTOS!$A418)=0),COUNT(J$4:J396)+1,"")</f>
+        <f>IF(AND(MOVIMIENTOS!$A422&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A421,MOVIMIENTOS!$A422)=0),COUNT(J$4:J396)+1,"")</f>
         <v/>
       </c>
       <c r="K397" s="57">
-        <f>MOVIMIENTOS!$A418</f>
+        <f>MOVIMIENTOS!$A422</f>
         <v>0</v>
       </c>
       <c r="L397" s="54"/>
@@ -23509,11 +23920,11 @@
       <c r="H398" s="54"/>
       <c r="I398" s="54"/>
       <c r="J398" s="54" t="str">
-        <f>IF(AND(MOVIMIENTOS!$A419&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A418,MOVIMIENTOS!$A419)=0),COUNT(J$4:J397)+1,"")</f>
+        <f>IF(AND(MOVIMIENTOS!$A423&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A422,MOVIMIENTOS!$A423)=0),COUNT(J$4:J397)+1,"")</f>
         <v/>
       </c>
       <c r="K398" s="57">
-        <f>MOVIMIENTOS!$A419</f>
+        <f>MOVIMIENTOS!$A423</f>
         <v>0</v>
       </c>
       <c r="L398" s="54"/>
@@ -23531,11 +23942,11 @@
       <c r="H399" s="54"/>
       <c r="I399" s="54"/>
       <c r="J399" s="54" t="str">
-        <f>IF(AND(MOVIMIENTOS!$A420&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A419,MOVIMIENTOS!$A420)=0),COUNT(J$4:J398)+1,"")</f>
+        <f>IF(AND(MOVIMIENTOS!$A424&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A423,MOVIMIENTOS!$A424)=0),COUNT(J$4:J398)+1,"")</f>
         <v/>
       </c>
       <c r="K399" s="57">
-        <f>MOVIMIENTOS!$A420</f>
+        <f>MOVIMIENTOS!$A424</f>
         <v>0</v>
       </c>
       <c r="L399" s="54"/>
@@ -23553,11 +23964,11 @@
       <c r="H400" s="54"/>
       <c r="I400" s="54"/>
       <c r="J400" s="54" t="str">
-        <f>IF(AND(MOVIMIENTOS!$A421&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A420,MOVIMIENTOS!$A421)=0),COUNT(J$4:J399)+1,"")</f>
+        <f>IF(AND(MOVIMIENTOS!$A425&lt;&gt;"",COUNTIF(MOVIMIENTOS!$A$5:$A424,MOVIMIENTOS!$A425)=0),COUNT(J$4:J399)+1,"")</f>
         <v/>
       </c>
       <c r="K400" s="57">
-        <f>MOVIMIENTOS!$A421</f>
+        <f>MOVIMIENTOS!$A425</f>
         <v>0</v>
       </c>
       <c r="L400" s="54"/>
@@ -23594,7 +24005,7 @@
   <sheetData>
     <row r="1" spans="1:20" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="88" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B1" s="87"/>
       <c r="C1" s="87"/>
@@ -23618,7 +24029,7 @@
     </row>
     <row r="2" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="86" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B2" s="87"/>
       <c r="C2" s="87"/>
@@ -23666,13 +24077,13 @@
       <c r="A4" s="54"/>
       <c r="B4" s="54"/>
       <c r="C4" s="58" t="s">
+        <v>102</v>
+      </c>
+      <c r="D4" s="59" t="s">
+        <v>103</v>
+      </c>
+      <c r="E4" s="60" t="s">
         <v>104</v>
-      </c>
-      <c r="D4" s="59" t="s">
-        <v>105</v>
-      </c>
-      <c r="E4" s="60" t="s">
-        <v>106</v>
       </c>
       <c r="F4" s="54"/>
       <c r="G4" s="54"/>
@@ -23695,22 +24106,22 @@
         <v>2</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="E5" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="G5" s="1" t="s">
         <v>110</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>112</v>
       </c>
       <c r="H5" s="54"/>
       <c r="I5" s="54"/>
@@ -23731,22 +24142,22 @@
         <v>46214</v>
       </c>
       <c r="B6" s="81" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C6" s="82">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,11))*(MOVIMIENTOS!$B$5:$B$421="COMPRA")*MOVIMIENTOS!$I$5:$I$421)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,11))*(MOVIMIENTOS!$B$5:$B$425="COMPRA")*MOVIMIENTOS!$I$5:$I$425)</f>
         <v>0</v>
       </c>
       <c r="D6" s="82">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,11))*(MOVIMIENTOS!$B$5:$B$421="PROCESO")*MOVIMIENTOS!$I$5:$I$421)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,11))*(MOVIMIENTOS!$B$5:$B$425="PROCESO")*MOVIMIENTOS!$I$5:$I$425)</f>
         <v>0</v>
       </c>
       <c r="E6" s="82">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,11))*((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$421="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="ENVIO A TOTTUS"))*MOVIMIENTOS!$I$5:$I$421)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,11))*((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS"))*MOVIMIENTOS!$I$5:$I$425)</f>
         <v>0</v>
       </c>
       <c r="F6" s="81" t="str">
-        <f>"Selección: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,11))*(MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$421),"#,##0")&amp;" kg  ·  Chancho: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,11))*(MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*MOVIMIENTOS!$I$5:$I$421),"#,##0")&amp;" kg"&amp;IF(C6&gt;0,"  ·  "&amp;TEXT(D6/C6,"0%")&amp;" del ingreso","")</f>
+        <f>"Selección: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,11))*(MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$425),"#,##0")&amp;" kg  ·  Chancho: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,11))*(MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*MOVIMIENTOS!$I$5:$I$425),"#,##0")&amp;" kg"&amp;IF(C6&gt;0,"  ·  "&amp;TEXT(D6/C6,"0%")&amp;" del ingreso","")</f>
         <v>Selección: 0 kg  ·  Chancho: 0 kg</v>
       </c>
       <c r="G6" s="82">
@@ -23781,7 +24192,7 @@
       <c r="D7" s="56"/>
       <c r="E7" s="56"/>
       <c r="F7" s="61" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G7" s="56">
         <f>N(0)+N(C7)-N(E7)</f>
@@ -23806,7 +24217,7 @@
         <v>46214</v>
       </c>
       <c r="B8" s="61" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C8" s="56">
         <f>N(MOVIMIENTOS!$I7)</f>
@@ -23841,22 +24252,22 @@
         <v>46215</v>
       </c>
       <c r="B9" s="81" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C9" s="82">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,12))*(MOVIMIENTOS!$B$5:$B$421="COMPRA")*MOVIMIENTOS!$I$5:$I$421)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,12))*(MOVIMIENTOS!$B$5:$B$425="COMPRA")*MOVIMIENTOS!$I$5:$I$425)</f>
         <v>2910</v>
       </c>
       <c r="D9" s="82">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,12))*(MOVIMIENTOS!$B$5:$B$421="PROCESO")*MOVIMIENTOS!$I$5:$I$421)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,12))*(MOVIMIENTOS!$B$5:$B$425="PROCESO")*MOVIMIENTOS!$I$5:$I$425)</f>
         <v>2957</v>
       </c>
       <c r="E9" s="82">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,12))*((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$421="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="ENVIO A TOTTUS"))*MOVIMIENTOS!$I$5:$I$421)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,12))*((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS"))*MOVIMIENTOS!$I$5:$I$425)</f>
         <v>2121</v>
       </c>
       <c r="F9" s="81" t="str">
-        <f>"Selección: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,12))*(MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$421),"#,##0")&amp;" kg  ·  Chancho: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,12))*(MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*MOVIMIENTOS!$I$5:$I$421),"#,##0")&amp;" kg"&amp;IF(C9&gt;0,"  ·  "&amp;TEXT(D9/C9,"0%")&amp;" del ingreso","")</f>
+        <f>"Selección: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,12))*(MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$425),"#,##0")&amp;" kg  ·  Chancho: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,12))*(MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*MOVIMIENTOS!$I$5:$I$425),"#,##0")&amp;" kg"&amp;IF(C9&gt;0,"  ·  "&amp;TEXT(D9/C9,"0%")&amp;" del ingreso","")</f>
         <v>Selección: 2,375 kg  ·  Chancho: 582 kg  ·  102% del ingreso</v>
       </c>
       <c r="G9" s="82">
@@ -23882,7 +24293,7 @@
         <v>46215</v>
       </c>
       <c r="B10" s="63" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C10" s="64">
         <f>N(MOVIMIENTOS!$I9)</f>
@@ -23917,16 +24328,16 @@
         <v>46215</v>
       </c>
       <c r="B11" s="84" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C11" s="85"/>
       <c r="D11" s="85">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,12))*(MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$421)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,12))*(MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$425)</f>
         <v>2375</v>
       </c>
       <c r="E11" s="85"/>
       <c r="F11" s="84" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="G11" s="85">
         <f>N(G10)</f>
@@ -23951,7 +24362,7 @@
         <v>46215</v>
       </c>
       <c r="B12" s="61" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C12" s="56"/>
       <c r="D12" s="56">
@@ -23998,7 +24409,7 @@
         <v>2121</v>
       </c>
       <c r="F13" s="61" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G13" s="56">
         <f>N(G12)+N(C13)-N(E13)</f>
@@ -24023,22 +24434,22 @@
         <v>46216</v>
       </c>
       <c r="B14" s="81" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C14" s="82">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,13))*(MOVIMIENTOS!$B$5:$B$421="COMPRA")*MOVIMIENTOS!$I$5:$I$421)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,13))*(MOVIMIENTOS!$B$5:$B$425="COMPRA")*MOVIMIENTOS!$I$5:$I$425)</f>
         <v>3880</v>
       </c>
       <c r="D14" s="82">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,13))*(MOVIMIENTOS!$B$5:$B$421="PROCESO")*MOVIMIENTOS!$I$5:$I$421)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,13))*(MOVIMIENTOS!$B$5:$B$425="PROCESO")*MOVIMIENTOS!$I$5:$I$425)</f>
         <v>4071</v>
       </c>
       <c r="E14" s="82">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,13))*((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$421="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="ENVIO A TOTTUS"))*MOVIMIENTOS!$I$5:$I$421)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,13))*((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS"))*MOVIMIENTOS!$I$5:$I$425)</f>
         <v>3056</v>
       </c>
       <c r="F14" s="81" t="str">
-        <f>"Selección: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,13))*(MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$421),"#,##0")&amp;" kg  ·  Chancho: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,13))*(MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*MOVIMIENTOS!$I$5:$I$421),"#,##0")&amp;" kg"&amp;IF(C14&gt;0,"  ·  "&amp;TEXT(D14/C14,"0%")&amp;" del ingreso","")</f>
+        <f>"Selección: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,13))*(MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$425),"#,##0")&amp;" kg  ·  Chancho: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,13))*(MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*MOVIMIENTOS!$I$5:$I$425),"#,##0")&amp;" kg"&amp;IF(C14&gt;0,"  ·  "&amp;TEXT(D14/C14,"0%")&amp;" del ingreso","")</f>
         <v>Selección: 3,877 kg  ·  Chancho: 194 kg  ·  105% del ingreso</v>
       </c>
       <c r="G14" s="82">
@@ -24064,7 +24475,7 @@
         <v>46216</v>
       </c>
       <c r="B15" s="63" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C15" s="64">
         <f>N(MOVIMIENTOS!$I19)</f>
@@ -24099,16 +24510,16 @@
         <v>46216</v>
       </c>
       <c r="B16" s="84" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C16" s="85"/>
       <c r="D16" s="85">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,13))*(MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$421)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,13))*(MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$425)</f>
         <v>3877</v>
       </c>
       <c r="E16" s="85"/>
       <c r="F16" s="84" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="G16" s="85">
         <f>N(G15)</f>
@@ -24133,7 +24544,7 @@
         <v>46216</v>
       </c>
       <c r="B17" s="61" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C17" s="56"/>
       <c r="D17" s="56">
@@ -24180,7 +24591,7 @@
         <v>3056</v>
       </c>
       <c r="F18" s="61" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="G18" s="56">
         <f>N(G17)+N(C18)-N(E18)</f>
@@ -24205,22 +24616,22 @@
         <v>46217</v>
       </c>
       <c r="B19" s="81" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C19" s="82">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,14))*(MOVIMIENTOS!$B$5:$B$421="COMPRA")*MOVIMIENTOS!$I$5:$I$421)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,14))*(MOVIMIENTOS!$B$5:$B$425="COMPRA")*MOVIMIENTOS!$I$5:$I$425)</f>
         <v>3880</v>
       </c>
       <c r="D19" s="82">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,14))*(MOVIMIENTOS!$B$5:$B$421="PROCESO")*MOVIMIENTOS!$I$5:$I$421)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,14))*(MOVIMIENTOS!$B$5:$B$425="PROCESO")*MOVIMIENTOS!$I$5:$I$425)</f>
         <v>3813</v>
       </c>
       <c r="E19" s="82">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,14))*((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$421="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="ENVIO A TOTTUS"))*MOVIMIENTOS!$I$5:$I$421)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,14))*((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS"))*MOVIMIENTOS!$I$5:$I$425)</f>
         <v>3379</v>
       </c>
       <c r="F19" s="81" t="str">
-        <f>"Selección: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,14))*(MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$421),"#,##0")&amp;" kg  ·  Chancho: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,14))*(MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*MOVIMIENTOS!$I$5:$I$421),"#,##0")&amp;" kg"&amp;IF(C19&gt;0,"  ·  "&amp;TEXT(D19/C19,"0%")&amp;" del ingreso","")</f>
+        <f>"Selección: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,14))*(MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$425),"#,##0")&amp;" kg  ·  Chancho: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,14))*(MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*MOVIMIENTOS!$I$5:$I$425),"#,##0")&amp;" kg"&amp;IF(C19&gt;0,"  ·  "&amp;TEXT(D19/C19,"0%")&amp;" del ingreso","")</f>
         <v>Selección: 3,134 kg  ·  Chancho: 679 kg  ·  98% del ingreso</v>
       </c>
       <c r="G19" s="82">
@@ -24246,7 +24657,7 @@
         <v>46217</v>
       </c>
       <c r="B20" s="63" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C20" s="64">
         <f>N(MOVIMIENTOS!$I29)</f>
@@ -24281,16 +24692,16 @@
         <v>46217</v>
       </c>
       <c r="B21" s="84" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C21" s="85"/>
       <c r="D21" s="85">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,14))*(MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$421)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,14))*(MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$425)</f>
         <v>3134</v>
       </c>
       <c r="E21" s="85"/>
       <c r="F21" s="84" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G21" s="85">
         <f>N(G20)</f>
@@ -24315,7 +24726,7 @@
         <v>46217</v>
       </c>
       <c r="B22" s="61" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C22" s="56"/>
       <c r="D22" s="56">
@@ -24362,7 +24773,7 @@
         <v>3379</v>
       </c>
       <c r="F23" s="61" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="G23" s="56">
         <f>N(G22)+N(C23)-N(E23)</f>
@@ -24387,22 +24798,22 @@
         <v>46218</v>
       </c>
       <c r="B24" s="81" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C24" s="82">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,15))*(MOVIMIENTOS!$B$5:$B$421="COMPRA")*MOVIMIENTOS!$I$5:$I$421)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,15))*(MOVIMIENTOS!$B$5:$B$425="COMPRA")*MOVIMIENTOS!$I$5:$I$425)</f>
         <v>3880</v>
       </c>
       <c r="D24" s="82">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,15))*(MOVIMIENTOS!$B$5:$B$421="PROCESO")*MOVIMIENTOS!$I$5:$I$421)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,15))*(MOVIMIENTOS!$B$5:$B$425="PROCESO")*MOVIMIENTOS!$I$5:$I$425)</f>
         <v>3834</v>
       </c>
       <c r="E24" s="82">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,15))*((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$421="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="ENVIO A TOTTUS"))*MOVIMIENTOS!$I$5:$I$421)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,15))*((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS"))*MOVIMIENTOS!$I$5:$I$425)</f>
         <v>2971</v>
       </c>
       <c r="F24" s="81" t="str">
-        <f>"Selección: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,15))*(MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$421),"#,##0")&amp;" kg  ·  Chancho: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,15))*(MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*MOVIMIENTOS!$I$5:$I$421),"#,##0")&amp;" kg"&amp;IF(C24&gt;0,"  ·  "&amp;TEXT(D24/C24,"0%")&amp;" del ingreso","")</f>
+        <f>"Selección: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,15))*(MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$425),"#,##0")&amp;" kg  ·  Chancho: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,15))*(MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*MOVIMIENTOS!$I$5:$I$425),"#,##0")&amp;" kg"&amp;IF(C24&gt;0,"  ·  "&amp;TEXT(D24/C24,"0%")&amp;" del ingreso","")</f>
         <v>Selección: 3,349 kg  ·  Chancho: 485 kg  ·  99% del ingreso</v>
       </c>
       <c r="G24" s="82">
@@ -24428,7 +24839,7 @@
         <v>46218</v>
       </c>
       <c r="B25" s="63" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C25" s="64">
         <f>N(MOVIMIENTOS!$I39)</f>
@@ -24463,16 +24874,16 @@
         <v>46218</v>
       </c>
       <c r="B26" s="84" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C26" s="85"/>
       <c r="D26" s="85">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,15))*(MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$421)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,15))*(MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$425)</f>
         <v>3349</v>
       </c>
       <c r="E26" s="85"/>
       <c r="F26" s="84" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="G26" s="85">
         <f>N(G25)</f>
@@ -24497,7 +24908,7 @@
         <v>46218</v>
       </c>
       <c r="B27" s="61" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C27" s="56"/>
       <c r="D27" s="56">
@@ -24544,7 +24955,7 @@
         <v>2971</v>
       </c>
       <c r="F28" s="61" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G28" s="56">
         <f>N(G27)+N(C28)-N(E28)</f>
@@ -24601,22 +25012,22 @@
         <v>46219</v>
       </c>
       <c r="B30" s="81" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C30" s="82">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,16))*(MOVIMIENTOS!$B$5:$B$421="COMPRA")*MOVIMIENTOS!$I$5:$I$421)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,16))*(MOVIMIENTOS!$B$5:$B$425="COMPRA")*MOVIMIENTOS!$I$5:$I$425)</f>
         <v>3880</v>
       </c>
       <c r="D30" s="82">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,16))*(MOVIMIENTOS!$B$5:$B$421="PROCESO")*MOVIMIENTOS!$I$5:$I$421)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,16))*(MOVIMIENTOS!$B$5:$B$425="PROCESO")*MOVIMIENTOS!$I$5:$I$425)</f>
         <v>3782</v>
       </c>
       <c r="E30" s="82">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,16))*((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$421="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="ENVIO A TOTTUS"))*MOVIMIENTOS!$I$5:$I$421)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,16))*((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS"))*MOVIMIENTOS!$I$5:$I$425)</f>
         <v>3302</v>
       </c>
       <c r="F30" s="81" t="str">
-        <f>"Selección: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,16))*(MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$421),"#,##0")&amp;" kg  ·  Chancho: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,16))*(MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*MOVIMIENTOS!$I$5:$I$421),"#,##0")&amp;" kg"&amp;IF(C30&gt;0,"  ·  "&amp;TEXT(D30/C30,"0%")&amp;" del ingreso","")</f>
+        <f>"Selección: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,16))*(MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$425),"#,##0")&amp;" kg  ·  Chancho: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,16))*(MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*MOVIMIENTOS!$I$5:$I$425),"#,##0")&amp;" kg"&amp;IF(C30&gt;0,"  ·  "&amp;TEXT(D30/C30,"0%")&amp;" del ingreso","")</f>
         <v>Selección: 3,394 kg  ·  Chancho: 388 kg  ·  97% del ingreso</v>
       </c>
       <c r="G30" s="82">
@@ -24642,7 +25053,7 @@
         <v>46219</v>
       </c>
       <c r="B31" s="63" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C31" s="64">
         <f>N(MOVIMIENTOS!$I50)</f>
@@ -24677,16 +25088,16 @@
         <v>46219</v>
       </c>
       <c r="B32" s="84" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C32" s="85"/>
       <c r="D32" s="85">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,16))*(MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$421)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,16))*(MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$425)</f>
         <v>3394</v>
       </c>
       <c r="E32" s="85"/>
       <c r="F32" s="84" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G32" s="85">
         <f>N(G31)</f>
@@ -24711,7 +25122,7 @@
         <v>46219</v>
       </c>
       <c r="B33" s="61" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C33" s="56"/>
       <c r="D33" s="56">
@@ -24758,7 +25169,7 @@
         <v>3302</v>
       </c>
       <c r="F34" s="61" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G34" s="56">
         <f>N(G33)+N(C34)-N(E34)</f>
@@ -24783,22 +25194,22 @@
         <v>46220</v>
       </c>
       <c r="B35" s="81" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C35" s="82">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,17))*(MOVIMIENTOS!$B$5:$B$421="COMPRA")*MOVIMIENTOS!$I$5:$I$421)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,17))*(MOVIMIENTOS!$B$5:$B$425="COMPRA")*MOVIMIENTOS!$I$5:$I$425)</f>
         <v>6305</v>
       </c>
       <c r="D35" s="82">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,17))*(MOVIMIENTOS!$B$5:$B$421="PROCESO")*MOVIMIENTOS!$I$5:$I$421)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,17))*(MOVIMIENTOS!$B$5:$B$425="PROCESO")*MOVIMIENTOS!$I$5:$I$425)</f>
         <v>6169</v>
       </c>
       <c r="E35" s="82">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,17))*((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$421="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="ENVIO A TOTTUS"))*MOVIMIENTOS!$I$5:$I$421)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,17))*((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS"))*MOVIMIENTOS!$I$5:$I$425)</f>
         <v>3413</v>
       </c>
       <c r="F35" s="81" t="str">
-        <f>"Selección: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,17))*(MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$421),"#,##0")&amp;" kg  ·  Chancho: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,17))*(MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*MOVIMIENTOS!$I$5:$I$421),"#,##0")&amp;" kg"&amp;IF(C35&gt;0,"  ·  "&amp;TEXT(D35/C35,"0%")&amp;" del ingreso","")</f>
+        <f>"Selección: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,17))*(MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$425),"#,##0")&amp;" kg  ·  Chancho: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,17))*(MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*MOVIMIENTOS!$I$5:$I$425),"#,##0")&amp;" kg"&amp;IF(C35&gt;0,"  ·  "&amp;TEXT(D35/C35,"0%")&amp;" del ingreso","")</f>
         <v>Selección: 5,102 kg  ·  Chancho: 1,067 kg  ·  98% del ingreso</v>
       </c>
       <c r="G35" s="82">
@@ -24824,7 +25235,7 @@
         <v>46220</v>
       </c>
       <c r="B36" s="63" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C36" s="64">
         <f>N(MOVIMIENTOS!$I60)</f>
@@ -24859,16 +25270,16 @@
         <v>46220</v>
       </c>
       <c r="B37" s="84" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C37" s="85"/>
       <c r="D37" s="85">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,17))*(MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$421)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,17))*(MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$425)</f>
         <v>5102</v>
       </c>
       <c r="E37" s="85"/>
       <c r="F37" s="84" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G37" s="85">
         <f>N(G36)</f>
@@ -24893,7 +25304,7 @@
         <v>46220</v>
       </c>
       <c r="B38" s="61" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C38" s="56"/>
       <c r="D38" s="56">
@@ -24940,7 +25351,7 @@
         <v>3413</v>
       </c>
       <c r="F39" s="61" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G39" s="56">
         <f>N(G38)+N(C39)-N(E39)</f>
@@ -24997,7 +25408,7 @@
         <v>46220</v>
       </c>
       <c r="B41" s="63" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C41" s="64">
         <f>N(MOVIMIENTOS!$I71)</f>
@@ -25032,7 +25443,7 @@
         <v>46220</v>
       </c>
       <c r="B42" s="61" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C42" s="56"/>
       <c r="D42" s="56">
@@ -25070,22 +25481,22 @@
         <v>46221</v>
       </c>
       <c r="B43" s="81" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C43" s="82">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,18))*(MOVIMIENTOS!$B$5:$B$421="COMPRA")*MOVIMIENTOS!$I$5:$I$421)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,18))*(MOVIMIENTOS!$B$5:$B$425="COMPRA")*MOVIMIENTOS!$I$5:$I$425)</f>
         <v>3201</v>
       </c>
       <c r="D43" s="82">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,18))*(MOVIMIENTOS!$B$5:$B$421="PROCESO")*MOVIMIENTOS!$I$5:$I$421)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,18))*(MOVIMIENTOS!$B$5:$B$425="PROCESO")*MOVIMIENTOS!$I$5:$I$425)</f>
         <v>3295</v>
       </c>
       <c r="E43" s="82">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,18))*((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$421="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="ENVIO A TOTTUS"))*MOVIMIENTOS!$I$5:$I$421)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,18))*((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS"))*MOVIMIENTOS!$I$5:$I$425)</f>
         <v>3168</v>
       </c>
       <c r="F43" s="81" t="str">
-        <f>"Selección: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,18))*(MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$421),"#,##0")&amp;" kg  ·  Chancho: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,18))*(MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*MOVIMIENTOS!$I$5:$I$421),"#,##0")&amp;" kg"&amp;IF(C43&gt;0,"  ·  "&amp;TEXT(D43/C43,"0%")&amp;" del ingreso","")</f>
+        <f>"Selección: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,18))*(MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$425),"#,##0")&amp;" kg  ·  Chancho: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,18))*(MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*MOVIMIENTOS!$I$5:$I$425),"#,##0")&amp;" kg"&amp;IF(C43&gt;0,"  ·  "&amp;TEXT(D43/C43,"0%")&amp;" del ingreso","")</f>
         <v>Selección: 2,325 kg  ·  Chancho: 970 kg  ·  103% del ingreso</v>
       </c>
       <c r="G43" s="82">
@@ -25120,7 +25531,7 @@
         <v>3168</v>
       </c>
       <c r="F44" s="61" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G44" s="56">
         <f>N(G42)+N(C44)-N(E44)</f>
@@ -25145,16 +25556,16 @@
         <v>46221</v>
       </c>
       <c r="B45" s="84" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C45" s="85"/>
       <c r="D45" s="85">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,18))*(MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$421)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,18))*(MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$425)</f>
         <v>2325</v>
       </c>
       <c r="E45" s="85"/>
       <c r="F45" s="84" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="G45" s="85">
         <f>N(G44)</f>
@@ -25179,7 +25590,7 @@
         <v>46221</v>
       </c>
       <c r="B46" s="61" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C46" s="56"/>
       <c r="D46" s="56">
@@ -25217,7 +25628,7 @@
         <v>46221</v>
       </c>
       <c r="B47" s="61" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C47" s="56"/>
       <c r="D47" s="56"/>
@@ -25249,7 +25660,7 @@
         <v>46221</v>
       </c>
       <c r="B48" s="63" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C48" s="64">
         <f>N(MOVIMIENTOS!$I85)</f>
@@ -25284,22 +25695,22 @@
         <v>46222</v>
       </c>
       <c r="B49" s="81" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C49" s="82">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,19))*(MOVIMIENTOS!$B$5:$B$421="COMPRA")*MOVIMIENTOS!$I$5:$I$421)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,19))*(MOVIMIENTOS!$B$5:$B$425="COMPRA")*MOVIMIENTOS!$I$5:$I$425)</f>
         <v>1649</v>
       </c>
       <c r="D49" s="82">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,19))*(MOVIMIENTOS!$B$5:$B$421="PROCESO")*MOVIMIENTOS!$I$5:$I$421)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,19))*(MOVIMIENTOS!$B$5:$B$425="PROCESO")*MOVIMIENTOS!$I$5:$I$425)</f>
         <v>1469</v>
       </c>
       <c r="E49" s="82">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,19))*((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$421="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="ENVIO A TOTTUS"))*MOVIMIENTOS!$I$5:$I$421)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,19))*((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS"))*MOVIMIENTOS!$I$5:$I$425)</f>
         <v>1883</v>
       </c>
       <c r="F49" s="81" t="str">
-        <f>"Selección: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,19))*(MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$421),"#,##0")&amp;" kg  ·  Chancho: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,19))*(MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*MOVIMIENTOS!$I$5:$I$421),"#,##0")&amp;" kg"&amp;IF(C49&gt;0,"  ·  "&amp;TEXT(D49/C49,"0%")&amp;" del ingreso","")</f>
+        <f>"Selección: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,19))*(MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$425),"#,##0")&amp;" kg  ·  Chancho: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,19))*(MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*MOVIMIENTOS!$I$5:$I$425),"#,##0")&amp;" kg"&amp;IF(C49&gt;0,"  ·  "&amp;TEXT(D49/C49,"0%")&amp;" del ingreso","")</f>
         <v>Selección: 1,178 kg  ·  Chancho: 291 kg  ·  89% del ingreso</v>
       </c>
       <c r="G49" s="82">
@@ -25325,16 +25736,16 @@
         <v>46222</v>
       </c>
       <c r="B50" s="84" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C50" s="85"/>
       <c r="D50" s="85">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,19))*(MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$421)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,19))*(MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$425)</f>
         <v>1178</v>
       </c>
       <c r="E50" s="85"/>
       <c r="F50" s="84" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="G50" s="85">
         <f>N(G48)</f>
@@ -25359,7 +25770,7 @@
         <v>46222</v>
       </c>
       <c r="B51" s="61" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C51" s="56"/>
       <c r="D51" s="56">
@@ -25406,7 +25817,7 @@
         <v>1883</v>
       </c>
       <c r="F52" s="61" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G52" s="56">
         <f>N(G51)+N(C52)-N(E52)</f>
@@ -25431,7 +25842,7 @@
         <v>46222</v>
       </c>
       <c r="B53" s="63" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C53" s="64">
         <f>N(MOVIMIENTOS!$I95)</f>
@@ -25466,22 +25877,22 @@
         <v>46223</v>
       </c>
       <c r="B54" s="81" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C54" s="82">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,20))*(MOVIMIENTOS!$B$5:$B$421="COMPRA")*MOVIMIENTOS!$I$5:$I$421)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,20))*(MOVIMIENTOS!$B$5:$B$425="COMPRA")*MOVIMIENTOS!$I$5:$I$425)</f>
         <v>4656</v>
       </c>
       <c r="D54" s="82">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,20))*(MOVIMIENTOS!$B$5:$B$421="PROCESO")*MOVIMIENTOS!$I$5:$I$421)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,20))*(MOVIMIENTOS!$B$5:$B$425="PROCESO")*MOVIMIENTOS!$I$5:$I$425)</f>
         <v>4648.5</v>
       </c>
       <c r="E54" s="82">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,20))*((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$421="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="ENVIO A TOTTUS"))*MOVIMIENTOS!$I$5:$I$421)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,20))*((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS"))*MOVIMIENTOS!$I$5:$I$425)</f>
         <v>3294</v>
       </c>
       <c r="F54" s="81" t="str">
-        <f>"Selección: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,20))*(MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$421),"#,##0")&amp;" kg  ·  Chancho: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,20))*(MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*MOVIMIENTOS!$I$5:$I$421),"#,##0")&amp;" kg"&amp;IF(C54&gt;0,"  ·  "&amp;TEXT(D54/C54,"0%")&amp;" del ingreso","")</f>
+        <f>"Selección: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,20))*(MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$425),"#,##0")&amp;" kg  ·  Chancho: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,20))*(MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*MOVIMIENTOS!$I$5:$I$425),"#,##0")&amp;" kg"&amp;IF(C54&gt;0,"  ·  "&amp;TEXT(D54/C54,"0%")&amp;" del ingreso","")</f>
         <v>Selección: 4,018 kg  ·  Chancho: 631 kg  ·  100% del ingreso</v>
       </c>
       <c r="G54" s="82">
@@ -25507,7 +25918,7 @@
         <v>46223</v>
       </c>
       <c r="B55" s="63" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C55" s="64">
         <f>N(MOVIMIENTOS!$I96)</f>
@@ -25542,16 +25953,16 @@
         <v>46223</v>
       </c>
       <c r="B56" s="84" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C56" s="85"/>
       <c r="D56" s="85">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,20))*(MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$421)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,20))*(MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$425)</f>
         <v>4018</v>
       </c>
       <c r="E56" s="85"/>
       <c r="F56" s="84" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G56" s="85">
         <f>N(G55)</f>
@@ -25576,7 +25987,7 @@
         <v>46223</v>
       </c>
       <c r="B57" s="61" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C57" s="56"/>
       <c r="D57" s="56">
@@ -25623,7 +26034,7 @@
         <v>3294</v>
       </c>
       <c r="F58" s="61" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="G58" s="56">
         <f>N(G57)+N(C58)-N(E58)</f>
@@ -25680,7 +26091,7 @@
         <v>46223</v>
       </c>
       <c r="B60" s="61" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C60" s="56"/>
       <c r="D60" s="56"/>
@@ -25712,7 +26123,7 @@
         <v>46223</v>
       </c>
       <c r="B61" s="61" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C61" s="56"/>
       <c r="D61" s="56"/>
@@ -25744,22 +26155,22 @@
         <v>46224</v>
       </c>
       <c r="B62" s="81" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C62" s="82">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,21))*(MOVIMIENTOS!$B$5:$B$421="COMPRA")*MOVIMIENTOS!$I$5:$I$421)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,21))*(MOVIMIENTOS!$B$5:$B$425="COMPRA")*MOVIMIENTOS!$I$5:$I$425)</f>
         <v>2134</v>
       </c>
       <c r="D62" s="82">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,21))*(MOVIMIENTOS!$B$5:$B$421="PROCESO")*MOVIMIENTOS!$I$5:$I$421)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,21))*(MOVIMIENTOS!$B$5:$B$425="PROCESO")*MOVIMIENTOS!$I$5:$I$425)</f>
         <v>4879</v>
       </c>
       <c r="E62" s="82">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,21))*((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$421="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="ENVIO A TOTTUS"))*MOVIMIENTOS!$I$5:$I$421)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,21))*((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS"))*MOVIMIENTOS!$I$5:$I$425)</f>
         <v>3260</v>
       </c>
       <c r="F62" s="81" t="str">
-        <f>"Selección: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,21))*(MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$421),"#,##0")&amp;" kg  ·  Chancho: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,21))*(MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*MOVIMIENTOS!$I$5:$I$421),"#,##0")&amp;" kg"&amp;IF(C62&gt;0,"  ·  "&amp;TEXT(D62/C62,"0%")&amp;" del ingreso","")</f>
+        <f>"Selección: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,21))*(MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$425),"#,##0")&amp;" kg  ·  Chancho: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,21))*(MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*MOVIMIENTOS!$I$5:$I$425),"#,##0")&amp;" kg"&amp;IF(C62&gt;0,"  ·  "&amp;TEXT(D62/C62,"0%")&amp;" del ingreso","")</f>
         <v>Selección: 4,200 kg  ·  Chancho: 679 kg  ·  229% del ingreso</v>
       </c>
       <c r="G62" s="82">
@@ -25785,7 +26196,7 @@
         <v>46224</v>
       </c>
       <c r="B63" s="63" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C63" s="64">
         <f>N(MOVIMIENTOS!$I109)</f>
@@ -25820,16 +26231,16 @@
         <v>46224</v>
       </c>
       <c r="B64" s="84" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C64" s="85"/>
       <c r="D64" s="85">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,21))*(MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$421)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,21))*(MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$425)</f>
         <v>4200</v>
       </c>
       <c r="E64" s="85"/>
       <c r="F64" s="84" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="G64" s="85">
         <f>N(G63)</f>
@@ -25854,7 +26265,7 @@
         <v>46224</v>
       </c>
       <c r="B65" s="61" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C65" s="56"/>
       <c r="D65" s="56">
@@ -25892,7 +26303,7 @@
         <v>46224</v>
       </c>
       <c r="B66" s="61" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C66" s="56"/>
       <c r="D66" s="56">
@@ -25939,7 +26350,7 @@
         <v>3260</v>
       </c>
       <c r="F67" s="61" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="G67" s="56">
         <f t="shared" si="0"/>
@@ -25964,13 +26375,13 @@
         <v>46224</v>
       </c>
       <c r="B68" s="61" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C68" s="56"/>
       <c r="D68" s="56"/>
       <c r="E68" s="56"/>
       <c r="F68" s="61" t="str">
-        <f>MOVIMIENTOS!$E122&amp;" jabas rechazadas · van a reproceso (merma del día: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=MOVIMIENTOS!$A122)*(MOVIMIENTOS!$B$5:$B$421="RECHAZO")*(MOVIMIENTOS!$D$5:$D$421="jabas")*MOVIMIENTOS!$E$5:$E$421*IFERROR(_xlfn.SWITCH(MOVIMIENTOS!$C$5:$C$421,"A",15,"P",18,"C",17,"M",17,0),0))-SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=MOVIMIENTOS!$A122)*(MOVIMIENTOS!$B$5:$B$421="REPROCESO")*MOVIMIENTOS!$I$5:$I$421),"+#,##0;-#,##0;0")&amp;" kg)"</f>
+        <f>MOVIMIENTOS!$E122&amp;" jabas rechazadas · van a reproceso (merma del día: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=MOVIMIENTOS!$A122)*(MOVIMIENTOS!$B$5:$B$425="RECHAZO")*(MOVIMIENTOS!$D$5:$D$425="jabas")*MOVIMIENTOS!$E$5:$E$425*IFERROR(_xlfn.SWITCH(MOVIMIENTOS!$C$5:$C$425,"A",15,"P",18,"C",17,"M",17,0),0))-SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=MOVIMIENTOS!$A122)*(MOVIMIENTOS!$B$5:$B$425="REPROCESO")*MOVIMIENTOS!$I$5:$I$425),"+#,##0;-#,##0;0")&amp;" kg)"</f>
         <v>1 jabas rechazadas · van a reproceso (merma del día: +17 kg)</v>
       </c>
       <c r="G68" s="56">
@@ -25996,13 +26407,13 @@
         <v>46224</v>
       </c>
       <c r="B69" s="61" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C69" s="56"/>
       <c r="D69" s="56"/>
       <c r="E69" s="56"/>
       <c r="F69" s="61" t="str">
-        <f>MOVIMIENTOS!$E123&amp;" jabas rechazadas · van a reproceso (merma del día: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=MOVIMIENTOS!$A123)*(MOVIMIENTOS!$B$5:$B$421="RECHAZO")*(MOVIMIENTOS!$D$5:$D$421="jabas")*MOVIMIENTOS!$E$5:$E$421*IFERROR(_xlfn.SWITCH(MOVIMIENTOS!$C$5:$C$421,"A",15,"P",18,"C",17,"M",17,0),0))-SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=MOVIMIENTOS!$A123)*(MOVIMIENTOS!$B$5:$B$421="REPROCESO")*MOVIMIENTOS!$I$5:$I$421),"+#,##0;-#,##0;0")&amp;" kg)"</f>
+        <f>MOVIMIENTOS!$E123&amp;" jabas rechazadas · van a reproceso (merma del día: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=MOVIMIENTOS!$A123)*(MOVIMIENTOS!$B$5:$B$425="RECHAZO")*(MOVIMIENTOS!$D$5:$D$425="jabas")*MOVIMIENTOS!$E$5:$E$425*IFERROR(_xlfn.SWITCH(MOVIMIENTOS!$C$5:$C$425,"A",15,"P",18,"C",17,"M",17,0),0))-SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=MOVIMIENTOS!$A123)*(MOVIMIENTOS!$B$5:$B$425="REPROCESO")*MOVIMIENTOS!$I$5:$I$425),"+#,##0;-#,##0;0")&amp;" kg)"</f>
         <v>1 jabas rechazadas · van a reproceso (merma del día: +17 kg)</v>
       </c>
       <c r="G69" s="56">
@@ -26028,7 +26439,7 @@
         <v>46224</v>
       </c>
       <c r="B70" s="61" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C70" s="56"/>
       <c r="D70" s="56"/>
@@ -26060,7 +26471,7 @@
         <v>46224</v>
       </c>
       <c r="B71" s="61" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C71" s="56"/>
       <c r="D71" s="56"/>
@@ -26101,7 +26512,7 @@
       <c r="D72" s="56"/>
       <c r="E72" s="56"/>
       <c r="F72" s="61" t="str">
-        <f>MOVIMIENTOS!$E126&amp;" kg recuperados (merma del día: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=MOVIMIENTOS!$A126)*(MOVIMIENTOS!$B$5:$B$421="RECHAZO")*(MOVIMIENTOS!$D$5:$D$421="jabas")*MOVIMIENTOS!$E$5:$E$421*IFERROR(_xlfn.SWITCH(MOVIMIENTOS!$C$5:$C$421,"A",15,"P",18,"C",17,"M",17,0),0))-SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=MOVIMIENTOS!$A126)*(MOVIMIENTOS!$B$5:$B$421="REPROCESO")*MOVIMIENTOS!$I$5:$I$421),"+#,##0;-#,##0;0")&amp;" kg)"</f>
+        <f>MOVIMIENTOS!$E126&amp;" kg recuperados (merma del día: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=MOVIMIENTOS!$A126)*(MOVIMIENTOS!$B$5:$B$425="RECHAZO")*(MOVIMIENTOS!$D$5:$D$425="jabas")*MOVIMIENTOS!$E$5:$E$425*IFERROR(_xlfn.SWITCH(MOVIMIENTOS!$C$5:$C$425,"A",15,"P",18,"C",17,"M",17,0),0))-SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=MOVIMIENTOS!$A126)*(MOVIMIENTOS!$B$5:$B$425="REPROCESO")*MOVIMIENTOS!$I$5:$I$425),"+#,##0;-#,##0;0")&amp;" kg)"</f>
         <v>17 kg recuperados (merma del día: +13 kg)</v>
       </c>
       <c r="G72" s="56">
@@ -26127,22 +26538,22 @@
         <v>46225</v>
       </c>
       <c r="B73" s="81" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C73" s="82">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,22))*(MOVIMIENTOS!$B$5:$B$421="COMPRA")*MOVIMIENTOS!$I$5:$I$421)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,22))*(MOVIMIENTOS!$B$5:$B$425="COMPRA")*MOVIMIENTOS!$I$5:$I$425)</f>
         <v>6790</v>
       </c>
       <c r="D73" s="82">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,22))*(MOVIMIENTOS!$B$5:$B$421="PROCESO")*MOVIMIENTOS!$I$5:$I$421)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,22))*(MOVIMIENTOS!$B$5:$B$425="PROCESO")*MOVIMIENTOS!$I$5:$I$425)</f>
         <v>4025</v>
       </c>
       <c r="E73" s="82">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,22))*((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$421="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="ENVIO A TOTTUS"))*MOVIMIENTOS!$I$5:$I$421)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,22))*((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS"))*MOVIMIENTOS!$I$5:$I$425)</f>
         <v>3294</v>
       </c>
       <c r="F73" s="81" t="str">
-        <f>"Selección: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,22))*(MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$421),"#,##0")&amp;" kg  ·  Chancho: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,22))*(MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*MOVIMIENTOS!$I$5:$I$421),"#,##0")&amp;" kg"&amp;IF(C73&gt;0,"  ·  "&amp;TEXT(D73/C73,"0%")&amp;" del ingreso","")</f>
+        <f>"Selección: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,22))*(MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$425),"#,##0")&amp;" kg  ·  Chancho: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,22))*(MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*MOVIMIENTOS!$I$5:$I$425),"#,##0")&amp;" kg"&amp;IF(C73&gt;0,"  ·  "&amp;TEXT(D73/C73,"0%")&amp;" del ingreso","")</f>
         <v>Selección: 3,249 kg  ·  Chancho: 776 kg  ·  59% del ingreso</v>
       </c>
       <c r="G73" s="82">
@@ -26168,7 +26579,7 @@
         <v>46225</v>
       </c>
       <c r="B74" s="63" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C74" s="64">
         <f>N(MOVIMIENTOS!$I127)</f>
@@ -26203,16 +26614,16 @@
         <v>46225</v>
       </c>
       <c r="B75" s="84" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C75" s="85"/>
       <c r="D75" s="85">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,22))*(MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$421)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,22))*(MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$425)</f>
         <v>3249</v>
       </c>
       <c r="E75" s="85"/>
       <c r="F75" s="84" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="G75" s="85">
         <f>N(G74)</f>
@@ -26237,7 +26648,7 @@
         <v>46225</v>
       </c>
       <c r="B76" s="61" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C76" s="56"/>
       <c r="D76" s="56">
@@ -26319,7 +26730,7 @@
         <v>3294</v>
       </c>
       <c r="F78" s="61" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G78" s="56">
         <f t="shared" si="1"/>
@@ -26351,7 +26762,7 @@
       <c r="E79" s="56"/>
       <c r="F79" s="61" t="str">
         <f>TRIM(IF(MOVIMIENTOS!$G138&lt;&gt;"",MOVIMIENTOS!$G138&amp;"  ","")&amp;IF(N(MOVIMIENTOS!$E138)&gt;0,MOVIMIENTOS!$E138&amp;" "&amp;MOVIMIENTOS!$D138&amp;"  ","")&amp;IF(MOVIMIENTOS!$H138&lt;&gt;"",MOVIMIENTOS!$H138,""))</f>
-        <v>S/T 10 sacos POR REGULARIZAR</v>
+        <v>FALTA 10 sacos FALTA</v>
       </c>
       <c r="G79" s="56">
         <f t="shared" si="1"/>
@@ -26376,13 +26787,13 @@
         <v>46225</v>
       </c>
       <c r="B80" s="61" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C80" s="56"/>
       <c r="D80" s="56"/>
       <c r="E80" s="56"/>
       <c r="F80" s="61" t="str">
-        <f>MOVIMIENTOS!$E139&amp;" jabas rechazadas · van a reproceso (merma del día: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=MOVIMIENTOS!$A139)*(MOVIMIENTOS!$B$5:$B$421="RECHAZO")*(MOVIMIENTOS!$D$5:$D$421="jabas")*MOVIMIENTOS!$E$5:$E$421*IFERROR(_xlfn.SWITCH(MOVIMIENTOS!$C$5:$C$421,"A",15,"P",18,"C",17,"M",17,0),0))-SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=MOVIMIENTOS!$A139)*(MOVIMIENTOS!$B$5:$B$421="REPROCESO")*MOVIMIENTOS!$I$5:$I$421),"+#,##0;-#,##0;0")&amp;" kg)"</f>
+        <f>MOVIMIENTOS!$E139&amp;" jabas rechazadas · van a reproceso (merma del día: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=MOVIMIENTOS!$A139)*(MOVIMIENTOS!$B$5:$B$425="RECHAZO")*(MOVIMIENTOS!$D$5:$D$425="jabas")*MOVIMIENTOS!$E$5:$E$425*IFERROR(_xlfn.SWITCH(MOVIMIENTOS!$C$5:$C$425,"A",15,"P",18,"C",17,"M",17,0),0))-SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=MOVIMIENTOS!$A139)*(MOVIMIENTOS!$B$5:$B$425="REPROCESO")*MOVIMIENTOS!$I$5:$I$425),"+#,##0;-#,##0;0")&amp;" kg)"</f>
         <v>1 jabas rechazadas · van a reproceso (merma del día: +9 kg)</v>
       </c>
       <c r="G80" s="56">
@@ -26408,7 +26819,7 @@
         <v>46225</v>
       </c>
       <c r="B81" s="61" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C81" s="56">
         <f>N(MOVIMIENTOS!$I140)</f>
@@ -26440,7 +26851,7 @@
         <v>46225</v>
       </c>
       <c r="B82" s="61" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C82" s="56"/>
       <c r="D82" s="56"/>
@@ -26481,7 +26892,7 @@
       <c r="D83" s="56"/>
       <c r="E83" s="56"/>
       <c r="F83" s="61" t="str">
-        <f>MOVIMIENTOS!$E142&amp;" kg recuperados (merma del día: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=MOVIMIENTOS!$A142)*(MOVIMIENTOS!$B$5:$B$421="RECHAZO")*(MOVIMIENTOS!$D$5:$D$421="jabas")*MOVIMIENTOS!$E$5:$E$421*IFERROR(_xlfn.SWITCH(MOVIMIENTOS!$C$5:$C$421,"A",15,"P",18,"C",17,"M",17,0),0))-SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=MOVIMIENTOS!$A142)*(MOVIMIENTOS!$B$5:$B$421="REPROCESO")*MOVIMIENTOS!$I$5:$I$421),"+#,##0;-#,##0;0")&amp;" kg)"</f>
+        <f>MOVIMIENTOS!$E142&amp;" kg recuperados (merma del día: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=MOVIMIENTOS!$A142)*(MOVIMIENTOS!$B$5:$B$425="RECHAZO")*(MOVIMIENTOS!$D$5:$D$425="jabas")*MOVIMIENTOS!$E$5:$E$425*IFERROR(_xlfn.SWITCH(MOVIMIENTOS!$C$5:$C$425,"A",15,"P",18,"C",17,"M",17,0),0))-SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=MOVIMIENTOS!$A142)*(MOVIMIENTOS!$B$5:$B$425="REPROCESO")*MOVIMIENTOS!$I$5:$I$425),"+#,##0;-#,##0;0")&amp;" kg)"</f>
         <v>9 kg recuperados (merma del día: -9 kg)</v>
       </c>
       <c r="G83" s="56">
@@ -26507,22 +26918,22 @@
         <v>46226</v>
       </c>
       <c r="B84" s="81" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C84" s="82">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,23))*(MOVIMIENTOS!$B$5:$B$421="COMPRA")*MOVIMIENTOS!$I$5:$I$421)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,23))*(MOVIMIENTOS!$B$5:$B$425="COMPRA")*MOVIMIENTOS!$I$5:$I$425)</f>
         <v>3880</v>
       </c>
       <c r="D84" s="82">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,23))*(MOVIMIENTOS!$B$5:$B$421="PROCESO")*MOVIMIENTOS!$I$5:$I$421)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,23))*(MOVIMIENTOS!$B$5:$B$425="PROCESO")*MOVIMIENTOS!$I$5:$I$425)</f>
         <v>3800.5</v>
       </c>
       <c r="E84" s="82">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,23))*((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$421="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="ENVIO A TOTTUS"))*MOVIMIENTOS!$I$5:$I$421)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,23))*((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS"))*MOVIMIENTOS!$I$5:$I$425)</f>
         <v>3413</v>
       </c>
       <c r="F84" s="81" t="str">
-        <f>"Selección: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,23))*(MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$421),"#,##0")&amp;" kg  ·  Chancho: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,23))*(MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*MOVIMIENTOS!$I$5:$I$421),"#,##0")&amp;" kg"&amp;IF(C84&gt;0,"  ·  "&amp;TEXT(D84/C84,"0%")&amp;" del ingreso","")</f>
+        <f>"Selección: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,23))*(MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$425),"#,##0")&amp;" kg  ·  Chancho: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,23))*(MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*MOVIMIENTOS!$I$5:$I$425),"#,##0")&amp;" kg"&amp;IF(C84&gt;0,"  ·  "&amp;TEXT(D84/C84,"0%")&amp;" del ingreso","")</f>
         <v>Selección: 3,170 kg  ·  Chancho: 631 kg  ·  98% del ingreso</v>
       </c>
       <c r="G84" s="82">
@@ -26548,7 +26959,7 @@
         <v>46226</v>
       </c>
       <c r="B85" s="63" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C85" s="64">
         <f>N(MOVIMIENTOS!$I143)</f>
@@ -26583,16 +26994,16 @@
         <v>46226</v>
       </c>
       <c r="B86" s="84" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C86" s="85"/>
       <c r="D86" s="85">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,23))*(MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$421)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,23))*(MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$425)</f>
         <v>3170</v>
       </c>
       <c r="E86" s="85"/>
       <c r="F86" s="84" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G86" s="85">
         <f>N(G85)</f>
@@ -26617,7 +27028,7 @@
         <v>46226</v>
       </c>
       <c r="B87" s="61" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C87" s="56"/>
       <c r="D87" s="56">
@@ -26664,7 +27075,7 @@
         <v>3413</v>
       </c>
       <c r="F88" s="61" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="G88" s="56">
         <f>N(G87)+N(C88)-N(E88)</f>
@@ -26689,22 +27100,22 @@
         <v>46227</v>
       </c>
       <c r="B89" s="81" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C89" s="82">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,24))*(MOVIMIENTOS!$B$5:$B$421="COMPRA")*MOVIMIENTOS!$I$5:$I$421)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,24))*(MOVIMIENTOS!$B$5:$B$425="COMPRA")*MOVIMIENTOS!$I$5:$I$425)</f>
         <v>4171</v>
       </c>
       <c r="D89" s="82">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,24))*(MOVIMIENTOS!$B$5:$B$421="PROCESO")*MOVIMIENTOS!$I$5:$I$421)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,24))*(MOVIMIENTOS!$B$5:$B$425="PROCESO")*MOVIMIENTOS!$I$5:$I$425)</f>
         <v>3056</v>
       </c>
       <c r="E89" s="82">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,24))*((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$421="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="ENVIO A TOTTUS"))*MOVIMIENTOS!$I$5:$I$421)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,24))*((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS"))*MOVIMIENTOS!$I$5:$I$425)</f>
         <v>3461</v>
       </c>
       <c r="F89" s="81" t="str">
-        <f>"Selección: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,24))*(MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$421),"#,##0")&amp;" kg  ·  Chancho: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,24))*(MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*MOVIMIENTOS!$I$5:$I$421),"#,##0")&amp;" kg"&amp;IF(C89&gt;0,"  ·  "&amp;TEXT(D89/C89,"0%")&amp;" del ingreso","")</f>
+        <f>"Selección: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,24))*(MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$425),"#,##0")&amp;" kg  ·  Chancho: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,24))*(MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*MOVIMIENTOS!$I$5:$I$425),"#,##0")&amp;" kg"&amp;IF(C89&gt;0,"  ·  "&amp;TEXT(D89/C89,"0%")&amp;" del ingreso","")</f>
         <v>Selección: 2,474 kg  ·  Chancho: 582 kg  ·  73% del ingreso</v>
       </c>
       <c r="G89" s="82">
@@ -26730,7 +27141,7 @@
         <v>46227</v>
       </c>
       <c r="B90" s="63" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C90" s="64">
         <f>N(MOVIMIENTOS!$I153)</f>
@@ -26765,16 +27176,16 @@
         <v>46227</v>
       </c>
       <c r="B91" s="84" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C91" s="85"/>
       <c r="D91" s="85">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,24))*(MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$421)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,24))*(MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$425)</f>
         <v>2474</v>
       </c>
       <c r="E91" s="85"/>
       <c r="F91" s="84" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="G91" s="85">
         <f>N(G90)</f>
@@ -26799,7 +27210,7 @@
         <v>46227</v>
       </c>
       <c r="B92" s="61" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C92" s="56"/>
       <c r="D92" s="56">
@@ -26846,7 +27257,7 @@
         <v>3413</v>
       </c>
       <c r="F93" s="61" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="G93" s="56">
         <f t="shared" si="2"/>
@@ -26871,13 +27282,13 @@
         <v>46227</v>
       </c>
       <c r="B94" s="61" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C94" s="56"/>
       <c r="D94" s="56"/>
       <c r="E94" s="56"/>
       <c r="F94" s="61" t="str">
-        <f>MOVIMIENTOS!$E163&amp;" jabas rechazadas · van a reproceso (merma del día: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=MOVIMIENTOS!$A163)*(MOVIMIENTOS!$B$5:$B$421="RECHAZO")*(MOVIMIENTOS!$D$5:$D$421="jabas")*MOVIMIENTOS!$E$5:$E$421*IFERROR(_xlfn.SWITCH(MOVIMIENTOS!$C$5:$C$421,"A",15,"P",18,"C",17,"M",17,0),0))-SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=MOVIMIENTOS!$A163)*(MOVIMIENTOS!$B$5:$B$421="REPROCESO")*MOVIMIENTOS!$I$5:$I$421),"+#,##0;-#,##0;0")&amp;" kg)"</f>
+        <f>MOVIMIENTOS!$E163&amp;" jabas rechazadas · van a reproceso (merma del día: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=MOVIMIENTOS!$A163)*(MOVIMIENTOS!$B$5:$B$425="RECHAZO")*(MOVIMIENTOS!$D$5:$D$425="jabas")*MOVIMIENTOS!$E$5:$E$425*IFERROR(_xlfn.SWITCH(MOVIMIENTOS!$C$5:$C$425,"A",15,"P",18,"C",17,"M",17,0),0))-SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=MOVIMIENTOS!$A163)*(MOVIMIENTOS!$B$5:$B$425="REPROCESO")*MOVIMIENTOS!$I$5:$I$425),"+#,##0;-#,##0;0")&amp;" kg)"</f>
         <v>1 jabas rechazadas · van a reproceso (merma del día: +13 kg)</v>
       </c>
       <c r="G94" s="56">
@@ -26912,7 +27323,7 @@
       <c r="D95" s="56"/>
       <c r="E95" s="56"/>
       <c r="F95" s="61" t="str">
-        <f>MOVIMIENTOS!$E164&amp;" kg recuperados (merma del día: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=MOVIMIENTOS!$A164)*(MOVIMIENTOS!$B$5:$B$421="RECHAZO")*(MOVIMIENTOS!$D$5:$D$421="jabas")*MOVIMIENTOS!$E$5:$E$421*IFERROR(_xlfn.SWITCH(MOVIMIENTOS!$C$5:$C$421,"A",15,"P",18,"C",17,"M",17,0),0))-SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=MOVIMIENTOS!$A164)*(MOVIMIENTOS!$B$5:$B$421="REPROCESO")*MOVIMIENTOS!$I$5:$I$421),"+#,##0;-#,##0;0")&amp;" kg)"</f>
+        <f>MOVIMIENTOS!$E164&amp;" kg recuperados (merma del día: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=MOVIMIENTOS!$A164)*(MOVIMIENTOS!$B$5:$B$425="RECHAZO")*(MOVIMIENTOS!$D$5:$D$425="jabas")*MOVIMIENTOS!$E$5:$E$425*IFERROR(_xlfn.SWITCH(MOVIMIENTOS!$C$5:$C$425,"A",15,"P",18,"C",17,"M",17,0),0))-SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=MOVIMIENTOS!$A164)*(MOVIMIENTOS!$B$5:$B$425="REPROCESO")*MOVIMIENTOS!$I$5:$I$425),"+#,##0;-#,##0;0")&amp;" kg)"</f>
         <v>11 kg recuperados (merma del día: -21 kg)</v>
       </c>
       <c r="G95" s="56">
@@ -26938,13 +27349,13 @@
         <v>46227</v>
       </c>
       <c r="B96" s="61" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C96" s="56"/>
       <c r="D96" s="56"/>
       <c r="E96" s="56"/>
       <c r="F96" s="61" t="str">
-        <f>MOVIMIENTOS!$E165&amp;" jabas rechazadas · van a reproceso (merma del día: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=MOVIMIENTOS!$A165)*(MOVIMIENTOS!$B$5:$B$421="RECHAZO")*(MOVIMIENTOS!$D$5:$D$421="jabas")*MOVIMIENTOS!$E$5:$E$421*IFERROR(_xlfn.SWITCH(MOVIMIENTOS!$C$5:$C$421,"A",15,"P",18,"C",17,"M",17,0),0))-SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=MOVIMIENTOS!$A165)*(MOVIMIENTOS!$B$5:$B$421="REPROCESO")*MOVIMIENTOS!$I$5:$I$421),"+#,##0;-#,##0;0")&amp;" kg)"</f>
+        <f>MOVIMIENTOS!$E165&amp;" jabas rechazadas · van a reproceso (merma del día: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=MOVIMIENTOS!$A165)*(MOVIMIENTOS!$B$5:$B$425="RECHAZO")*(MOVIMIENTOS!$D$5:$D$425="jabas")*MOVIMIENTOS!$E$5:$E$425*IFERROR(_xlfn.SWITCH(MOVIMIENTOS!$C$5:$C$425,"A",15,"P",18,"C",17,"M",17,0),0))-SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=MOVIMIENTOS!$A165)*(MOVIMIENTOS!$B$5:$B$425="REPROCESO")*MOVIMIENTOS!$I$5:$I$425),"+#,##0;-#,##0;0")&amp;" kg)"</f>
         <v>1 jabas rechazadas · van a reproceso (merma del día: -21 kg)</v>
       </c>
       <c r="G96" s="56">
@@ -26979,7 +27390,7 @@
       <c r="D97" s="56"/>
       <c r="E97" s="56"/>
       <c r="F97" s="61" t="str">
-        <f>MOVIMIENTOS!$E166&amp;" kg recuperados (merma del día: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=MOVIMIENTOS!$A166)*(MOVIMIENTOS!$B$5:$B$421="RECHAZO")*(MOVIMIENTOS!$D$5:$D$421="jabas")*MOVIMIENTOS!$E$5:$E$421*IFERROR(_xlfn.SWITCH(MOVIMIENTOS!$C$5:$C$421,"A",15,"P",18,"C",17,"M",17,0),0))-SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=MOVIMIENTOS!$A166)*(MOVIMIENTOS!$B$5:$B$421="REPROCESO")*MOVIMIENTOS!$I$5:$I$421),"+#,##0;-#,##0;0")&amp;" kg)"</f>
+        <f>MOVIMIENTOS!$E166&amp;" kg recuperados (merma del día: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=MOVIMIENTOS!$A166)*(MOVIMIENTOS!$B$5:$B$425="RECHAZO")*(MOVIMIENTOS!$D$5:$D$425="jabas")*MOVIMIENTOS!$E$5:$E$425*IFERROR(_xlfn.SWITCH(MOVIMIENTOS!$C$5:$C$425,"A",15,"P",18,"C",17,"M",17,0),0))-SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=MOVIMIENTOS!$A166)*(MOVIMIENTOS!$B$5:$B$425="REPROCESO")*MOVIMIENTOS!$I$5:$I$425),"+#,##0;-#,##0;0")&amp;" kg)"</f>
         <v>10 kg recuperados (merma del día: +9 kg)</v>
       </c>
       <c r="G97" s="56">
@@ -27069,7 +27480,7 @@
         <v>46227</v>
       </c>
       <c r="B100" s="61" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C100" s="56"/>
       <c r="D100" s="56"/>
@@ -27101,22 +27512,22 @@
         <v>46228</v>
       </c>
       <c r="B101" s="81" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C101" s="82">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,25))*(MOVIMIENTOS!$B$5:$B$421="COMPRA")*MOVIMIENTOS!$I$5:$I$421)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,25))*(MOVIMIENTOS!$B$5:$B$425="COMPRA")*MOVIMIENTOS!$I$5:$I$425)</f>
         <v>3589</v>
       </c>
       <c r="D101" s="82">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,25))*(MOVIMIENTOS!$B$5:$B$421="PROCESO")*MOVIMIENTOS!$I$5:$I$421)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,25))*(MOVIMIENTOS!$B$5:$B$425="PROCESO")*MOVIMIENTOS!$I$5:$I$425)</f>
         <v>4813.5</v>
       </c>
       <c r="E101" s="82">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,25))*((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$421="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="ENVIO A TOTTUS"))*MOVIMIENTOS!$I$5:$I$421)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,25))*((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS"))*MOVIMIENTOS!$I$5:$I$425)</f>
         <v>3168</v>
       </c>
       <c r="F101" s="81" t="str">
-        <f>"Selección: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,25))*(MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$421),"#,##0")&amp;" kg  ·  Chancho: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,25))*(MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*MOVIMIENTOS!$I$5:$I$421),"#,##0")&amp;" kg"&amp;IF(C101&gt;0,"  ·  "&amp;TEXT(D101/C101,"0%")&amp;" del ingreso","")</f>
+        <f>"Selección: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,25))*(MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$425),"#,##0")&amp;" kg  ·  Chancho: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,25))*(MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*MOVIMIENTOS!$I$5:$I$425),"#,##0")&amp;" kg"&amp;IF(C101&gt;0,"  ·  "&amp;TEXT(D101/C101,"0%")&amp;" del ingreso","")</f>
         <v>Selección: 3,892 kg  ·  Chancho: 922 kg  ·  134% del ingreso</v>
       </c>
       <c r="G101" s="82">
@@ -27142,7 +27553,7 @@
         <v>46228</v>
       </c>
       <c r="B102" s="63" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C102" s="64">
         <f>N(MOVIMIENTOS!$I170)</f>
@@ -27186,7 +27597,7 @@
         <v>3168</v>
       </c>
       <c r="F103" s="61" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="G103" s="56">
         <f>N(G102)+N(C103)-N(E103)</f>
@@ -27211,16 +27622,16 @@
         <v>46228</v>
       </c>
       <c r="B104" s="84" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C104" s="85"/>
       <c r="D104" s="85">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,25))*(MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$421)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,25))*(MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$425)</f>
         <v>3892</v>
       </c>
       <c r="E104" s="85"/>
       <c r="F104" s="84" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G104" s="85">
         <f>N(G103)</f>
@@ -27245,7 +27656,7 @@
         <v>46228</v>
       </c>
       <c r="B105" s="61" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C105" s="56"/>
       <c r="D105" s="56">
@@ -27283,22 +27694,22 @@
         <v>46229</v>
       </c>
       <c r="B106" s="81" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C106" s="82">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,26))*(MOVIMIENTOS!$B$5:$B$421="COMPRA")*MOVIMIENTOS!$I$5:$I$421)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,26))*(MOVIMIENTOS!$B$5:$B$425="COMPRA")*MOVIMIENTOS!$I$5:$I$425)</f>
         <v>0</v>
       </c>
       <c r="D106" s="82">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,26))*(MOVIMIENTOS!$B$5:$B$421="PROCESO")*MOVIMIENTOS!$I$5:$I$421)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,26))*(MOVIMIENTOS!$B$5:$B$425="PROCESO")*MOVIMIENTOS!$I$5:$I$425)</f>
         <v>0</v>
       </c>
       <c r="E106" s="82">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,26))*((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$421="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="ENVIO A TOTTUS"))*MOVIMIENTOS!$I$5:$I$421)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,26))*((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS"))*MOVIMIENTOS!$I$5:$I$425)</f>
         <v>1407</v>
       </c>
       <c r="F106" s="81" t="str">
-        <f>"Selección: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,26))*(MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$421),"#,##0")&amp;" kg  ·  Chancho: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,26))*(MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*MOVIMIENTOS!$I$5:$I$421),"#,##0")&amp;" kg"&amp;IF(C106&gt;0,"  ·  "&amp;TEXT(D106/C106,"0%")&amp;" del ingreso","")</f>
+        <f>"Selección: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,26))*(MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$425),"#,##0")&amp;" kg  ·  Chancho: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,26))*(MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*MOVIMIENTOS!$I$5:$I$425),"#,##0")&amp;" kg"&amp;IF(C106&gt;0,"  ·  "&amp;TEXT(D106/C106,"0%")&amp;" del ingreso","")</f>
         <v>Selección: 0 kg  ·  Chancho: 0 kg</v>
       </c>
       <c r="G106" s="82">
@@ -27333,7 +27744,7 @@
         <v>1407</v>
       </c>
       <c r="F107" s="61" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="G107" s="56">
         <f>N(G105)+N(C107)-N(E107)</f>
@@ -27358,22 +27769,22 @@
         <v>46230</v>
       </c>
       <c r="B108" s="81" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C108" s="82">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,27))*(MOVIMIENTOS!$B$5:$B$421="COMPRA")*MOVIMIENTOS!$I$5:$I$421)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,27))*(MOVIMIENTOS!$B$5:$B$425="COMPRA")*MOVIMIENTOS!$I$5:$I$425)</f>
         <v>4459</v>
       </c>
       <c r="D108" s="82">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,27))*(MOVIMIENTOS!$B$5:$B$421="PROCESO")*MOVIMIENTOS!$I$5:$I$421)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,27))*(MOVIMIENTOS!$B$5:$B$425="PROCESO")*MOVIMIENTOS!$I$5:$I$425)</f>
         <v>4128.5</v>
       </c>
       <c r="E108" s="82">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,27))*((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$421="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="ENVIO A TOTTUS"))*MOVIMIENTOS!$I$5:$I$421)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,27))*((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS"))*MOVIMIENTOS!$I$5:$I$425)</f>
         <v>1339</v>
       </c>
       <c r="F108" s="81" t="str">
-        <f>"Selección: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,27))*(MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$421),"#,##0")&amp;" kg  ·  Chancho: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,27))*(MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*MOVIMIENTOS!$I$5:$I$421),"#,##0")&amp;" kg"&amp;IF(C108&gt;0,"  ·  "&amp;TEXT(D108/C108,"0%")&amp;" del ingreso","")</f>
+        <f>"Selección: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,27))*(MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$425),"#,##0")&amp;" kg  ·  Chancho: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,27))*(MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*MOVIMIENTOS!$I$5:$I$425),"#,##0")&amp;" kg"&amp;IF(C108&gt;0,"  ·  "&amp;TEXT(D108/C108,"0%")&amp;" del ingreso","")</f>
         <v>Selección: 3,304 kg  ·  Chancho: 825 kg  ·  93% del ingreso</v>
       </c>
       <c r="G108" s="82">
@@ -27399,7 +27810,7 @@
         <v>46230</v>
       </c>
       <c r="B109" s="63" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C109" s="64">
         <f>N(MOVIMIENTOS!$I183)</f>
@@ -27434,16 +27845,16 @@
         <v>46230</v>
       </c>
       <c r="B110" s="84" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C110" s="85"/>
       <c r="D110" s="85">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,27))*(MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$421)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,27))*(MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$425)</f>
         <v>3304</v>
       </c>
       <c r="E110" s="85"/>
       <c r="F110" s="84" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G110" s="85">
         <f>N(G109)</f>
@@ -27468,7 +27879,7 @@
         <v>46230</v>
       </c>
       <c r="B111" s="61" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C111" s="56"/>
       <c r="D111" s="56">
@@ -27515,7 +27926,7 @@
         <v>1339</v>
       </c>
       <c r="F112" s="61" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="G112" s="56">
         <f t="shared" si="3"/>
@@ -27611,7 +28022,7 @@
       <c r="E115" s="56"/>
       <c r="F115" s="61" t="str">
         <f>TRIM(IF(MOVIMIENTOS!$G194&lt;&gt;"",MOVIMIENTOS!$G194&amp;"  ","")&amp;IF(N(MOVIMIENTOS!$E194)&gt;0,MOVIMIENTOS!$E194&amp;" "&amp;MOVIMIENTOS!$D194&amp;"  ","")&amp;IF(MOVIMIENTOS!$H194&lt;&gt;"",MOVIMIENTOS!$H194,""))</f>
-        <v>2 sacos FALTA</v>
+        <v>FALTA 2 sacos FALTA</v>
       </c>
       <c r="G115" s="56">
         <f t="shared" si="3"/>
@@ -27636,13 +28047,13 @@
         <v>46230</v>
       </c>
       <c r="B116" s="61" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C116" s="56"/>
       <c r="D116" s="56"/>
       <c r="E116" s="56"/>
       <c r="F116" s="61" t="str">
-        <f>MOVIMIENTOS!$E195&amp;" jabas rechazadas · van a reproceso (merma del día: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=MOVIMIENTOS!$A195)*(MOVIMIENTOS!$B$5:$B$421="RECHAZO")*(MOVIMIENTOS!$D$5:$D$421="jabas")*MOVIMIENTOS!$E$5:$E$421*IFERROR(_xlfn.SWITCH(MOVIMIENTOS!$C$5:$C$421,"A",15,"P",18,"C",17,"M",17,0),0))-SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=MOVIMIENTOS!$A195)*(MOVIMIENTOS!$B$5:$B$421="REPROCESO")*MOVIMIENTOS!$I$5:$I$421),"+#,##0;-#,##0;0")&amp;" kg)"</f>
+        <f>MOVIMIENTOS!$E195&amp;" jabas rechazadas · van a reproceso (merma del día: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=MOVIMIENTOS!$A195)*(MOVIMIENTOS!$B$5:$B$425="RECHAZO")*(MOVIMIENTOS!$D$5:$D$425="jabas")*MOVIMIENTOS!$E$5:$E$425*IFERROR(_xlfn.SWITCH(MOVIMIENTOS!$C$5:$C$425,"A",15,"P",18,"C",17,"M",17,0),0))-SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=MOVIMIENTOS!$A195)*(MOVIMIENTOS!$B$5:$B$425="REPROCESO")*MOVIMIENTOS!$I$5:$I$425),"+#,##0;-#,##0;0")&amp;" kg)"</f>
         <v>1 jabas rechazadas · van a reproceso (merma del día: +10 kg)</v>
       </c>
       <c r="G116" s="56">
@@ -27677,7 +28088,7 @@
       <c r="D117" s="56"/>
       <c r="E117" s="56"/>
       <c r="F117" s="61" t="str">
-        <f>MOVIMIENTOS!$E196&amp;" kg recuperados (merma del día: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=MOVIMIENTOS!$A196)*(MOVIMIENTOS!$B$5:$B$421="RECHAZO")*(MOVIMIENTOS!$D$5:$D$421="jabas")*MOVIMIENTOS!$E$5:$E$421*IFERROR(_xlfn.SWITCH(MOVIMIENTOS!$C$5:$C$421,"A",15,"P",18,"C",17,"M",17,0),0))-SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=MOVIMIENTOS!$A196)*(MOVIMIENTOS!$B$5:$B$421="REPROCESO")*MOVIMIENTOS!$I$5:$I$421),"+#,##0;-#,##0;0")&amp;" kg)"</f>
+        <f>MOVIMIENTOS!$E196&amp;" kg recuperados (merma del día: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=MOVIMIENTOS!$A196)*(MOVIMIENTOS!$B$5:$B$425="RECHAZO")*(MOVIMIENTOS!$D$5:$D$425="jabas")*MOVIMIENTOS!$E$5:$E$425*IFERROR(_xlfn.SWITCH(MOVIMIENTOS!$C$5:$C$425,"A",15,"P",18,"C",17,"M",17,0),0))-SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=MOVIMIENTOS!$A196)*(MOVIMIENTOS!$B$5:$B$425="REPROCESO")*MOVIMIENTOS!$I$5:$I$425),"+#,##0;-#,##0;0")&amp;" kg)"</f>
         <v>7 kg recuperados (merma del día: -7 kg)</v>
       </c>
       <c r="G117" s="56">
@@ -27703,22 +28114,22 @@
         <v>46231</v>
       </c>
       <c r="B118" s="81" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C118" s="82">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,28))*(MOVIMIENTOS!$B$5:$B$421="COMPRA")*MOVIMIENTOS!$I$5:$I$421)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,28))*(MOVIMIENTOS!$B$5:$B$425="COMPRA")*MOVIMIENTOS!$I$5:$I$425)</f>
         <v>5451</v>
       </c>
       <c r="D118" s="82">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,28))*(MOVIMIENTOS!$B$5:$B$421="PROCESO")*MOVIMIENTOS!$I$5:$I$421)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,28))*(MOVIMIENTOS!$B$5:$B$425="PROCESO")*MOVIMIENTOS!$I$5:$I$425)</f>
         <v>5275.5</v>
       </c>
       <c r="E118" s="82">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,28))*((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$421="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="ENVIO A TOTTUS"))*MOVIMIENTOS!$I$5:$I$421)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,28))*((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS"))*MOVIMIENTOS!$I$5:$I$425)</f>
         <v>3379</v>
       </c>
       <c r="F118" s="81" t="str">
-        <f>"Selección: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,28))*(MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$421),"#,##0")&amp;" kg  ·  Chancho: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,28))*(MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*MOVIMIENTOS!$I$5:$I$421),"#,##0")&amp;" kg"&amp;IF(C118&gt;0,"  ·  "&amp;TEXT(D118/C118,"0%")&amp;" del ingreso","")</f>
+        <f>"Selección: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,28))*(MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$425),"#,##0")&amp;" kg  ·  Chancho: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,28))*(MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*MOVIMIENTOS!$I$5:$I$425),"#,##0")&amp;" kg"&amp;IF(C118&gt;0,"  ·  "&amp;TEXT(D118/C118,"0%")&amp;" del ingreso","")</f>
         <v>Selección: 3,869 kg  ·  Chancho: 1,407 kg  ·  97% del ingreso</v>
       </c>
       <c r="G118" s="82">
@@ -27744,7 +28155,7 @@
         <v>46231</v>
       </c>
       <c r="B119" s="63" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C119" s="64">
         <f>N(MOVIMIENTOS!$I197)</f>
@@ -27779,16 +28190,16 @@
         <v>46231</v>
       </c>
       <c r="B120" s="84" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C120" s="85"/>
       <c r="D120" s="85">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,28))*(MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$421)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,28))*(MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$425)</f>
         <v>3869</v>
       </c>
       <c r="E120" s="85"/>
       <c r="F120" s="84" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="G120" s="85">
         <f>N(G119)</f>
@@ -27813,7 +28224,7 @@
         <v>46231</v>
       </c>
       <c r="B121" s="61" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C121" s="56"/>
       <c r="D121" s="56">
@@ -27860,7 +28271,7 @@
         <v>3379</v>
       </c>
       <c r="F122" s="61" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="G122" s="56">
         <f>N(G121)+N(C122)-N(E122)</f>
@@ -27885,22 +28296,22 @@
         <v>46232</v>
       </c>
       <c r="B123" s="81" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C123" s="82">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,29))*(MOVIMIENTOS!$B$5:$B$421="COMPRA")*MOVIMIENTOS!$I$5:$I$421)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,29))*(MOVIMIENTOS!$B$5:$B$425="COMPRA")*MOVIMIENTOS!$I$5:$I$425)</f>
         <v>0</v>
       </c>
       <c r="D123" s="82">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,29))*(MOVIMIENTOS!$B$5:$B$421="PROCESO")*MOVIMIENTOS!$I$5:$I$421)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,29))*(MOVIMIENTOS!$B$5:$B$425="PROCESO")*MOVIMIENTOS!$I$5:$I$425)</f>
         <v>0</v>
       </c>
       <c r="E123" s="82">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,29))*((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$421="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="ENVIO A TOTTUS"))*MOVIMIENTOS!$I$5:$I$421)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,29))*((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS"))*MOVIMIENTOS!$I$5:$I$425)</f>
         <v>2794</v>
       </c>
       <c r="F123" s="81" t="str">
-        <f>"Selección: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,29))*(MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$421),"#,##0")&amp;" kg  ·  Chancho: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,29))*(MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*MOVIMIENTOS!$I$5:$I$421),"#,##0")&amp;" kg"&amp;IF(C123&gt;0,"  ·  "&amp;TEXT(D123/C123,"0%")&amp;" del ingreso","")</f>
+        <f>"Selección: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,29))*(MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$425),"#,##0")&amp;" kg  ·  Chancho: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,29))*(MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*MOVIMIENTOS!$I$5:$I$425),"#,##0")&amp;" kg"&amp;IF(C123&gt;0,"  ·  "&amp;TEXT(D123/C123,"0%")&amp;" del ingreso","")</f>
         <v>Selección: 0 kg  ·  Chancho: 0 kg</v>
       </c>
       <c r="G123" s="82">
@@ -27935,7 +28346,7 @@
         <v>2794</v>
       </c>
       <c r="F124" s="61" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="G124" s="56">
         <f>N(G122)+N(C124)-N(E124)</f>
@@ -27992,22 +28403,22 @@
         <v>46233</v>
       </c>
       <c r="B126" s="81" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C126" s="82">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,30))*(MOVIMIENTOS!$B$5:$B$421="COMPRA")*MOVIMIENTOS!$I$5:$I$421)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,30))*(MOVIMIENTOS!$B$5:$B$425="COMPRA")*MOVIMIENTOS!$I$5:$I$425)</f>
         <v>2910</v>
       </c>
       <c r="D126" s="82">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,30))*(MOVIMIENTOS!$B$5:$B$421="PROCESO")*MOVIMIENTOS!$I$5:$I$421)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,30))*(MOVIMIENTOS!$B$5:$B$425="PROCESO")*MOVIMIENTOS!$I$5:$I$425)</f>
         <v>2988</v>
       </c>
       <c r="E126" s="82">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,30))*((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$421="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="ENVIO A TOTTUS"))*MOVIMIENTOS!$I$5:$I$421)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,30))*((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS"))*MOVIMIENTOS!$I$5:$I$425)</f>
         <v>3294</v>
       </c>
       <c r="F126" s="81" t="str">
-        <f>"Selección: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,30))*(MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$421),"#,##0")&amp;" kg  ·  Chancho: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,30))*(MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*MOVIMIENTOS!$I$5:$I$421),"#,##0")&amp;" kg"&amp;IF(C126&gt;0,"  ·  "&amp;TEXT(D126/C126,"0%")&amp;" del ingreso","")</f>
+        <f>"Selección: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,30))*(MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$425),"#,##0")&amp;" kg  ·  Chancho: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,30))*(MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*MOVIMIENTOS!$I$5:$I$425),"#,##0")&amp;" kg"&amp;IF(C126&gt;0,"  ·  "&amp;TEXT(D126/C126,"0%")&amp;" del ingreso","")</f>
         <v>Selección: 2,503 kg  ·  Chancho: 485 kg  ·  103% del ingreso</v>
       </c>
       <c r="G126" s="82">
@@ -28033,7 +28444,7 @@
         <v>46233</v>
       </c>
       <c r="B127" s="63" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C127" s="64">
         <f>N(MOVIMIENTOS!$I212)</f>
@@ -28068,16 +28479,16 @@
         <v>46233</v>
       </c>
       <c r="B128" s="84" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C128" s="85"/>
       <c r="D128" s="85">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,30))*(MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$421)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,30))*(MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$425)</f>
         <v>2503</v>
       </c>
       <c r="E128" s="85"/>
       <c r="F128" s="84" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="G128" s="85">
         <f>N(G127)</f>
@@ -28102,7 +28513,7 @@
         <v>46233</v>
       </c>
       <c r="B129" s="61" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C129" s="56"/>
       <c r="D129" s="56">
@@ -28140,7 +28551,7 @@
         <v>46233</v>
       </c>
       <c r="B130" s="61" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C130" s="56"/>
       <c r="D130" s="56"/>
@@ -28181,7 +28592,7 @@
         <v>3294</v>
       </c>
       <c r="F131" s="61" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="G131" s="56">
         <f>N(G130)+N(C131)-N(E131)</f>
@@ -28206,22 +28617,22 @@
         <v>46234</v>
       </c>
       <c r="B132" s="81" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C132" s="82">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,31))*(MOVIMIENTOS!$B$5:$B$421="COMPRA")*MOVIMIENTOS!$I$5:$I$421)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,31))*(MOVIMIENTOS!$B$5:$B$425="COMPRA")*MOVIMIENTOS!$I$5:$I$425)</f>
         <v>6790</v>
       </c>
       <c r="D132" s="82">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,31))*(MOVIMIENTOS!$B$5:$B$421="PROCESO")*MOVIMIENTOS!$I$5:$I$421)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,31))*(MOVIMIENTOS!$B$5:$B$425="PROCESO")*MOVIMIENTOS!$I$5:$I$425)</f>
         <v>6957.5</v>
       </c>
       <c r="E132" s="82">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,31))*((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$421="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="ENVIO A TOTTUS"))*MOVIMIENTOS!$I$5:$I$421)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,31))*((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS"))*MOVIMIENTOS!$I$5:$I$425)</f>
         <v>3413</v>
       </c>
       <c r="F132" s="81" t="str">
-        <f>"Selección: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,31))*(MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$421),"#,##0")&amp;" kg  ·  Chancho: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,31))*(MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*MOVIMIENTOS!$I$5:$I$421),"#,##0")&amp;" kg"&amp;IF(C132&gt;0,"  ·  "&amp;TEXT(D132/C132,"0%")&amp;" del ingreso","")</f>
+        <f>"Selección: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,31))*(MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$425),"#,##0")&amp;" kg  ·  Chancho: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,31))*(MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*MOVIMIENTOS!$I$5:$I$425),"#,##0")&amp;" kg"&amp;IF(C132&gt;0,"  ·  "&amp;TEXT(D132/C132,"0%")&amp;" del ingreso","")</f>
         <v>Selección: 5,551 kg  ·  Chancho: 1,407 kg  ·  102% del ingreso</v>
       </c>
       <c r="G132" s="82">
@@ -28247,7 +28658,7 @@
         <v>46234</v>
       </c>
       <c r="B133" s="63" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C133" s="64">
         <f>N(MOVIMIENTOS!$I223)</f>
@@ -28282,16 +28693,16 @@
         <v>46234</v>
       </c>
       <c r="B134" s="84" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C134" s="85"/>
       <c r="D134" s="85">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,7,31))*(MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$421)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,7,31))*(MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$425)</f>
         <v>5551</v>
       </c>
       <c r="E134" s="85"/>
       <c r="F134" s="84" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="G134" s="85">
         <f>N(G133)</f>
@@ -28316,7 +28727,7 @@
         <v>46234</v>
       </c>
       <c r="B135" s="61" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C135" s="56"/>
       <c r="D135" s="56">
@@ -28363,7 +28774,7 @@
         <v>3413</v>
       </c>
       <c r="F136" s="61" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="G136" s="56">
         <f>N(G135)+N(C136)-N(E136)</f>
@@ -28420,22 +28831,22 @@
         <v>46235</v>
       </c>
       <c r="B138" s="54" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C138" s="54">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,8,1))*(MOVIMIENTOS!$B$5:$B$421="COMPRA")*MOVIMIENTOS!$I$5:$I$421)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,8,1))*(MOVIMIENTOS!$B$5:$B$425="COMPRA")*MOVIMIENTOS!$I$5:$I$425)</f>
         <v>3850</v>
       </c>
       <c r="D138" s="54">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,8,1))*(MOVIMIENTOS!$B$5:$B$421="PROCESO")*MOVIMIENTOS!$I$5:$I$421)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,8,1))*(MOVIMIENTOS!$B$5:$B$425="PROCESO")*MOVIMIENTOS!$I$5:$I$425)</f>
         <v>3724</v>
       </c>
       <c r="E138" s="54">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,8,1))*((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$421="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="ENVIO A TOTTUS"))*MOVIMIENTOS!$I$5:$I$421)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,8,1))*((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS"))*MOVIMIENTOS!$I$5:$I$425)</f>
         <v>3289</v>
       </c>
       <c r="F138" s="54" t="str">
-        <f>"Selección: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,8,1))*(MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$421),"#,##0")&amp;" kg  ·  Chancho: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,8,1))*(MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*MOVIMIENTOS!$I$5:$I$421),"#,##0")&amp;" kg"&amp;IF(C138&gt;0,"  ·  "&amp;TEXT(D138/C138,"0%")&amp;" del ingreso","")</f>
+        <f>"Selección: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,8,1))*(MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$425),"#,##0")&amp;" kg  ·  Chancho: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,8,1))*(MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*MOVIMIENTOS!$I$5:$I$425),"#,##0")&amp;" kg"&amp;IF(C138&gt;0,"  ·  "&amp;TEXT(D138/C138,"0%")&amp;" del ingreso","")</f>
         <v>Selección: 2,948 kg  ·  Chancho: 776 kg  ·  97% del ingreso</v>
       </c>
       <c r="G138" s="54">
@@ -28461,7 +28872,7 @@
         <v>46235</v>
       </c>
       <c r="B139" s="54" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C139" s="54">
         <f>N(MOVIMIENTOS!$I236)</f>
@@ -28496,16 +28907,16 @@
         <v>46235</v>
       </c>
       <c r="B140" s="54" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C140" s="54"/>
       <c r="D140" s="54">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,8,1))*(MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$421)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,8,1))*(MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$425)</f>
         <v>2948</v>
       </c>
       <c r="E140" s="54"/>
       <c r="F140" s="54" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="G140" s="54">
         <f>N(G139)+N(C140)-N(E140)</f>
@@ -28530,7 +28941,7 @@
         <v>46235</v>
       </c>
       <c r="B141" s="54" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C141" s="54"/>
       <c r="D141" s="54">
@@ -28577,7 +28988,7 @@
         <v>3289</v>
       </c>
       <c r="F142" s="54" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="G142" s="54">
         <f>N(G141)+N(C142)-N(E142)</f>
@@ -28634,22 +29045,22 @@
         <v>46236</v>
       </c>
       <c r="B144" s="54" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C144" s="54">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,8,2))*(MOVIMIENTOS!$B$5:$B$421="COMPRA")*MOVIMIENTOS!$I$5:$I$421)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,8,2))*(MOVIMIENTOS!$B$5:$B$425="COMPRA")*MOVIMIENTOS!$I$5:$I$425)</f>
         <v>5965.82</v>
       </c>
       <c r="D144" s="54">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,8,2))*(MOVIMIENTOS!$B$5:$B$421="PROCESO")*MOVIMIENTOS!$I$5:$I$421)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,8,2))*(MOVIMIENTOS!$B$5:$B$425="PROCESO")*MOVIMIENTOS!$I$5:$I$425)</f>
         <v>5715.5</v>
       </c>
       <c r="E144" s="54">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,8,2))*((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$421="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="ENVIO A TOTTUS"))*MOVIMIENTOS!$I$5:$I$421)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,8,2))*((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS"))*MOVIMIENTOS!$I$5:$I$425)</f>
         <v>1951</v>
       </c>
       <c r="F144" s="54" t="str">
-        <f>"Selección: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,8,2))*(MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$421),"#,##0")&amp;" kg  ·  Chancho: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,8,2))*(MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*MOVIMIENTOS!$I$5:$I$421),"#,##0")&amp;" kg"&amp;IF(C144&gt;0,"  ·  "&amp;TEXT(D144/C144,"0%")&amp;" del ingreso","")</f>
+        <f>"Selección: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,8,2))*(MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$425),"#,##0")&amp;" kg  ·  Chancho: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,8,2))*(MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*MOVIMIENTOS!$I$5:$I$425),"#,##0")&amp;" kg"&amp;IF(C144&gt;0,"  ·  "&amp;TEXT(D144/C144,"0%")&amp;" del ingreso","")</f>
         <v>Selección: 4,697 kg  ·  Chancho: 1,019 kg  ·  96% del ingreso</v>
       </c>
       <c r="G144" s="54">
@@ -28707,7 +29118,7 @@
         <v>46236</v>
       </c>
       <c r="B146" s="54" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C146" s="54">
         <f>N(MOVIMIENTOS!$I250)</f>
@@ -28742,16 +29153,16 @@
         <v>46236</v>
       </c>
       <c r="B147" s="54" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C147" s="54"/>
       <c r="D147" s="54">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,8,2))*(MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$421)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,8,2))*(MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$425)</f>
         <v>4697</v>
       </c>
       <c r="E147" s="54"/>
       <c r="F147" s="54" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="G147" s="54">
         <f>N(G146)+N(C147)-N(E147)</f>
@@ -28776,7 +29187,7 @@
         <v>46236</v>
       </c>
       <c r="B148" s="54" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C148" s="54"/>
       <c r="D148" s="54">
@@ -28823,7 +29234,7 @@
         <v>1951</v>
       </c>
       <c r="F149" s="54" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="G149" s="54">
         <f>N(G148)+N(C149)-N(E149)</f>
@@ -28880,22 +29291,22 @@
         <v>46237</v>
       </c>
       <c r="B151" s="54" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C151" s="54">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,8,3))*(MOVIMIENTOS!$B$5:$B$421="COMPRA")*MOVIMIENTOS!$I$5:$I$421)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,8,3))*(MOVIMIENTOS!$B$5:$B$425="COMPRA")*MOVIMIENTOS!$I$5:$I$425)</f>
         <v>0</v>
       </c>
       <c r="D151" s="54">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,8,3))*(MOVIMIENTOS!$B$5:$B$421="PROCESO")*MOVIMIENTOS!$I$5:$I$421)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,8,3))*(MOVIMIENTOS!$B$5:$B$425="PROCESO")*MOVIMIENTOS!$I$5:$I$425)</f>
         <v>0</v>
       </c>
       <c r="E151" s="54">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,8,3))*((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$421="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="ENVIO A TOTTUS"))*MOVIMIENTOS!$I$5:$I$421)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,8,3))*((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS"))*MOVIMIENTOS!$I$5:$I$425)</f>
         <v>3413</v>
       </c>
       <c r="F151" s="54" t="str">
-        <f>"Selección: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,8,3))*(MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$421),"#,##0")&amp;" kg  ·  Chancho: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,8,3))*(MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*MOVIMIENTOS!$I$5:$I$421),"#,##0")&amp;" kg"&amp;IF(C151&gt;0,"  ·  "&amp;TEXT(D151/C151,"0%")&amp;" del ingreso","")</f>
+        <f>"Selección: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,8,3))*(MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$425),"#,##0")&amp;" kg  ·  Chancho: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,8,3))*(MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*MOVIMIENTOS!$I$5:$I$425),"#,##0")&amp;" kg"&amp;IF(C151&gt;0,"  ·  "&amp;TEXT(D151/C151,"0%")&amp;" del ingreso","")</f>
         <v>Selección: 0 kg  ·  Chancho: 0 kg</v>
       </c>
       <c r="G151" s="54">
@@ -28921,7 +29332,7 @@
         <v>46237</v>
       </c>
       <c r="B152" s="54" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C152" s="54"/>
       <c r="D152" s="54"/>
@@ -28953,7 +29364,7 @@
         <v>46237</v>
       </c>
       <c r="B153" s="54" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C153" s="54">
         <f>N(MOVIMIENTOS!$I268)</f>
@@ -28997,7 +29408,7 @@
         <v>3413</v>
       </c>
       <c r="F154" s="54" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="G154" s="54">
         <f>N(G153)+N(C154)-N(E154)</f>
@@ -29022,22 +29433,22 @@
         <v>46238</v>
       </c>
       <c r="B155" s="54" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C155" s="54">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,8,4))*(MOVIMIENTOS!$B$5:$B$421="COMPRA")*MOVIMIENTOS!$I$5:$I$421)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,8,4))*(MOVIMIENTOS!$B$5:$B$425="COMPRA")*MOVIMIENTOS!$I$5:$I$425)</f>
         <v>3450</v>
       </c>
       <c r="D155" s="54">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,8,4))*(MOVIMIENTOS!$B$5:$B$421="PROCESO")*MOVIMIENTOS!$I$5:$I$421)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,8,4))*(MOVIMIENTOS!$B$5:$B$425="PROCESO")*MOVIMIENTOS!$I$5:$I$425)</f>
         <v>3447</v>
       </c>
       <c r="E155" s="54">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,8,4))*((MOVIMIENTOS!$B$5:$B$421="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$421="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$421="ENVIO A TOTTUS"))*MOVIMIENTOS!$I$5:$I$421)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,8,4))*((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS"))*MOVIMIENTOS!$I$5:$I$425)</f>
         <v>3413</v>
       </c>
       <c r="F155" s="54" t="str">
-        <f>"Selección: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,8,4))*(MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$421),"#,##0")&amp;" kg  ·  Chancho: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,8,4))*(MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421="Chancho")*MOVIMIENTOS!$I$5:$I$421),"#,##0")&amp;" kg"&amp;IF(C155&gt;0,"  ·  "&amp;TEXT(D155/C155,"0%")&amp;" del ingreso","")</f>
+        <f>"Selección: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,8,4))*(MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$425),"#,##0")&amp;" kg  ·  Chancho: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,8,4))*(MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*MOVIMIENTOS!$I$5:$I$425),"#,##0")&amp;" kg"&amp;IF(C155&gt;0,"  ·  "&amp;TEXT(D155/C155,"0%")&amp;" del ingreso","")</f>
         <v>Selección: 2,283 kg  ·  Chancho: 1,164 kg  ·  100% del ingreso</v>
       </c>
       <c r="G155" s="54">
@@ -29063,7 +29474,7 @@
         <v>46238</v>
       </c>
       <c r="B156" s="54" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C156" s="54">
         <f>N(MOVIMIENTOS!$I269)</f>
@@ -29098,16 +29509,16 @@
         <v>46238</v>
       </c>
       <c r="B157" s="54" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C157" s="54"/>
       <c r="D157" s="54">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$421=DATE(2026,8,4))*(MOVIMIENTOS!$B$5:$B$421="PROCESO")*(MOVIMIENTOS!$C$5:$C$421&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$421)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$425=DATE(2026,8,4))*(MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$425)</f>
         <v>2283</v>
       </c>
       <c r="E157" s="54"/>
       <c r="F157" s="54" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="G157" s="54">
         <f>N(G156)+N(C157)-N(E157)</f>
@@ -29132,7 +29543,7 @@
         <v>46238</v>
       </c>
       <c r="B158" s="54" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C158" s="54"/>
       <c r="D158" s="54">
@@ -29179,7 +29590,7 @@
         <v>3413</v>
       </c>
       <c r="F159" s="54" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="G159" s="54">
         <f>N(G158)+N(C159)-N(E159)</f>
@@ -29204,22 +29615,22 @@
         <v>46239</v>
       </c>
       <c r="B160" s="54" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C160" s="54">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$416=DATE(2026,8,5))*(MOVIMIENTOS!$B$5:$B$416="COMPRA")*MOVIMIENTOS!$I$5:$I$416)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$420=DATE(2026,8,5))*(MOVIMIENTOS!$B$5:$B$420="COMPRA")*MOVIMIENTOS!$I$5:$I$420)</f>
         <v>5044</v>
       </c>
       <c r="D160" s="54">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$416=DATE(2026,8,5))*(MOVIMIENTOS!$B$5:$B$416="PROCESO")*MOVIMIENTOS!$I$5:$I$416)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$420=DATE(2026,8,5))*(MOVIMIENTOS!$B$5:$B$420="PROCESO")*MOVIMIENTOS!$I$5:$I$420)</f>
         <v>5361.5</v>
       </c>
       <c r="E160" s="54">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$416=DATE(2026,8,5))*((MOVIMIENTOS!$B$5:$B$416="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$416="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$416="ENVIO A TOTTUS"))*MOVIMIENTOS!$I$5:$I$416)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$420=DATE(2026,8,5))*((MOVIMIENTOS!$B$5:$B$420="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$420="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$420="ENVIO A TOTTUS"))*MOVIMIENTOS!$I$5:$I$420)</f>
         <v>3158</v>
       </c>
       <c r="F160" s="54" t="str">
-        <f>"Selección: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$416=DATE(2026,8,5))*(MOVIMIENTOS!$B$5:$B$416="PROCESO")*(MOVIMIENTOS!$C$5:$C$416&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$416),"#,##0")&amp;" kg  ·  Chancho: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$416=DATE(2026,8,5))*(MOVIMIENTOS!$B$5:$B$416="PROCESO")*(MOVIMIENTOS!$C$5:$C$416="Chancho")*MOVIMIENTOS!$I$5:$I$416),"#,##0")&amp;" kg"&amp;IF(C160&gt;0,"  ·  "&amp;TEXT(D160/C160,"0%")&amp;" del ingreso","")</f>
+        <f>"Selección: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$420=DATE(2026,8,5))*(MOVIMIENTOS!$B$5:$B$420="PROCESO")*(MOVIMIENTOS!$C$5:$C$420&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$420),"#,##0")&amp;" kg  ·  Chancho: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$420=DATE(2026,8,5))*(MOVIMIENTOS!$B$5:$B$420="PROCESO")*(MOVIMIENTOS!$C$5:$C$420="Chancho")*MOVIMIENTOS!$I$5:$I$420),"#,##0")&amp;" kg"&amp;IF(C160&gt;0,"  ·  "&amp;TEXT(D160/C160,"0%")&amp;" del ingreso","")</f>
         <v>Selección: 4,828 kg  ·  Chancho: 534 kg  ·  106% del ingreso</v>
       </c>
       <c r="G160" s="54">
@@ -29245,7 +29656,7 @@
         <v>46239</v>
       </c>
       <c r="B161" s="54" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C161" s="54">
         <f>N(MOVIMIENTOS!$I279)</f>
@@ -29280,16 +29691,16 @@
         <v>46239</v>
       </c>
       <c r="B162" s="54" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C162" s="54"/>
       <c r="D162" s="54">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$416=DATE(2026,8,5))*(MOVIMIENTOS!$B$5:$B$416="PROCESO")*(MOVIMIENTOS!$C$5:$C$416&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$416)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$420=DATE(2026,8,5))*(MOVIMIENTOS!$B$5:$B$420="PROCESO")*(MOVIMIENTOS!$C$5:$C$420&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$420)</f>
         <v>4828</v>
       </c>
       <c r="E162" s="54"/>
       <c r="F162" s="54" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="G162" s="54">
         <f t="shared" ref="G162:G168" si="4">N(G161)+N(C162)-N(E162)</f>
@@ -29314,7 +29725,7 @@
         <v>46239</v>
       </c>
       <c r="B163" s="54" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C163" s="54"/>
       <c r="D163" s="54">
@@ -29361,7 +29772,7 @@
         <v>3158</v>
       </c>
       <c r="F164" s="54" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="G164" s="54">
         <f t="shared" si="4"/>
@@ -29489,7 +29900,7 @@
       <c r="E168" s="54"/>
       <c r="F168" s="54" t="str">
         <f>TRIM(IF(MOVIMIENTOS!$G292&lt;&gt;"",MOVIMIENTOS!$G292&amp;"  ","")&amp;IF(N(MOVIMIENTOS!$E292)&gt;0,MOVIMIENTOS!$E292&amp;" "&amp;MOVIMIENTOS!$D292&amp;"  ","")&amp;IF(MOVIMIENTOS!$H292&lt;&gt;"",MOVIMIENTOS!$H292,""))</f>
-        <v>1 sacos FALTA</v>
+        <v>FALTA 1 sacos FALTA</v>
       </c>
       <c r="G168" s="54">
         <f t="shared" si="4"/>
@@ -29514,22 +29925,22 @@
         <v>46240</v>
       </c>
       <c r="B169" s="54" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C169" s="54">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$414=DATE(2026,8,6))*(MOVIMIENTOS!$B$5:$B$414="COMPRA")*MOVIMIENTOS!$I$5:$I$414)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$418=DATE(2026,8,6))*(MOVIMIENTOS!$B$5:$B$418="COMPRA")*MOVIMIENTOS!$I$5:$I$418)</f>
         <v>4656</v>
       </c>
       <c r="D169" s="54">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$414=DATE(2026,8,6))*(MOVIMIENTOS!$B$5:$B$414="PROCESO")*MOVIMIENTOS!$I$5:$I$414)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$418=DATE(2026,8,6))*(MOVIMIENTOS!$B$5:$B$418="PROCESO")*MOVIMIENTOS!$I$5:$I$418)</f>
         <v>4716.5</v>
       </c>
       <c r="E169" s="54">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$414=DATE(2026,8,6))*((MOVIMIENTOS!$B$5:$B$414="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$414="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$414="ENVIO A TOTTUS"))*MOVIMIENTOS!$I$5:$I$414)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$418=DATE(2026,8,6))*((MOVIMIENTOS!$B$5:$B$418="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$418="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$418="ENVIO A TOTTUS"))*MOVIMIENTOS!$I$5:$I$418)</f>
         <v>3413</v>
       </c>
       <c r="F169" s="54" t="str">
-        <f>"Selección: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$414=DATE(2026,8,6))*(MOVIMIENTOS!$B$5:$B$414="PROCESO")*(MOVIMIENTOS!$C$5:$C$414&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$414),"#,##0")&amp;" kg  ·  Chancho: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$414=DATE(2026,8,6))*(MOVIMIENTOS!$B$5:$B$414="PROCESO")*(MOVIMIENTOS!$C$5:$C$414="Chancho")*MOVIMIENTOS!$I$5:$I$414),"#,##0")&amp;" kg"&amp;IF(C169&gt;0,"  ·  "&amp;TEXT(D169/C169,"0%")&amp;" del ingreso","")</f>
+        <f>"Selección: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$418=DATE(2026,8,6))*(MOVIMIENTOS!$B$5:$B$418="PROCESO")*(MOVIMIENTOS!$C$5:$C$418&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$418),"#,##0")&amp;" kg  ·  Chancho: "&amp;TEXT(SUMPRODUCT((MOVIMIENTOS!$A$5:$A$418=DATE(2026,8,6))*(MOVIMIENTOS!$B$5:$B$418="PROCESO")*(MOVIMIENTOS!$C$5:$C$418="Chancho")*MOVIMIENTOS!$I$5:$I$418),"#,##0")&amp;" kg"&amp;IF(C169&gt;0,"  ·  "&amp;TEXT(D169/C169,"0%")&amp;" del ingreso","")</f>
         <v>Selección: 4,086 kg  ·  Chancho: 631 kg  ·  101% del ingreso</v>
       </c>
       <c r="G169" s="54">
@@ -29555,7 +29966,7 @@
         <v>46240</v>
       </c>
       <c r="B170" s="54" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C170" s="54">
         <f>N(MOVIMIENTOS!$I295)</f>
@@ -29590,16 +30001,16 @@
         <v>46240</v>
       </c>
       <c r="B171" s="54" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C171" s="54"/>
       <c r="D171" s="54">
-        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$414=DATE(2026,8,6))*(MOVIMIENTOS!$B$5:$B$414="PROCESO")*(MOVIMIENTOS!$C$5:$C$414&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$414)</f>
+        <f>SUMPRODUCT((MOVIMIENTOS!$A$5:$A$418=DATE(2026,8,6))*(MOVIMIENTOS!$B$5:$B$418="PROCESO")*(MOVIMIENTOS!$C$5:$C$418&lt;&gt;"Chancho")*MOVIMIENTOS!$I$5:$I$418)</f>
         <v>4086</v>
       </c>
       <c r="E171" s="54"/>
       <c r="F171" s="54" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="G171" s="54">
         <f>N(G170)+N(C171)-N(E171)</f>
@@ -29624,7 +30035,7 @@
         <v>46240</v>
       </c>
       <c r="B172" s="54" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C172" s="54"/>
       <c r="D172" s="54">
@@ -29671,7 +30082,7 @@
         <v>3413</v>
       </c>
       <c r="F173" s="54" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="G173" s="54">
         <f>N(G172)+N(C173)-N(E173)</f>
@@ -34741,13 +35152,13 @@
         <v>7</v>
       </c>
       <c r="D1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F1" t="s">
+        <v>170</v>
+      </c>
+      <c r="H1" t="s">
         <v>171</v>
-      </c>
-      <c r="F1" t="s">
-        <v>172</v>
-      </c>
-      <c r="H1" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -34809,7 +35220,7 @@
         <v>17</v>
       </c>
       <c r="D5" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="F5" t="s">
         <v>13</v>
@@ -34823,7 +35234,7 @@
         <v>95</v>
       </c>
       <c r="D6" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F6" t="s">
         <v>15</v>
@@ -34839,21 +35250,21 @@
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D8" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="F8" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="65" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D9" t="s">
         <v>42</v>
       </c>
       <c r="F9" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -34863,7 +35274,7 @@
     </row>
     <row r="11" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D11" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -34873,7 +35284,7 @@
     </row>
     <row r="13" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D13" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -34931,24 +35342,24 @@
   <sheetData>
     <row r="1" spans="1:51" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="66" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="2" spans="1:51" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="67" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="4" spans="1:51" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F4" s="90" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="G4" s="87"/>
       <c r="H4" s="87"/>
       <c r="I4" s="87"/>
       <c r="J4" s="87"/>
       <c r="M4" s="93" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="N4" s="87"/>
       <c r="O4" s="87"/>
@@ -34958,14 +35369,14 @@
       <c r="S4" s="87"/>
       <c r="T4" s="87"/>
       <c r="U4" s="95" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="V4" s="87"/>
       <c r="W4" s="87"/>
       <c r="X4" s="87"/>
       <c r="Y4" s="87"/>
       <c r="Z4" s="94" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="AA4" s="87"/>
       <c r="AB4" s="87"/>
@@ -34973,11 +35384,11 @@
       <c r="AD4" s="87"/>
       <c r="AE4" s="87"/>
       <c r="AF4" s="91" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="AG4" s="87"/>
       <c r="AI4" s="92" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="AJ4" s="87"/>
       <c r="AK4" s="87"/>
@@ -34987,7 +35398,7 @@
       <c r="AO4" s="87"/>
       <c r="AP4" s="87"/>
       <c r="AR4" s="92" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="AS4" s="87"/>
       <c r="AT4" s="87"/>
@@ -35002,148 +35413,148 @@
         <v>2</v>
       </c>
       <c r="B5" s="68" t="s">
+        <v>186</v>
+      </c>
+      <c r="C5" s="68" t="s">
+        <v>187</v>
+      </c>
+      <c r="D5" s="68" t="s">
         <v>188</v>
       </c>
-      <c r="C5" s="68" t="s">
+      <c r="E5" s="69" t="s">
         <v>189</v>
       </c>
-      <c r="D5" s="68" t="s">
+      <c r="F5" s="68" t="s">
         <v>190</v>
       </c>
-      <c r="E5" s="69" t="s">
+      <c r="G5" s="68" t="s">
         <v>191</v>
       </c>
-      <c r="F5" s="68" t="s">
+      <c r="H5" s="68" t="s">
         <v>192</v>
       </c>
-      <c r="G5" s="68" t="s">
+      <c r="I5" s="68" t="s">
         <v>193</v>
       </c>
-      <c r="H5" s="68" t="s">
+      <c r="J5" s="68" t="s">
         <v>194</v>
       </c>
-      <c r="I5" s="68" t="s">
+      <c r="K5" s="69" t="s">
         <v>195</v>
       </c>
-      <c r="J5" s="68" t="s">
+      <c r="L5" s="69" t="s">
         <v>196</v>
       </c>
-      <c r="K5" s="69" t="s">
+      <c r="M5" s="68" t="s">
         <v>197</v>
       </c>
-      <c r="L5" s="69" t="s">
+      <c r="N5" s="68" t="s">
         <v>198</v>
       </c>
-      <c r="M5" s="68" t="s">
+      <c r="O5" s="68" t="s">
         <v>199</v>
       </c>
-      <c r="N5" s="68" t="s">
+      <c r="P5" s="68" t="s">
         <v>200</v>
       </c>
-      <c r="O5" s="68" t="s">
+      <c r="Q5" s="68" t="s">
         <v>201</v>
       </c>
-      <c r="P5" s="68" t="s">
+      <c r="R5" s="68" t="s">
         <v>202</v>
       </c>
-      <c r="Q5" s="68" t="s">
+      <c r="S5" s="68" t="s">
         <v>203</v>
       </c>
-      <c r="R5" s="68" t="s">
+      <c r="T5" s="69" t="s">
         <v>204</v>
       </c>
-      <c r="S5" s="68" t="s">
+      <c r="U5" s="68" t="s">
         <v>205</v>
       </c>
-      <c r="T5" s="69" t="s">
+      <c r="V5" s="68" t="s">
         <v>206</v>
       </c>
-      <c r="U5" s="68" t="s">
+      <c r="W5" s="68" t="s">
         <v>207</v>
       </c>
-      <c r="V5" s="68" t="s">
+      <c r="X5" s="68" t="s">
         <v>208</v>
       </c>
-      <c r="W5" s="68" t="s">
+      <c r="Y5" s="68" t="s">
         <v>209</v>
       </c>
-      <c r="X5" s="68" t="s">
+      <c r="Z5" s="68" t="s">
         <v>210</v>
       </c>
-      <c r="Y5" s="68" t="s">
+      <c r="AA5" s="69" t="s">
         <v>211</v>
       </c>
-      <c r="Z5" s="68" t="s">
+      <c r="AB5" s="68" t="s">
         <v>212</v>
       </c>
-      <c r="AA5" s="69" t="s">
+      <c r="AC5" s="69" t="s">
         <v>213</v>
       </c>
-      <c r="AB5" s="68" t="s">
+      <c r="AD5" s="68" t="s">
         <v>214</v>
       </c>
-      <c r="AC5" s="69" t="s">
+      <c r="AE5" s="68" t="s">
         <v>215</v>
       </c>
-      <c r="AD5" s="68" t="s">
+      <c r="AF5" s="69" t="s">
         <v>216</v>
       </c>
-      <c r="AE5" s="68" t="s">
+      <c r="AG5" s="68" t="s">
         <v>217</v>
-      </c>
-      <c r="AF5" s="69" t="s">
-        <v>218</v>
-      </c>
-      <c r="AG5" s="68" t="s">
-        <v>219</v>
       </c>
       <c r="AI5" s="68" t="s">
         <v>2</v>
       </c>
       <c r="AJ5" s="69" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="AK5" s="69" t="s">
+        <v>218</v>
+      </c>
+      <c r="AL5" s="69" t="s">
+        <v>219</v>
+      </c>
+      <c r="AM5" s="70" t="s">
         <v>220</v>
       </c>
-      <c r="AL5" s="69" t="s">
+      <c r="AN5" s="69" t="s">
         <v>221</v>
       </c>
-      <c r="AM5" s="70" t="s">
-        <v>222</v>
-      </c>
-      <c r="AN5" s="69" t="s">
-        <v>223</v>
-      </c>
       <c r="AO5" s="69" t="s">
+        <v>216</v>
+      </c>
+      <c r="AP5" s="68" t="s">
+        <v>217</v>
+      </c>
+      <c r="AR5" s="68" t="s">
+        <v>187</v>
+      </c>
+      <c r="AS5" s="69" t="s">
+        <v>189</v>
+      </c>
+      <c r="AT5" s="69" t="s">
         <v>218</v>
       </c>
-      <c r="AP5" s="68" t="s">
+      <c r="AU5" s="69" t="s">
         <v>219</v>
       </c>
-      <c r="AR5" s="68" t="s">
-        <v>189</v>
-      </c>
-      <c r="AS5" s="69" t="s">
-        <v>191</v>
-      </c>
-      <c r="AT5" s="69" t="s">
+      <c r="AV5" s="70" t="s">
         <v>220</v>
       </c>
-      <c r="AU5" s="69" t="s">
+      <c r="AW5" s="69" t="s">
         <v>221</v>
       </c>
-      <c r="AV5" s="70" t="s">
-        <v>222</v>
-      </c>
-      <c r="AW5" s="69" t="s">
-        <v>223</v>
-      </c>
       <c r="AX5" s="69" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="AY5" s="68" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="6" spans="1:51" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -35151,10 +35562,10 @@
         <v>46208</v>
       </c>
       <c r="B6" s="72" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C6" s="72" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D6" s="73">
         <f>SUMIFS(MOVIMIENTOS!$E:$E,MOVIMIENTOS!$A:$A,$A6,MOVIMIENTOS!$B:$B,"COMPRA")</f>
@@ -35197,7 +35608,7 @@
         <v/>
       </c>
       <c r="N6" s="73" t="str">
-        <f>IFERROR(IF(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A6)*((MOVIMIENTOS!$B$5:$B$1021="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1021="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1021="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021)&lt;&gt;"","G-"&amp;LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A6)*((MOVIMIENTOS!$B$5:$B$1021="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1021="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1021="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021),""),"")</f>
+        <f>IFERROR(IF(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A6)*((MOVIMIENTOS!$B$5:$B$1025="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1025="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1025="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025)&lt;&gt;"","G-"&amp;LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A6)*((MOVIMIENTOS!$B$5:$B$1025="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1025="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1025="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025),""),"")</f>
         <v/>
       </c>
       <c r="O6" s="73">
@@ -35261,7 +35672,7 @@
         <v>0</v>
       </c>
       <c r="AD6" s="73" t="str">
-        <f>IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A6)*(MOVIMIENTOS!$B$5:$B$1021="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1021="Chancho")*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021),IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A6)*(MOVIMIENTOS!$B$5:$B$1021="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1021="Chancho")*(MOVIMIENTOS!$H$5:$H$1021&lt;&gt;"")),MOVIMIENTOS!$H$5:$H$1021),""))</f>
+        <f>IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A6)*(MOVIMIENTOS!$B$5:$B$1025="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1025="Chancho")*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025),IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A6)*(MOVIMIENTOS!$B$5:$B$1025="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1025="Chancho")*(MOVIMIENTOS!$H$5:$H$1025&lt;&gt;"")),MOVIMIENTOS!$H$5:$H$1025),""))</f>
         <v/>
       </c>
       <c r="AE6" s="73">
@@ -35309,7 +35720,7 @@
         <v>0</v>
       </c>
       <c r="AR6" s="73" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="AS6" s="74">
         <f>SUMIF($C$6:$C$200,$AR6,$E$6:$E$200)</f>
@@ -35345,10 +35756,10 @@
         <v>46209</v>
       </c>
       <c r="B7" s="72" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C7" s="72" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D7" s="73">
         <f>SUMIFS(MOVIMIENTOS!$E:$E,MOVIMIENTOS!$A:$A,$A7,MOVIMIENTOS!$B:$B,"COMPRA")</f>
@@ -35391,7 +35802,7 @@
         <v/>
       </c>
       <c r="N7" s="73" t="str">
-        <f>IFERROR(IF(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A7)*((MOVIMIENTOS!$B$5:$B$1021="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1021="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1021="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021)&lt;&gt;"","G-"&amp;LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A7)*((MOVIMIENTOS!$B$5:$B$1021="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1021="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1021="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021),""),"")</f>
+        <f>IFERROR(IF(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A7)*((MOVIMIENTOS!$B$5:$B$1025="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1025="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1025="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025)&lt;&gt;"","G-"&amp;LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A7)*((MOVIMIENTOS!$B$5:$B$1025="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1025="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1025="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025),""),"")</f>
         <v/>
       </c>
       <c r="O7" s="73">
@@ -35455,7 +35866,7 @@
         <v>0</v>
       </c>
       <c r="AD7" s="73" t="str">
-        <f>IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A7)*(MOVIMIENTOS!$B$5:$B$1021="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1021="Chancho")*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021),IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A7)*(MOVIMIENTOS!$B$5:$B$1021="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1021="Chancho")*(MOVIMIENTOS!$H$5:$H$1021&lt;&gt;"")),MOVIMIENTOS!$H$5:$H$1021),""))</f>
+        <f>IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A7)*(MOVIMIENTOS!$B$5:$B$1025="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1025="Chancho")*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025),IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A7)*(MOVIMIENTOS!$B$5:$B$1025="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1025="Chancho")*(MOVIMIENTOS!$H$5:$H$1025&lt;&gt;"")),MOVIMIENTOS!$H$5:$H$1025),""))</f>
         <v/>
       </c>
       <c r="AE7" s="73">
@@ -35503,7 +35914,7 @@
         <v>0</v>
       </c>
       <c r="AR7" s="73" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="AS7" s="74">
         <f>SUMIF($C$6:$C$200,$AR7,$E$6:$E$200)</f>
@@ -35539,10 +35950,10 @@
         <v>46210</v>
       </c>
       <c r="B8" s="72" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C8" s="72" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D8" s="73">
         <f>SUMIFS(MOVIMIENTOS!$E:$E,MOVIMIENTOS!$A:$A,$A8,MOVIMIENTOS!$B:$B,"COMPRA")</f>
@@ -35585,7 +35996,7 @@
         <v/>
       </c>
       <c r="N8" s="73" t="str">
-        <f>IFERROR(IF(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A8)*((MOVIMIENTOS!$B$5:$B$1021="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1021="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1021="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021)&lt;&gt;"","G-"&amp;LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A8)*((MOVIMIENTOS!$B$5:$B$1021="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1021="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1021="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021),""),"")</f>
+        <f>IFERROR(IF(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A8)*((MOVIMIENTOS!$B$5:$B$1025="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1025="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1025="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025)&lt;&gt;"","G-"&amp;LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A8)*((MOVIMIENTOS!$B$5:$B$1025="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1025="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1025="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025),""),"")</f>
         <v/>
       </c>
       <c r="O8" s="73">
@@ -35649,7 +36060,7 @@
         <v>0</v>
       </c>
       <c r="AD8" s="73" t="str">
-        <f>IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A8)*(MOVIMIENTOS!$B$5:$B$1021="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1021="Chancho")*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021),IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A8)*(MOVIMIENTOS!$B$5:$B$1021="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1021="Chancho")*(MOVIMIENTOS!$H$5:$H$1021&lt;&gt;"")),MOVIMIENTOS!$H$5:$H$1021),""))</f>
+        <f>IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A8)*(MOVIMIENTOS!$B$5:$B$1025="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1025="Chancho")*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025),IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A8)*(MOVIMIENTOS!$B$5:$B$1025="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1025="Chancho")*(MOVIMIENTOS!$H$5:$H$1025&lt;&gt;"")),MOVIMIENTOS!$H$5:$H$1025),""))</f>
         <v/>
       </c>
       <c r="AE8" s="73">
@@ -35697,7 +36108,7 @@
         <v>0</v>
       </c>
       <c r="AR8" s="73" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="AS8" s="74">
         <f>SUMIF($C$6:$C$200,$AR8,$E$6:$E$200)</f>
@@ -35733,10 +36144,10 @@
         <v>46211</v>
       </c>
       <c r="B9" s="72" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C9" s="72" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D9" s="73">
         <f>SUMIFS(MOVIMIENTOS!$E:$E,MOVIMIENTOS!$A:$A,$A9,MOVIMIENTOS!$B:$B,"COMPRA")</f>
@@ -35779,7 +36190,7 @@
         <v/>
       </c>
       <c r="N9" s="73" t="str">
-        <f>IFERROR(IF(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A9)*((MOVIMIENTOS!$B$5:$B$1021="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1021="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1021="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021)&lt;&gt;"","G-"&amp;LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A9)*((MOVIMIENTOS!$B$5:$B$1021="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1021="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1021="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021),""),"")</f>
+        <f>IFERROR(IF(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A9)*((MOVIMIENTOS!$B$5:$B$1025="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1025="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1025="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025)&lt;&gt;"","G-"&amp;LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A9)*((MOVIMIENTOS!$B$5:$B$1025="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1025="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1025="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025),""),"")</f>
         <v/>
       </c>
       <c r="O9" s="73">
@@ -35843,7 +36254,7 @@
         <v>0</v>
       </c>
       <c r="AD9" s="73" t="str">
-        <f>IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A9)*(MOVIMIENTOS!$B$5:$B$1021="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1021="Chancho")*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021),IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A9)*(MOVIMIENTOS!$B$5:$B$1021="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1021="Chancho")*(MOVIMIENTOS!$H$5:$H$1021&lt;&gt;"")),MOVIMIENTOS!$H$5:$H$1021),""))</f>
+        <f>IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A9)*(MOVIMIENTOS!$B$5:$B$1025="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1025="Chancho")*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025),IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A9)*(MOVIMIENTOS!$B$5:$B$1025="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1025="Chancho")*(MOVIMIENTOS!$H$5:$H$1025&lt;&gt;"")),MOVIMIENTOS!$H$5:$H$1025),""))</f>
         <v/>
       </c>
       <c r="AE9" s="73">
@@ -35891,7 +36302,7 @@
         <v>0</v>
       </c>
       <c r="AR9" s="73" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="AS9" s="74">
         <f>SUMIF($C$6:$C$200,$AR9,$E$6:$E$200)</f>
@@ -35927,10 +36338,10 @@
         <v>46212</v>
       </c>
       <c r="B10" s="72" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C10" s="72" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D10" s="73">
         <f>SUMIFS(MOVIMIENTOS!$E:$E,MOVIMIENTOS!$A:$A,$A10,MOVIMIENTOS!$B:$B,"COMPRA")</f>
@@ -35973,7 +36384,7 @@
         <v/>
       </c>
       <c r="N10" s="73" t="str">
-        <f>IFERROR(IF(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A10)*((MOVIMIENTOS!$B$5:$B$1021="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1021="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1021="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021)&lt;&gt;"","G-"&amp;LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A10)*((MOVIMIENTOS!$B$5:$B$1021="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1021="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1021="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021),""),"")</f>
+        <f>IFERROR(IF(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A10)*((MOVIMIENTOS!$B$5:$B$1025="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1025="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1025="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025)&lt;&gt;"","G-"&amp;LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A10)*((MOVIMIENTOS!$B$5:$B$1025="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1025="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1025="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025),""),"")</f>
         <v/>
       </c>
       <c r="O10" s="73">
@@ -36037,7 +36448,7 @@
         <v>0</v>
       </c>
       <c r="AD10" s="73" t="str">
-        <f>IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A10)*(MOVIMIENTOS!$B$5:$B$1021="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1021="Chancho")*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021),IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A10)*(MOVIMIENTOS!$B$5:$B$1021="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1021="Chancho")*(MOVIMIENTOS!$H$5:$H$1021&lt;&gt;"")),MOVIMIENTOS!$H$5:$H$1021),""))</f>
+        <f>IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A10)*(MOVIMIENTOS!$B$5:$B$1025="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1025="Chancho")*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025),IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A10)*(MOVIMIENTOS!$B$5:$B$1025="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1025="Chancho")*(MOVIMIENTOS!$H$5:$H$1025&lt;&gt;"")),MOVIMIENTOS!$H$5:$H$1025),""))</f>
         <v/>
       </c>
       <c r="AE10" s="73">
@@ -36085,7 +36496,7 @@
         <v>0</v>
       </c>
       <c r="AR10" s="73" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="AS10" s="74">
         <f>SUMIF($C$6:$C$200,$AR10,$E$6:$E$200)</f>
@@ -36121,10 +36532,10 @@
         <v>46213</v>
       </c>
       <c r="B11" s="72" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C11" s="72" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D11" s="73">
         <f>SUMIFS(MOVIMIENTOS!$E:$E,MOVIMIENTOS!$A:$A,$A11,MOVIMIENTOS!$B:$B,"COMPRA")</f>
@@ -36167,7 +36578,7 @@
         <v/>
       </c>
       <c r="N11" s="73" t="str">
-        <f>IFERROR(IF(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A11)*((MOVIMIENTOS!$B$5:$B$1021="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1021="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1021="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021)&lt;&gt;"","G-"&amp;LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A11)*((MOVIMIENTOS!$B$5:$B$1021="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1021="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1021="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021),""),"")</f>
+        <f>IFERROR(IF(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A11)*((MOVIMIENTOS!$B$5:$B$1025="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1025="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1025="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025)&lt;&gt;"","G-"&amp;LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A11)*((MOVIMIENTOS!$B$5:$B$1025="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1025="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1025="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025),""),"")</f>
         <v/>
       </c>
       <c r="O11" s="73">
@@ -36231,7 +36642,7 @@
         <v>0</v>
       </c>
       <c r="AD11" s="73" t="str">
-        <f>IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A11)*(MOVIMIENTOS!$B$5:$B$1021="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1021="Chancho")*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021),IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A11)*(MOVIMIENTOS!$B$5:$B$1021="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1021="Chancho")*(MOVIMIENTOS!$H$5:$H$1021&lt;&gt;"")),MOVIMIENTOS!$H$5:$H$1021),""))</f>
+        <f>IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A11)*(MOVIMIENTOS!$B$5:$B$1025="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1025="Chancho")*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025),IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A11)*(MOVIMIENTOS!$B$5:$B$1025="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1025="Chancho")*(MOVIMIENTOS!$H$5:$H$1025&lt;&gt;"")),MOVIMIENTOS!$H$5:$H$1025),""))</f>
         <v/>
       </c>
       <c r="AE11" s="73">
@@ -36279,7 +36690,7 @@
         <v>0</v>
       </c>
       <c r="AR11" s="73" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="AS11" s="74">
         <f t="shared" ref="AS11:AX11" si="14">SUM(AS6:AS10)</f>
@@ -36315,10 +36726,10 @@
         <v>46214</v>
       </c>
       <c r="B12" s="72" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C12" s="72" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D12" s="73">
         <f>SUMIFS(MOVIMIENTOS!$E:$E,MOVIMIENTOS!$A:$A,$A12,MOVIMIENTOS!$B:$B,"COMPRA")</f>
@@ -36361,7 +36772,7 @@
         <v/>
       </c>
       <c r="N12" s="73" t="str">
-        <f>IFERROR(IF(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A12)*((MOVIMIENTOS!$B$5:$B$1021="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1021="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1021="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021)&lt;&gt;"","G-"&amp;LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A12)*((MOVIMIENTOS!$B$5:$B$1021="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1021="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1021="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021),""),"")</f>
+        <f>IFERROR(IF(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A12)*((MOVIMIENTOS!$B$5:$B$1025="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1025="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1025="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025)&lt;&gt;"","G-"&amp;LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A12)*((MOVIMIENTOS!$B$5:$B$1025="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1025="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1025="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025),""),"")</f>
         <v/>
       </c>
       <c r="O12" s="73">
@@ -36425,7 +36836,7 @@
         <v>0</v>
       </c>
       <c r="AD12" s="73" t="str">
-        <f>IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A12)*(MOVIMIENTOS!$B$5:$B$1021="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1021="Chancho")*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021),IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A12)*(MOVIMIENTOS!$B$5:$B$1021="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1021="Chancho")*(MOVIMIENTOS!$H$5:$H$1021&lt;&gt;"")),MOVIMIENTOS!$H$5:$H$1021),""))</f>
+        <f>IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A12)*(MOVIMIENTOS!$B$5:$B$1025="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1025="Chancho")*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025),IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A12)*(MOVIMIENTOS!$B$5:$B$1025="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1025="Chancho")*(MOVIMIENTOS!$H$5:$H$1025&lt;&gt;"")),MOVIMIENTOS!$H$5:$H$1025),""))</f>
         <v/>
       </c>
       <c r="AE12" s="78">
@@ -36486,10 +36897,10 @@
         <v>46215</v>
       </c>
       <c r="B13" s="72" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C13" s="72" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D13" s="73">
         <f>SUMIFS(MOVIMIENTOS!$E:$E,MOVIMIENTOS!$A:$A,$A13,MOVIMIENTOS!$B:$B,"COMPRA")</f>
@@ -36532,7 +36943,7 @@
         <v>Supesa</v>
       </c>
       <c r="N13" s="73" t="str">
-        <f>IFERROR(IF(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A13)*((MOVIMIENTOS!$B$5:$B$1021="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1021="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1021="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021)&lt;&gt;"","G-"&amp;LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A13)*((MOVIMIENTOS!$B$5:$B$1021="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1021="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1021="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021),""),"")</f>
+        <f>IFERROR(IF(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A13)*((MOVIMIENTOS!$B$5:$B$1025="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1025="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1025="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025)&lt;&gt;"","G-"&amp;LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A13)*((MOVIMIENTOS!$B$5:$B$1025="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1025="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1025="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025),""),"")</f>
         <v>G-2977</v>
       </c>
       <c r="O13" s="73">
@@ -36596,7 +37007,7 @@
         <v>0</v>
       </c>
       <c r="AD13" s="73" t="str">
-        <f>IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A13)*(MOVIMIENTOS!$B$5:$B$1021="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1021="Chancho")*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021),IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A13)*(MOVIMIENTOS!$B$5:$B$1021="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1021="Chancho")*(MOVIMIENTOS!$H$5:$H$1021&lt;&gt;"")),MOVIMIENTOS!$H$5:$H$1021),""))</f>
+        <f>IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A13)*(MOVIMIENTOS!$B$5:$B$1025="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1025="Chancho")*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025),IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A13)*(MOVIMIENTOS!$B$5:$B$1025="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1025="Chancho")*(MOVIMIENTOS!$H$5:$H$1025&lt;&gt;"")),MOVIMIENTOS!$H$5:$H$1025),""))</f>
         <v/>
       </c>
       <c r="AE13" s="78">
@@ -36657,10 +37068,10 @@
         <v>46216</v>
       </c>
       <c r="B14" s="72" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C14" s="72" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D14" s="73">
         <f>SUMIFS(MOVIMIENTOS!$E:$E,MOVIMIENTOS!$A:$A,$A14,MOVIMIENTOS!$B:$B,"COMPRA")</f>
@@ -36703,7 +37114,7 @@
         <v>Supesa</v>
       </c>
       <c r="N14" s="73" t="str">
-        <f>IFERROR(IF(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A14)*((MOVIMIENTOS!$B$5:$B$1021="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1021="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1021="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021)&lt;&gt;"","G-"&amp;LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A14)*((MOVIMIENTOS!$B$5:$B$1021="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1021="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1021="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021),""),"")</f>
+        <f>IFERROR(IF(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A14)*((MOVIMIENTOS!$B$5:$B$1025="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1025="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1025="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025)&lt;&gt;"","G-"&amp;LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A14)*((MOVIMIENTOS!$B$5:$B$1025="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1025="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1025="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025),""),"")</f>
         <v>G-2980</v>
       </c>
       <c r="O14" s="73">
@@ -36767,7 +37178,7 @@
         <v>0</v>
       </c>
       <c r="AD14" s="73" t="str">
-        <f>IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A14)*(MOVIMIENTOS!$B$5:$B$1021="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1021="Chancho")*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021),IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A14)*(MOVIMIENTOS!$B$5:$B$1021="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1021="Chancho")*(MOVIMIENTOS!$H$5:$H$1021&lt;&gt;"")),MOVIMIENTOS!$H$5:$H$1021),""))</f>
+        <f>IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A14)*(MOVIMIENTOS!$B$5:$B$1025="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1025="Chancho")*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025),IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A14)*(MOVIMIENTOS!$B$5:$B$1025="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1025="Chancho")*(MOVIMIENTOS!$H$5:$H$1025&lt;&gt;"")),MOVIMIENTOS!$H$5:$H$1025),""))</f>
         <v/>
       </c>
       <c r="AE14" s="78">
@@ -36828,10 +37239,10 @@
         <v>46217</v>
       </c>
       <c r="B15" s="72" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C15" s="72" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D15" s="73">
         <f>SUMIFS(MOVIMIENTOS!$E:$E,MOVIMIENTOS!$A:$A,$A15,MOVIMIENTOS!$B:$B,"COMPRA")</f>
@@ -36874,7 +37285,7 @@
         <v>Supesa</v>
       </c>
       <c r="N15" s="73" t="str">
-        <f>IFERROR(IF(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A15)*((MOVIMIENTOS!$B$5:$B$1021="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1021="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1021="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021)&lt;&gt;"","G-"&amp;LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A15)*((MOVIMIENTOS!$B$5:$B$1021="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1021="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1021="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021),""),"")</f>
+        <f>IFERROR(IF(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A15)*((MOVIMIENTOS!$B$5:$B$1025="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1025="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1025="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025)&lt;&gt;"","G-"&amp;LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A15)*((MOVIMIENTOS!$B$5:$B$1025="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1025="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1025="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025),""),"")</f>
         <v>G-2984</v>
       </c>
       <c r="O15" s="73">
@@ -36938,7 +37349,7 @@
         <v>0</v>
       </c>
       <c r="AD15" s="73" t="str">
-        <f>IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A15)*(MOVIMIENTOS!$B$5:$B$1021="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1021="Chancho")*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021),IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A15)*(MOVIMIENTOS!$B$5:$B$1021="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1021="Chancho")*(MOVIMIENTOS!$H$5:$H$1021&lt;&gt;"")),MOVIMIENTOS!$H$5:$H$1021),""))</f>
+        <f>IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A15)*(MOVIMIENTOS!$B$5:$B$1025="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1025="Chancho")*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025),IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A15)*(MOVIMIENTOS!$B$5:$B$1025="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1025="Chancho")*(MOVIMIENTOS!$H$5:$H$1025&lt;&gt;"")),MOVIMIENTOS!$H$5:$H$1025),""))</f>
         <v/>
       </c>
       <c r="AE15" s="78">
@@ -36999,10 +37410,10 @@
         <v>46218</v>
       </c>
       <c r="B16" s="72" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C16" s="72" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D16" s="73">
         <f>SUMIFS(MOVIMIENTOS!$E:$E,MOVIMIENTOS!$A:$A,$A16,MOVIMIENTOS!$B:$B,"COMPRA")</f>
@@ -37045,7 +37456,7 @@
         <v>Supesa</v>
       </c>
       <c r="N16" s="73" t="str">
-        <f>IFERROR(IF(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A16)*((MOVIMIENTOS!$B$5:$B$1021="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1021="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1021="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021)&lt;&gt;"","G-"&amp;LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A16)*((MOVIMIENTOS!$B$5:$B$1021="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1021="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1021="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021),""),"")</f>
+        <f>IFERROR(IF(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A16)*((MOVIMIENTOS!$B$5:$B$1025="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1025="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1025="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025)&lt;&gt;"","G-"&amp;LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A16)*((MOVIMIENTOS!$B$5:$B$1025="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1025="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1025="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025),""),"")</f>
         <v>G-2986</v>
       </c>
       <c r="O16" s="73">
@@ -37109,7 +37520,7 @@
         <v>3395</v>
       </c>
       <c r="AD16" s="73" t="str">
-        <f>IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A16)*(MOVIMIENTOS!$B$5:$B$1021="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1021="Chancho")*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021),IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A16)*(MOVIMIENTOS!$B$5:$B$1021="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1021="Chancho")*(MOVIMIENTOS!$H$5:$H$1021&lt;&gt;"")),MOVIMIENTOS!$H$5:$H$1021),""))</f>
+        <f>IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A16)*(MOVIMIENTOS!$B$5:$B$1025="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1025="Chancho")*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025),IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A16)*(MOVIMIENTOS!$B$5:$B$1025="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1025="Chancho")*(MOVIMIENTOS!$H$5:$H$1025&lt;&gt;"")),MOVIMIENTOS!$H$5:$H$1025),""))</f>
         <v>TCK002-724</v>
       </c>
       <c r="AE16" s="78">
@@ -37170,10 +37581,10 @@
         <v>46219</v>
       </c>
       <c r="B17" s="72" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C17" s="72" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D17" s="73">
         <f>SUMIFS(MOVIMIENTOS!$E:$E,MOVIMIENTOS!$A:$A,$A17,MOVIMIENTOS!$B:$B,"COMPRA")</f>
@@ -37216,7 +37627,7 @@
         <v>Supesa</v>
       </c>
       <c r="N17" s="73" t="str">
-        <f>IFERROR(IF(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A17)*((MOVIMIENTOS!$B$5:$B$1021="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1021="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1021="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021)&lt;&gt;"","G-"&amp;LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A17)*((MOVIMIENTOS!$B$5:$B$1021="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1021="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1021="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021),""),"")</f>
+        <f>IFERROR(IF(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A17)*((MOVIMIENTOS!$B$5:$B$1025="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1025="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1025="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025)&lt;&gt;"","G-"&amp;LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A17)*((MOVIMIENTOS!$B$5:$B$1025="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1025="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1025="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025),""),"")</f>
         <v>G-2992</v>
       </c>
       <c r="O17" s="73">
@@ -37280,7 +37691,7 @@
         <v>0</v>
       </c>
       <c r="AD17" s="73" t="str">
-        <f>IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A17)*(MOVIMIENTOS!$B$5:$B$1021="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1021="Chancho")*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021),IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A17)*(MOVIMIENTOS!$B$5:$B$1021="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1021="Chancho")*(MOVIMIENTOS!$H$5:$H$1021&lt;&gt;"")),MOVIMIENTOS!$H$5:$H$1021),""))</f>
+        <f>IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A17)*(MOVIMIENTOS!$B$5:$B$1025="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1025="Chancho")*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025),IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A17)*(MOVIMIENTOS!$B$5:$B$1025="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1025="Chancho")*(MOVIMIENTOS!$H$5:$H$1025&lt;&gt;"")),MOVIMIENTOS!$H$5:$H$1025),""))</f>
         <v/>
       </c>
       <c r="AE17" s="78">
@@ -37341,10 +37752,10 @@
         <v>46220</v>
       </c>
       <c r="B18" s="72" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C18" s="72" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D18" s="73">
         <f>SUMIFS(MOVIMIENTOS!$E:$E,MOVIMIENTOS!$A:$A,$A18,MOVIMIENTOS!$B:$B,"COMPRA")</f>
@@ -37387,7 +37798,7 @@
         <v>Supesa</v>
       </c>
       <c r="N18" s="73" t="str">
-        <f>IFERROR(IF(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A18)*((MOVIMIENTOS!$B$5:$B$1021="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1021="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1021="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021)&lt;&gt;"","G-"&amp;LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A18)*((MOVIMIENTOS!$B$5:$B$1021="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1021="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1021="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021),""),"")</f>
+        <f>IFERROR(IF(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A18)*((MOVIMIENTOS!$B$5:$B$1025="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1025="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1025="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025)&lt;&gt;"","G-"&amp;LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A18)*((MOVIMIENTOS!$B$5:$B$1025="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1025="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1025="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025),""),"")</f>
         <v>G-2994</v>
       </c>
       <c r="O18" s="73">
@@ -37451,7 +37862,7 @@
         <v>1455</v>
       </c>
       <c r="AD18" s="73" t="str">
-        <f>IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A18)*(MOVIMIENTOS!$B$5:$B$1021="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1021="Chancho")*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021),IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A18)*(MOVIMIENTOS!$B$5:$B$1021="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1021="Chancho")*(MOVIMIENTOS!$H$5:$H$1021&lt;&gt;"")),MOVIMIENTOS!$H$5:$H$1021),""))</f>
+        <f>IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A18)*(MOVIMIENTOS!$B$5:$B$1025="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1025="Chancho")*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025),IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A18)*(MOVIMIENTOS!$B$5:$B$1025="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1025="Chancho")*(MOVIMIENTOS!$H$5:$H$1025&lt;&gt;"")),MOVIMIENTOS!$H$5:$H$1025),""))</f>
         <v>TCK002-725</v>
       </c>
       <c r="AE18" s="78">
@@ -37512,10 +37923,10 @@
         <v>46221</v>
       </c>
       <c r="B19" s="72" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C19" s="72" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D19" s="73">
         <f>SUMIFS(MOVIMIENTOS!$E:$E,MOVIMIENTOS!$A:$A,$A19,MOVIMIENTOS!$B:$B,"COMPRA")</f>
@@ -37558,7 +37969,7 @@
         <v>Supesa</v>
       </c>
       <c r="N19" s="73" t="str">
-        <f>IFERROR(IF(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A19)*((MOVIMIENTOS!$B$5:$B$1021="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1021="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1021="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021)&lt;&gt;"","G-"&amp;LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A19)*((MOVIMIENTOS!$B$5:$B$1021="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1021="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1021="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021),""),"")</f>
+        <f>IFERROR(IF(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A19)*((MOVIMIENTOS!$B$5:$B$1025="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1025="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1025="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025)&lt;&gt;"","G-"&amp;LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A19)*((MOVIMIENTOS!$B$5:$B$1025="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1025="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1025="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025),""),"")</f>
         <v>G-2996</v>
       </c>
       <c r="O19" s="73">
@@ -37622,7 +38033,7 @@
         <v>0</v>
       </c>
       <c r="AD19" s="73" t="str">
-        <f>IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A19)*(MOVIMIENTOS!$B$5:$B$1021="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1021="Chancho")*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021),IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A19)*(MOVIMIENTOS!$B$5:$B$1021="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1021="Chancho")*(MOVIMIENTOS!$H$5:$H$1021&lt;&gt;"")),MOVIMIENTOS!$H$5:$H$1021),""))</f>
+        <f>IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A19)*(MOVIMIENTOS!$B$5:$B$1025="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1025="Chancho")*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025),IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A19)*(MOVIMIENTOS!$B$5:$B$1025="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1025="Chancho")*(MOVIMIENTOS!$H$5:$H$1025&lt;&gt;"")),MOVIMIENTOS!$H$5:$H$1025),""))</f>
         <v/>
       </c>
       <c r="AE19" s="78">
@@ -37683,10 +38094,10 @@
         <v>46222</v>
       </c>
       <c r="B20" s="72" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C20" s="72" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D20" s="73">
         <f>SUMIFS(MOVIMIENTOS!$E:$E,MOVIMIENTOS!$A:$A,$A20,MOVIMIENTOS!$B:$B,"COMPRA")</f>
@@ -37729,7 +38140,7 @@
         <v>Supesa</v>
       </c>
       <c r="N20" s="73" t="str">
-        <f>IFERROR(IF(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A20)*((MOVIMIENTOS!$B$5:$B$1021="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1021="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1021="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021)&lt;&gt;"","G-"&amp;LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A20)*((MOVIMIENTOS!$B$5:$B$1021="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1021="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1021="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021),""),"")</f>
+        <f>IFERROR(IF(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A20)*((MOVIMIENTOS!$B$5:$B$1025="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1025="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1025="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025)&lt;&gt;"","G-"&amp;LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A20)*((MOVIMIENTOS!$B$5:$B$1025="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1025="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1025="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025),""),"")</f>
         <v>G-2998</v>
       </c>
       <c r="O20" s="73">
@@ -37793,7 +38204,7 @@
         <v>0</v>
       </c>
       <c r="AD20" s="73" t="str">
-        <f>IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A20)*(MOVIMIENTOS!$B$5:$B$1021="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1021="Chancho")*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021),IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A20)*(MOVIMIENTOS!$B$5:$B$1021="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1021="Chancho")*(MOVIMIENTOS!$H$5:$H$1021&lt;&gt;"")),MOVIMIENTOS!$H$5:$H$1021),""))</f>
+        <f>IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A20)*(MOVIMIENTOS!$B$5:$B$1025="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1025="Chancho")*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025),IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A20)*(MOVIMIENTOS!$B$5:$B$1025="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1025="Chancho")*(MOVIMIENTOS!$H$5:$H$1025&lt;&gt;"")),MOVIMIENTOS!$H$5:$H$1025),""))</f>
         <v/>
       </c>
       <c r="AE20" s="78">
@@ -37854,10 +38265,10 @@
         <v>46223</v>
       </c>
       <c r="B21" s="72" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C21" s="72" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D21" s="73">
         <f>SUMIFS(MOVIMIENTOS!$E:$E,MOVIMIENTOS!$A:$A,$A21,MOVIMIENTOS!$B:$B,"COMPRA")</f>
@@ -37900,7 +38311,7 @@
         <v>Supesa</v>
       </c>
       <c r="N21" s="73" t="str">
-        <f>IFERROR(IF(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A21)*((MOVIMIENTOS!$B$5:$B$1021="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1021="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1021="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021)&lt;&gt;"","G-"&amp;LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A21)*((MOVIMIENTOS!$B$5:$B$1021="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1021="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1021="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021),""),"")</f>
+        <f>IFERROR(IF(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A21)*((MOVIMIENTOS!$B$5:$B$1025="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1025="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1025="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025)&lt;&gt;"","G-"&amp;LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A21)*((MOVIMIENTOS!$B$5:$B$1025="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1025="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1025="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025),""),"")</f>
         <v>G-3001</v>
       </c>
       <c r="O21" s="73">
@@ -37964,7 +38375,7 @@
         <v>1746</v>
       </c>
       <c r="AD21" s="73" t="str">
-        <f>IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A21)*(MOVIMIENTOS!$B$5:$B$1021="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1021="Chancho")*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021),IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A21)*(MOVIMIENTOS!$B$5:$B$1021="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1021="Chancho")*(MOVIMIENTOS!$H$5:$H$1021&lt;&gt;"")),MOVIMIENTOS!$H$5:$H$1021),""))</f>
+        <f>IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A21)*(MOVIMIENTOS!$B$5:$B$1025="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1025="Chancho")*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025),IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A21)*(MOVIMIENTOS!$B$5:$B$1025="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1025="Chancho")*(MOVIMIENTOS!$H$5:$H$1025&lt;&gt;"")),MOVIMIENTOS!$H$5:$H$1025),""))</f>
         <v>TCK002-726</v>
       </c>
       <c r="AE21" s="78">
@@ -38025,10 +38436,10 @@
         <v>46224</v>
       </c>
       <c r="B22" s="72" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C22" s="72" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D22" s="73">
         <f>SUMIFS(MOVIMIENTOS!$E:$E,MOVIMIENTOS!$A:$A,$A22,MOVIMIENTOS!$B:$B,"COMPRA")</f>
@@ -38071,7 +38482,7 @@
         <v>Supesa</v>
       </c>
       <c r="N22" s="73" t="str">
-        <f>IFERROR(IF(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A22)*((MOVIMIENTOS!$B$5:$B$1021="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1021="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1021="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021)&lt;&gt;"","G-"&amp;LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A22)*((MOVIMIENTOS!$B$5:$B$1021="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1021="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1021="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021),""),"")</f>
+        <f>IFERROR(IF(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A22)*((MOVIMIENTOS!$B$5:$B$1025="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1025="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1025="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025)&lt;&gt;"","G-"&amp;LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A22)*((MOVIMIENTOS!$B$5:$B$1025="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1025="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1025="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025),""),"")</f>
         <v>G-3004</v>
       </c>
       <c r="O22" s="73">
@@ -38135,7 +38546,7 @@
         <v>0</v>
       </c>
       <c r="AD22" s="73" t="str">
-        <f>IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A22)*(MOVIMIENTOS!$B$5:$B$1021="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1021="Chancho")*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021),IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A22)*(MOVIMIENTOS!$B$5:$B$1021="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1021="Chancho")*(MOVIMIENTOS!$H$5:$H$1021&lt;&gt;"")),MOVIMIENTOS!$H$5:$H$1021),""))</f>
+        <f>IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A22)*(MOVIMIENTOS!$B$5:$B$1025="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1025="Chancho")*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025),IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A22)*(MOVIMIENTOS!$B$5:$B$1025="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1025="Chancho")*(MOVIMIENTOS!$H$5:$H$1025&lt;&gt;"")),MOVIMIENTOS!$H$5:$H$1025),""))</f>
         <v/>
       </c>
       <c r="AE22" s="78">
@@ -38196,10 +38607,10 @@
         <v>46225</v>
       </c>
       <c r="B23" s="72" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C23" s="72" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D23" s="73">
         <f>SUMIFS(MOVIMIENTOS!$E:$E,MOVIMIENTOS!$A:$A,$A23,MOVIMIENTOS!$B:$B,"COMPRA")</f>
@@ -38242,7 +38653,7 @@
         <v>Supesa</v>
       </c>
       <c r="N23" s="73" t="str">
-        <f>IFERROR(IF(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A23)*((MOVIMIENTOS!$B$5:$B$1021="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1021="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1021="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021)&lt;&gt;"","G-"&amp;LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A23)*((MOVIMIENTOS!$B$5:$B$1021="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1021="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1021="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021),""),"")</f>
+        <f>IFERROR(IF(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A23)*((MOVIMIENTOS!$B$5:$B$1025="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1025="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1025="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025)&lt;&gt;"","G-"&amp;LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A23)*((MOVIMIENTOS!$B$5:$B$1025="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1025="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1025="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025),""),"")</f>
         <v>G-3006</v>
       </c>
       <c r="O23" s="73">
@@ -38306,8 +38717,8 @@
         <v>970</v>
       </c>
       <c r="AD23" s="73" t="str">
-        <f>IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A23)*(MOVIMIENTOS!$B$5:$B$1021="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1021="Chancho")*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021),IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A23)*(MOVIMIENTOS!$B$5:$B$1021="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1021="Chancho")*(MOVIMIENTOS!$H$5:$H$1021&lt;&gt;"")),MOVIMIENTOS!$H$5:$H$1021),""))</f>
-        <v>S/T</v>
+        <f>IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A23)*(MOVIMIENTOS!$B$5:$B$1025="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1025="Chancho")*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025),IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A23)*(MOVIMIENTOS!$B$5:$B$1025="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1025="Chancho")*(MOVIMIENTOS!$H$5:$H$1025&lt;&gt;"")),MOVIMIENTOS!$H$5:$H$1025),""))</f>
+        <v>FALTA</v>
       </c>
       <c r="AE23" s="78">
         <f>IFERROR(INDEX('SALDO DIARIO'!$F:$F,MATCH($A23,'SALDO DIARIO'!$A:$A,0)),0)</f>
@@ -38367,10 +38778,10 @@
         <v>46226</v>
       </c>
       <c r="B24" s="72" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C24" s="72" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D24" s="73">
         <f>SUMIFS(MOVIMIENTOS!$E:$E,MOVIMIENTOS!$A:$A,$A24,MOVIMIENTOS!$B:$B,"COMPRA")</f>
@@ -38413,7 +38824,7 @@
         <v>Supesa</v>
       </c>
       <c r="N24" s="73" t="str">
-        <f>IFERROR(IF(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A24)*((MOVIMIENTOS!$B$5:$B$1021="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1021="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1021="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021)&lt;&gt;"","G-"&amp;LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A24)*((MOVIMIENTOS!$B$5:$B$1021="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1021="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1021="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021),""),"")</f>
+        <f>IFERROR(IF(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A24)*((MOVIMIENTOS!$B$5:$B$1025="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1025="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1025="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025)&lt;&gt;"","G-"&amp;LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A24)*((MOVIMIENTOS!$B$5:$B$1025="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1025="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1025="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025),""),"")</f>
         <v>G-3008</v>
       </c>
       <c r="O24" s="73">
@@ -38477,7 +38888,7 @@
         <v>0</v>
       </c>
       <c r="AD24" s="73" t="str">
-        <f>IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A24)*(MOVIMIENTOS!$B$5:$B$1021="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1021="Chancho")*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021),IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A24)*(MOVIMIENTOS!$B$5:$B$1021="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1021="Chancho")*(MOVIMIENTOS!$H$5:$H$1021&lt;&gt;"")),MOVIMIENTOS!$H$5:$H$1021),""))</f>
+        <f>IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A24)*(MOVIMIENTOS!$B$5:$B$1025="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1025="Chancho")*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025),IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A24)*(MOVIMIENTOS!$B$5:$B$1025="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1025="Chancho")*(MOVIMIENTOS!$H$5:$H$1025&lt;&gt;"")),MOVIMIENTOS!$H$5:$H$1025),""))</f>
         <v/>
       </c>
       <c r="AE24" s="78">
@@ -38530,10 +38941,10 @@
         <v>46227</v>
       </c>
       <c r="B25" s="72" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C25" s="72" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D25" s="73">
         <f>SUMIFS(MOVIMIENTOS!$E:$E,MOVIMIENTOS!$A:$A,$A25,MOVIMIENTOS!$B:$B,"COMPRA")</f>
@@ -38576,7 +38987,7 @@
         <v>Supesa Tottus</v>
       </c>
       <c r="N25" s="73" t="str">
-        <f>IFERROR(IF(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A25)*((MOVIMIENTOS!$B$5:$B$1021="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1021="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1021="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021)&lt;&gt;"","G-"&amp;LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A25)*((MOVIMIENTOS!$B$5:$B$1021="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1021="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1021="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021),""),"")</f>
+        <f>IFERROR(IF(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A25)*((MOVIMIENTOS!$B$5:$B$1025="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1025="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1025="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025)&lt;&gt;"","G-"&amp;LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A25)*((MOVIMIENTOS!$B$5:$B$1025="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1025="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1025="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025),""),"")</f>
         <v>G-3011</v>
       </c>
       <c r="O25" s="73">
@@ -38640,7 +39051,7 @@
         <v>970</v>
       </c>
       <c r="AD25" s="73" t="str">
-        <f>IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A25)*(MOVIMIENTOS!$B$5:$B$1021="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1021="Chancho")*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021),IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A25)*(MOVIMIENTOS!$B$5:$B$1021="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1021="Chancho")*(MOVIMIENTOS!$H$5:$H$1021&lt;&gt;"")),MOVIMIENTOS!$H$5:$H$1021),""))</f>
+        <f>IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A25)*(MOVIMIENTOS!$B$5:$B$1025="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1025="Chancho")*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025),IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A25)*(MOVIMIENTOS!$B$5:$B$1025="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1025="Chancho")*(MOVIMIENTOS!$H$5:$H$1025&lt;&gt;"")),MOVIMIENTOS!$H$5:$H$1025),""))</f>
         <v>TCK002-734</v>
       </c>
       <c r="AE25" s="78">
@@ -38693,10 +39104,10 @@
         <v>46228</v>
       </c>
       <c r="B26" s="72" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C26" s="72" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D26" s="73">
         <f>SUMIFS(MOVIMIENTOS!$E:$E,MOVIMIENTOS!$A:$A,$A26,MOVIMIENTOS!$B:$B,"COMPRA")</f>
@@ -38739,7 +39150,7 @@
         <v>Supesa</v>
       </c>
       <c r="N26" s="73" t="str">
-        <f>IFERROR(IF(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A26)*((MOVIMIENTOS!$B$5:$B$1021="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1021="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1021="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021)&lt;&gt;"","G-"&amp;LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A26)*((MOVIMIENTOS!$B$5:$B$1021="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1021="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1021="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021),""),"")</f>
+        <f>IFERROR(IF(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A26)*((MOVIMIENTOS!$B$5:$B$1025="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1025="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1025="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025)&lt;&gt;"","G-"&amp;LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A26)*((MOVIMIENTOS!$B$5:$B$1025="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1025="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1025="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025),""),"")</f>
         <v>G-3014</v>
       </c>
       <c r="O26" s="73">
@@ -38803,7 +39214,7 @@
         <v>0</v>
       </c>
       <c r="AD26" s="73" t="str">
-        <f>IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A26)*(MOVIMIENTOS!$B$5:$B$1021="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1021="Chancho")*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021),IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A26)*(MOVIMIENTOS!$B$5:$B$1021="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1021="Chancho")*(MOVIMIENTOS!$H$5:$H$1021&lt;&gt;"")),MOVIMIENTOS!$H$5:$H$1021),""))</f>
+        <f>IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A26)*(MOVIMIENTOS!$B$5:$B$1025="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1025="Chancho")*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025),IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A26)*(MOVIMIENTOS!$B$5:$B$1025="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1025="Chancho")*(MOVIMIENTOS!$H$5:$H$1025&lt;&gt;"")),MOVIMIENTOS!$H$5:$H$1025),""))</f>
         <v/>
       </c>
       <c r="AE26" s="78">
@@ -38856,10 +39267,10 @@
         <v>46229</v>
       </c>
       <c r="B27" s="72" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C27" s="72" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D27" s="73">
         <f>SUMIFS(MOVIMIENTOS!$E:$E,MOVIMIENTOS!$A:$A,$A27,MOVIMIENTOS!$B:$B,"COMPRA")</f>
@@ -38902,7 +39313,7 @@
         <v>Supesa</v>
       </c>
       <c r="N27" s="73" t="str">
-        <f>IFERROR(IF(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A27)*((MOVIMIENTOS!$B$5:$B$1021="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1021="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1021="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021)&lt;&gt;"","G-"&amp;LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A27)*((MOVIMIENTOS!$B$5:$B$1021="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1021="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1021="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021),""),"")</f>
+        <f>IFERROR(IF(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A27)*((MOVIMIENTOS!$B$5:$B$1025="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1025="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1025="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025)&lt;&gt;"","G-"&amp;LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A27)*((MOVIMIENTOS!$B$5:$B$1025="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1025="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1025="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025),""),"")</f>
         <v>G-3018</v>
       </c>
       <c r="O27" s="73">
@@ -38966,7 +39377,7 @@
         <v>0</v>
       </c>
       <c r="AD27" s="73" t="str">
-        <f>IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A27)*(MOVIMIENTOS!$B$5:$B$1021="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1021="Chancho")*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021),IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A27)*(MOVIMIENTOS!$B$5:$B$1021="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1021="Chancho")*(MOVIMIENTOS!$H$5:$H$1021&lt;&gt;"")),MOVIMIENTOS!$H$5:$H$1021),""))</f>
+        <f>IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A27)*(MOVIMIENTOS!$B$5:$B$1025="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1025="Chancho")*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025),IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A27)*(MOVIMIENTOS!$B$5:$B$1025="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1025="Chancho")*(MOVIMIENTOS!$H$5:$H$1025&lt;&gt;"")),MOVIMIENTOS!$H$5:$H$1025),""))</f>
         <v/>
       </c>
       <c r="AE27" s="78">
@@ -39019,10 +39430,10 @@
         <v>46230</v>
       </c>
       <c r="B28" s="72" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C28" s="72" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D28" s="73">
         <f>SUMIFS(MOVIMIENTOS!$E:$E,MOVIMIENTOS!$A:$A,$A28,MOVIMIENTOS!$B:$B,"COMPRA")</f>
@@ -39065,7 +39476,7 @@
         <v>Supesa</v>
       </c>
       <c r="N28" s="73" t="str">
-        <f>IFERROR(IF(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A28)*((MOVIMIENTOS!$B$5:$B$1021="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1021="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1021="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021)&lt;&gt;"","G-"&amp;LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A28)*((MOVIMIENTOS!$B$5:$B$1021="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1021="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1021="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021),""),"")</f>
+        <f>IFERROR(IF(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A28)*((MOVIMIENTOS!$B$5:$B$1025="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1025="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1025="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025)&lt;&gt;"","G-"&amp;LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A28)*((MOVIMIENTOS!$B$5:$B$1025="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1025="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1025="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025),""),"")</f>
         <v>G-3021</v>
       </c>
       <c r="O28" s="73">
@@ -39129,8 +39540,8 @@
         <v>2425</v>
       </c>
       <c r="AD28" s="73" t="str">
-        <f>IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A28)*(MOVIMIENTOS!$B$5:$B$1021="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1021="Chancho")*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021),IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A28)*(MOVIMIENTOS!$B$5:$B$1021="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1021="Chancho")*(MOVIMIENTOS!$H$5:$H$1021&lt;&gt;"")),MOVIMIENTOS!$H$5:$H$1021),""))</f>
-        <v>TCK002-731</v>
+        <f>IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A28)*(MOVIMIENTOS!$B$5:$B$1025="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1025="Chancho")*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025),IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A28)*(MOVIMIENTOS!$B$5:$B$1025="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1025="Chancho")*(MOVIMIENTOS!$H$5:$H$1025&lt;&gt;"")),MOVIMIENTOS!$H$5:$H$1025),""))</f>
+        <v>FALTA</v>
       </c>
       <c r="AE28" s="78">
         <f>IFERROR(INDEX('SALDO DIARIO'!$F:$F,MATCH($A28,'SALDO DIARIO'!$A:$A,0)),0)</f>
@@ -39182,10 +39593,10 @@
         <v>46231</v>
       </c>
       <c r="B29" s="72" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C29" s="72" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D29" s="73">
         <f>SUMIFS(MOVIMIENTOS!$E:$E,MOVIMIENTOS!$A:$A,$A29,MOVIMIENTOS!$B:$B,"COMPRA")</f>
@@ -39228,7 +39639,7 @@
         <v>Supesa</v>
       </c>
       <c r="N29" s="73" t="str">
-        <f>IFERROR(IF(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A29)*((MOVIMIENTOS!$B$5:$B$1021="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1021="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1021="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021)&lt;&gt;"","G-"&amp;LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A29)*((MOVIMIENTOS!$B$5:$B$1021="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1021="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1021="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021),""),"")</f>
+        <f>IFERROR(IF(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A29)*((MOVIMIENTOS!$B$5:$B$1025="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1025="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1025="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025)&lt;&gt;"","G-"&amp;LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A29)*((MOVIMIENTOS!$B$5:$B$1025="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1025="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1025="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025),""),"")</f>
         <v>G-3023</v>
       </c>
       <c r="O29" s="73">
@@ -39292,7 +39703,7 @@
         <v>0</v>
       </c>
       <c r="AD29" s="73" t="str">
-        <f>IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A29)*(MOVIMIENTOS!$B$5:$B$1021="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1021="Chancho")*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021),IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A29)*(MOVIMIENTOS!$B$5:$B$1021="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1021="Chancho")*(MOVIMIENTOS!$H$5:$H$1021&lt;&gt;"")),MOVIMIENTOS!$H$5:$H$1021),""))</f>
+        <f>IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A29)*(MOVIMIENTOS!$B$5:$B$1025="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1025="Chancho")*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025),IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A29)*(MOVIMIENTOS!$B$5:$B$1025="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1025="Chancho")*(MOVIMIENTOS!$H$5:$H$1025&lt;&gt;"")),MOVIMIENTOS!$H$5:$H$1025),""))</f>
         <v/>
       </c>
       <c r="AE29" s="78">
@@ -39345,10 +39756,10 @@
         <v>46232</v>
       </c>
       <c r="B30" s="72" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C30" s="72" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D30" s="73">
         <f>SUMIFS(MOVIMIENTOS!$E:$E,MOVIMIENTOS!$A:$A,$A30,MOVIMIENTOS!$B:$B,"COMPRA")</f>
@@ -39391,7 +39802,7 @@
         <v>Supesa</v>
       </c>
       <c r="N30" s="73" t="str">
-        <f>IFERROR(IF(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A30)*((MOVIMIENTOS!$B$5:$B$1021="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1021="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1021="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021)&lt;&gt;"","G-"&amp;LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A30)*((MOVIMIENTOS!$B$5:$B$1021="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1021="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1021="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021),""),"")</f>
+        <f>IFERROR(IF(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A30)*((MOVIMIENTOS!$B$5:$B$1025="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1025="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1025="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025)&lt;&gt;"","G-"&amp;LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A30)*((MOVIMIENTOS!$B$5:$B$1025="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1025="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1025="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025),""),"")</f>
         <v>G-3025</v>
       </c>
       <c r="O30" s="73">
@@ -39455,7 +39866,7 @@
         <v>970</v>
       </c>
       <c r="AD30" s="73" t="str">
-        <f>IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A30)*(MOVIMIENTOS!$B$5:$B$1021="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1021="Chancho")*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021),IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A30)*(MOVIMIENTOS!$B$5:$B$1021="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1021="Chancho")*(MOVIMIENTOS!$H$5:$H$1021&lt;&gt;"")),MOVIMIENTOS!$H$5:$H$1021),""))</f>
+        <f>IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A30)*(MOVIMIENTOS!$B$5:$B$1025="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1025="Chancho")*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025),IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A30)*(MOVIMIENTOS!$B$5:$B$1025="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1025="Chancho")*(MOVIMIENTOS!$H$5:$H$1025&lt;&gt;"")),MOVIMIENTOS!$H$5:$H$1025),""))</f>
         <v>TCK002-730</v>
       </c>
       <c r="AE30" s="78">
@@ -39508,10 +39919,10 @@
         <v>46233</v>
       </c>
       <c r="B31" s="72" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C31" s="72" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D31" s="73">
         <f>SUMIFS(MOVIMIENTOS!$E:$E,MOVIMIENTOS!$A:$A,$A31,MOVIMIENTOS!$B:$B,"COMPRA")</f>
@@ -39554,7 +39965,7 @@
         <v>Supesa</v>
       </c>
       <c r="N31" s="73" t="str">
-        <f>IFERROR(IF(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A31)*((MOVIMIENTOS!$B$5:$B$1021="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1021="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1021="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021)&lt;&gt;"","G-"&amp;LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A31)*((MOVIMIENTOS!$B$5:$B$1021="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1021="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1021="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021),""),"")</f>
+        <f>IFERROR(IF(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A31)*((MOVIMIENTOS!$B$5:$B$1025="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1025="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1025="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025)&lt;&gt;"","G-"&amp;LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A31)*((MOVIMIENTOS!$B$5:$B$1025="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1025="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1025="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025),""),"")</f>
         <v>G-3031</v>
       </c>
       <c r="O31" s="73">
@@ -39618,7 +40029,7 @@
         <v>0</v>
       </c>
       <c r="AD31" s="73" t="str">
-        <f>IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A31)*(MOVIMIENTOS!$B$5:$B$1021="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1021="Chancho")*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021),IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A31)*(MOVIMIENTOS!$B$5:$B$1021="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1021="Chancho")*(MOVIMIENTOS!$H$5:$H$1021&lt;&gt;"")),MOVIMIENTOS!$H$5:$H$1021),""))</f>
+        <f>IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A31)*(MOVIMIENTOS!$B$5:$B$1025="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1025="Chancho")*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025),IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A31)*(MOVIMIENTOS!$B$5:$B$1025="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1025="Chancho")*(MOVIMIENTOS!$H$5:$H$1025&lt;&gt;"")),MOVIMIENTOS!$H$5:$H$1025),""))</f>
         <v/>
       </c>
       <c r="AE31" s="78">
@@ -39671,10 +40082,10 @@
         <v>46234</v>
       </c>
       <c r="B32" s="72" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C32" s="72" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D32" s="73">
         <f>SUMIFS(MOVIMIENTOS!$E:$E,MOVIMIENTOS!$A:$A,$A32,MOVIMIENTOS!$B:$B,"COMPRA")</f>
@@ -39717,7 +40128,7 @@
         <v>Supesa</v>
       </c>
       <c r="N32" s="73" t="str">
-        <f>IFERROR(IF(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A32)*((MOVIMIENTOS!$B$5:$B$1021="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1021="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1021="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021)&lt;&gt;"","G-"&amp;LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A32)*((MOVIMIENTOS!$B$5:$B$1021="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1021="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1021="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021),""),"")</f>
+        <f>IFERROR(IF(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A32)*((MOVIMIENTOS!$B$5:$B$1025="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1025="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1025="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025)&lt;&gt;"","G-"&amp;LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A32)*((MOVIMIENTOS!$B$5:$B$1025="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1025="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1025="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025),""),"")</f>
         <v>G-3035</v>
       </c>
       <c r="O32" s="73">
@@ -39781,7 +40192,7 @@
         <v>776</v>
       </c>
       <c r="AD32" s="73" t="str">
-        <f>IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A32)*(MOVIMIENTOS!$B$5:$B$1021="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1021="Chancho")*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021),IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A32)*(MOVIMIENTOS!$B$5:$B$1021="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1021="Chancho")*(MOVIMIENTOS!$H$5:$H$1021&lt;&gt;"")),MOVIMIENTOS!$H$5:$H$1021),""))</f>
+        <f>IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A32)*(MOVIMIENTOS!$B$5:$B$1025="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1025="Chancho")*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025),IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A32)*(MOVIMIENTOS!$B$5:$B$1025="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1025="Chancho")*(MOVIMIENTOS!$H$5:$H$1025&lt;&gt;"")),MOVIMIENTOS!$H$5:$H$1025),""))</f>
         <v>TCK002-733</v>
       </c>
       <c r="AE32" s="78">
@@ -39834,10 +40245,10 @@
         <v>46235</v>
       </c>
       <c r="B33" s="72" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C33" s="72" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D33" s="73">
         <f>SUMIFS(MOVIMIENTOS!$E:$E,MOVIMIENTOS!$A:$A,$A33,MOVIMIENTOS!$B:$B,"COMPRA")</f>
@@ -39880,7 +40291,7 @@
         <v>Supesa</v>
       </c>
       <c r="N33" s="73" t="str">
-        <f>IFERROR(IF(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A33)*((MOVIMIENTOS!$B$5:$B$1021="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1021="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1021="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021)&lt;&gt;"","G-"&amp;LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A33)*((MOVIMIENTOS!$B$5:$B$1021="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1021="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1021="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021),""),"")</f>
+        <f>IFERROR(IF(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A33)*((MOVIMIENTOS!$B$5:$B$1025="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1025="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1025="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025)&lt;&gt;"","G-"&amp;LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A33)*((MOVIMIENTOS!$B$5:$B$1025="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1025="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1025="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025),""),"")</f>
         <v>G-3042</v>
       </c>
       <c r="O33" s="73">
@@ -39944,7 +40355,7 @@
         <v>485</v>
       </c>
       <c r="AD33" s="73" t="str">
-        <f>IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A33)*(MOVIMIENTOS!$B$5:$B$1021="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1021="Chancho")*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021),IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A33)*(MOVIMIENTOS!$B$5:$B$1021="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1021="Chancho")*(MOVIMIENTOS!$H$5:$H$1021&lt;&gt;"")),MOVIMIENTOS!$H$5:$H$1021),""))</f>
+        <f>IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A33)*(MOVIMIENTOS!$B$5:$B$1025="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1025="Chancho")*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025),IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A33)*(MOVIMIENTOS!$B$5:$B$1025="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1025="Chancho")*(MOVIMIENTOS!$H$5:$H$1025&lt;&gt;"")),MOVIMIENTOS!$H$5:$H$1025),""))</f>
         <v>TCK002-735</v>
       </c>
       <c r="AE33" s="78">
@@ -39997,10 +40408,10 @@
         <v>46236</v>
       </c>
       <c r="B34" s="72" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C34" s="72" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D34" s="73">
         <f>SUMIFS(MOVIMIENTOS!$E:$E,MOVIMIENTOS!$A:$A,$A34,MOVIMIENTOS!$B:$B,"COMPRA")</f>
@@ -40043,7 +40454,7 @@
         <v>Supesa</v>
       </c>
       <c r="N34" s="73" t="str">
-        <f>IFERROR(IF(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A34)*((MOVIMIENTOS!$B$5:$B$1021="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1021="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1021="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021)&lt;&gt;"","G-"&amp;LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A34)*((MOVIMIENTOS!$B$5:$B$1021="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1021="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1021="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021),""),"")</f>
+        <f>IFERROR(IF(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A34)*((MOVIMIENTOS!$B$5:$B$1025="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1025="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1025="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025)&lt;&gt;"","G-"&amp;LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A34)*((MOVIMIENTOS!$B$5:$B$1025="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1025="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1025="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025),""),"")</f>
         <v>G-3040</v>
       </c>
       <c r="O34" s="73">
@@ -40107,7 +40518,7 @@
         <v>1649</v>
       </c>
       <c r="AD34" s="73" t="str">
-        <f>IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A34)*(MOVIMIENTOS!$B$5:$B$1021="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1021="Chancho")*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021),IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A34)*(MOVIMIENTOS!$B$5:$B$1021="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1021="Chancho")*(MOVIMIENTOS!$H$5:$H$1021&lt;&gt;"")),MOVIMIENTOS!$H$5:$H$1021),""))</f>
+        <f>IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A34)*(MOVIMIENTOS!$B$5:$B$1025="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1025="Chancho")*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025),IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A34)*(MOVIMIENTOS!$B$5:$B$1025="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1025="Chancho")*(MOVIMIENTOS!$H$5:$H$1025&lt;&gt;"")),MOVIMIENTOS!$H$5:$H$1025),""))</f>
         <v>TCK002-737</v>
       </c>
       <c r="AE34" s="78">
@@ -40160,10 +40571,10 @@
         <v>46237</v>
       </c>
       <c r="B35" s="72" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C35" s="72" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D35" s="73">
         <f>SUMIFS(MOVIMIENTOS!$E:$E,MOVIMIENTOS!$A:$A,$A35,MOVIMIENTOS!$B:$B,"COMPRA")</f>
@@ -40206,7 +40617,7 @@
         <v>Supesa</v>
       </c>
       <c r="N35" s="73" t="str">
-        <f>IFERROR(IF(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A35)*((MOVIMIENTOS!$B$5:$B$1021="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1021="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1021="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021)&lt;&gt;"","G-"&amp;LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A35)*((MOVIMIENTOS!$B$5:$B$1021="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1021="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1021="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021),""),"")</f>
+        <f>IFERROR(IF(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A35)*((MOVIMIENTOS!$B$5:$B$1025="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1025="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1025="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025)&lt;&gt;"","G-"&amp;LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A35)*((MOVIMIENTOS!$B$5:$B$1025="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1025="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1025="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025),""),"")</f>
         <v>G-3046</v>
       </c>
       <c r="O35" s="73">
@@ -40270,7 +40681,7 @@
         <v>0</v>
       </c>
       <c r="AD35" s="73" t="str">
-        <f>IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A35)*(MOVIMIENTOS!$B$5:$B$1021="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1021="Chancho")*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021),IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A35)*(MOVIMIENTOS!$B$5:$B$1021="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1021="Chancho")*(MOVIMIENTOS!$H$5:$H$1021&lt;&gt;"")),MOVIMIENTOS!$H$5:$H$1021),""))</f>
+        <f>IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A35)*(MOVIMIENTOS!$B$5:$B$1025="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1025="Chancho")*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025),IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A35)*(MOVIMIENTOS!$B$5:$B$1025="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1025="Chancho")*(MOVIMIENTOS!$H$5:$H$1025&lt;&gt;"")),MOVIMIENTOS!$H$5:$H$1025),""))</f>
         <v/>
       </c>
       <c r="AE35" s="78">
@@ -40323,10 +40734,10 @@
         <v>46238</v>
       </c>
       <c r="B36" s="72" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C36" s="72" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D36" s="73">
         <f>SUMIFS(MOVIMIENTOS!$E:$E,MOVIMIENTOS!$A:$A,$A36,MOVIMIENTOS!$B:$B,"COMPRA")</f>
@@ -40369,7 +40780,7 @@
         <v>Supesa</v>
       </c>
       <c r="N36" s="73" t="str">
-        <f>IFERROR(IF(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A36)*((MOVIMIENTOS!$B$5:$B$1021="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1021="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1021="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021)&lt;&gt;"","G-"&amp;LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A36)*((MOVIMIENTOS!$B$5:$B$1021="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1021="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1021="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021),""),"")</f>
+        <f>IFERROR(IF(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A36)*((MOVIMIENTOS!$B$5:$B$1025="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1025="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1025="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025)&lt;&gt;"","G-"&amp;LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A36)*((MOVIMIENTOS!$B$5:$B$1025="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1025="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1025="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025),""),"")</f>
         <v>G-3051</v>
       </c>
       <c r="O36" s="73">
@@ -40433,7 +40844,7 @@
         <v>0</v>
       </c>
       <c r="AD36" s="73" t="str">
-        <f>IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A36)*(MOVIMIENTOS!$B$5:$B$1021="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1021="Chancho")*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021),IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A36)*(MOVIMIENTOS!$B$5:$B$1021="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1021="Chancho")*(MOVIMIENTOS!$H$5:$H$1021&lt;&gt;"")),MOVIMIENTOS!$H$5:$H$1021),""))</f>
+        <f>IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A36)*(MOVIMIENTOS!$B$5:$B$1025="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1025="Chancho")*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025),IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A36)*(MOVIMIENTOS!$B$5:$B$1025="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1025="Chancho")*(MOVIMIENTOS!$H$5:$H$1025&lt;&gt;"")),MOVIMIENTOS!$H$5:$H$1025),""))</f>
         <v/>
       </c>
       <c r="AE36" s="78">
@@ -40486,10 +40897,10 @@
         <v>46239</v>
       </c>
       <c r="B37" s="72" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C37" s="72" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D37" s="73">
         <f>SUMIFS(MOVIMIENTOS!$E:$E,MOVIMIENTOS!$A:$A,$A37,MOVIMIENTOS!$B:$B,"COMPRA")</f>
@@ -40532,7 +40943,7 @@
         <v>Supesa</v>
       </c>
       <c r="N37" s="73" t="str">
-        <f>IFERROR(IF(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A37)*((MOVIMIENTOS!$B$5:$B$1021="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1021="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1021="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021)&lt;&gt;"","G-"&amp;LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A37)*((MOVIMIENTOS!$B$5:$B$1021="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1021="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1021="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021),""),"")</f>
+        <f>IFERROR(IF(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A37)*((MOVIMIENTOS!$B$5:$B$1025="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1025="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1025="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025)&lt;&gt;"","G-"&amp;LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A37)*((MOVIMIENTOS!$B$5:$B$1025="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1025="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1025="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025),""),"")</f>
         <v>G-3054</v>
       </c>
       <c r="O37" s="73">
@@ -40596,8 +41007,8 @@
         <v>1940</v>
       </c>
       <c r="AD37" s="73" t="str">
-        <f>IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A37)*(MOVIMIENTOS!$B$5:$B$1021="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1021="Chancho")*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021),IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A37)*(MOVIMIENTOS!$B$5:$B$1021="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1021="Chancho")*(MOVIMIENTOS!$H$5:$H$1021&lt;&gt;"")),MOVIMIENTOS!$H$5:$H$1021),""))</f>
-        <v>TCK002-741</v>
+        <f>IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A37)*(MOVIMIENTOS!$B$5:$B$1025="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1025="Chancho")*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025),IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A37)*(MOVIMIENTOS!$B$5:$B$1025="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1025="Chancho")*(MOVIMIENTOS!$H$5:$H$1025&lt;&gt;"")),MOVIMIENTOS!$H$5:$H$1025),""))</f>
+        <v>FALTA</v>
       </c>
       <c r="AE37" s="78">
         <f>IFERROR(INDEX('SALDO DIARIO'!$F:$F,MATCH($A37,'SALDO DIARIO'!$A:$A,0)),0)</f>
@@ -40649,10 +41060,10 @@
         <v>46240</v>
       </c>
       <c r="B38" s="72" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C38" s="72" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D38" s="73">
         <f>SUMIFS(MOVIMIENTOS!$E:$E,MOVIMIENTOS!$A:$A,$A38,MOVIMIENTOS!$B:$B,"COMPRA")</f>
@@ -40695,7 +41106,7 @@
         <v>Supesa</v>
       </c>
       <c r="N38" s="73" t="str">
-        <f>IFERROR(IF(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A38)*((MOVIMIENTOS!$B$5:$B$1021="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1021="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1021="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021)&lt;&gt;"","G-"&amp;LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A38)*((MOVIMIENTOS!$B$5:$B$1021="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1021="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1021="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021),""),"")</f>
+        <f>IFERROR(IF(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A38)*((MOVIMIENTOS!$B$5:$B$1025="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1025="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1025="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025)&lt;&gt;"","G-"&amp;LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A38)*((MOVIMIENTOS!$B$5:$B$1025="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1025="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1025="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025),""),"")</f>
         <v>G-3058</v>
       </c>
       <c r="O38" s="73">
@@ -40759,7 +41170,7 @@
         <v>1649</v>
       </c>
       <c r="AD38" s="73" t="str">
-        <f>IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A38)*(MOVIMIENTOS!$B$5:$B$1021="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1021="Chancho")*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021),IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A38)*(MOVIMIENTOS!$B$5:$B$1021="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1021="Chancho")*(MOVIMIENTOS!$H$5:$H$1021&lt;&gt;"")),MOVIMIENTOS!$H$5:$H$1021),""))</f>
+        <f>IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A38)*(MOVIMIENTOS!$B$5:$B$1025="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1025="Chancho")*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025),IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A38)*(MOVIMIENTOS!$B$5:$B$1025="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1025="Chancho")*(MOVIMIENTOS!$H$5:$H$1025&lt;&gt;"")),MOVIMIENTOS!$H$5:$H$1025),""))</f>
         <v>TCK002-740</v>
       </c>
       <c r="AE38" s="78">
@@ -40812,10 +41223,10 @@
         <v>46241</v>
       </c>
       <c r="B39" s="72" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C39" s="72" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D39" s="73">
         <f>SUMIFS(MOVIMIENTOS!$E:$E,MOVIMIENTOS!$A:$A,$A39,MOVIMIENTOS!$B:$B,"COMPRA")</f>
@@ -40858,7 +41269,7 @@
         <v>Supesa</v>
       </c>
       <c r="N39" s="73" t="str">
-        <f>IFERROR(IF(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A39)*((MOVIMIENTOS!$B$5:$B$1021="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1021="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1021="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021)&lt;&gt;"","G-"&amp;LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A39)*((MOVIMIENTOS!$B$5:$B$1021="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1021="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1021="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021),""),"")</f>
+        <f>IFERROR(IF(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A39)*((MOVIMIENTOS!$B$5:$B$1025="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1025="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1025="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025)&lt;&gt;"","G-"&amp;LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A39)*((MOVIMIENTOS!$B$5:$B$1025="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1025="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1025="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025),""),"")</f>
         <v>G-3060</v>
       </c>
       <c r="O39" s="73">
@@ -40922,7 +41333,7 @@
         <v>582</v>
       </c>
       <c r="AD39" s="73" t="str">
-        <f>IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A39)*(MOVIMIENTOS!$B$5:$B$1021="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1021="Chancho")*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021),IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A39)*(MOVIMIENTOS!$B$5:$B$1021="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1021="Chancho")*(MOVIMIENTOS!$H$5:$H$1021&lt;&gt;"")),MOVIMIENTOS!$H$5:$H$1021),""))</f>
+        <f>IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A39)*(MOVIMIENTOS!$B$5:$B$1025="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1025="Chancho")*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025),IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A39)*(MOVIMIENTOS!$B$5:$B$1025="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1025="Chancho")*(MOVIMIENTOS!$H$5:$H$1025&lt;&gt;"")),MOVIMIENTOS!$H$5:$H$1025),""))</f>
         <v>TCK002-741</v>
       </c>
       <c r="AE39" s="78">
@@ -40943,10 +41354,10 @@
         <v>46242</v>
       </c>
       <c r="B40" s="72" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C40" s="72" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D40" s="73">
         <f>SUMIFS(MOVIMIENTOS!$E:$E,MOVIMIENTOS!$A:$A,$A40,MOVIMIENTOS!$B:$B,"COMPRA")</f>
@@ -40989,7 +41400,7 @@
         <v>Supesa</v>
       </c>
       <c r="N40" s="73" t="str">
-        <f>IFERROR(IF(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A40)*((MOVIMIENTOS!$B$5:$B$1021="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1021="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1021="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021)&lt;&gt;"","G-"&amp;LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A40)*((MOVIMIENTOS!$B$5:$B$1021="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1021="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1021="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021),""),"")</f>
+        <f>IFERROR(IF(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A40)*((MOVIMIENTOS!$B$5:$B$1025="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1025="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1025="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025)&lt;&gt;"","G-"&amp;LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A40)*((MOVIMIENTOS!$B$5:$B$1025="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$1025="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$1025="ENVIO A TOTTUS"))*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025),""),"")</f>
         <v>G-3064</v>
       </c>
       <c r="O40" s="73">
@@ -41053,8 +41464,8 @@
         <v>436.5</v>
       </c>
       <c r="AD40" s="73" t="str">
-        <f>IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A40)*(MOVIMIENTOS!$B$5:$B$1021="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1021="Chancho")*(MOVIMIENTOS!$G$5:$G$1021&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1021),IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1021=$A40)*(MOVIMIENTOS!$B$5:$B$1021="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1021="Chancho")*(MOVIMIENTOS!$H$5:$H$1021&lt;&gt;"")),MOVIMIENTOS!$H$5:$H$1021),""))</f>
-        <v>TCK002-742</v>
+        <f>IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A40)*(MOVIMIENTOS!$B$5:$B$1025="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1025="Chancho")*(MOVIMIENTOS!$G$5:$G$1025&lt;&gt;"")),MOVIMIENTOS!$G$5:$G$1025),IFERROR(LOOKUP(2,1/((MOVIMIENTOS!$A$5:$A$1025=$A40)*(MOVIMIENTOS!$B$5:$B$1025="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$1025="Chancho")*(MOVIMIENTOS!$H$5:$H$1025&lt;&gt;"")),MOVIMIENTOS!$H$5:$H$1025),""))</f>
+        <v>PENDIENTE</v>
       </c>
       <c r="AE40" s="78">
         <f>IFERROR(INDEX('SALDO DIARIO'!$F:$F,MATCH($A40,'SALDO DIARIO'!$A:$A,0)),0)</f>

--- a/PROCESO DE PLANTA.xlsx
+++ b/PROCESO DE PLANTA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mirianmartinez/Desktop/Agro Pacayales/GESTION COSTOS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94200E4D-6ED3-C547-8511-139048B5D936}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDD6FCD0-E1F8-E545-A6CF-A58983967BED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4320" yWindow="600" windowWidth="24480" windowHeight="17400" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MOVIMIENTOS" sheetId="1" r:id="rId1"/>
@@ -22,9 +22,9 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'BALANCE SEMANAL'!$A$5:$AG$33</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">KARDEX!$A$5:$G$137</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">MOVIMIENTOS!$A$4:$H$425</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">MOVIMIENTOS!$A$4:$H$424</definedName>
   </definedNames>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -77,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1679" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1732" uniqueCount="251">
   <si>
     <t>AGRO PACAYALES · PLANTA CAMOTE 2026  |  MOVIMIENTOS — registra aquí un evento por fila</t>
   </si>
@@ -858,7 +858,19 @@
     <t>SE COMPRÓ 103 SACOS</t>
   </si>
   <si>
-    <t>saldo de los 103 quedan aún 33 sacos</t>
+    <t>TCK002-749</t>
+  </si>
+  <si>
+    <t>Lourdes Quispe</t>
+  </si>
+  <si>
+    <t>COMPRARON 50 SACOS</t>
+  </si>
+  <si>
+    <t>saldo de los 103 quedan aún 38 sacos</t>
+  </si>
+  <si>
+    <t>Se terminó de procesar los 103 sacos</t>
   </si>
 </sst>
 </file>
@@ -2020,7 +2032,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O438"/>
+  <dimension ref="A1:O437"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -12373,19 +12385,19 @@
         <v>16</v>
       </c>
       <c r="E375" s="41">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="F375" s="41">
         <f>IF($B375="","",IF($D375="kg",N($E375),IF($D375="sacos",N($E375)*97,IF($D375="jabas",N($E375)*IFERROR(VLOOKUP($C375,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
-        <v>4365</v>
+        <v>3880</v>
       </c>
       <c r="G375" s="40"/>
       <c r="H375" s="40" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="I375">
         <f t="shared" si="9"/>
-        <v>4365</v>
+        <v>3880</v>
       </c>
     </row>
     <row r="376" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -12634,292 +12646,466 @@
       </c>
     </row>
     <row r="385" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A385" s="39"/>
-      <c r="B385" s="40"/>
-      <c r="C385" s="40"/>
-      <c r="D385" s="40"/>
-      <c r="E385" s="41"/>
-      <c r="F385" s="41" t="str">
+      <c r="A385" s="39">
+        <v>46248</v>
+      </c>
+      <c r="B385" s="40" t="s">
+        <v>28</v>
+      </c>
+      <c r="C385" s="40" t="s">
+        <v>15</v>
+      </c>
+      <c r="D385" s="40" t="s">
+        <v>16</v>
+      </c>
+      <c r="E385" s="41">
+        <v>5</v>
+      </c>
+      <c r="F385" s="41">
         <f>IF($B385="","",IF($D385="kg",N($E385),IF($D385="sacos",N($E385)*97,IF($D385="jabas",N($E385)*IFERROR(VLOOKUP($C385,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
-        <v/>
-      </c>
-      <c r="G385" s="40"/>
-      <c r="H385" s="40"/>
+        <v>485</v>
+      </c>
+      <c r="G385" s="40" t="s">
+        <v>246</v>
+      </c>
+      <c r="H385" s="40" t="s">
+        <v>247</v>
+      </c>
       <c r="I385">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>485</v>
       </c>
     </row>
     <row r="386" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A386" s="39"/>
-      <c r="B386" s="40"/>
+      <c r="A386" s="39">
+        <v>46248</v>
+      </c>
+      <c r="B386" s="40" t="s">
+        <v>17</v>
+      </c>
       <c r="C386" s="40"/>
-      <c r="D386" s="40"/>
-      <c r="E386" s="41"/>
-      <c r="F386" s="41" t="str">
+      <c r="D386" s="40" t="s">
+        <v>16</v>
+      </c>
+      <c r="E386" s="41">
+        <v>38</v>
+      </c>
+      <c r="F386" s="41">
         <f>IF($B386="","",IF($D386="kg",N($E386),IF($D386="sacos",N($E386)*97,IF($D386="jabas",N($E386)*IFERROR(VLOOKUP($C386,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
-        <v/>
+        <v>3686</v>
       </c>
       <c r="G386" s="40"/>
-      <c r="H386" s="40"/>
+      <c r="H386" s="40" t="s">
+        <v>250</v>
+      </c>
       <c r="I386">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>3686</v>
       </c>
     </row>
     <row r="387" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A387" s="39"/>
-      <c r="B387" s="40"/>
-      <c r="C387" s="40"/>
-      <c r="D387" s="40"/>
-      <c r="E387" s="41"/>
-      <c r="F387" s="41" t="str">
+      <c r="A387" s="39">
+        <v>46248</v>
+      </c>
+      <c r="B387" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C387" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="D387" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E387" s="13">
+        <v>60</v>
+      </c>
+      <c r="F387" s="41">
         <f>IF($B387="","",IF($D387="kg",N($E387),IF($D387="sacos",N($E387)*97,IF($D387="jabas",N($E387)*IFERROR(VLOOKUP($C387,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
-        <v/>
+        <v>900</v>
       </c>
       <c r="G387" s="40"/>
       <c r="H387" s="40"/>
       <c r="I387">
-        <f t="shared" ref="I387:I418" si="10">N($F387)</f>
-        <v>0</v>
+        <f t="shared" ref="I387:I417" si="10">N($F387)</f>
+        <v>900</v>
       </c>
     </row>
     <row r="388" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A388" s="39"/>
-      <c r="B388" s="40"/>
-      <c r="C388" s="40"/>
-      <c r="D388" s="40"/>
-      <c r="E388" s="41"/>
-      <c r="F388" s="41" t="str">
+      <c r="A388" s="39">
+        <v>46248</v>
+      </c>
+      <c r="B388" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C388" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D388" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E388" s="13">
+        <v>11</v>
+      </c>
+      <c r="F388" s="41">
         <f>IF($B388="","",IF($D388="kg",N($E388),IF($D388="sacos",N($E388)*97,IF($D388="jabas",N($E388)*IFERROR(VLOOKUP($C388,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
-        <v/>
+        <v>198</v>
       </c>
       <c r="G388" s="40"/>
       <c r="H388" s="40"/>
       <c r="I388">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>198</v>
       </c>
     </row>
     <row r="389" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A389" s="39"/>
-      <c r="B389" s="40"/>
-      <c r="C389" s="40"/>
-      <c r="D389" s="40"/>
-      <c r="E389" s="41"/>
-      <c r="F389" s="41" t="str">
+      <c r="A389" s="39">
+        <v>46248</v>
+      </c>
+      <c r="B389" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C389" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D389" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E389" s="13">
+        <v>12</v>
+      </c>
+      <c r="F389" s="41">
         <f>IF($B389="","",IF($D389="kg",N($E389),IF($D389="sacos",N($E389)*97,IF($D389="jabas",N($E389)*IFERROR(VLOOKUP($C389,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
-        <v/>
+        <v>204</v>
       </c>
       <c r="G389" s="40"/>
       <c r="H389" s="40"/>
       <c r="I389">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>204</v>
       </c>
     </row>
     <row r="390" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A390" s="39"/>
-      <c r="B390" s="40"/>
-      <c r="C390" s="40"/>
-      <c r="D390" s="40"/>
-      <c r="E390" s="41"/>
-      <c r="F390" s="41" t="str">
+      <c r="A390" s="39">
+        <v>46248</v>
+      </c>
+      <c r="B390" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C390" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D390" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E390" s="13">
+        <v>108</v>
+      </c>
+      <c r="F390" s="41">
         <f>IF($B390="","",IF($D390="kg",N($E390),IF($D390="sacos",N($E390)*97,IF($D390="jabas",N($E390)*IFERROR(VLOOKUP($C390,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
-        <v/>
+        <v>1836</v>
       </c>
       <c r="G390" s="40"/>
       <c r="H390" s="40"/>
       <c r="I390">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1836</v>
       </c>
     </row>
     <row r="391" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A391" s="39"/>
-      <c r="B391" s="40"/>
-      <c r="C391" s="40"/>
-      <c r="D391" s="40"/>
-      <c r="E391" s="41"/>
-      <c r="F391" s="41" t="str">
+      <c r="A391" s="39">
+        <v>46248</v>
+      </c>
+      <c r="B391" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C391" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D391" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="E391" s="13">
+        <v>3</v>
+      </c>
+      <c r="F391" s="41">
         <f>IF($B391="","",IF($D391="kg",N($E391),IF($D391="sacos",N($E391)*97,IF($D391="jabas",N($E391)*IFERROR(VLOOKUP($C391,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
-        <v/>
+        <v>291</v>
       </c>
       <c r="G391" s="40"/>
       <c r="H391" s="40"/>
       <c r="I391">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>291</v>
       </c>
     </row>
     <row r="392" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A392" s="39"/>
-      <c r="B392" s="40"/>
-      <c r="C392" s="40"/>
-      <c r="D392" s="40"/>
-      <c r="E392" s="41"/>
-      <c r="F392" s="41" t="str">
+      <c r="A392" s="39">
+        <v>46248</v>
+      </c>
+      <c r="B392" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C392" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D392" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="E392" s="16">
+        <v>67</v>
+      </c>
+      <c r="F392" s="41">
         <f>IF($B392="","",IF($D392="kg",N($E392),IF($D392="sacos",N($E392)*97,IF($D392="jabas",N($E392)*IFERROR(VLOOKUP($C392,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
-        <v/>
+        <v>1005</v>
       </c>
       <c r="G392" s="40"/>
       <c r="H392" s="40"/>
       <c r="I392">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="393" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A393" s="39"/>
-      <c r="B393" s="40"/>
-      <c r="C393" s="40"/>
-      <c r="D393" s="40"/>
-      <c r="E393" s="41"/>
-      <c r="F393" s="41" t="str">
+      <c r="A393" s="39">
+        <v>46248</v>
+      </c>
+      <c r="B393" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C393" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D393" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="E393" s="16">
+        <v>11</v>
+      </c>
+      <c r="F393" s="41">
         <f>IF($B393="","",IF($D393="kg",N($E393),IF($D393="sacos",N($E393)*97,IF($D393="jabas",N($E393)*IFERROR(VLOOKUP($C393,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
-        <v/>
+        <v>198</v>
       </c>
       <c r="G393" s="40"/>
       <c r="H393" s="40"/>
       <c r="I393">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>198</v>
       </c>
     </row>
     <row r="394" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A394" s="39"/>
-      <c r="B394" s="40"/>
-      <c r="C394" s="40"/>
-      <c r="D394" s="40"/>
-      <c r="E394" s="41"/>
-      <c r="F394" s="41" t="str">
+      <c r="A394" s="39">
+        <v>46248</v>
+      </c>
+      <c r="B394" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C394" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="D394" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="E394" s="16">
+        <v>12</v>
+      </c>
+      <c r="F394" s="41">
         <f>IF($B394="","",IF($D394="kg",N($E394),IF($D394="sacos",N($E394)*97,IF($D394="jabas",N($E394)*IFERROR(VLOOKUP($C394,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
-        <v/>
+        <v>204</v>
       </c>
       <c r="G394" s="40"/>
       <c r="H394" s="40"/>
       <c r="I394">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>204</v>
       </c>
     </row>
     <row r="395" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A395" s="39"/>
-      <c r="B395" s="40"/>
-      <c r="C395" s="40"/>
-      <c r="D395" s="40"/>
-      <c r="E395" s="41"/>
-      <c r="F395" s="41" t="str">
+      <c r="A395" s="39">
+        <v>46248</v>
+      </c>
+      <c r="B395" s="44" t="s">
+        <v>23</v>
+      </c>
+      <c r="C395" s="44" t="s">
+        <v>13</v>
+      </c>
+      <c r="D395" s="44" t="s">
+        <v>12</v>
+      </c>
+      <c r="E395" s="45">
+        <v>118</v>
+      </c>
+      <c r="F395" s="41">
         <f>IF($B395="","",IF($D395="kg",N($E395),IF($D395="sacos",N($E395)*97,IF($D395="jabas",N($E395)*IFERROR(VLOOKUP($C395,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
-        <v/>
+        <v>2006</v>
       </c>
       <c r="G395" s="40"/>
       <c r="H395" s="40"/>
       <c r="I395">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>2006</v>
       </c>
     </row>
     <row r="396" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A396" s="39"/>
-      <c r="B396" s="40"/>
+      <c r="A396" s="39">
+        <v>46248</v>
+      </c>
+      <c r="B396" s="40" t="s">
+        <v>17</v>
+      </c>
       <c r="C396" s="40"/>
-      <c r="D396" s="40"/>
-      <c r="E396" s="41"/>
-      <c r="F396" s="41" t="str">
+      <c r="D396" s="40" t="s">
+        <v>16</v>
+      </c>
+      <c r="E396" s="41">
+        <v>24</v>
+      </c>
+      <c r="F396" s="41">
         <f>IF($B396="","",IF($D396="kg",N($E396),IF($D396="sacos",N($E396)*97,IF($D396="jabas",N($E396)*IFERROR(VLOOKUP($C396,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
-        <v/>
+        <v>2328</v>
       </c>
       <c r="G396" s="40"/>
-      <c r="H396" s="40"/>
+      <c r="H396" s="40" t="s">
+        <v>248</v>
+      </c>
       <c r="I396">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>2328</v>
       </c>
     </row>
     <row r="397" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A397" s="39"/>
-      <c r="B397" s="40"/>
-      <c r="C397" s="40"/>
-      <c r="D397" s="40"/>
-      <c r="E397" s="41"/>
-      <c r="F397" s="41" t="str">
+      <c r="A397" s="39">
+        <v>46248</v>
+      </c>
+      <c r="B397" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C397" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="D397" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E397" s="13">
+        <v>51</v>
+      </c>
+      <c r="F397" s="41">
         <f>IF($B397="","",IF($D397="kg",N($E397),IF($D397="sacos",N($E397)*97,IF($D397="jabas",N($E397)*IFERROR(VLOOKUP($C397,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
-        <v/>
+        <v>765</v>
       </c>
       <c r="G397" s="40"/>
       <c r="H397" s="40"/>
       <c r="I397">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>765</v>
       </c>
     </row>
     <row r="398" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A398" s="39"/>
-      <c r="B398" s="40"/>
-      <c r="C398" s="40"/>
-      <c r="D398" s="40"/>
-      <c r="E398" s="41"/>
-      <c r="F398" s="41" t="str">
+      <c r="A398" s="39">
+        <v>46248</v>
+      </c>
+      <c r="B398" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C398" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D398" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E398" s="13">
+        <v>6</v>
+      </c>
+      <c r="F398" s="41">
         <f>IF($B398="","",IF($D398="kg",N($E398),IF($D398="sacos",N($E398)*97,IF($D398="jabas",N($E398)*IFERROR(VLOOKUP($C398,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
-        <v/>
+        <v>108</v>
       </c>
       <c r="G398" s="40"/>
       <c r="H398" s="40"/>
       <c r="I398">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>108</v>
       </c>
     </row>
     <row r="399" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A399" s="39"/>
-      <c r="B399" s="40"/>
-      <c r="C399" s="40"/>
-      <c r="D399" s="40"/>
-      <c r="E399" s="41"/>
-      <c r="F399" s="41" t="str">
+      <c r="A399" s="39">
+        <v>46248</v>
+      </c>
+      <c r="B399" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C399" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D399" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E399" s="13">
+        <v>10</v>
+      </c>
+      <c r="F399" s="41">
         <f>IF($B399="","",IF($D399="kg",N($E399),IF($D399="sacos",N($E399)*97,IF($D399="jabas",N($E399)*IFERROR(VLOOKUP($C399,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
-        <v/>
+        <v>170</v>
       </c>
       <c r="G399" s="40"/>
       <c r="H399" s="40"/>
       <c r="I399">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>170</v>
       </c>
     </row>
     <row r="400" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A400" s="39"/>
-      <c r="B400" s="40"/>
-      <c r="C400" s="40"/>
-      <c r="D400" s="40"/>
-      <c r="E400" s="41"/>
-      <c r="F400" s="41" t="str">
+      <c r="A400" s="39">
+        <v>46248</v>
+      </c>
+      <c r="B400" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C400" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D400" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E400" s="13">
+        <v>74</v>
+      </c>
+      <c r="F400" s="41">
         <f>IF($B400="","",IF($D400="kg",N($E400),IF($D400="sacos",N($E400)*97,IF($D400="jabas",N($E400)*IFERROR(VLOOKUP($C400,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
-        <v/>
+        <v>1258</v>
       </c>
       <c r="G400" s="40"/>
       <c r="H400" s="40"/>
       <c r="I400">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="401" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A401" s="39"/>
-      <c r="B401" s="40"/>
-      <c r="C401" s="40"/>
-      <c r="D401" s="40"/>
-      <c r="E401" s="41"/>
-      <c r="F401" s="41" t="str">
+      <c r="A401" s="39">
+        <v>46248</v>
+      </c>
+      <c r="B401" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C401" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D401" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="E401" s="13">
+        <v>1</v>
+      </c>
+      <c r="F401" s="41">
         <f>IF($B401="","",IF($D401="kg",N($E401),IF($D401="sacos",N($E401)*97,IF($D401="jabas",N($E401)*IFERROR(VLOOKUP($C401,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
-        <v/>
+        <v>97</v>
       </c>
       <c r="G401" s="40"/>
       <c r="H401" s="40"/>
       <c r="I401">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>97</v>
       </c>
     </row>
     <row r="402" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -13207,7 +13393,7 @@
       <c r="G418" s="40"/>
       <c r="H418" s="40"/>
       <c r="I418">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="I418:I437" si="11">N($F418)</f>
         <v>0</v>
       </c>
     </row>
@@ -13224,7 +13410,7 @@
       <c r="G419" s="40"/>
       <c r="H419" s="40"/>
       <c r="I419">
-        <f t="shared" ref="I419:I438" si="11">N($F419)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
     </row>
@@ -13313,7 +13499,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="425" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A425" s="39"/>
       <c r="B425" s="40"/>
       <c r="C425" s="40"/>
@@ -13330,14 +13516,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="426" spans="1:9" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A426" s="39"/>
       <c r="B426" s="40"/>
       <c r="C426" s="40"/>
       <c r="D426" s="40"/>
       <c r="E426" s="41"/>
       <c r="F426" s="41" t="str">
-        <f>IF($B426="","",IF($D426="kg",N($E426),IF($D426="sacos",N($E426)*97,IF($D426="jabas",N($E426)*IFERROR(VLOOKUP($C426,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
+        <f>IF($B426="","",IF($D426="kg",N($E426),IF($D426="sacos",N($E426)*95,IF($D426="jabas",N($E426)*IFERROR(VLOOKUP($C426,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
         <v/>
       </c>
       <c r="G426" s="40"/>
@@ -13534,30 +13720,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="438" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A438" s="39"/>
-      <c r="B438" s="40"/>
-      <c r="C438" s="40"/>
-      <c r="D438" s="40"/>
-      <c r="E438" s="41"/>
-      <c r="F438" s="41" t="str">
-        <f>IF($B438="","",IF($D438="kg",N($E438),IF($D438="sacos",N($E438)*95,IF($D438="jabas",N($E438)*IFERROR(VLOOKUP($C438,LISTAS!$A$2:$B$12,2,0),0),""))))</f>
-        <v/>
-      </c>
-      <c r="G438" s="40"/>
-      <c r="H438" s="40"/>
-      <c r="I438">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A4:H425" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A4:H424" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="2">
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:H438">
+  <conditionalFormatting sqref="A5:H437">
     <cfRule type="expression" dxfId="14" priority="3">
       <formula>$B5="COMPRA"</formula>
     </cfRule>
@@ -13598,7 +13767,7 @@
       <formula>$B5="SALDO INICIAL"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E5:H438">
+  <conditionalFormatting sqref="E5:H437">
     <cfRule type="expression" dxfId="1" priority="2">
       <formula>ISNUMBER(SEARCH("FALTA",$H5))</formula>
     </cfRule>
@@ -13715,23 +13884,23 @@
         <v>46214</v>
       </c>
       <c r="B5" s="56">
-        <f>IF($A5="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A5)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A5)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A5)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A5)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A5)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A5)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A5)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A5)*MOVIMIENTOS!$E$5:$E$425))</f>
+        <f>IF($A5="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A5)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="PROCESO")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A5)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A5)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A5)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A5)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="REGALO")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A5)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="VENTA")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A5)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="AJUSTE")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A5)*MOVIMIENTOS!$E$5:$E$424))</f>
         <v>2</v>
       </c>
       <c r="C5" s="56">
-        <f>IF($A5="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A5)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A5)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A5)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A5)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A5)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A5)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A5)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A5)*MOVIMIENTOS!$E$5:$E$425))</f>
+        <f>IF($A5="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A5)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="PROCESO")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A5)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A5)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A5)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A5)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="REGALO")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A5)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="VENTA")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A5)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="AJUSTE")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A5)*MOVIMIENTOS!$E$5:$E$424))</f>
         <v>0</v>
       </c>
       <c r="D5" s="56">
-        <f>IF($A5="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A5)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A5)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A5)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A5)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A5)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A5)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A5)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A5)*MOVIMIENTOS!$E$5:$E$425))</f>
+        <f>IF($A5="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A5)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="PROCESO")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A5)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A5)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A5)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A5)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="REGALO")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A5)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="VENTA")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A5)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="AJUSTE")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A5)*MOVIMIENTOS!$E$5:$E$424))</f>
         <v>0</v>
       </c>
       <c r="E5" s="56">
-        <f>IF($A5="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A5)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A5)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A5)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A5)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A5)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A5)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A5)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A5)*MOVIMIENTOS!$E$5:$E$425))</f>
+        <f>IF($A5="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A5)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="PROCESO")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A5)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A5)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A5)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A5)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="REGALO")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A5)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="VENTA")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A5)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="AJUSTE")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A5)*MOVIMIENTOS!$E$5:$E$424))</f>
         <v>8</v>
       </c>
       <c r="F5" s="56">
-        <f>IF($A5="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A5)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A5)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A5)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A5)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A5)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A5)*MOVIMIENTOS!$E$5:$E$425))</f>
+        <f>IF($A5="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$424="Chancho")*(MOVIMIENTOS!$D$5:$D$424="sacos")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A5)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="PROCESO")*(MOVIMIENTOS!$C$5:$C$424="Chancho")*(MOVIMIENTOS!$D$5:$D$424="sacos")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A5)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$424="Chancho")*(MOVIMIENTOS!$D$5:$D$424="sacos")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A5)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="REGALO")*(MOVIMIENTOS!$C$5:$C$424="Chancho")*(MOVIMIENTOS!$D$5:$D$424="sacos")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A5)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="VENTA")*(MOVIMIENTOS!$C$5:$C$424="Chancho")*(MOVIMIENTOS!$D$5:$D$424="sacos")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A5)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="AJUSTE")*(MOVIMIENTOS!$C$5:$C$424="Chancho")*(MOVIMIENTOS!$D$5:$D$424="sacos")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A5)*MOVIMIENTOS!$E$5:$E$424))</f>
         <v>20</v>
       </c>
       <c r="G5" s="56">
@@ -13739,7 +13908,7 @@
         <v>10</v>
       </c>
       <c r="H5" s="56">
-        <f>IF($A5="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$425="COMPRA")+(MOVIMIENTOS!$B$5:$B$425="REPROCESO")+(MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A5)*MOVIMIENTOS!$I$5:$I$425)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$425="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho"))+((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A5)*MOVIMIENTOS!$I$5:$I$425))</f>
+        <f>IF($A5="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$424="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$424&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$424="COMPRA")+(MOVIMIENTOS!$B$5:$B$424="REPROCESO")+(MOVIMIENTOS!$B$5:$B$424="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$424="AJUSTE")*(MOVIMIENTOS!$C$5:$C$424&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A5)*MOVIMIENTOS!$I$5:$I$424)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$424="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$424="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$424="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$424="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$424="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$424="PROCESO")*(MOVIMIENTOS!$C$5:$C$424="Chancho"))+((MOVIMIENTOS!$B$5:$B$424="REGALO")*(MOVIMIENTOS!$C$5:$C$424&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$424="VENTA")*(MOVIMIENTOS!$C$5:$C$424&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A5)*MOVIMIENTOS!$I$5:$I$424))</f>
         <v>166</v>
       </c>
       <c r="I5" s="54"/>
@@ -13761,23 +13930,23 @@
         <v>46215</v>
       </c>
       <c r="B6" s="56">
-        <f>IF($A6="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A6)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A6)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A6)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A6)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A6)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A6)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A6)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A6)*MOVIMIENTOS!$E$5:$E$425))</f>
+        <f>IF($A6="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A6)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="PROCESO")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A6)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A6)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A6)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A6)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="REGALO")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A6)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="VENTA")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A6)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="AJUSTE")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A6)*MOVIMIENTOS!$E$5:$E$424))</f>
         <v>-6</v>
       </c>
       <c r="C6" s="56">
-        <f>IF($A6="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A6)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A6)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A6)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A6)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A6)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A6)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A6)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A6)*MOVIMIENTOS!$E$5:$E$425))</f>
+        <f>IF($A6="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A6)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="PROCESO")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A6)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A6)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A6)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A6)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="REGALO")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A6)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="VENTA")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A6)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="AJUSTE")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A6)*MOVIMIENTOS!$E$5:$E$424))</f>
         <v>0</v>
       </c>
       <c r="D6" s="56">
-        <f>IF($A6="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A6)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A6)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A6)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A6)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A6)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A6)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A6)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A6)*MOVIMIENTOS!$E$5:$E$425))</f>
+        <f>IF($A6="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A6)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="PROCESO")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A6)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A6)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A6)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A6)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="REGALO")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A6)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="VENTA")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A6)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="AJUSTE")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A6)*MOVIMIENTOS!$E$5:$E$424))</f>
         <v>0</v>
       </c>
       <c r="E6" s="56">
-        <f>IF($A6="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A6)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A6)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A6)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A6)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A6)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A6)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A6)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A6)*MOVIMIENTOS!$E$5:$E$425))</f>
+        <f>IF($A6="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A6)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="PROCESO")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A6)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A6)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A6)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A6)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="REGALO")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A6)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="VENTA")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A6)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="AJUSTE")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A6)*MOVIMIENTOS!$E$5:$E$424))</f>
         <v>30</v>
       </c>
       <c r="F6" s="56">
-        <f>IF($A6="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A6)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A6)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A6)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A6)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A6)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A6)*MOVIMIENTOS!$E$5:$E$425))</f>
+        <f>IF($A6="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$424="Chancho")*(MOVIMIENTOS!$D$5:$D$424="sacos")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A6)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="PROCESO")*(MOVIMIENTOS!$C$5:$C$424="Chancho")*(MOVIMIENTOS!$D$5:$D$424="sacos")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A6)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$424="Chancho")*(MOVIMIENTOS!$D$5:$D$424="sacos")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A6)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="REGALO")*(MOVIMIENTOS!$C$5:$C$424="Chancho")*(MOVIMIENTOS!$D$5:$D$424="sacos")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A6)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="VENTA")*(MOVIMIENTOS!$C$5:$C$424="Chancho")*(MOVIMIENTOS!$D$5:$D$424="sacos")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A6)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="AJUSTE")*(MOVIMIENTOS!$C$5:$C$424="Chancho")*(MOVIMIENTOS!$D$5:$D$424="sacos")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A6)*MOVIMIENTOS!$E$5:$E$424))</f>
         <v>26</v>
       </c>
       <c r="G6" s="56">
@@ -13785,7 +13954,7 @@
         <v>24</v>
       </c>
       <c r="H6" s="56">
-        <f>IF($A6="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$425="COMPRA")+(MOVIMIENTOS!$B$5:$B$425="REPROCESO")+(MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A6)*MOVIMIENTOS!$I$5:$I$425)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$425="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho"))+((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A6)*MOVIMIENTOS!$I$5:$I$425))</f>
+        <f>IF($A6="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$424="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$424&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$424="COMPRA")+(MOVIMIENTOS!$B$5:$B$424="REPROCESO")+(MOVIMIENTOS!$B$5:$B$424="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$424="AJUSTE")*(MOVIMIENTOS!$C$5:$C$424&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A6)*MOVIMIENTOS!$I$5:$I$424)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$424="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$424="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$424="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$424="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$424="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$424="PROCESO")*(MOVIMIENTOS!$C$5:$C$424="Chancho"))+((MOVIMIENTOS!$B$5:$B$424="REGALO")*(MOVIMIENTOS!$C$5:$C$424&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$424="VENTA")*(MOVIMIENTOS!$C$5:$C$424&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A6)*MOVIMIENTOS!$I$5:$I$424))</f>
         <v>373</v>
       </c>
       <c r="I6" s="54"/>
@@ -13807,23 +13976,23 @@
         <v>46216</v>
       </c>
       <c r="B7" s="56">
-        <f>IF($A7="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A7)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A7)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A7)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A7)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A7)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A7)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A7)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A7)*MOVIMIENTOS!$E$5:$E$425))</f>
+        <f>IF($A7="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A7)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="PROCESO")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A7)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A7)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A7)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A7)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="REGALO")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A7)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="VENTA")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A7)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="AJUSTE")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A7)*MOVIMIENTOS!$E$5:$E$424))</f>
         <v>34</v>
       </c>
       <c r="C7" s="56">
-        <f>IF($A7="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A7)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A7)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A7)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A7)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A7)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A7)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A7)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A7)*MOVIMIENTOS!$E$5:$E$425))</f>
+        <f>IF($A7="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A7)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="PROCESO")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A7)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A7)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A7)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A7)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="REGALO")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A7)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="VENTA")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A7)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="AJUSTE")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A7)*MOVIMIENTOS!$E$5:$E$424))</f>
         <v>0</v>
       </c>
       <c r="D7" s="56">
-        <f>IF($A7="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A7)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A7)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A7)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A7)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A7)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A7)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A7)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A7)*MOVIMIENTOS!$E$5:$E$425))</f>
+        <f>IF($A7="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A7)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="PROCESO")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A7)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A7)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A7)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A7)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="REGALO")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A7)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="VENTA")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A7)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="AJUSTE")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A7)*MOVIMIENTOS!$E$5:$E$424))</f>
         <v>0</v>
       </c>
       <c r="E7" s="56">
-        <f>IF($A7="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A7)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A7)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A7)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A7)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A7)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A7)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A7)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A7)*MOVIMIENTOS!$E$5:$E$425))</f>
+        <f>IF($A7="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A7)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="PROCESO")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A7)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A7)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A7)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A7)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="REGALO")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A7)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="VENTA")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A7)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="AJUSTE")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A7)*MOVIMIENTOS!$E$5:$E$424))</f>
         <v>43</v>
       </c>
       <c r="F7" s="56">
-        <f>IF($A7="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A7)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A7)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A7)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A7)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A7)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A7)*MOVIMIENTOS!$E$5:$E$425))</f>
+        <f>IF($A7="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$424="Chancho")*(MOVIMIENTOS!$D$5:$D$424="sacos")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A7)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="PROCESO")*(MOVIMIENTOS!$C$5:$C$424="Chancho")*(MOVIMIENTOS!$D$5:$D$424="sacos")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A7)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$424="Chancho")*(MOVIMIENTOS!$D$5:$D$424="sacos")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A7)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="REGALO")*(MOVIMIENTOS!$C$5:$C$424="Chancho")*(MOVIMIENTOS!$D$5:$D$424="sacos")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A7)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="VENTA")*(MOVIMIENTOS!$C$5:$C$424="Chancho")*(MOVIMIENTOS!$D$5:$D$424="sacos")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A7)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="AJUSTE")*(MOVIMIENTOS!$C$5:$C$424="Chancho")*(MOVIMIENTOS!$D$5:$D$424="sacos")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A7)*MOVIMIENTOS!$E$5:$E$424))</f>
         <v>28</v>
       </c>
       <c r="G7" s="56">
@@ -13831,7 +14000,7 @@
         <v>77</v>
       </c>
       <c r="H7" s="56">
-        <f>IF($A7="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$425="COMPRA")+(MOVIMIENTOS!$B$5:$B$425="REPROCESO")+(MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A7)*MOVIMIENTOS!$I$5:$I$425)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$425="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho"))+((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A7)*MOVIMIENTOS!$I$5:$I$425))</f>
+        <f>IF($A7="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$424="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$424&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$424="COMPRA")+(MOVIMIENTOS!$B$5:$B$424="REPROCESO")+(MOVIMIENTOS!$B$5:$B$424="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$424="AJUSTE")*(MOVIMIENTOS!$C$5:$C$424&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A7)*MOVIMIENTOS!$I$5:$I$424)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$424="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$424="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$424="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$424="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$424="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$424="PROCESO")*(MOVIMIENTOS!$C$5:$C$424="Chancho"))+((MOVIMIENTOS!$B$5:$B$424="REGALO")*(MOVIMIENTOS!$C$5:$C$424&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$424="VENTA")*(MOVIMIENTOS!$C$5:$C$424&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A7)*MOVIMIENTOS!$I$5:$I$424))</f>
         <v>1003</v>
       </c>
       <c r="I7" s="54"/>
@@ -13853,23 +14022,23 @@
         <v>46217</v>
       </c>
       <c r="B8" s="56">
-        <f>IF($A8="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A8)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A8)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A8)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A8)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A8)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A8)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A8)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A8)*MOVIMIENTOS!$E$5:$E$425))</f>
+        <f>IF($A8="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A8)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="PROCESO")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A8)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A8)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A8)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A8)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="REGALO")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A8)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="VENTA")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A8)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="AJUSTE")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A8)*MOVIMIENTOS!$E$5:$E$424))</f>
         <v>12</v>
       </c>
       <c r="C8" s="56">
-        <f>IF($A8="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A8)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A8)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A8)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A8)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A8)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A8)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A8)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A8)*MOVIMIENTOS!$E$5:$E$425))</f>
+        <f>IF($A8="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A8)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="PROCESO")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A8)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A8)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A8)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A8)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="REGALO")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A8)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="VENTA")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A8)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="AJUSTE")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A8)*MOVIMIENTOS!$E$5:$E$424))</f>
         <v>0</v>
       </c>
       <c r="D8" s="56">
-        <f>IF($A8="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A8)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A8)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A8)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A8)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A8)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A8)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A8)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A8)*MOVIMIENTOS!$E$5:$E$425))</f>
+        <f>IF($A8="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A8)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="PROCESO")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A8)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A8)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A8)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A8)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="REGALO")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A8)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="VENTA")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A8)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="AJUSTE")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A8)*MOVIMIENTOS!$E$5:$E$424))</f>
         <v>0</v>
       </c>
       <c r="E8" s="56">
-        <f>IF($A8="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A8)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A8)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A8)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A8)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A8)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A8)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A8)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A8)*MOVIMIENTOS!$E$5:$E$425))</f>
+        <f>IF($A8="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A8)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="PROCESO")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A8)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A8)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A8)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A8)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="REGALO")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A8)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="VENTA")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A8)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="AJUSTE")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A8)*MOVIMIENTOS!$E$5:$E$424))</f>
         <v>48</v>
       </c>
       <c r="F8" s="56">
-        <f>IF($A8="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A8)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A8)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A8)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A8)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A8)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A8)*MOVIMIENTOS!$E$5:$E$425))</f>
+        <f>IF($A8="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$424="Chancho")*(MOVIMIENTOS!$D$5:$D$424="sacos")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A8)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="PROCESO")*(MOVIMIENTOS!$C$5:$C$424="Chancho")*(MOVIMIENTOS!$D$5:$D$424="sacos")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A8)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$424="Chancho")*(MOVIMIENTOS!$D$5:$D$424="sacos")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A8)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="REGALO")*(MOVIMIENTOS!$C$5:$C$424="Chancho")*(MOVIMIENTOS!$D$5:$D$424="sacos")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A8)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="VENTA")*(MOVIMIENTOS!$C$5:$C$424="Chancho")*(MOVIMIENTOS!$D$5:$D$424="sacos")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A8)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="AJUSTE")*(MOVIMIENTOS!$C$5:$C$424="Chancho")*(MOVIMIENTOS!$D$5:$D$424="sacos")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A8)*MOVIMIENTOS!$E$5:$E$424))</f>
         <v>35</v>
       </c>
       <c r="G8" s="56">
@@ -13877,7 +14046,7 @@
         <v>60</v>
       </c>
       <c r="H8" s="56">
-        <f>IF($A8="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$425="COMPRA")+(MOVIMIENTOS!$B$5:$B$425="REPROCESO")+(MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A8)*MOVIMIENTOS!$I$5:$I$425)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$425="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho"))+((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A8)*MOVIMIENTOS!$I$5:$I$425))</f>
+        <f>IF($A8="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$424="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$424&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$424="COMPRA")+(MOVIMIENTOS!$B$5:$B$424="REPROCESO")+(MOVIMIENTOS!$B$5:$B$424="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$424="AJUSTE")*(MOVIMIENTOS!$C$5:$C$424&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A8)*MOVIMIENTOS!$I$5:$I$424)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$424="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$424="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$424="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$424="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$424="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$424="PROCESO")*(MOVIMIENTOS!$C$5:$C$424="Chancho"))+((MOVIMIENTOS!$B$5:$B$424="REGALO")*(MOVIMIENTOS!$C$5:$C$424&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$424="VENTA")*(MOVIMIENTOS!$C$5:$C$424&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A8)*MOVIMIENTOS!$I$5:$I$424))</f>
         <v>825</v>
       </c>
       <c r="I8" s="54"/>
@@ -13899,23 +14068,23 @@
         <v>46218</v>
       </c>
       <c r="B9" s="56">
-        <f>IF($A9="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A9)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A9)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A9)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A9)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A9)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A9)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A9)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A9)*MOVIMIENTOS!$E$5:$E$425))</f>
+        <f>IF($A9="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A9)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="PROCESO")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A9)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A9)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A9)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A9)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="REGALO")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A9)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="VENTA")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A9)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="AJUSTE")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A9)*MOVIMIENTOS!$E$5:$E$424))</f>
         <v>24</v>
       </c>
       <c r="C9" s="56">
-        <f>IF($A9="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A9)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A9)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A9)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A9)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A9)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A9)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A9)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A9)*MOVIMIENTOS!$E$5:$E$425))</f>
+        <f>IF($A9="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A9)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="PROCESO")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A9)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A9)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A9)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A9)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="REGALO")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A9)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="VENTA")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A9)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="AJUSTE")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A9)*MOVIMIENTOS!$E$5:$E$424))</f>
         <v>11</v>
       </c>
       <c r="D9" s="56">
-        <f>IF($A9="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A9)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A9)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A9)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A9)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A9)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A9)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A9)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A9)*MOVIMIENTOS!$E$5:$E$425))</f>
+        <f>IF($A9="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A9)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="PROCESO")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A9)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A9)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A9)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A9)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="REGALO")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A9)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="VENTA")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A9)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="AJUSTE")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A9)*MOVIMIENTOS!$E$5:$E$424))</f>
         <v>12</v>
       </c>
       <c r="E9" s="56">
-        <f>IF($A9="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A9)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A9)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A9)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A9)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A9)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A9)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A9)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A9)*MOVIMIENTOS!$E$5:$E$425))</f>
+        <f>IF($A9="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A9)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="PROCESO")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A9)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A9)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A9)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A9)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="REGALO")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A9)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="VENTA")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A9)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="AJUSTE")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A9)*MOVIMIENTOS!$E$5:$E$424))</f>
         <v>36</v>
       </c>
       <c r="F9" s="56">
-        <f>IF($A9="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A9)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A9)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A9)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A9)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A9)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A9)*MOVIMIENTOS!$E$5:$E$425))</f>
+        <f>IF($A9="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$424="Chancho")*(MOVIMIENTOS!$D$5:$D$424="sacos")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A9)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="PROCESO")*(MOVIMIENTOS!$C$5:$C$424="Chancho")*(MOVIMIENTOS!$D$5:$D$424="sacos")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A9)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$424="Chancho")*(MOVIMIENTOS!$D$5:$D$424="sacos")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A9)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="REGALO")*(MOVIMIENTOS!$C$5:$C$424="Chancho")*(MOVIMIENTOS!$D$5:$D$424="sacos")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A9)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="VENTA")*(MOVIMIENTOS!$C$5:$C$424="Chancho")*(MOVIMIENTOS!$D$5:$D$424="sacos")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A9)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="AJUSTE")*(MOVIMIENTOS!$C$5:$C$424="Chancho")*(MOVIMIENTOS!$D$5:$D$424="sacos")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A9)*MOVIMIENTOS!$E$5:$E$424))</f>
         <v>5</v>
       </c>
       <c r="G9" s="56">
@@ -13923,7 +14092,7 @@
         <v>83</v>
       </c>
       <c r="H9" s="56">
-        <f>IF($A9="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$425="COMPRA")+(MOVIMIENTOS!$B$5:$B$425="REPROCESO")+(MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A9)*MOVIMIENTOS!$I$5:$I$425)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$425="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho"))+((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A9)*MOVIMIENTOS!$I$5:$I$425))</f>
+        <f>IF($A9="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$424="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$424&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$424="COMPRA")+(MOVIMIENTOS!$B$5:$B$424="REPROCESO")+(MOVIMIENTOS!$B$5:$B$424="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$424="AJUSTE")*(MOVIMIENTOS!$C$5:$C$424&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A9)*MOVIMIENTOS!$I$5:$I$424)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$424="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$424="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$424="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$424="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$424="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$424="PROCESO")*(MOVIMIENTOS!$C$5:$C$424="Chancho"))+((MOVIMIENTOS!$B$5:$B$424="REGALO")*(MOVIMIENTOS!$C$5:$C$424&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$424="VENTA")*(MOVIMIENTOS!$C$5:$C$424&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A9)*MOVIMIENTOS!$I$5:$I$424))</f>
         <v>1249</v>
       </c>
       <c r="I9" s="54"/>
@@ -13945,23 +14114,23 @@
         <v>46219</v>
       </c>
       <c r="B10" s="56">
-        <f>IF($A10="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A10)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A10)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A10)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A10)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A10)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A10)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A10)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A10)*MOVIMIENTOS!$E$5:$E$425))</f>
+        <f>IF($A10="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A10)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="PROCESO")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A10)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A10)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A10)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A10)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="REGALO")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A10)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="VENTA")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A10)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="AJUSTE")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A10)*MOVIMIENTOS!$E$5:$E$424))</f>
         <v>29</v>
       </c>
       <c r="C10" s="56">
-        <f>IF($A10="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A10)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A10)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A10)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A10)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A10)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A10)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A10)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A10)*MOVIMIENTOS!$E$5:$E$425))</f>
+        <f>IF($A10="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A10)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="PROCESO")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A10)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A10)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A10)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A10)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="REGALO")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A10)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="VENTA")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A10)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="AJUSTE")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A10)*MOVIMIENTOS!$E$5:$E$424))</f>
         <v>11</v>
       </c>
       <c r="D10" s="56">
-        <f>IF($A10="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A10)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A10)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A10)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A10)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A10)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A10)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A10)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A10)*MOVIMIENTOS!$E$5:$E$425))</f>
+        <f>IF($A10="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A10)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="PROCESO")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A10)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A10)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A10)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A10)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="REGALO")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A10)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="VENTA")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A10)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="AJUSTE")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A10)*MOVIMIENTOS!$E$5:$E$424))</f>
         <v>12</v>
       </c>
       <c r="E10" s="56">
-        <f>IF($A10="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A10)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A10)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A10)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A10)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A10)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A10)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A10)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A10)*MOVIMIENTOS!$E$5:$E$425))</f>
+        <f>IF($A10="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A10)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="PROCESO")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A10)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A10)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A10)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A10)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="REGALO")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A10)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="VENTA")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A10)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="AJUSTE")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A10)*MOVIMIENTOS!$E$5:$E$424))</f>
         <v>37</v>
       </c>
       <c r="F10" s="56">
-        <f>IF($A10="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A10)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A10)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A10)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A10)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A10)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A10)*MOVIMIENTOS!$E$5:$E$425))</f>
+        <f>IF($A10="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$424="Chancho")*(MOVIMIENTOS!$D$5:$D$424="sacos")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A10)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="PROCESO")*(MOVIMIENTOS!$C$5:$C$424="Chancho")*(MOVIMIENTOS!$D$5:$D$424="sacos")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A10)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$424="Chancho")*(MOVIMIENTOS!$D$5:$D$424="sacos")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A10)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="REGALO")*(MOVIMIENTOS!$C$5:$C$424="Chancho")*(MOVIMIENTOS!$D$5:$D$424="sacos")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A10)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="VENTA")*(MOVIMIENTOS!$C$5:$C$424="Chancho")*(MOVIMIENTOS!$D$5:$D$424="sacos")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A10)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="AJUSTE")*(MOVIMIENTOS!$C$5:$C$424="Chancho")*(MOVIMIENTOS!$D$5:$D$424="sacos")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A10)*MOVIMIENTOS!$E$5:$E$424))</f>
         <v>9</v>
       </c>
       <c r="G10" s="56">
@@ -13969,7 +14138,7 @@
         <v>89</v>
       </c>
       <c r="H10" s="56">
-        <f>IF($A10="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$425="COMPRA")+(MOVIMIENTOS!$B$5:$B$425="REPROCESO")+(MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A10)*MOVIMIENTOS!$I$5:$I$425)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$425="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho"))+((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A10)*MOVIMIENTOS!$I$5:$I$425))</f>
+        <f>IF($A10="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$424="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$424&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$424="COMPRA")+(MOVIMIENTOS!$B$5:$B$424="REPROCESO")+(MOVIMIENTOS!$B$5:$B$424="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$424="AJUSTE")*(MOVIMIENTOS!$C$5:$C$424&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A10)*MOVIMIENTOS!$I$5:$I$424)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$424="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$424="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$424="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$424="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$424="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$424="PROCESO")*(MOVIMIENTOS!$C$5:$C$424="Chancho"))+((MOVIMIENTOS!$B$5:$B$424="REGALO")*(MOVIMIENTOS!$C$5:$C$424&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$424="VENTA")*(MOVIMIENTOS!$C$5:$C$424&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A10)*MOVIMIENTOS!$I$5:$I$424))</f>
         <v>1439</v>
       </c>
       <c r="I10" s="54"/>
@@ -13991,23 +14160,23 @@
         <v>46220</v>
       </c>
       <c r="B11" s="56">
-        <f>IF($A11="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A11)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A11)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A11)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A11)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A11)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A11)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A11)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A11)*MOVIMIENTOS!$E$5:$E$425))</f>
+        <f>IF($A11="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A11)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="PROCESO")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A11)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A11)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A11)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A11)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="REGALO")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A11)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="VENTA")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A11)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="AJUSTE")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A11)*MOVIMIENTOS!$E$5:$E$424))</f>
         <v>65</v>
       </c>
       <c r="C11" s="56">
-        <f>IF($A11="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A11)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A11)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A11)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A11)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A11)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A11)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A11)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A11)*MOVIMIENTOS!$E$5:$E$425))</f>
+        <f>IF($A11="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A11)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="PROCESO")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A11)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A11)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A11)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A11)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="REGALO")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A11)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="VENTA")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A11)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="AJUSTE")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A11)*MOVIMIENTOS!$E$5:$E$424))</f>
         <v>4</v>
       </c>
       <c r="D11" s="56">
-        <f>IF($A11="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A11)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A11)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A11)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A11)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A11)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A11)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A11)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A11)*MOVIMIENTOS!$E$5:$E$425))</f>
+        <f>IF($A11="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A11)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="PROCESO")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A11)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A11)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A11)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A11)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="REGALO")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A11)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="VENTA")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A11)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="AJUSTE")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A11)*MOVIMIENTOS!$E$5:$E$424))</f>
         <v>9</v>
       </c>
       <c r="E11" s="56">
-        <f>IF($A11="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A11)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A11)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A11)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A11)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A11)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A11)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A11)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A11)*MOVIMIENTOS!$E$5:$E$425))</f>
+        <f>IF($A11="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A11)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="PROCESO")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A11)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A11)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A11)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A11)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="REGALO")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A11)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="VENTA")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A11)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="AJUSTE")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A11)*MOVIMIENTOS!$E$5:$E$424))</f>
         <v>115</v>
       </c>
       <c r="F11" s="56">
-        <f>IF($A11="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A11)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A11)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A11)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A11)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A11)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A11)*MOVIMIENTOS!$E$5:$E$425))</f>
+        <f>IF($A11="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$424="Chancho")*(MOVIMIENTOS!$D$5:$D$424="sacos")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A11)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="PROCESO")*(MOVIMIENTOS!$C$5:$C$424="Chancho")*(MOVIMIENTOS!$D$5:$D$424="sacos")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A11)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$424="Chancho")*(MOVIMIENTOS!$D$5:$D$424="sacos")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A11)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="REGALO")*(MOVIMIENTOS!$C$5:$C$424="Chancho")*(MOVIMIENTOS!$D$5:$D$424="sacos")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A11)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="VENTA")*(MOVIMIENTOS!$C$5:$C$424="Chancho")*(MOVIMIENTOS!$D$5:$D$424="sacos")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A11)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="AJUSTE")*(MOVIMIENTOS!$C$5:$C$424="Chancho")*(MOVIMIENTOS!$D$5:$D$424="sacos")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A11)*MOVIMIENTOS!$E$5:$E$424))</f>
         <v>5</v>
       </c>
       <c r="G11" s="56">
@@ -14015,7 +14184,7 @@
         <v>193</v>
       </c>
       <c r="H11" s="56">
-        <f>IF($A11="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$425="COMPRA")+(MOVIMIENTOS!$B$5:$B$425="REPROCESO")+(MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A11)*MOVIMIENTOS!$I$5:$I$425)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$425="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho"))+((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A11)*MOVIMIENTOS!$I$5:$I$425))</f>
+        <f>IF($A11="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$424="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$424&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$424="COMPRA")+(MOVIMIENTOS!$B$5:$B$424="REPROCESO")+(MOVIMIENTOS!$B$5:$B$424="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$424="AJUSTE")*(MOVIMIENTOS!$C$5:$C$424&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A11)*MOVIMIENTOS!$I$5:$I$424)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$424="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$424="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$424="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$424="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$424="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$424="PROCESO")*(MOVIMIENTOS!$C$5:$C$424="Chancho"))+((MOVIMIENTOS!$B$5:$B$424="REGALO")*(MOVIMIENTOS!$C$5:$C$424&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$424="VENTA")*(MOVIMIENTOS!$C$5:$C$424&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A11)*MOVIMIENTOS!$I$5:$I$424))</f>
         <v>3264</v>
       </c>
       <c r="I11" s="54"/>
@@ -14037,23 +14206,23 @@
         <v>46221</v>
       </c>
       <c r="B12" s="56">
-        <f>IF($A12="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A12)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A12)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A12)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A12)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A12)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A12)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A12)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A12)*MOVIMIENTOS!$E$5:$E$425))</f>
+        <f>IF($A12="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A12)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="PROCESO")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A12)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A12)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A12)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A12)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="REGALO")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A12)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="VENTA")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A12)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="AJUSTE")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A12)*MOVIMIENTOS!$E$5:$E$424))</f>
         <v>64</v>
       </c>
       <c r="C12" s="56">
-        <f>IF($A12="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A12)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A12)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A12)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A12)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A12)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A12)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A12)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A12)*MOVIMIENTOS!$E$5:$E$425))</f>
+        <f>IF($A12="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A12)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="PROCESO")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A12)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A12)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A12)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A12)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="REGALO")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A12)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="VENTA")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A12)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="AJUSTE")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A12)*MOVIMIENTOS!$E$5:$E$424))</f>
         <v>11</v>
       </c>
       <c r="D12" s="56">
-        <f>IF($A12="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A12)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A12)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A12)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A12)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A12)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A12)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A12)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A12)*MOVIMIENTOS!$E$5:$E$425))</f>
+        <f>IF($A12="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A12)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="PROCESO")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A12)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A12)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A12)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A12)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="REGALO")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A12)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="VENTA")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A12)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="AJUSTE")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A12)*MOVIMIENTOS!$E$5:$E$424))</f>
         <v>12</v>
       </c>
       <c r="E12" s="56">
-        <f>IF($A12="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A12)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A12)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A12)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A12)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A12)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A12)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A12)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A12)*MOVIMIENTOS!$E$5:$E$425))</f>
+        <f>IF($A12="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A12)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="PROCESO")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A12)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A12)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A12)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A12)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="REGALO")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A12)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="VENTA")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A12)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="AJUSTE")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A12)*MOVIMIENTOS!$E$5:$E$424))</f>
         <v>55</v>
       </c>
       <c r="F12" s="56">
-        <f>IF($A12="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A12)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A12)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A12)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A12)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A12)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A12)*MOVIMIENTOS!$E$5:$E$425))</f>
+        <f>IF($A12="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$424="Chancho")*(MOVIMIENTOS!$D$5:$D$424="sacos")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A12)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="PROCESO")*(MOVIMIENTOS!$C$5:$C$424="Chancho")*(MOVIMIENTOS!$D$5:$D$424="sacos")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A12)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$424="Chancho")*(MOVIMIENTOS!$D$5:$D$424="sacos")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A12)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="REGALO")*(MOVIMIENTOS!$C$5:$C$424="Chancho")*(MOVIMIENTOS!$D$5:$D$424="sacos")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A12)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="VENTA")*(MOVIMIENTOS!$C$5:$C$424="Chancho")*(MOVIMIENTOS!$D$5:$D$424="sacos")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A12)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="AJUSTE")*(MOVIMIENTOS!$C$5:$C$424="Chancho")*(MOVIMIENTOS!$D$5:$D$424="sacos")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A12)*MOVIMIENTOS!$E$5:$E$424))</f>
         <v>15</v>
       </c>
       <c r="G12" s="56">
@@ -14061,7 +14230,7 @@
         <v>142</v>
       </c>
       <c r="H12" s="56">
-        <f>IF($A12="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$425="COMPRA")+(MOVIMIENTOS!$B$5:$B$425="REPROCESO")+(MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A12)*MOVIMIENTOS!$I$5:$I$425)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$425="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho"))+((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A12)*MOVIMIENTOS!$I$5:$I$425))</f>
+        <f>IF($A12="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$424="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$424&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$424="COMPRA")+(MOVIMIENTOS!$B$5:$B$424="REPROCESO")+(MOVIMIENTOS!$B$5:$B$424="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$424="AJUSTE")*(MOVIMIENTOS!$C$5:$C$424&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A12)*MOVIMIENTOS!$I$5:$I$424)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$424="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$424="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$424="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$424="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$424="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$424="PROCESO")*(MOVIMIENTOS!$C$5:$C$424="Chancho"))+((MOVIMIENTOS!$B$5:$B$424="REGALO")*(MOVIMIENTOS!$C$5:$C$424&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$424="VENTA")*(MOVIMIENTOS!$C$5:$C$424&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A12)*MOVIMIENTOS!$I$5:$I$424))</f>
         <v>2327</v>
       </c>
       <c r="I12" s="54"/>
@@ -14083,23 +14252,23 @@
         <v>46222</v>
       </c>
       <c r="B13" s="56">
-        <f>IF($A13="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A13)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A13)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A13)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A13)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A13)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A13)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A13)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A13)*MOVIMIENTOS!$E$5:$E$425))</f>
+        <f>IF($A13="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A13)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="PROCESO")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A13)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A13)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A13)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A13)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="REGALO")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A13)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="VENTA")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A13)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="AJUSTE")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A13)*MOVIMIENTOS!$E$5:$E$424))</f>
         <v>37</v>
       </c>
       <c r="C13" s="56">
-        <f>IF($A13="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A13)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A13)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A13)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A13)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A13)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A13)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A13)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A13)*MOVIMIENTOS!$E$5:$E$425))</f>
+        <f>IF($A13="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A13)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="PROCESO")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A13)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A13)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A13)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A13)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="REGALO")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A13)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="VENTA")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A13)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="AJUSTE")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A13)*MOVIMIENTOS!$E$5:$E$424))</f>
         <v>0</v>
       </c>
       <c r="D13" s="56">
-        <f>IF($A13="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A13)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A13)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A13)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A13)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A13)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A13)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A13)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A13)*MOVIMIENTOS!$E$5:$E$425))</f>
+        <f>IF($A13="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A13)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="PROCESO")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A13)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A13)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A13)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A13)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="REGALO")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A13)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="VENTA")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A13)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="AJUSTE")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A13)*MOVIMIENTOS!$E$5:$E$424))</f>
         <v>0</v>
       </c>
       <c r="E13" s="56">
-        <f>IF($A13="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A13)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A13)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A13)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A13)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A13)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A13)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A13)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A13)*MOVIMIENTOS!$E$5:$E$425))</f>
+        <f>IF($A13="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A13)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="PROCESO")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A13)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A13)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A13)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A13)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="REGALO")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A13)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="VENTA")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A13)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="AJUSTE")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A13)*MOVIMIENTOS!$E$5:$E$424))</f>
         <v>61</v>
       </c>
       <c r="F13" s="56">
-        <f>IF($A13="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A13)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A13)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A13)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A13)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A13)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A13)*MOVIMIENTOS!$E$5:$E$425))</f>
+        <f>IF($A13="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$424="Chancho")*(MOVIMIENTOS!$D$5:$D$424="sacos")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A13)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="PROCESO")*(MOVIMIENTOS!$C$5:$C$424="Chancho")*(MOVIMIENTOS!$D$5:$D$424="sacos")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A13)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$424="Chancho")*(MOVIMIENTOS!$D$5:$D$424="sacos")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A13)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="REGALO")*(MOVIMIENTOS!$C$5:$C$424="Chancho")*(MOVIMIENTOS!$D$5:$D$424="sacos")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A13)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="VENTA")*(MOVIMIENTOS!$C$5:$C$424="Chancho")*(MOVIMIENTOS!$D$5:$D$424="sacos")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A13)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="AJUSTE")*(MOVIMIENTOS!$C$5:$C$424="Chancho")*(MOVIMIENTOS!$D$5:$D$424="sacos")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A13)*MOVIMIENTOS!$E$5:$E$424))</f>
         <v>18</v>
       </c>
       <c r="G13" s="56">
@@ -14107,7 +14276,7 @@
         <v>98</v>
       </c>
       <c r="H13" s="56">
-        <f>IF($A13="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$425="COMPRA")+(MOVIMIENTOS!$B$5:$B$425="REPROCESO")+(MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A13)*MOVIMIENTOS!$I$5:$I$425)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$425="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho"))+((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A13)*MOVIMIENTOS!$I$5:$I$425))</f>
+        <f>IF($A13="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$424="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$424&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$424="COMPRA")+(MOVIMIENTOS!$B$5:$B$424="REPROCESO")+(MOVIMIENTOS!$B$5:$B$424="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$424="AJUSTE")*(MOVIMIENTOS!$C$5:$C$424&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A13)*MOVIMIENTOS!$I$5:$I$424)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$424="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$424="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$424="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$424="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$424="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$424="PROCESO")*(MOVIMIENTOS!$C$5:$C$424="Chancho"))+((MOVIMIENTOS!$B$5:$B$424="REGALO")*(MOVIMIENTOS!$C$5:$C$424&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$424="VENTA")*(MOVIMIENTOS!$C$5:$C$424&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A13)*MOVIMIENTOS!$I$5:$I$424))</f>
         <v>1802</v>
       </c>
       <c r="I13" s="54"/>
@@ -14129,23 +14298,23 @@
         <v>46223</v>
       </c>
       <c r="B14" s="56">
-        <f>IF($A14="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A14)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A14)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A14)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A14)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A14)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A14)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A14)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A14)*MOVIMIENTOS!$E$5:$E$425))</f>
+        <f>IF($A14="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A14)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="PROCESO")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A14)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A14)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A14)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A14)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="REGALO")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A14)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="VENTA")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A14)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="AJUSTE")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A14)*MOVIMIENTOS!$E$5:$E$424))</f>
         <v>38</v>
       </c>
       <c r="C14" s="56">
-        <f>IF($A14="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A14)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A14)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A14)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A14)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A14)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A14)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A14)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A14)*MOVIMIENTOS!$E$5:$E$425))</f>
+        <f>IF($A14="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A14)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="PROCESO")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A14)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A14)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A14)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A14)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="REGALO")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A14)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="VENTA")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A14)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="AJUSTE")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A14)*MOVIMIENTOS!$E$5:$E$424))</f>
         <v>11</v>
       </c>
       <c r="D14" s="56">
-        <f>IF($A14="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A14)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A14)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A14)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A14)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A14)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A14)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A14)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A14)*MOVIMIENTOS!$E$5:$E$425))</f>
+        <f>IF($A14="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A14)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="PROCESO")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A14)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A14)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A14)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A14)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="REGALO")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A14)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="VENTA")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A14)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="AJUSTE")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A14)*MOVIMIENTOS!$E$5:$E$424))</f>
         <v>10</v>
       </c>
       <c r="E14" s="56">
-        <f>IF($A14="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A14)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A14)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A14)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A14)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A14)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A14)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A14)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A14)*MOVIMIENTOS!$E$5:$E$425))</f>
+        <f>IF($A14="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A14)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="PROCESO")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A14)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A14)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A14)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A14)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="REGALO")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A14)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="VENTA")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A14)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="AJUSTE")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A14)*MOVIMIENTOS!$E$5:$E$424))</f>
         <v>79</v>
       </c>
       <c r="F14" s="56">
-        <f>IF($A14="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A14)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A14)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A14)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A14)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A14)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A14)*MOVIMIENTOS!$E$5:$E$425))</f>
+        <f>IF($A14="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$424="Chancho")*(MOVIMIENTOS!$D$5:$D$424="sacos")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A14)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="PROCESO")*(MOVIMIENTOS!$C$5:$C$424="Chancho")*(MOVIMIENTOS!$D$5:$D$424="sacos")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A14)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$424="Chancho")*(MOVIMIENTOS!$D$5:$D$424="sacos")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A14)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="REGALO")*(MOVIMIENTOS!$C$5:$C$424="Chancho")*(MOVIMIENTOS!$D$5:$D$424="sacos")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A14)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="VENTA")*(MOVIMIENTOS!$C$5:$C$424="Chancho")*(MOVIMIENTOS!$D$5:$D$424="sacos")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A14)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="AJUSTE")*(MOVIMIENTOS!$C$5:$C$424="Chancho")*(MOVIMIENTOS!$D$5:$D$424="sacos")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A14)*MOVIMIENTOS!$E$5:$E$424))</f>
         <v>6.5</v>
       </c>
       <c r="G14" s="56">
@@ -14153,7 +14322,7 @@
         <v>138</v>
       </c>
       <c r="H14" s="56">
-        <f>IF($A14="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$425="COMPRA")+(MOVIMIENTOS!$B$5:$B$425="REPROCESO")+(MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A14)*MOVIMIENTOS!$I$5:$I$425)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$425="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho"))+((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A14)*MOVIMIENTOS!$I$5:$I$425))</f>
+        <f>IF($A14="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$424="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$424&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$424="COMPRA")+(MOVIMIENTOS!$B$5:$B$424="REPROCESO")+(MOVIMIENTOS!$B$5:$B$424="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$424="AJUSTE")*(MOVIMIENTOS!$C$5:$C$424&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A14)*MOVIMIENTOS!$I$5:$I$424)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$424="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$424="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$424="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$424="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$424="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$424="PROCESO")*(MOVIMIENTOS!$C$5:$C$424="Chancho"))+((MOVIMIENTOS!$B$5:$B$424="REGALO")*(MOVIMIENTOS!$C$5:$C$424&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$424="VENTA")*(MOVIMIENTOS!$C$5:$C$424&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A14)*MOVIMIENTOS!$I$5:$I$424))</f>
         <v>2533.5</v>
       </c>
       <c r="I14" s="54"/>
@@ -14175,23 +14344,23 @@
         <v>46224</v>
       </c>
       <c r="B15" s="56">
-        <f>IF($A15="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A15)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A15)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A15)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A15)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A15)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A15)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A15)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A15)*MOVIMIENTOS!$E$5:$E$425))</f>
+        <f>IF($A15="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A15)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="PROCESO")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A15)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A15)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A15)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A15)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="REGALO")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A15)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="VENTA")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A15)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="AJUSTE")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A15)*MOVIMIENTOS!$E$5:$E$424))</f>
         <v>60</v>
       </c>
       <c r="C15" s="56">
-        <f>IF($A15="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A15)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A15)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A15)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A15)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A15)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A15)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A15)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A15)*MOVIMIENTOS!$E$5:$E$425))</f>
+        <f>IF($A15="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A15)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="PROCESO")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A15)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A15)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A15)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A15)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="REGALO")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A15)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="VENTA")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A15)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="AJUSTE")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A15)*MOVIMIENTOS!$E$5:$E$424))</f>
         <v>11</v>
       </c>
       <c r="D15" s="56">
-        <f>IF($A15="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A15)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A15)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A15)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A15)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A15)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A15)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A15)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A15)*MOVIMIENTOS!$E$5:$E$425))</f>
+        <f>IF($A15="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A15)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="PROCESO")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A15)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A15)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A15)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A15)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="REGALO")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A15)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="VENTA")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A15)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="AJUSTE")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A15)*MOVIMIENTOS!$E$5:$E$424))</f>
         <v>12</v>
       </c>
       <c r="E15" s="56">
-        <f>IF($A15="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A15)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A15)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A15)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A15)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A15)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A15)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A15)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A15)*MOVIMIENTOS!$E$5:$E$425))</f>
+        <f>IF($A15="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A15)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="PROCESO")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A15)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A15)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A15)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A15)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="REGALO")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A15)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="VENTA")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A15)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="AJUSTE")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A15)*MOVIMIENTOS!$E$5:$E$424))</f>
         <v>111</v>
       </c>
       <c r="F15" s="56">
-        <f>IF($A15="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A15)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A15)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A15)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A15)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A15)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A15)*MOVIMIENTOS!$E$5:$E$425))</f>
+        <f>IF($A15="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$424="Chancho")*(MOVIMIENTOS!$D$5:$D$424="sacos")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A15)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="PROCESO")*(MOVIMIENTOS!$C$5:$C$424="Chancho")*(MOVIMIENTOS!$D$5:$D$424="sacos")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A15)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$424="Chancho")*(MOVIMIENTOS!$D$5:$D$424="sacos")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A15)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="REGALO")*(MOVIMIENTOS!$C$5:$C$424="Chancho")*(MOVIMIENTOS!$D$5:$D$424="sacos")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A15)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="VENTA")*(MOVIMIENTOS!$C$5:$C$424="Chancho")*(MOVIMIENTOS!$D$5:$D$424="sacos")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A15)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="AJUSTE")*(MOVIMIENTOS!$C$5:$C$424="Chancho")*(MOVIMIENTOS!$D$5:$D$424="sacos")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A15)*MOVIMIENTOS!$E$5:$E$424))</f>
         <v>13.5</v>
       </c>
       <c r="G15" s="56">
@@ -14199,7 +14368,7 @@
         <v>194</v>
       </c>
       <c r="H15" s="56">
-        <f>IF($A15="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$425="COMPRA")+(MOVIMIENTOS!$B$5:$B$425="REPROCESO")+(MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A15)*MOVIMIENTOS!$I$5:$I$425)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$425="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho"))+((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A15)*MOVIMIENTOS!$I$5:$I$425))</f>
+        <f>IF($A15="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$424="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$424&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$424="COMPRA")+(MOVIMIENTOS!$B$5:$B$424="REPROCESO")+(MOVIMIENTOS!$B$5:$B$424="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$424="AJUSTE")*(MOVIMIENTOS!$C$5:$C$424&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A15)*MOVIMIENTOS!$I$5:$I$424)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$424="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$424="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$424="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$424="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$424="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$424="PROCESO")*(MOVIMIENTOS!$C$5:$C$424="Chancho"))+((MOVIMIENTOS!$B$5:$B$424="REGALO")*(MOVIMIENTOS!$C$5:$C$424&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$424="VENTA")*(MOVIMIENTOS!$C$5:$C$424&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A15)*MOVIMIENTOS!$I$5:$I$424))</f>
         <v>745.5</v>
       </c>
       <c r="I15" s="54"/>
@@ -14221,23 +14390,23 @@
         <v>46225</v>
       </c>
       <c r="B16" s="56">
-        <f>IF($A16="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A16)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A16)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A16)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A16)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A16)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A16)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A16)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A16)*MOVIMIENTOS!$E$5:$E$425))</f>
+        <f>IF($A16="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A16)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="PROCESO")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A16)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A16)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A16)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A16)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="REGALO")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A16)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="VENTA")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A16)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="AJUSTE")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A16)*MOVIMIENTOS!$E$5:$E$424))</f>
         <v>56</v>
       </c>
       <c r="C16" s="56">
-        <f>IF($A16="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A16)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A16)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A16)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A16)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A16)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A16)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A16)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A16)*MOVIMIENTOS!$E$5:$E$425))</f>
+        <f>IF($A16="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A16)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="PROCESO")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A16)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A16)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A16)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A16)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="REGALO")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A16)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="VENTA")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A16)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="AJUSTE")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A16)*MOVIMIENTOS!$E$5:$E$424))</f>
         <v>11</v>
       </c>
       <c r="D16" s="56">
-        <f>IF($A16="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A16)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A16)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A16)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A16)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A16)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A16)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A16)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A16)*MOVIMIENTOS!$E$5:$E$425))</f>
+        <f>IF($A16="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A16)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="PROCESO")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A16)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A16)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A16)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A16)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="REGALO")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A16)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="VENTA")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A16)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="AJUSTE")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A16)*MOVIMIENTOS!$E$5:$E$424))</f>
         <v>12</v>
       </c>
       <c r="E16" s="56">
-        <f>IF($A16="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A16)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A16)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A16)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A16)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A16)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A16)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A16)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A16)*MOVIMIENTOS!$E$5:$E$425))</f>
+        <f>IF($A16="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A16)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="PROCESO")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A16)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A16)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A16)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A16)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="REGALO")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A16)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="VENTA")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A16)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="AJUSTE")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A16)*MOVIMIENTOS!$E$5:$E$424))</f>
         <v>120</v>
       </c>
       <c r="F16" s="56">
-        <f>IF($A16="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A16)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A16)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A16)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A16)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A16)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A16)*MOVIMIENTOS!$E$5:$E$425))</f>
+        <f>IF($A16="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$424="Chancho")*(MOVIMIENTOS!$D$5:$D$424="sacos")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A16)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="PROCESO")*(MOVIMIENTOS!$C$5:$C$424="Chancho")*(MOVIMIENTOS!$D$5:$D$424="sacos")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A16)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$424="Chancho")*(MOVIMIENTOS!$D$5:$D$424="sacos")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A16)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="REGALO")*(MOVIMIENTOS!$C$5:$C$424="Chancho")*(MOVIMIENTOS!$D$5:$D$424="sacos")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A16)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="VENTA")*(MOVIMIENTOS!$C$5:$C$424="Chancho")*(MOVIMIENTOS!$D$5:$D$424="sacos")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A16)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="AJUSTE")*(MOVIMIENTOS!$C$5:$C$424="Chancho")*(MOVIMIENTOS!$D$5:$D$424="sacos")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A16)*MOVIMIENTOS!$E$5:$E$424))</f>
         <v>11.5</v>
       </c>
       <c r="G16" s="56">
@@ -14245,7 +14414,7 @@
         <v>199</v>
       </c>
       <c r="H16" s="56">
-        <f>IF($A16="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$425="COMPRA")+(MOVIMIENTOS!$B$5:$B$425="REPROCESO")+(MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A16)*MOVIMIENTOS!$I$5:$I$425)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$425="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho"))+((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A16)*MOVIMIENTOS!$I$5:$I$425))</f>
+        <f>IF($A16="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$424="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$424&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$424="COMPRA")+(MOVIMIENTOS!$B$5:$B$424="REPROCESO")+(MOVIMIENTOS!$B$5:$B$424="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$424="AJUSTE")*(MOVIMIENTOS!$C$5:$C$424&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A16)*MOVIMIENTOS!$I$5:$I$424)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$424="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$424="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$424="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$424="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$424="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$424="PROCESO")*(MOVIMIENTOS!$C$5:$C$424="Chancho"))+((MOVIMIENTOS!$B$5:$B$424="REGALO")*(MOVIMIENTOS!$C$5:$C$424&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$424="VENTA")*(MOVIMIENTOS!$C$5:$C$424&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A16)*MOVIMIENTOS!$I$5:$I$424))</f>
         <v>3577.5</v>
       </c>
       <c r="I16" s="54"/>
@@ -14267,23 +14436,23 @@
         <v>46226</v>
       </c>
       <c r="B17" s="56">
-        <f>IF($A17="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A17)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A17)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A17)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A17)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A17)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A17)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A17)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A17)*MOVIMIENTOS!$E$5:$E$425))</f>
+        <f>IF($A17="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A17)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="PROCESO")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A17)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A17)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A17)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A17)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="REGALO")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A17)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="VENTA")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A17)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="AJUSTE")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A17)*MOVIMIENTOS!$E$5:$E$424))</f>
         <v>67</v>
       </c>
       <c r="C17" s="56">
-        <f>IF($A17="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A17)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A17)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A17)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A17)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A17)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A17)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A17)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A17)*MOVIMIENTOS!$E$5:$E$425))</f>
+        <f>IF($A17="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A17)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="PROCESO")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A17)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A17)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A17)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A17)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="REGALO")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A17)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="VENTA")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A17)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="AJUSTE")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A17)*MOVIMIENTOS!$E$5:$E$424))</f>
         <v>11</v>
       </c>
       <c r="D17" s="56">
-        <f>IF($A17="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A17)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A17)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A17)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A17)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A17)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A17)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A17)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A17)*MOVIMIENTOS!$E$5:$E$425))</f>
+        <f>IF($A17="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A17)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="PROCESO")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A17)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A17)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A17)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A17)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="REGALO")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A17)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="VENTA")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A17)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="AJUSTE")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A17)*MOVIMIENTOS!$E$5:$E$424))</f>
         <v>12</v>
       </c>
       <c r="E17" s="56">
-        <f>IF($A17="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A17)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A17)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A17)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A17)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A17)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A17)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A17)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A17)*MOVIMIENTOS!$E$5:$E$425))</f>
+        <f>IF($A17="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A17)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="PROCESO")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A17)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A17)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A17)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A17)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="REGALO")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A17)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="VENTA")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A17)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="AJUSTE")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A17)*MOVIMIENTOS!$E$5:$E$424))</f>
         <v>96</v>
       </c>
       <c r="F17" s="56">
-        <f>IF($A17="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A17)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A17)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A17)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A17)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A17)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A17)*MOVIMIENTOS!$E$5:$E$425))</f>
+        <f>IF($A17="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$424="Chancho")*(MOVIMIENTOS!$D$5:$D$424="sacos")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A17)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="PROCESO")*(MOVIMIENTOS!$C$5:$C$424="Chancho")*(MOVIMIENTOS!$D$5:$D$424="sacos")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A17)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$424="Chancho")*(MOVIMIENTOS!$D$5:$D$424="sacos")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A17)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="REGALO")*(MOVIMIENTOS!$C$5:$C$424="Chancho")*(MOVIMIENTOS!$D$5:$D$424="sacos")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A17)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="VENTA")*(MOVIMIENTOS!$C$5:$C$424="Chancho")*(MOVIMIENTOS!$D$5:$D$424="sacos")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A17)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="AJUSTE")*(MOVIMIENTOS!$C$5:$C$424="Chancho")*(MOVIMIENTOS!$D$5:$D$424="sacos")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A17)*MOVIMIENTOS!$E$5:$E$424))</f>
         <v>18</v>
       </c>
       <c r="G17" s="56">
@@ -14291,7 +14460,7 @@
         <v>186</v>
       </c>
       <c r="H17" s="56">
-        <f>IF($A17="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$425="COMPRA")+(MOVIMIENTOS!$B$5:$B$425="REPROCESO")+(MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A17)*MOVIMIENTOS!$I$5:$I$425)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$425="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho"))+((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A17)*MOVIMIENTOS!$I$5:$I$425))</f>
+        <f>IF($A17="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$424="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$424&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$424="COMPRA")+(MOVIMIENTOS!$B$5:$B$424="REPROCESO")+(MOVIMIENTOS!$B$5:$B$424="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$424="AJUSTE")*(MOVIMIENTOS!$C$5:$C$424&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A17)*MOVIMIENTOS!$I$5:$I$424)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$424="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$424="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$424="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$424="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$424="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$424="PROCESO")*(MOVIMIENTOS!$C$5:$C$424="Chancho"))+((MOVIMIENTOS!$B$5:$B$424="REGALO")*(MOVIMIENTOS!$C$5:$C$424&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$424="VENTA")*(MOVIMIENTOS!$C$5:$C$424&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A17)*MOVIMIENTOS!$I$5:$I$424))</f>
         <v>3414</v>
       </c>
       <c r="I17" s="54"/>
@@ -14313,23 +14482,23 @@
         <v>46227</v>
       </c>
       <c r="B18" s="56">
-        <f>IF($A18="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A18)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A18)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A18)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A18)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A18)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A18)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A18)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A18)*MOVIMIENTOS!$E$5:$E$425))</f>
+        <f>IF($A18="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A18)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="PROCESO")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A18)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A18)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A18)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A18)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="REGALO")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A18)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="VENTA")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A18)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="AJUSTE")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A18)*MOVIMIENTOS!$E$5:$E$424))</f>
         <v>48</v>
       </c>
       <c r="C18" s="56">
-        <f>IF($A18="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A18)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A18)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A18)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A18)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A18)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A18)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A18)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A18)*MOVIMIENTOS!$E$5:$E$425))</f>
+        <f>IF($A18="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A18)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="PROCESO")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A18)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A18)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A18)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A18)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="REGALO")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A18)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="VENTA")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A18)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="AJUSTE")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A18)*MOVIMIENTOS!$E$5:$E$424))</f>
         <v>3</v>
       </c>
       <c r="D18" s="56">
-        <f>IF($A18="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A18)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A18)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A18)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A18)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A18)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A18)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A18)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A18)*MOVIMIENTOS!$E$5:$E$425))</f>
+        <f>IF($A18="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A18)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="PROCESO")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A18)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A18)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A18)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A18)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="REGALO")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A18)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="VENTA")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A18)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="AJUSTE")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A18)*MOVIMIENTOS!$E$5:$E$424))</f>
         <v>5</v>
       </c>
       <c r="E18" s="56">
-        <f>IF($A18="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A18)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A18)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A18)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A18)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A18)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A18)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A18)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A18)*MOVIMIENTOS!$E$5:$E$425))</f>
+        <f>IF($A18="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A18)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="PROCESO")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A18)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A18)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A18)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A18)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="REGALO")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A18)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="VENTA")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A18)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="AJUSTE")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A18)*MOVIMIENTOS!$E$5:$E$424))</f>
         <v>73</v>
       </c>
       <c r="F18" s="56">
-        <f>IF($A18="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A18)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A18)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A18)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A18)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A18)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A18)*MOVIMIENTOS!$E$5:$E$425))</f>
+        <f>IF($A18="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$424="Chancho")*(MOVIMIENTOS!$D$5:$D$424="sacos")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A18)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="PROCESO")*(MOVIMIENTOS!$C$5:$C$424="Chancho")*(MOVIMIENTOS!$D$5:$D$424="sacos")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A18)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$424="Chancho")*(MOVIMIENTOS!$D$5:$D$424="sacos")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A18)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="REGALO")*(MOVIMIENTOS!$C$5:$C$424="Chancho")*(MOVIMIENTOS!$D$5:$D$424="sacos")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A18)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="VENTA")*(MOVIMIENTOS!$C$5:$C$424="Chancho")*(MOVIMIENTOS!$D$5:$D$424="sacos")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A18)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="AJUSTE")*(MOVIMIENTOS!$C$5:$C$424="Chancho")*(MOVIMIENTOS!$D$5:$D$424="sacos")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A18)*MOVIMIENTOS!$E$5:$E$424))</f>
         <v>14</v>
       </c>
       <c r="G18" s="56">
@@ -14337,7 +14506,7 @@
         <v>129</v>
       </c>
       <c r="H18" s="56">
-        <f>IF($A18="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$425="COMPRA")+(MOVIMIENTOS!$B$5:$B$425="REPROCESO")+(MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A18)*MOVIMIENTOS!$I$5:$I$425)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$425="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho"))+((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A18)*MOVIMIENTOS!$I$5:$I$425))</f>
+        <f>IF($A18="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$424="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$424&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$424="COMPRA")+(MOVIMIENTOS!$B$5:$B$424="REPROCESO")+(MOVIMIENTOS!$B$5:$B$424="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$424="AJUSTE")*(MOVIMIENTOS!$C$5:$C$424&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A18)*MOVIMIENTOS!$I$5:$I$424)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$424="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$424="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$424="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$424="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$424="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$424="PROCESO")*(MOVIMIENTOS!$C$5:$C$424="Chancho"))+((MOVIMIENTOS!$B$5:$B$424="REGALO")*(MOVIMIENTOS!$C$5:$C$424&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$424="VENTA")*(MOVIMIENTOS!$C$5:$C$424&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A18)*MOVIMIENTOS!$I$5:$I$424))</f>
         <v>3563</v>
       </c>
       <c r="I18" s="54"/>
@@ -14359,23 +14528,23 @@
         <v>46228</v>
       </c>
       <c r="B19" s="56">
-        <f>IF($A19="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A19)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A19)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A19)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A19)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A19)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A19)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A19)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A19)*MOVIMIENTOS!$E$5:$E$425))</f>
+        <f>IF($A19="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A19)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="PROCESO")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A19)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A19)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A19)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A19)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="REGALO")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A19)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="VENTA")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A19)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="AJUSTE")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A19)*MOVIMIENTOS!$E$5:$E$424))</f>
         <v>77</v>
       </c>
       <c r="C19" s="56">
-        <f>IF($A19="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A19)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A19)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A19)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A19)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A19)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A19)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A19)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A19)*MOVIMIENTOS!$E$5:$E$425))</f>
+        <f>IF($A19="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A19)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="PROCESO")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A19)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A19)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A19)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A19)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="REGALO")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A19)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="VENTA")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A19)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="AJUSTE")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A19)*MOVIMIENTOS!$E$5:$E$424))</f>
         <v>20</v>
       </c>
       <c r="D19" s="56">
-        <f>IF($A19="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A19)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A19)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A19)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A19)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A19)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A19)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A19)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A19)*MOVIMIENTOS!$E$5:$E$425))</f>
+        <f>IF($A19="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A19)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="PROCESO")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A19)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A19)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A19)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A19)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="REGALO")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A19)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="VENTA")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A19)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="AJUSTE")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A19)*MOVIMIENTOS!$E$5:$E$424))</f>
         <v>12</v>
       </c>
       <c r="E19" s="56">
-        <f>IF($A19="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A19)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A19)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A19)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A19)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A19)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A19)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A19)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A19)*MOVIMIENTOS!$E$5:$E$425))</f>
+        <f>IF($A19="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A19)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="PROCESO")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A19)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A19)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A19)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A19)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="REGALO")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A19)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="VENTA")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A19)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="AJUSTE")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A19)*MOVIMIENTOS!$E$5:$E$424))</f>
         <v>65</v>
       </c>
       <c r="F19" s="56">
-        <f>IF($A19="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A19)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A19)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A19)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A19)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A19)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A19)*MOVIMIENTOS!$E$5:$E$425))</f>
+        <f>IF($A19="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$424="Chancho")*(MOVIMIENTOS!$D$5:$D$424="sacos")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A19)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="PROCESO")*(MOVIMIENTOS!$C$5:$C$424="Chancho")*(MOVIMIENTOS!$D$5:$D$424="sacos")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A19)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$424="Chancho")*(MOVIMIENTOS!$D$5:$D$424="sacos")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A19)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="REGALO")*(MOVIMIENTOS!$C$5:$C$424="Chancho")*(MOVIMIENTOS!$D$5:$D$424="sacos")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A19)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="VENTA")*(MOVIMIENTOS!$C$5:$C$424="Chancho")*(MOVIMIENTOS!$D$5:$D$424="sacos")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A19)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="AJUSTE")*(MOVIMIENTOS!$C$5:$C$424="Chancho")*(MOVIMIENTOS!$D$5:$D$424="sacos")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A19)*MOVIMIENTOS!$E$5:$E$424))</f>
         <v>23.5</v>
       </c>
       <c r="G19" s="56">
@@ -14383,7 +14552,7 @@
         <v>174</v>
       </c>
       <c r="H19" s="56">
-        <f>IF($A19="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$425="COMPRA")+(MOVIMIENTOS!$B$5:$B$425="REPROCESO")+(MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A19)*MOVIMIENTOS!$I$5:$I$425)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$425="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho"))+((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A19)*MOVIMIENTOS!$I$5:$I$425))</f>
+        <f>IF($A19="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$424="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$424&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$424="COMPRA")+(MOVIMIENTOS!$B$5:$B$424="REPROCESO")+(MOVIMIENTOS!$B$5:$B$424="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$424="AJUSTE")*(MOVIMIENTOS!$C$5:$C$424&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A19)*MOVIMIENTOS!$I$5:$I$424)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$424="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$424="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$424="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$424="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$424="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$424="PROCESO")*(MOVIMIENTOS!$C$5:$C$424="Chancho"))+((MOVIMIENTOS!$B$5:$B$424="REGALO")*(MOVIMIENTOS!$C$5:$C$424&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$424="VENTA")*(MOVIMIENTOS!$C$5:$C$424&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A19)*MOVIMIENTOS!$I$5:$I$424))</f>
         <v>3062.5</v>
       </c>
       <c r="I19" s="54"/>
@@ -14405,23 +14574,23 @@
         <v>46229</v>
       </c>
       <c r="B20" s="56">
-        <f>IF($A20="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A20)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A20)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A20)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A20)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A20)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A20)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A20)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A20)*MOVIMIENTOS!$E$5:$E$425))</f>
+        <f>IF($A20="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A20)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="PROCESO")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A20)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A20)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A20)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A20)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="REGALO")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A20)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="VENTA")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A20)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="AJUSTE")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A20)*MOVIMIENTOS!$E$5:$E$424))</f>
         <v>10</v>
       </c>
       <c r="C20" s="56">
-        <f>IF($A20="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A20)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A20)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A20)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A20)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A20)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A20)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A20)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A20)*MOVIMIENTOS!$E$5:$E$425))</f>
+        <f>IF($A20="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A20)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="PROCESO")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A20)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A20)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A20)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A20)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="REGALO")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A20)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="VENTA")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A20)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="AJUSTE")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A20)*MOVIMIENTOS!$E$5:$E$424))</f>
         <v>9</v>
       </c>
       <c r="D20" s="56">
-        <f>IF($A20="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A20)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A20)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A20)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A20)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A20)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A20)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A20)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="C")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A20)*MOVIMIENTOS!$E$5:$E$425))</f>
+        <f>IF($A20="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A20)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="PROCESO")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A20)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A20)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A20)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A20)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="REGALO")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A20)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="VENTA")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A20)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="AJUSTE")*(MOVIMIENTOS!$C$5:$C$424="C")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A20)*MOVIMIENTOS!$E$5:$E$424))</f>
         <v>0</v>
       </c>
       <c r="E20" s="56">
-        <f>IF($A20="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A20)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A20)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A20)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A20)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A20)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A20)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A20)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="M")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A20)*MOVIMIENTOS!$E$5:$E$425))</f>
+        <f>IF($A20="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A20)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="PROCESO")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A20)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A20)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A20)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A20)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="REGALO")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A20)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="VENTA")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A20)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="AJUSTE")*(MOVIMIENTOS!$C$5:$C$424="M")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A20)*MOVIMIENTOS!$E$5:$E$424))</f>
         <v>65</v>
       </c>
       <c r="F20" s="56">
-        <f>IF($A20="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A20)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A20)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A20)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A20)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A20)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="Chancho")*(MOVIMIENTOS!$D$5:$D$425="sacos")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A20)*MOVIMIENTOS!$E$5:$E$425))</f>
+        <f>IF($A20="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$424="Chancho")*(MOVIMIENTOS!$D$5:$D$424="sacos")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A20)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="PROCESO")*(MOVIMIENTOS!$C$5:$C$424="Chancho")*(MOVIMIENTOS!$D$5:$D$424="sacos")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A20)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="VENTA CHANCHO")*(MOVIMIENTOS!$C$5:$C$424="Chancho")*(MOVIMIENTOS!$D$5:$D$424="sacos")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A20)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="REGALO")*(MOVIMIENTOS!$C$5:$C$424="Chancho")*(MOVIMIENTOS!$D$5:$D$424="sacos")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A20)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="VENTA")*(MOVIMIENTOS!$C$5:$C$424="Chancho")*(MOVIMIENTOS!$D$5:$D$424="sacos")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A20)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="AJUSTE")*(MOVIMIENTOS!$C$5:$C$424="Chancho")*(MOVIMIENTOS!$D$5:$D$424="sacos")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A20)*MOVIMIENTOS!$E$5:$E$424))</f>
         <v>23.5</v>
       </c>
       <c r="G20" s="56">
@@ -14429,7 +14598,7 @@
         <v>84</v>
       </c>
       <c r="H20" s="56">
-        <f>IF($A20="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$425="COMPRA")+(MOVIMIENTOS!$B$5:$B$425="REPROCESO")+(MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A20)*MOVIMIENTOS!$I$5:$I$425)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$425="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$425="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$425="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="Chancho"))+((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A20)*MOVIMIENTOS!$I$5:$I$425))</f>
+        <f>IF($A20="","",SUMPRODUCT((((MOVIMIENTOS!$B$5:$B$424="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$424&lt;&gt;"Chancho"))+(MOVIMIENTOS!$B$5:$B$424="COMPRA")+(MOVIMIENTOS!$B$5:$B$424="REPROCESO")+(MOVIMIENTOS!$B$5:$B$424="DEVOLUCIÓN")+((MOVIMIENTOS!$B$5:$B$424="AJUSTE")*(MOVIMIENTOS!$C$5:$C$424&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A20)*MOVIMIENTOS!$I$5:$I$424)-SUMPRODUCT(((MOVIMIENTOS!$B$5:$B$424="ENVÍO A SUPESA")+(MOVIMIENTOS!$B$5:$B$424="ENVÍO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$424="ENVIO A TOTTUS")+(MOVIMIENTOS!$B$5:$B$424="MALOGRADO")+(MOVIMIENTOS!$B$5:$B$424="OTRA SALIDA")+((MOVIMIENTOS!$B$5:$B$424="PROCESO")*(MOVIMIENTOS!$C$5:$C$424="Chancho"))+((MOVIMIENTOS!$B$5:$B$424="REGALO")*(MOVIMIENTOS!$C$5:$C$424&lt;&gt;"Chancho"))+((MOVIMIENTOS!$B$5:$B$424="VENTA")*(MOVIMIENTOS!$C$5:$C$424&lt;&gt;"Chancho")))*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A20)*MOVIMIENTOS!$I$5:$I$424))</f>
         <v>1655.5</v>
       </c>
       <c r="I20" s="54"/>
@@ -14451,23 +14620,23 @@
         <v>46230</v>
       </c>
       <c r="B21" s="56">
-        <f>IF($A21="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A21)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A21)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A21)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A21)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A21)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A21)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A21)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="A")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A21)*MOVIMIENTOS!$E$5:$E$425))</f>
+        <f>IF($A21="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A21)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="PROCESO")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A21)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A21)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A21)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A21)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="REGALO")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A21)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="VENTA")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A21)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="AJUSTE")*(MOVIMIENTOS!$C$5:$C$424="A")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A21)*MOVIMIENTOS!$E$5:$E$424))</f>
         <v>40</v>
       </c>
       <c r="C21" s="56">
-        <f>IF($A21="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A21)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="PROCESO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A21)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A21)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A21)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A21)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="REGALO")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A21)*MOVIMIENTOS!$E$5:$E$425)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="VENTA")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A21)*MOVIMIENTOS!$E$5:$E$425)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$425="AJUSTE")*(MOVIMIENTOS!$C$5:$C$425="P")*(MOVIMIENTOS!$D$5:$D$425="jabas")*(MOVIMIENTOS!$A$5:$A$425&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$425&lt;=$A21)*MOVIMIENTOS!$E$5:$E$425))</f>
+        <f>IF($A21="","",SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="SALDO INICIAL")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A21)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="PROCESO")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A21)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="ENVÍO A SUPESA")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A21)*MOVIMIENTOS!$E$5:$E$424)+SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="DEVOLUCIÓN")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A21)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="TRASIEGO")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A21)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="REGALO")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A21)*MOVIMIENTOS!$E$5:$E$424)-SUMPRODUCT((MOVIMIENTOS!$B$5:$B$424="VENTA")*(MOVIMIENTOS!$C$5:$C$424="P")*(MOVIMIENTOS!$D$5:$D$424="jabas")*(MOVIMIENTOS!$A$5:$A$424&lt;&gt;"")*(MOVIMIENTOS!$A$5:$A$424&lt;=$A21)*MO